--- a/MIR/bin/Debug/net8.0-windows/data.xlsx
+++ b/MIR/bin/Debug/net8.0-windows/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Id</t>
   </si>
@@ -39,13 +39,13 @@
     <t>CreatedAt</t>
   </si>
   <si>
-    <t>a4aa2c84-6c45-49af-9aee-943ba8fb1535</t>
+    <t>f4f3f874-b984-498b-99bb-4417371526a9</t>
   </si>
   <si>
     <t>admin</t>
   </si>
   <si>
-    <t>$2a$11$GsKxbnIankQkmNnu8zD4xuYvpD86TRz3UM3MLKaOujv9L8i4Qu9Q.</t>
+    <t>$2a$11$VOP4cmv9IqpGbDD1Y8X9NO39xTkZ.I.y4tQRpCxtkcZUpd9hyMcBC</t>
   </si>
   <si>
     <t>Administrator</t>
@@ -54,7 +54,7 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>2026-02-01T20:06:13.5441986+08:00</t>
+    <t>2026-02-01T19:54:53.6861593+08:00</t>
   </si>
   <si>
     <t>Code</t>
@@ -84,6 +84,60 @@
     <t>LastUpdated</t>
   </si>
   <si>
+    <t>aaab711a-4390-489e-beaa-f56543e57280</t>
+  </si>
+  <si>
+    <t>MAT-202602012013</t>
+  </si>
+  <si>
+    <t>egg</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>Raw Materials</t>
+  </si>
+  <si>
+    <t>2026-02-01T20:13:07.2262291+08:00</t>
+  </si>
+  <si>
+    <t>d92829e8-7789-43f8-a1dd-8565fe9cca59</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>2026-02-01T20:13:19.7691453+08:00</t>
+  </si>
+  <si>
+    <t>5d171112-732a-45cd-a90b-3325e392ef33</t>
+  </si>
+  <si>
+    <t>sambal</t>
+  </si>
+  <si>
+    <t>2026-02-01T20:13:30.2899484+08:00</t>
+  </si>
+  <si>
+    <t>16762699-04e6-46ed-af6f-7552f9279a3f</t>
+  </si>
+  <si>
+    <t>PRD-202602012013</t>
+  </si>
+  <si>
+    <t>nasi lemak</t>
+  </si>
+  <si>
+    <t>Finished Goods</t>
+  </si>
+  <si>
+    <t>2026-02-01T20:13:44.4094990+08:00</t>
+  </si>
+  <si>
     <t>ProductId</t>
   </si>
   <si>
@@ -91,6 +145,15 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>62d17645-657c-48bd-a267-81dff1f6038b</t>
+  </si>
+  <si>
+    <t>f3e36b80-ea1e-4903-a797-ea847348d19a</t>
+  </si>
+  <si>
+    <t>15eeb5b3-cfc0-40f8-ab6f-b9d179cc9a46</t>
   </si>
   <si>
     <t>Type</t>
@@ -204,7 +267,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -239,6 +302,102 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="0">
+        <v>50</v>
+      </c>
+      <c r="G2" s="0">
+        <v>20</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="0">
+        <v>100</v>
+      </c>
+      <c r="G3" s="0">
+        <v>20</v>
+      </c>
+      <c r="H3" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="0">
+        <v>50</v>
+      </c>
+      <c r="G4" s="0">
+        <v>10</v>
+      </c>
+      <c r="H4" s="0">
+        <v>0.6</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
@@ -246,7 +405,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -272,6 +431,29 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
@@ -279,7 +461,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -287,13 +469,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>24</v>
+      <c r="D2" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -311,22 +535,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/MIR/bin/Debug/net8.0-windows/data.xlsx
+++ b/MIR/bin/Debug/net8.0-windows/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pehya\Downloads\Materials-and-inventory-resource\MIR\bin\Debug\net8.0-windows\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A5E638-37DE-4CF1-A07B-EFE1A3CEB39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74D900A-06AE-42BA-A2C7-8379DB619DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,13 +48,13 @@
     <t>CreatedAt</t>
   </si>
   <si>
-    <t>6e31e8a4-30f9-4565-950a-0111cc75c280</t>
+    <t>75f56071-12f1-4dbc-a082-932a2eceda96</t>
   </si>
   <si>
     <t>admin</t>
   </si>
   <si>
-    <t>$2a$11$.sR85SbI9X/PfkoTwxSSIeQsMX.GqZA9QOO77fn2thSWbjGQ7mXzy</t>
+    <t>$2a$11$O3aMcFJJCTCYOZGRibMjaeJTkXbx5PNeX3I.4mVRC5XglmO3LXYVG</t>
   </si>
   <si>
     <t>Administrator</t>
@@ -63,7 +63,7 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>2026-02-23T21:49:38.3836121+08:00</t>
+    <t>2026-02-24T03:05:34.5873258+08:00</t>
   </si>
   <si>
     <t>Code</t>
@@ -93,7 +93,7 @@
     <t>LastUpdated</t>
   </si>
   <si>
-    <t>1e80d40a-e4a9-4b41-81d5-9284d8bc514a</t>
+    <t>fe309e97-b424-44be-8dfb-52a9a93c18c5</t>
   </si>
   <si>
     <t>CIF-MM705P1.20-0131</t>
@@ -108,1099 +108,1099 @@
     <t>Raw Materials</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.5504198+08:00</t>
-  </si>
-  <si>
-    <t>01bb03f7-fbaa-499a-b662-9a48f5404d90</t>
+    <t>2026-02-24T03:06:24.7468505+08:00</t>
+  </si>
+  <si>
+    <t>73f87d18-439e-476c-8132-f908ca2d4dc3</t>
   </si>
   <si>
     <t>CHE-UV-GLUE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.6456360+08:00</t>
-  </si>
-  <si>
-    <t>4acdc760-31ff-44df-9d02-19b85bd39f53</t>
+    <t>2026-02-24T03:06:24.7468557+08:00</t>
+  </si>
+  <si>
+    <t>82ee61ba-01d2-4d9a-93d4-bb331006b2da</t>
   </si>
   <si>
     <t>CHE-UV-GLUE-FL</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.7803828+08:00</t>
-  </si>
-  <si>
-    <t>4f71a1be-42b7-4468-9715-503b0db37c9c</t>
+    <t>2026-02-24T03:06:24.7468603+08:00</t>
+  </si>
+  <si>
+    <t>1c5954d3-53ab-414c-85eb-b64cd6f4eb66</t>
   </si>
   <si>
     <t>PVC 68A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.8666298+08:00</t>
-  </si>
-  <si>
-    <t>1524d7d6-4459-4e2f-bc0a-b87c661c6645</t>
+    <t>2026-02-24T03:06:24.7468643+08:00</t>
+  </si>
+  <si>
+    <t>c9d68ed2-8e2b-4a96-b327-b79b173c4630</t>
   </si>
   <si>
     <t>CIF-LLC-0313</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.9602688+08:00</t>
-  </si>
-  <si>
-    <t>5112d670-9f51-4446-beb7-039fa7315a19</t>
+    <t>2026-02-24T03:06:24.7468685+08:00</t>
+  </si>
+  <si>
+    <t>49e90dd0-aab0-486f-8ed4-2743d2ece73b</t>
   </si>
   <si>
     <t>CIF-LL-0213</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.0696907+08:00</t>
-  </si>
-  <si>
-    <t>bad18f3c-1e5b-465f-8de9-a516a5347664</t>
+    <t>2026-02-24T03:06:24.7468729+08:00</t>
+  </si>
+  <si>
+    <t>e9cea2ad-aae8-4a1d-9126-7812ac4b9ff5</t>
   </si>
   <si>
     <t>CIF-HS-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.1714764+08:00</t>
-  </si>
-  <si>
-    <t>e861f7aa-9803-4330-ab8b-954cc46ce82e</t>
+    <t>2026-02-24T03:06:24.7468769+08:00</t>
+  </si>
+  <si>
+    <t>4fa20f2a-2960-4a2c-bf91-6bbec07049e0</t>
   </si>
   <si>
     <t>CIF-RL-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.2874527+08:00</t>
-  </si>
-  <si>
-    <t>558b885f-4c2c-4ebb-a1e5-88c77bcf5ce7</t>
+    <t>2026-02-24T03:06:24.7468806+08:00</t>
+  </si>
+  <si>
+    <t>621faccc-cf2c-407f-ac78-f5c91e8a7ef7</t>
   </si>
   <si>
     <t>CIF-YP-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.3807426+08:00</t>
-  </si>
-  <si>
-    <t>1b7e9bd8-30b4-416e-bde7-16821dadc721</t>
+    <t>2026-02-24T03:06:24.7468849+08:00</t>
+  </si>
+  <si>
+    <t>af48f7ef-a0b2-4333-962d-cb7a123d85e2</t>
   </si>
   <si>
     <t>CIF-AVS20D-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.4598338+08:00</t>
-  </si>
-  <si>
-    <t>dd3cfd35-9526-4920-934f-7fd772e1a94f</t>
+    <t>2026-02-24T03:06:24.7468887+08:00</t>
+  </si>
+  <si>
+    <t>0b62f64d-7a50-4200-940a-b138e18317e2</t>
   </si>
   <si>
     <t>CIF-SC-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.5626271+08:00</t>
-  </si>
-  <si>
-    <t>609750f4-394b-4eaa-91c8-1f2f257b9d26</t>
+    <t>2026-02-24T03:06:24.7468926+08:00</t>
+  </si>
+  <si>
+    <t>d6ddce92-6921-4cb6-bc26-fd718b584873</t>
   </si>
   <si>
     <t>CIF-AVC-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.6339085+08:00</t>
-  </si>
-  <si>
-    <t>94b1d41a-acd5-49e3-9a35-54c3ee8ffdf8</t>
+    <t>2026-02-24T03:06:24.7468966+08:00</t>
+  </si>
+  <si>
+    <t>5d0c0adb-026c-473c-b123-30eba3f4188e</t>
   </si>
   <si>
     <t>CIF-DC-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.7131817+08:00</t>
-  </si>
-  <si>
-    <t>2548e88f-6eef-497e-b8e8-88a5e1628879</t>
+    <t>2026-02-24T03:06:24.7469002+08:00</t>
+  </si>
+  <si>
+    <t>f5b5f48e-fdae-4b48-a3e1-fc04cc5b88fd</t>
   </si>
   <si>
     <t>PIF-F70M85-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.8053428+08:00</t>
-  </si>
-  <si>
-    <t>7e092982-5b2c-42fe-a29a-fca7dfe70c93</t>
+    <t>2026-02-24T03:06:24.7469039+08:00</t>
+  </si>
+  <si>
+    <t>43c1ee48-fd41-41b9-91dc-a13e9253adca</t>
   </si>
   <si>
     <t>P-F90M423-0154</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:10.9210201+08:00</t>
-  </si>
-  <si>
-    <t>4591df8a-ffbd-4956-92a3-d1a6f64fc12f</t>
+    <t>2026-02-24T03:06:24.7469081+08:00</t>
+  </si>
+  <si>
+    <t>3a55a4d2-9bf1-4b60-b788-625d67f644a0</t>
   </si>
   <si>
     <t>P-MP-0154</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.0280464+08:00</t>
-  </si>
-  <si>
-    <t>4ecdf686-9714-4a02-8a7e-7f8a21abef3a</t>
+    <t>2026-02-24T03:06:24.7469118+08:00</t>
+  </si>
+  <si>
+    <t>4f43ef52-f2a6-406a-a508-097e9a462523</t>
   </si>
   <si>
     <t>CIF-MM720P5.00-0238</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.0985531+08:00</t>
-  </si>
-  <si>
-    <t>efffd89b-3333-4875-b975-06200c821fbb</t>
+    <t>2026-02-24T03:06:24.7469155+08:00</t>
+  </si>
+  <si>
+    <t>0d1ad955-48e0-438c-b29b-39ce949d3877</t>
   </si>
   <si>
     <t>PVC 75A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.1645399+08:00</t>
-  </si>
-  <si>
-    <t>d6ed2d66-0fa7-48af-9949-0838fcba0388</t>
+    <t>2026-02-24T03:06:24.7469194+08:00</t>
+  </si>
+  <si>
+    <t>26f1643d-b2f5-4f05-95b0-a8bffb65e246</t>
   </si>
   <si>
     <t>CIF-NP-0125</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.2304036+08:00</t>
-  </si>
-  <si>
-    <t>65808677-9dd3-4131-b7fb-2020c6fae3fe</t>
+    <t>2026-02-24T03:06:24.7469232+08:00</t>
+  </si>
+  <si>
+    <t>71a0903d-35d8-49d3-903a-a94086a480a4</t>
   </si>
   <si>
     <t>CIF-SRC-0413</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.2982276+08:00</t>
-  </si>
-  <si>
-    <t>af6b1ba5-8d93-4e9a-9b17-b5a093d581c9</t>
+    <t>2026-02-24T03:06:24.7469269+08:00</t>
+  </si>
+  <si>
+    <t>7b369940-7059-48e7-a6ba-394c3e89a880</t>
   </si>
   <si>
     <t>CIF-AVS20D-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.3621445+08:00</t>
-  </si>
-  <si>
-    <t>ddcb9d49-8a04-49c3-8c8e-207f61c7e3c0</t>
+    <t>2026-02-24T03:06:24.7469307+08:00</t>
+  </si>
+  <si>
+    <t>3ba1ef02-6ed8-4724-a78e-7277612b9c00</t>
   </si>
   <si>
     <t>CIF-DC-0313</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.4332850+08:00</t>
-  </si>
-  <si>
-    <t>bfdf76a1-9feb-4fef-824c-a07c1d7c7ded</t>
+    <t>2026-02-24T03:06:24.7469348+08:00</t>
+  </si>
+  <si>
+    <t>01cc0dae-301c-401f-8aad-9e077caf1f0a</t>
   </si>
   <si>
     <t>CIF-FL(9909-1)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.5277836+08:00</t>
-  </si>
-  <si>
-    <t>771002d0-cfb0-4139-a125-bb6336ed7eef</t>
+    <t>2026-02-24T03:06:24.7469385+08:00</t>
+  </si>
+  <si>
+    <t>892b9dd5-2062-423d-a97b-f9b62accf15a</t>
   </si>
   <si>
     <t>CIF-EPC-0213</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.6097547+08:00</t>
-  </si>
-  <si>
-    <t>f4d1a879-df6e-408e-81f8-6d90779d6acf</t>
+    <t>2026-02-24T03:06:24.7469422+08:00</t>
+  </si>
+  <si>
+    <t>a0c6f591-c7fe-41c0-996c-1b6b975b080e</t>
   </si>
   <si>
     <t>CIF-CC-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.7094215+08:00</t>
-  </si>
-  <si>
-    <t>95e364d6-a396-4127-800b-ec3808a2268b</t>
+    <t>2026-02-24T03:06:24.7469463+08:00</t>
+  </si>
+  <si>
+    <t>7d5f08a7-95fb-4ff7-80d6-4233262ed26b</t>
   </si>
   <si>
     <t>CIF-2WC-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.8086759+08:00</t>
-  </si>
-  <si>
-    <t>45cbd2c5-c19c-413c-b38d-c82e673829f3</t>
+    <t>2026-02-24T03:06:24.7469497+08:00</t>
+  </si>
+  <si>
+    <t>935eff37-fb24-4539-bab6-5fd78ea4c78b</t>
   </si>
   <si>
     <t>CIF-3WC-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.8774263+08:00</t>
-  </si>
-  <si>
-    <t>e7bef20e-19a3-4c10-8a82-eacca9f7d70b</t>
+    <t>2026-02-24T03:06:24.7469534+08:00</t>
+  </si>
+  <si>
+    <t>0ed7b8de-b8cf-4991-aa4b-39a3698e8023</t>
   </si>
   <si>
     <t>CIF-SLC-0104</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:11.9712053+08:00</t>
-  </si>
-  <si>
-    <t>8907d1be-8028-4860-976a-7e897025e4d4</t>
+    <t>2026-02-24T03:06:24.7469574+08:00</t>
+  </si>
+  <si>
+    <t>b539f9b4-f8ad-415d-8441-150e4ab313c4</t>
   </si>
   <si>
     <t>CIF-EP-0125</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.0498163+08:00</t>
-  </si>
-  <si>
-    <t>66337ff3-1869-42e6-bc72-c0e30d8c6a0e</t>
+    <t>2026-02-24T03:06:24.7469612+08:00</t>
+  </si>
+  <si>
+    <t>d3cdcb83-2af6-45bb-8500-0e07675d4a61</t>
   </si>
   <si>
     <t>CIF-DC-0108Y</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.1177023+08:00</t>
-  </si>
-  <si>
-    <t>05605560-c031-4720-a234-4b56dd8e85eb</t>
+    <t>2026-02-24T03:06:24.7469649+08:00</t>
+  </si>
+  <si>
+    <t>ced815f8-f3c7-403a-8c49-e0931ce6fe7b</t>
   </si>
   <si>
     <t>RM-PVC75A-JM</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.1872072+08:00</t>
-  </si>
-  <si>
-    <t>6b6f441b-2fd1-4537-8132-44a8a417aa33</t>
+    <t>2026-02-24T03:06:24.7469691+08:00</t>
+  </si>
+  <si>
+    <t>aeebc570-4b64-4b60-ad30-1872b97263e7</t>
   </si>
   <si>
     <t>CHE - UV-GLUE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.2553828+08:00</t>
-  </si>
-  <si>
-    <t>c6526604-9b6a-45ac-9a43-b01c195b939a</t>
+    <t>2026-02-24T03:06:24.7469727+08:00</t>
+  </si>
+  <si>
+    <t>328e51f2-6285-46aa-80a1-0706bfa97fea</t>
   </si>
   <si>
     <t>CHE - UV-GLUE-FL</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.3279276+08:00</t>
-  </si>
-  <si>
-    <t>0ab2aa5c-f8b4-4afd-8879-aefdd3dcb260</t>
+    <t>2026-02-24T03:06:24.7469763+08:00</t>
+  </si>
+  <si>
+    <t>dc52198e-edef-43b9-b6a1-8145fe64d3bf</t>
   </si>
   <si>
     <t>CIF-N60D-0104</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.4086533+08:00</t>
-  </si>
-  <si>
-    <t>ab02d4dc-5c21-4cae-820a-9bbeb6bff465</t>
+    <t>2026-02-24T03:06:24.7469802+08:00</t>
+  </si>
+  <si>
+    <t>f166e0a0-cd47-4f16-9754-ecc9cae65073</t>
   </si>
   <si>
     <t>P-MP-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.5018176+08:00</t>
-  </si>
-  <si>
-    <t>89329632-0331-4745-8785-e201131fbed1</t>
+    <t>2026-02-24T03:06:24.7469839+08:00</t>
+  </si>
+  <si>
+    <t>d9fc9616-5884-4083-87ba-ff0c6accaebf</t>
   </si>
   <si>
     <t>CIF-SR-0126</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.6073366+08:00</t>
-  </si>
-  <si>
-    <t>327fdb7f-966e-4c2f-af0d-ef291914fc8a</t>
+    <t>2026-02-24T03:06:24.7469875+08:00</t>
+  </si>
+  <si>
+    <t>25e1fbb1-7fde-4938-9855-bc01a23fa1df</t>
   </si>
   <si>
     <t>CISP-ID-0140</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.7081789+08:00</t>
-  </si>
-  <si>
-    <t>87f47326-a154-439c-b312-7fe73e5e5de0</t>
+    <t>2026-02-24T03:06:24.7469917+08:00</t>
+  </si>
+  <si>
+    <t>c8c08b72-3327-4386-acca-b58726d545a7</t>
   </si>
   <si>
     <t>CISP-SG-0137</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.8096632+08:00</t>
-  </si>
-  <si>
-    <t>785fff9d-ddc6-415d-88d2-827bd2301443</t>
+    <t>2026-02-24T03:06:24.7469954+08:00</t>
+  </si>
+  <si>
+    <t>6a71fa66-dd62-4e44-8138-089a2e2a44f7</t>
   </si>
   <si>
     <t>CISP-ST-0121</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:12.9104812+08:00</t>
-  </si>
-  <si>
-    <t>d33ce186-07f4-48e6-8c93-a5b73a58011a</t>
+    <t>2026-02-24T03:06:24.7469991+08:00</t>
+  </si>
+  <si>
+    <t>82f302e6-fc7c-46fb-9bfa-7034f2158877</t>
   </si>
   <si>
     <t>CISP-SS-0253</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.0259154+08:00</t>
-  </si>
-  <si>
-    <t>fea56934-27e2-434e-98b5-27b705b23686</t>
+    <t>2026-02-24T03:06:24.7470031+08:00</t>
+  </si>
+  <si>
+    <t>1c3d74ad-86e4-4784-9146-caf8272b0bc5</t>
   </si>
   <si>
     <t>CISP-SP-0237</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.1260969+08:00</t>
-  </si>
-  <si>
-    <t>80968351-8bdc-4fdf-8c9f-5e1511e17e27</t>
+    <t>2026-02-24T03:06:24.7470066+08:00</t>
+  </si>
+  <si>
+    <t>60df407b-24a3-438e-8d4b-7c8f4323cab3</t>
   </si>
   <si>
     <t>CISP-TF-0121</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.2294919+08:00</t>
-  </si>
-  <si>
-    <t>db2545b1-228b-4aa5-9d19-81283bf1fea9</t>
+    <t>2026-02-24T03:06:24.7470104+08:00</t>
+  </si>
+  <si>
+    <t>3b88df16-ecb8-4414-a864-db9044237df6</t>
   </si>
   <si>
     <t>CISP-TQ-0221</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.3276572+08:00</t>
-  </si>
-  <si>
-    <t>89ed0488-bc9b-457b-b293-83661255def1</t>
+    <t>2026-02-24T03:06:24.7470143+08:00</t>
+  </si>
+  <si>
+    <t>24d4114a-3d41-4ff9-bdcd-acb21c8cb560</t>
   </si>
   <si>
     <t>PVC 80A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.4382065+08:00</t>
-  </si>
-  <si>
-    <t>ba6d789c-de3c-496b-b125-9649ba354ee3</t>
+    <t>2026-02-24T03:06:24.7470181+08:00</t>
+  </si>
+  <si>
+    <t>ad5b412b-3093-4e84-8402-c928c71e264c</t>
   </si>
   <si>
     <t>CIF-LLC-0213</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.5518060+08:00</t>
-  </si>
-  <si>
-    <t>f489074e-ef93-4199-a669-f09c1b932d18</t>
+    <t>2026-02-24T03:06:24.7470216+08:00</t>
+  </si>
+  <si>
+    <t>b0dc4ef7-55fa-463d-b4bc-04185e7bb8fc</t>
   </si>
   <si>
     <t>CIF-R2WC-0342</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.6741900+08:00</t>
-  </si>
-  <si>
-    <t>5a297fcb-c6a5-4511-9903-2fce6a31e915</t>
+    <t>2026-02-24T03:06:24.7470257+08:00</t>
+  </si>
+  <si>
+    <t>9e965e57-db3f-4944-b352-cdd3eaa07cf0</t>
   </si>
   <si>
     <t>CIF-SLC-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.7784008+08:00</t>
-  </si>
-  <si>
-    <t>81fb2249-2772-4b95-b4af-1b7dcfa57797</t>
+    <t>2026-02-24T03:06:24.7470293+08:00</t>
+  </si>
+  <si>
+    <t>6417bcd2-9c44-41a2-aecd-293241441a42</t>
   </si>
   <si>
     <t>CIF-SLC-0208</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.8704324+08:00</t>
-  </si>
-  <si>
-    <t>2330f919-5c14-4f64-9a55-711ab456a114</t>
+    <t>2026-02-24T03:06:24.7470329+08:00</t>
+  </si>
+  <si>
+    <t>5f4bdea1-869e-4887-8741-97be7d993876</t>
   </si>
   <si>
     <t>CIF-EP-0225</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.9703382+08:00</t>
-  </si>
-  <si>
-    <t>a928588a-9867-48a5-8b76-19cef5a5b217</t>
+    <t>2026-02-24T03:06:24.7470369+08:00</t>
+  </si>
+  <si>
+    <t>89976e7b-9ce1-4c10-8adb-f1459f0a2fcd</t>
   </si>
   <si>
     <t>CIF-BCV-0413</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.1453571+08:00</t>
-  </si>
-  <si>
-    <t>509ee277-bb0b-4e76-8a8a-83c26f87ebee</t>
+    <t>2026-02-24T03:06:24.7470406+08:00</t>
+  </si>
+  <si>
+    <t>470df4ba-213c-4c31-a757-8d6ee97bd092</t>
   </si>
   <si>
     <t>CIF-NC-0125</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.2500797+08:00</t>
-  </si>
-  <si>
-    <t>d8443972-975e-4fd0-a029-8da0af522a65</t>
+    <t>2026-02-24T03:06:24.7470440+08:00</t>
+  </si>
+  <si>
+    <t>cd274c0b-97e1-426e-a2cb-2b21267c9bec</t>
   </si>
   <si>
     <t>CIF-CC-0313</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.3448742+08:00</t>
-  </si>
-  <si>
-    <t>0158480e-eab8-4654-a79a-df2397f64693</t>
+    <t>2026-02-24T03:06:24.7470481+08:00</t>
+  </si>
+  <si>
+    <t>0a37cad5-b1a4-4f90-8a6c-c0f3b54ea62e</t>
   </si>
   <si>
     <t>CIF-CRLL-0513</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.4419805+08:00</t>
-  </si>
-  <si>
-    <t>ddcdaa8c-58f1-4860-8d9c-57885b826c37</t>
+    <t>2026-02-24T03:06:24.7470516+08:00</t>
+  </si>
+  <si>
+    <t>46046d7e-cc14-4cb1-8e16-74beb63de195</t>
   </si>
   <si>
     <t>CIF-LL-0413</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.5377819+08:00</t>
-  </si>
-  <si>
-    <t>52b61ed2-5487-47ba-9ab0-45c6ecbfe254</t>
+    <t>2026-02-24T03:06:24.7470552+08:00</t>
+  </si>
+  <si>
+    <t>3d193536-c870-4e60-afac-59902f39dc03</t>
   </si>
   <si>
     <t>CIF-LLC-0513</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.6252196+08:00</t>
-  </si>
-  <si>
-    <t>9b90522d-d3d1-4f91-b57c-fbc2e5182ca0</t>
+    <t>2026-02-24T03:06:24.7470592+08:00</t>
+  </si>
+  <si>
+    <t>ae435059-8315-4d59-a6ce-ad14f9e0f932</t>
   </si>
   <si>
     <t>CIF-LL-0313</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.7353694+08:00</t>
-  </si>
-  <si>
-    <t>b5411553-6d50-47aa-b016-50b691a7d04b</t>
+    <t>2026-02-24T03:06:24.7470628+08:00</t>
+  </si>
+  <si>
+    <t>66415f27-4bbd-4204-91bd-3babebbab32d</t>
   </si>
   <si>
     <t>CIF-LL-0613</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.8489711+08:00</t>
-  </si>
-  <si>
-    <t>52310678-fdea-407b-87e2-75f32814e3d0</t>
+    <t>2026-02-24T03:06:24.7470664+08:00</t>
+  </si>
+  <si>
+    <t>4acc41b0-aa61-4b24-9106-4850bf44bbb1</t>
   </si>
   <si>
     <t>PVC 85A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:14.9589832+08:00</t>
-  </si>
-  <si>
-    <t>02a32765-e88b-4019-a845-dbbe96dcdf9c</t>
+    <t>2026-02-24T03:06:24.7470704+08:00</t>
+  </si>
+  <si>
+    <t>952e1bea-f6b0-4872-a360-9deb59650f77</t>
   </si>
   <si>
     <t>CSC-FC-0114</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.0611156+08:00</t>
-  </si>
-  <si>
-    <t>69c622d6-6613-4340-b30c-82fc540e0dfc</t>
+    <t>2026-02-24T03:06:24.7470742+08:00</t>
+  </si>
+  <si>
+    <t>abcebb6c-883a-43d5-b993-fc838aa4002b</t>
   </si>
   <si>
     <t>CSC-T00PVC22-0148</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.1521933+08:00</t>
-  </si>
-  <si>
-    <t>318800c1-0c47-4f94-b176-9d9ab44913e2</t>
+    <t>2026-02-24T03:06:24.7470779+08:00</t>
+  </si>
+  <si>
+    <t>8f5d2999-9785-4ba2-806e-810e1e0bb87d</t>
   </si>
   <si>
     <t>BAG HDPE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.2589310+08:00</t>
-  </si>
-  <si>
-    <t>766fe72b-60fc-48ae-b651-72a58ff8e6d3</t>
+    <t>2026-02-24T03:06:24.7470820+08:00</t>
+  </si>
+  <si>
+    <t>ecc9a75c-c5ab-47da-b390-6a0bc71668d9</t>
   </si>
   <si>
     <t>BAG LDPE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.3680410+08:00</t>
-  </si>
-  <si>
-    <t>d67a681a-e107-4e29-b84d-ee8406b04d93</t>
+    <t>2026-02-24T03:06:24.7470861+08:00</t>
+  </si>
+  <si>
+    <t>512c4ee8-dab0-4889-bdd3-df2dbb375a83</t>
   </si>
   <si>
     <t>CIF-CRLL-0342</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.4831520+08:00</t>
-  </si>
-  <si>
-    <t>53f069af-b5a6-4803-be02-9e0a290ac301</t>
+    <t>2026-02-24T03:06:24.7470902+08:00</t>
+  </si>
+  <si>
+    <t>4b30542a-11b0-4ffa-b2b4-0d1b82a7b5bb</t>
   </si>
   <si>
     <t>P-MPSM001-0154</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.5642494+08:00</t>
-  </si>
-  <si>
-    <t>f8b5742e-d760-4973-b845-ac03caec04e8</t>
+    <t>2026-02-24T03:06:24.7470943+08:00</t>
+  </si>
+  <si>
+    <t>88502903-0589-4886-8edf-ccdc641b193e</t>
   </si>
   <si>
     <t>CIF-R3WC-0342</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.6608021+08:00</t>
-  </si>
-  <si>
-    <t>61c32e45-7d9c-4ec9-a42a-69a0f6cc68f9</t>
+    <t>2026-02-24T03:06:24.7470979+08:00</t>
+  </si>
+  <si>
+    <t>2fbea53c-3ea2-400b-a1e6-d7d7501235f0</t>
   </si>
   <si>
     <t>CIF-SLC-0308</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.7611588+08:00</t>
-  </si>
-  <si>
-    <t>3415f66a-9b4b-460f-93aa-8574a31ff2db</t>
+    <t>2026-02-24T03:06:24.7471015+08:00</t>
+  </si>
+  <si>
+    <t>0259640c-413e-4bec-9a15-432b02e668c1</t>
   </si>
   <si>
     <t>CIF-R4WC-0342</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.8523787+08:00</t>
-  </si>
-  <si>
-    <t>ef2a8d49-d4c7-4b5d-bafe-6f78f13df9da</t>
+    <t>2026-02-24T03:06:24.7471052+08:00</t>
+  </si>
+  <si>
+    <t>a7a939b5-a16f-4f35-aa8a-49789c1fd9a7</t>
   </si>
   <si>
     <t>CIF-SLC-0542</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:15.9548819+08:00</t>
-  </si>
-  <si>
-    <t>99143678-8cc0-4626-b54b-0b8aab394abe</t>
+    <t>2026-02-24T03:06:24.7471094+08:00</t>
+  </si>
+  <si>
+    <t>5f549a46-8558-4bbf-80b0-2fdec966ceb9</t>
   </si>
   <si>
     <t>P-F140M423-0313</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.0315038+08:00</t>
-  </si>
-  <si>
-    <t>8c9d30d8-79aa-4c81-9854-38f73c797502</t>
+    <t>2026-02-24T03:06:24.7471131+08:00</t>
+  </si>
+  <si>
+    <t>9fde8bed-e8da-4d68-a49f-98bf4515e1fa</t>
   </si>
   <si>
     <t>CIF-TC-0142</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.1250101+08:00</t>
-  </si>
-  <si>
-    <t>672a9720-7fd6-4b38-8aee-c91e03e8957d</t>
+    <t>2026-02-24T03:06:24.7471166+08:00</t>
+  </si>
+  <si>
+    <t>cc7ad5ea-e35a-41f2-8146-ced87acc8272</t>
   </si>
   <si>
     <t>CIF-TC-0242</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.2203139+08:00</t>
-  </si>
-  <si>
-    <t>0a766606-197f-427e-bc2c-fc46db4c1f32</t>
+    <t>2026-02-24T03:06:24.7471208+08:00</t>
+  </si>
+  <si>
+    <t>ad5416db-e6cf-4199-8993-76c154dc184a</t>
   </si>
   <si>
     <t>CIF-CC-0542</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.3141174+08:00</t>
-  </si>
-  <si>
-    <t>004c87e0-12f3-4f67-ab7f-de5b5a66cad6</t>
+    <t>2026-02-24T03:06:24.7471244+08:00</t>
+  </si>
+  <si>
+    <t>a8e3ccbf-8fe7-4026-af1d-d54476a8da45</t>
   </si>
   <si>
     <t>CIF-NAVS20D-0249</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.4228288+08:00</t>
-  </si>
-  <si>
-    <t>99cbad60-4a30-46ad-90b4-e698fc31fb92</t>
+    <t>2026-02-24T03:06:24.7471282+08:00</t>
+  </si>
+  <si>
+    <t>41fff471-115f-4ef1-9b1b-69772892424c</t>
   </si>
   <si>
     <t>CIF-NRFMC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.5816496+08:00</t>
-  </si>
-  <si>
-    <t>53160e4a-f527-429e-b9d9-c2494835ce89</t>
+    <t>2026-02-24T03:06:24.7471322+08:00</t>
+  </si>
+  <si>
+    <t>9dcca8e8-2d50-41d0-ad3b-d88410c9d120</t>
   </si>
   <si>
     <t>CIF-NRFFLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.6873133+08:00</t>
-  </si>
-  <si>
-    <t>0aa1a4e3-98c3-4f14-8b97-0c8097802533</t>
+    <t>2026-02-24T03:06:24.7471356+08:00</t>
+  </si>
+  <si>
+    <t>6b14d4e7-bdee-4959-be70-225843e3a3b5</t>
   </si>
   <si>
     <t>CIF-3WYC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.7885996+08:00</t>
-  </si>
-  <si>
-    <t>32faf600-eb0b-4ac2-ad0f-7f62f757e260</t>
+    <t>2026-02-24T03:06:24.7471393+08:00</t>
+  </si>
+  <si>
+    <t>56551e96-4513-469b-85c4-e558028b6830</t>
   </si>
   <si>
     <t>CIF-NRFLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.9035008+08:00</t>
-  </si>
-  <si>
-    <t>8a179ec5-2f1c-48b4-a9d1-10cad9fb2ff0</t>
+    <t>2026-02-24T03:06:24.7471433+08:00</t>
+  </si>
+  <si>
+    <t>df4d73ed-e260-4627-a0d6-8f4f534f9efd</t>
   </si>
   <si>
     <t>CIF-LLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.0205324+08:00</t>
-  </si>
-  <si>
-    <t>5204df5b-a0e9-44eb-a66d-005001d8446c</t>
+    <t>2026-02-24T03:06:24.7471470+08:00</t>
+  </si>
+  <si>
+    <t>4a23afe8-4f70-44f3-9d00-1aa210b51903</t>
   </si>
   <si>
     <t>CIF-RCTW-0159</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.1327196+08:00</t>
-  </si>
-  <si>
-    <t>e649fc22-6e29-49b8-a932-f9228798ac6f</t>
+    <t>2026-02-24T03:06:24.7471517+08:00</t>
+  </si>
+  <si>
+    <t>18451196-3714-45bd-9c67-78dd898081ea</t>
   </si>
   <si>
     <t>P-F140M423-0154</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.2356972+08:00</t>
-  </si>
-  <si>
-    <t>83d8587a-757f-47a2-86f3-9fb4bed3cee9</t>
+    <t>2026-02-24T03:06:24.7471559+08:00</t>
+  </si>
+  <si>
+    <t>2cf7c80b-2e3c-4e72-a4ba-7a4e071adc6c</t>
   </si>
   <si>
     <t>CIF-CC-0342</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.3533360+08:00</t>
-  </si>
-  <si>
-    <t>21e7bf7d-6dc7-442f-bc33-971fe29017bd</t>
+    <t>2026-02-24T03:06:24.7471595+08:00</t>
+  </si>
+  <si>
+    <t>3bac0dc9-7bac-4026-bc9f-0b96c9871d6e</t>
   </si>
   <si>
     <t>CIF-BCV-0332</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.4595139+08:00</t>
-  </si>
-  <si>
-    <t>3f36ea0c-21e3-40bf-b954-8a16adb13c17</t>
+    <t>2026-02-24T03:06:24.7471632+08:00</t>
+  </si>
+  <si>
+    <t>16b8707c-b80c-4680-a1f5-a57b91c4fd27</t>
   </si>
   <si>
     <t>CIF-FL-0118</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.5650330+08:00</t>
-  </si>
-  <si>
-    <t>231c0943-9543-429d-b146-82842925d9d0</t>
+    <t>2026-02-24T03:06:24.7471671+08:00</t>
+  </si>
+  <si>
+    <t>bb82c5ea-a63d-4301-aafa-4d643c84b7d9</t>
   </si>
   <si>
     <t>ART WHITE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.6679530+08:00</t>
-  </si>
-  <si>
-    <t>20b941d7-9474-45c6-8ae9-b2076081abde</t>
+    <t>2026-02-24T03:06:24.7471704+08:00</t>
+  </si>
+  <si>
+    <t>805bc37f-4aaf-4b4f-9d6b-b7f3a2e7edc6</t>
   </si>
   <si>
     <t>ART BLUE</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.7847908+08:00</t>
-  </si>
-  <si>
-    <t>7300bb63-f307-49fa-88ef-ec62d1313495</t>
+    <t>2026-02-24T03:06:24.7471741+08:00</t>
+  </si>
+  <si>
+    <t>454f99e3-6bc6-4d16-99a5-6219679adbfb</t>
   </si>
   <si>
     <t>ART YELLOW</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.8853636+08:00</t>
-  </si>
-  <si>
-    <t>843f6cd9-adbc-4488-b591-e45fb4d65650</t>
+    <t>2026-02-24T03:06:24.7471780+08:00</t>
+  </si>
+  <si>
+    <t>a0674e43-f549-4dad-ae5b-133aaf7ce1d1</t>
   </si>
   <si>
     <t>ART RAINBOW</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:17.9975613+08:00</t>
-  </si>
-  <si>
-    <t>ddd26f29-e622-4dea-ae2e-e7722b29a813</t>
+    <t>2026-02-24T03:06:24.7471816+08:00</t>
+  </si>
+  <si>
+    <t>7a1fa467-1d76-4e82-8a0d-cb7d7452eb26</t>
   </si>
   <si>
     <t>CIF-CC-0442</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.1172707+08:00</t>
-  </si>
-  <si>
-    <t>5b803ded-ed2e-4c84-9413-e442f700708d</t>
+    <t>2026-02-24T03:06:24.7471851+08:00</t>
+  </si>
+  <si>
+    <t>35cedf60-1e8f-4cbd-bdea-ed102fa158df</t>
   </si>
   <si>
     <t>CIF-2WC-0242</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.2305830+08:00</t>
-  </si>
-  <si>
-    <t>d4845112-bdf3-4a6c-b7b2-07db9b805b6f</t>
+    <t>2026-02-24T03:06:24.7471890+08:00</t>
+  </si>
+  <si>
+    <t>36a1f832-58c2-49f1-b9fd-7dbed94df17a</t>
   </si>
   <si>
     <t>CIPS-LLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.3458009+08:00</t>
-  </si>
-  <si>
-    <t>82028d8d-7625-4888-9dac-0acf5e9ed4da</t>
+    <t>2026-02-24T03:06:24.7471925+08:00</t>
+  </si>
+  <si>
+    <t>c4ab8b08-e0c5-4aa3-9b69-8dc036913044</t>
   </si>
   <si>
     <t>CIPS-CLLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.4579346+08:00</t>
-  </si>
-  <si>
-    <t>3f0f1e7d-4451-4ee2-b415-707624949780</t>
+    <t>2026-02-24T03:06:24.7471961+08:00</t>
+  </si>
+  <si>
+    <t>d1942c00-19b5-4afc-8081-7b990364d16b</t>
   </si>
   <si>
     <t>CIPS-BCV-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.5798383+08:00</t>
-  </si>
-  <si>
-    <t>72586c3c-58be-4720-aba0-af3bb0ebb8d5</t>
+    <t>2026-02-24T03:06:24.7472001+08:00</t>
+  </si>
+  <si>
+    <t>f42cc723-5dd5-48ee-9218-54a37dc9216b</t>
   </si>
   <si>
     <t>CIPS-CC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.7017488+08:00</t>
-  </si>
-  <si>
-    <t>39be0db1-0d20-4913-93cf-e87f46967211</t>
+    <t>2026-02-24T03:06:24.7472038+08:00</t>
+  </si>
+  <si>
+    <t>2bab2390-dfb2-4f71-ab98-0cd5d778c179</t>
   </si>
   <si>
     <t>CIPS-BCV-0332</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.8146574+08:00</t>
-  </si>
-  <si>
-    <t>121ff823-15d7-4cb5-82c9-92590d38bf58</t>
+    <t>2026-02-24T03:06:24.7472074+08:00</t>
+  </si>
+  <si>
+    <t>9805496f-6e7f-4d50-a704-3823c54412b4</t>
   </si>
   <si>
     <t>CIPS-YP-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:18.9261595+08:00</t>
-  </si>
-  <si>
-    <t>71f48d8f-1eee-4d28-b25b-cd14060bd366</t>
+    <t>2026-02-24T03:06:24.7472114+08:00</t>
+  </si>
+  <si>
+    <t>07595d5c-066e-418a-ad90-60bfaaaeef1c</t>
   </si>
   <si>
     <t>CIPS-CRLL-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.0342652+08:00</t>
-  </si>
-  <si>
-    <t>4c0d821d-d743-4dc9-89e7-2d830005f1c1</t>
+    <t>2026-02-24T03:06:24.7472151+08:00</t>
+  </si>
+  <si>
+    <t>2b210bac-5610-4fb5-a869-eacde26b700d</t>
   </si>
   <si>
     <t>CIPS-MLLC-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.1430967+08:00</t>
-  </si>
-  <si>
-    <t>3fa1f032-8412-4163-8895-c40f937e3e8c</t>
+    <t>2026-02-24T03:06:24.7472184+08:00</t>
+  </si>
+  <si>
+    <t>a617a967-060c-4836-81f1-caa51ff0a2cb</t>
   </si>
   <si>
     <t>CIPS-T00TRI-PVC165-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.2703484+08:00</t>
-  </si>
-  <si>
-    <t>016d635f-93f8-4b3c-a826-63e79c431b8e</t>
+    <t>2026-02-24T03:06:24.7472223+08:00</t>
+  </si>
+  <si>
+    <t>509d7019-fdda-49d0-a777-65edbd652e18</t>
   </si>
   <si>
     <t>CIPS-T00TRI-EVA165-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.3988420+08:00</t>
-  </si>
-  <si>
-    <t>20ea1af6-9348-41b8-a7b1-1362fbffb864</t>
+    <t>2026-02-24T03:06:24.7472258+08:00</t>
+  </si>
+  <si>
+    <t>9f93bb1b-dbc0-42f8-ac8d-662847d2bdd4</t>
   </si>
   <si>
     <t>CIPS-T00TRI-PE165-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.5098027+08:00</t>
-  </si>
-  <si>
-    <t>b2a9fe2b-c882-454a-9a88-fdc1447541e0</t>
+    <t>2026-02-24T03:06:24.7472295+08:00</t>
+  </si>
+  <si>
+    <t>a3374a99-1ddb-4056-9b56-9916cbd44f9d</t>
   </si>
   <si>
     <t>CIPS-T00DEHP0.2-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.6281092+08:00</t>
-  </si>
-  <si>
-    <t>a4b9c655-711e-466a-8496-b76da66d7fed</t>
+    <t>2026-02-24T03:06:24.7472335+08:00</t>
+  </si>
+  <si>
+    <t>11bfc3b0-5094-482f-8563-bbf290b6d840</t>
   </si>
   <si>
     <t>CIPS-T00PE15-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.7354671+08:00</t>
-  </si>
-  <si>
-    <t>6c8f7721-6644-4a5f-919c-f6bdb221bac3</t>
+    <t>2026-02-24T03:06:24.7472370+08:00</t>
+  </si>
+  <si>
+    <t>61464abc-1686-4c54-a17f-a5481231b636</t>
   </si>
   <si>
     <t>CIPS-T00EVA15-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.8302060+08:00</t>
-  </si>
-  <si>
-    <t>5713d6b5-6840-42fe-838b-1ea265231b91</t>
+    <t>2026-02-24T03:06:24.7472405+08:00</t>
+  </si>
+  <si>
+    <t>c9bc9085-902a-42ab-a7e2-47ce2fbbebb5</t>
   </si>
   <si>
     <t>CIPS-T00PVC15-0108</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:19.9299426+08:00</t>
-  </si>
-  <si>
-    <t>b6814526-6581-498f-b473-e3d7fc4da8f2</t>
+    <t>2026-02-24T03:06:24.7472447+08:00</t>
+  </si>
+  <si>
+    <t>2fe3ac07-ea6e-45de-854b-9e8495368b62</t>
   </si>
   <si>
     <t>PIF-SMESC02.2-0150</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.0328314+08:00</t>
-  </si>
-  <si>
-    <t>d4339473-8abc-482a-8243-3bc4abb6e0cf</t>
+    <t>2026-02-24T03:06:24.7472481+08:00</t>
+  </si>
+  <si>
+    <t>51d6a02a-28d3-4b01-ba1c-771b23988e82</t>
   </si>
   <si>
     <t>PIF-SMESB02.2-0150</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.1070199+08:00</t>
-  </si>
-  <si>
-    <t>070b65af-bc5a-47b6-846b-39786fbce28e</t>
+    <t>2026-02-24T03:06:24.7472515+08:00</t>
+  </si>
+  <si>
+    <t>7aebb747-67e8-46c7-bb54-a4b72f2fc6b5</t>
   </si>
   <si>
     <t>CIF-T00PU30(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.1834841+08:00</t>
-  </si>
-  <si>
-    <t>24491693-3adb-4335-863d-4296c03b30e9</t>
+    <t>2026-02-24T03:06:24.7472557+08:00</t>
+  </si>
+  <si>
+    <t>c9ddef6a-1f73-4272-91df-047725407f23</t>
   </si>
   <si>
     <t>CIF-LLC-0751</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.2829314+08:00</t>
-  </si>
-  <si>
-    <t>8a528c52-ca53-4b67-82fd-586be9fd8e87</t>
+    <t>2026-02-24T03:06:24.7472594+08:00</t>
+  </si>
+  <si>
+    <t>31404a4b-8c10-473f-8d5d-2c3bd96d10bc</t>
   </si>
   <si>
     <t>CIF-LL-0551</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.3765258+08:00</t>
-  </si>
-  <si>
-    <t>0bce5df6-050c-4376-acd9-aeb8959d46f5</t>
+    <t>2026-02-24T03:06:24.7472630+08:00</t>
+  </si>
+  <si>
+    <t>627b5178-2848-424c-a97d-cd173a30ad39</t>
   </si>
   <si>
     <t>CIF-LL-0652</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.4772720+08:00</t>
-  </si>
-  <si>
-    <t>acbb6de1-8479-4a68-949d-8eb8d89e814b</t>
+    <t>2026-02-24T03:06:24.7472665+08:00</t>
+  </si>
+  <si>
+    <t>22679f62-b111-4214-8859-998e64011305</t>
   </si>
   <si>
     <t>CIF-4WC-0252</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.5612721+08:00</t>
-  </si>
-  <si>
-    <t>5811e07b-d4e4-4c88-878d-a37787debd19</t>
+    <t>2026-02-24T03:06:24.7472704+08:00</t>
+  </si>
+  <si>
+    <t>7089daa8-9583-471f-8df0-005bf714a63b</t>
   </si>
   <si>
     <t>CIF-AVS20D-0613</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.6470218+08:00</t>
-  </si>
-  <si>
-    <t>e35c0b7e-ca68-4d9d-9bf3-1e5ea07afbdf</t>
+    <t>2026-02-24T03:06:24.7472740+08:00</t>
+  </si>
+  <si>
+    <t>61c3190c-a9e5-43b1-89bb-ecdcab4ccbe6</t>
   </si>
   <si>
     <t>CIF-T00PU37(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.7366920+08:00</t>
-  </si>
-  <si>
-    <t>359cc5c4-584f-4fab-beb4-fff7ea5b8217</t>
+    <t>2026-02-24T03:06:24.7472775+08:00</t>
+  </si>
+  <si>
+    <t>5b65ac03-19f0-4a11-8d88-1e3771b0f4e6</t>
   </si>
   <si>
     <t>CIF-CRLL-0413</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.8121823+08:00</t>
-  </si>
-  <si>
-    <t>657637e2-02a1-40a9-a0a1-b5e72254c9ee</t>
+    <t>2026-02-24T03:06:24.7472813+08:00</t>
+  </si>
+  <si>
+    <t>76c7d514-d9d5-44bb-9747-7d0a83145ee4</t>
   </si>
   <si>
     <t>CIF-NC-0225</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.8954929+08:00</t>
-  </si>
-  <si>
-    <t>f0e81a0b-1bca-4b84-b982-7c9870527cc9</t>
+    <t>2026-02-24T03:06:24.7472848+08:00</t>
+  </si>
+  <si>
+    <t>f328d934-43e4-4d37-9421-508f76c65c62</t>
   </si>
   <si>
     <t>CIF-T00PU187(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:20.9683510+08:00</t>
-  </si>
-  <si>
-    <t>5ae0c629-13b3-47a4-9529-32abef053cb3</t>
+    <t>2026-02-24T03:06:24.7472883+08:00</t>
+  </si>
+  <si>
+    <t>6a9dec6f-09d0-4711-a455-0246403b6958</t>
   </si>
   <si>
     <t>CIF-DCC-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.0583311+08:00</t>
-  </si>
-  <si>
-    <t>26aa90c6-249e-43df-862e-06f4dfdb4f62</t>
+    <t>2026-02-24T03:06:24.7472922+08:00</t>
+  </si>
+  <si>
+    <t>1fe4222c-3710-40da-bd83-279f24c670f4</t>
   </si>
   <si>
     <t>CIF-T00PU22(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.1368923+08:00</t>
-  </si>
-  <si>
-    <t>33c5b8e0-c9d0-403e-b532-49ebb5ed862f</t>
+    <t>2026-02-24T03:06:24.7472956+08:00</t>
+  </si>
+  <si>
+    <t>ac095974-6bdc-4e3e-96bd-7f1aedbf3128</t>
   </si>
   <si>
     <t>CIF-T00PU12(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.2125089+08:00</t>
-  </si>
-  <si>
-    <t>c562a1ac-464a-4d75-8fa3-27ac3aeb75cf</t>
+    <t>2026-02-24T03:06:24.7472991+08:00</t>
+  </si>
+  <si>
+    <t>4b733fb2-92a1-48a4-b0df-2a42885beb21</t>
   </si>
   <si>
     <t>CIF-BCV-0232</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.2987808+08:00</t>
-  </si>
-  <si>
-    <t>c0d2b12d-a6e2-4f48-829e-ef246b7fc6fd</t>
+    <t>2026-02-24T03:06:24.7473031+08:00</t>
+  </si>
+  <si>
+    <t>b1c71c3c-553c-415a-bb1f-c7c498b6d82e</t>
   </si>
   <si>
     <t>CIF-CRLL-0213</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.3924520+08:00</t>
-  </si>
-  <si>
-    <t>f16255ff-eb91-4f04-b64f-54dda45da99c</t>
+    <t>2026-02-24T03:06:24.7473065+08:00</t>
+  </si>
+  <si>
+    <t>f51c0850-0219-474d-aa52-aebc1d539173</t>
   </si>
   <si>
     <t>CIF-CTW-0159</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:21.4715391+08:00</t>
-  </si>
-  <si>
-    <t>b0c3d7d5-5850-4904-91c4-d975a69f0acf</t>
+    <t>2026-02-24T03:06:24.7473100+08:00</t>
+  </si>
+  <si>
+    <t>d949bb70-3905-434e-93d8-a34895691620</t>
   </si>
   <si>
     <t>ED-CF-R45</t>
@@ -1212,10 +1212,10 @@
     <t>Finished Goods</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.7457702+08:00</t>
-  </si>
-  <si>
-    <t>edbee818-04c3-48aa-86ed-eafd77a93645</t>
+    <t>2026-02-24T03:06:24.7416462+08:00</t>
+  </si>
+  <si>
+    <t>cbef9b31-d4f5-4394-88af-67f5ab04cc3d</t>
   </si>
   <si>
     <t>ED-CF-R55</t>
@@ -1224,37 +1224,37 @@
     <t>Imported plan quantity: 800.00</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.8059932+08:00</t>
-  </si>
-  <si>
-    <t>24dd235d-185a-42a2-8d48-5c70b6f651b7</t>
+    <t>2026-02-24T03:06:24.7426097+08:00</t>
+  </si>
+  <si>
+    <t>b9c5743d-22ba-4c33-85b3-e0b82595df01</t>
   </si>
   <si>
     <t>ED-CF-R65</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.8451397+08:00</t>
-  </si>
-  <si>
-    <t>5746831d-c0fd-48f7-a072-4f42d4175d02</t>
+    <t>2026-02-24T03:06:24.7426243+08:00</t>
+  </si>
+  <si>
+    <t>8d2a6b20-bd6b-46e8-a2d6-4218d772b27d</t>
   </si>
   <si>
     <t>ED-CF-R80</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.8814756+08:00</t>
-  </si>
-  <si>
-    <t>1a4a55e4-47c3-4d5b-8d2f-ba1d0e44a0f2</t>
+    <t>2026-02-24T03:06:24.7426302+08:00</t>
+  </si>
+  <si>
+    <t>61c8a970-ab46-49ad-a4b7-4d807caafc63</t>
   </si>
   <si>
     <t>ED-CF-R85</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.9315886+08:00</t>
-  </si>
-  <si>
-    <t>062b024f-cada-4316-9eac-192fdd815d01</t>
+    <t>2026-02-24T03:06:24.7428672+08:00</t>
+  </si>
+  <si>
+    <t>5e6dbead-3b7e-4e0d-b71d-5f326f852294</t>
   </si>
   <si>
     <t>ED-UC-R20</t>
@@ -1263,415 +1263,415 @@
     <t>Imported plan quantity: 700.00</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:05.9711273+08:00</t>
-  </si>
-  <si>
-    <t>cec70bf1-c752-4ec3-8f21-f3f0e617cf5e</t>
+    <t>2026-02-24T03:06:24.7428718+08:00</t>
+  </si>
+  <si>
+    <t>a7abfe9b-e44f-4660-bde9-8bdc00c0d84a</t>
   </si>
   <si>
     <t>ED-UC-R30</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.0092335+08:00</t>
-  </si>
-  <si>
-    <t>69751f70-1165-4902-aae1-97a767709647</t>
+    <t>2026-02-24T03:06:24.7428748+08:00</t>
+  </si>
+  <si>
+    <t>5a865fb0-adc9-4f3b-8c7f-493a612c3a07</t>
   </si>
   <si>
     <t>ED-UC-R35</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.0473046+08:00</t>
-  </si>
-  <si>
-    <t>c9440d0f-a3d8-442f-a5fd-33c0a7dc65fb</t>
+    <t>2026-02-24T03:06:24.7428787+08:00</t>
+  </si>
+  <si>
+    <t>1262cfb6-5990-4437-9c41-0625b157e894</t>
   </si>
   <si>
     <t>ED-UC-R40</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.0854258+08:00</t>
-  </si>
-  <si>
-    <t>a0624171-c36d-4cc5-a45b-afe654376a28</t>
+    <t>2026-02-24T03:06:24.7428827+08:00</t>
+  </si>
+  <si>
+    <t>bfed8a58-b751-4f00-8663-5938c980b611</t>
   </si>
   <si>
     <t>ED-UC-R45</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.1249929+08:00</t>
-  </si>
-  <si>
-    <t>91ee0f9f-9bd5-428f-a098-6a0a5109f797</t>
+    <t>2026-02-24T03:06:24.7428859+08:00</t>
+  </si>
+  <si>
+    <t>49410a88-c6f4-483f-b0d0-c8a07f9252d8</t>
   </si>
   <si>
     <t>ED-UC-R65</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.1637511+08:00</t>
-  </si>
-  <si>
-    <t>b2584373-5751-4c6b-b401-a30370f83b34</t>
+    <t>2026-02-24T03:06:24.7428895+08:00</t>
+  </si>
+  <si>
+    <t>da5fa94c-fb9b-4850-8db6-8ef575c82c84</t>
   </si>
   <si>
     <t>IB-6002</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.2097955+08:00</t>
-  </si>
-  <si>
-    <t>04cc59ae-0c70-4cb6-b603-472180f01cff</t>
+    <t>2026-02-24T03:06:24.7428920+08:00</t>
+  </si>
+  <si>
+    <t>a06ffd4b-c893-4dc1-b91b-8b1cdae30d9f</t>
   </si>
   <si>
     <t>IC-1181</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.2517019+08:00</t>
-  </si>
-  <si>
-    <t>e3e9cdd9-1707-462c-b264-ec60c1030a9a</t>
+    <t>2026-02-24T03:06:24.7428942+08:00</t>
+  </si>
+  <si>
+    <t>64cac8a3-d839-46aa-8690-4e9a0deaede1</t>
   </si>
   <si>
     <t>IC-1182</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.3081116+08:00</t>
-  </si>
-  <si>
-    <t>084620d5-474f-4e54-9436-3d8f3b833fea</t>
+    <t>2026-02-24T03:06:24.7428967+08:00</t>
+  </si>
+  <si>
+    <t>29e5050b-9ea1-47a4-bff4-7a4cf087bade</t>
   </si>
   <si>
     <t>IC-1200</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.3442247+08:00</t>
-  </si>
-  <si>
-    <t>87933d65-d13e-47ae-9d3e-933f2d09dbd0</t>
+    <t>2026-02-24T03:06:24.7428994+08:00</t>
+  </si>
+  <si>
+    <t>74f625b8-eda5-4d53-b42f-59ef9dc8f596</t>
   </si>
   <si>
     <t>IC-1220</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.3882586+08:00</t>
-  </si>
-  <si>
-    <t>d3121490-9525-4f2d-b2ee-2201d989ff4a</t>
+    <t>2026-02-24T03:06:24.7429027+08:00</t>
+  </si>
+  <si>
+    <t>acf33b8c-6eb7-4174-9f0b-8ae2bae3d249</t>
   </si>
   <si>
     <t>IC-1240</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.4386225+08:00</t>
-  </si>
-  <si>
-    <t>ba0a29b8-7b2a-4f7d-be36-a21ce19fed50</t>
+    <t>2026-02-24T03:06:24.7429056+08:00</t>
+  </si>
+  <si>
+    <t>5a0b5e3c-c382-4247-804e-827d8189df15</t>
   </si>
   <si>
     <t>IF-2003</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.4859635+08:00</t>
-  </si>
-  <si>
-    <t>4aec1756-9799-4f6b-ad3c-922128ce3889</t>
+    <t>2026-02-24T03:06:24.7429088+08:00</t>
+  </si>
+  <si>
+    <t>41528ed0-55d8-487e-8dd1-46e29e2b5e81</t>
   </si>
   <si>
     <t>IF-2005</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.5197041+08:00</t>
-  </si>
-  <si>
-    <t>9730a36b-4fd1-4b96-b503-8aae6a484485</t>
+    <t>2026-02-24T03:06:24.7429118+08:00</t>
+  </si>
+  <si>
+    <t>ae4cdf60-ae10-4dcf-9f64-c838c296e0d3</t>
   </si>
   <si>
     <t>IF-2007</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.5525828+08:00</t>
-  </si>
-  <si>
-    <t>900d5d12-56e5-4c82-9dcc-39619805411f</t>
+    <t>2026-02-24T03:06:24.7429149+08:00</t>
+  </si>
+  <si>
+    <t>d2b1c485-170f-4906-98de-5679c0b7a292</t>
   </si>
   <si>
     <t>IF-2008</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.5838894+08:00</t>
-  </si>
-  <si>
-    <t>2ec9da0b-2037-4033-b7f7-9fd1dd872636</t>
+    <t>2026-02-24T03:06:24.7429173+08:00</t>
+  </si>
+  <si>
+    <t>db397c11-70f2-4379-bad2-a112188b0211</t>
   </si>
   <si>
     <t>IF-2022</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.6390169+08:00</t>
-  </si>
-  <si>
-    <t>5ce090a1-cb4a-49eb-8c8d-20a3b2d1e45e</t>
+    <t>2026-02-24T03:06:24.7429196+08:00</t>
+  </si>
+  <si>
+    <t>20e9c9e0-986c-425f-955a-4beb7e9e221b</t>
   </si>
   <si>
     <t>IF-2023</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.7019703+08:00</t>
-  </si>
-  <si>
-    <t>96edb553-c251-4e64-8b5c-ff1f0a3aa4f4</t>
+    <t>2026-02-24T03:06:24.7429221+08:00</t>
+  </si>
+  <si>
+    <t>84641271-a11a-4ab6-94c4-2ec8f1dd0f0c</t>
   </si>
   <si>
     <t>IF-2027</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.7570799+08:00</t>
-  </si>
-  <si>
-    <t>e0df0add-9469-4b9c-9c06-62e63e79bf97</t>
+    <t>2026-02-24T03:06:24.7429251+08:00</t>
+  </si>
+  <si>
+    <t>36e1c734-2cc3-4a02-82ad-7f9597769b3c</t>
   </si>
   <si>
     <t>IF-2030</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.7975205+08:00</t>
-  </si>
-  <si>
-    <t>59ebe283-fa4e-4740-baae-a6a0724673ab</t>
+    <t>2026-02-24T03:06:24.7429274+08:00</t>
+  </si>
+  <si>
+    <t>2a5295fd-1cf3-4795-a436-a2cd8b590931</t>
   </si>
   <si>
     <t>IF-2079A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.8312725+08:00</t>
-  </si>
-  <si>
-    <t>486e8d59-8b8a-4a02-a7b9-6fa12128f9c6</t>
+    <t>2026-02-24T03:06:24.7429298+08:00</t>
+  </si>
+  <si>
+    <t>79680452-647f-42ad-8491-9ce41d28a783</t>
   </si>
   <si>
     <t>IF-6001</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.8791787+08:00</t>
-  </si>
-  <si>
-    <t>c03b845d-1818-49ae-a319-9cf5ab8867c0</t>
+    <t>2026-02-24T03:06:24.7429329+08:00</t>
+  </si>
+  <si>
+    <t>803b2deb-7a90-432f-b7a0-8e785ab33f19</t>
   </si>
   <si>
     <t>IF-6002</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.9313859+08:00</t>
-  </si>
-  <si>
-    <t>3680b7b2-5398-4727-9975-390a13e85d99</t>
+    <t>2026-02-24T03:06:24.7429373+08:00</t>
+  </si>
+  <si>
+    <t>3dc2af89-6e67-4e43-8cb4-10640f51acb1</t>
   </si>
   <si>
     <t>IF-6006</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:06.9707219+08:00</t>
-  </si>
-  <si>
-    <t>25311e05-80e7-4487-bb44-a97a04c2c4c9</t>
+    <t>2026-02-24T03:06:24.7429403+08:00</t>
+  </si>
+  <si>
+    <t>c8acac01-e0fd-4c40-b701-b16bd28b299e</t>
   </si>
   <si>
     <t>IF-6023</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.0047629+08:00</t>
-  </si>
-  <si>
-    <t>58f76260-6117-43dc-a085-63db60e7b6c7</t>
+    <t>2026-02-24T03:06:24.7429437+08:00</t>
+  </si>
+  <si>
+    <t>839fc9ee-aea3-481d-a349-acda6b3cc189</t>
   </si>
   <si>
     <t>IF-6030</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.0508188+08:00</t>
-  </si>
-  <si>
-    <t>76485251-dc57-433d-adbc-27ac48150abc</t>
+    <t>2026-02-24T03:06:24.7429461+08:00</t>
+  </si>
+  <si>
+    <t>d3d4f475-eb46-47c1-b92b-99a679b6e69a</t>
   </si>
   <si>
     <t>IF-BR-001</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.1060211+08:00</t>
-  </si>
-  <si>
-    <t>a4ede2c3-d204-4d0d-8125-c78863900baa</t>
+    <t>2026-02-24T03:06:24.7429498+08:00</t>
+  </si>
+  <si>
+    <t>4a9facf7-0ccb-460c-8cb5-3f4c12bb0b09</t>
   </si>
   <si>
     <t>ISP-09</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.1482224+08:00</t>
-  </si>
-  <si>
-    <t>1629d9aa-0533-4bd4-86ec-ac2c872eb45e</t>
+    <t>2026-02-24T03:06:24.7429526+08:00</t>
+  </si>
+  <si>
+    <t>209b5adf-a927-4a46-b64a-db6cd0483a4f</t>
   </si>
   <si>
     <t>NE-02</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.2082119+08:00</t>
-  </si>
-  <si>
-    <t>e69311f2-c4d7-4137-942e-7d72444f6cb8</t>
+    <t>2026-02-24T03:06:24.7429552+08:00</t>
+  </si>
+  <si>
+    <t>360fc072-a1fa-4cc2-b344-258df8ad960b</t>
   </si>
   <si>
     <t>PT-2075</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.2409896+08:00</t>
-  </si>
-  <si>
-    <t>8bdf6b7c-5d59-4c74-a2d9-beccf3b2e41b</t>
+    <t>2026-02-24T03:06:24.7429575+08:00</t>
+  </si>
+  <si>
+    <t>e1a1a943-cc7b-4e0e-aad3-4843e876c6a3</t>
   </si>
   <si>
     <t>PT-2150</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.2757091+08:00</t>
-  </si>
-  <si>
-    <t>d32d7cbe-7b31-492d-9fdc-98ff9aea4ce6</t>
+    <t>2026-02-24T03:06:24.7429605+08:00</t>
+  </si>
+  <si>
+    <t>3cb1d359-306c-4bd4-b963-2b899832e522</t>
   </si>
   <si>
     <t>PT-2200</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.3108562+08:00</t>
-  </si>
-  <si>
-    <t>5ef099d3-035d-4889-9c29-50e4b7cff5e7</t>
+    <t>2026-02-24T03:06:24.7429627+08:00</t>
+  </si>
+  <si>
+    <t>478996ac-988c-4ae8-988d-323ed9875b40</t>
   </si>
   <si>
     <t>PT-3150</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.3629059+08:00</t>
-  </si>
-  <si>
-    <t>b1937b09-3cbf-4d2c-815b-d001ca3cf069</t>
+    <t>2026-02-24T03:06:24.7429656+08:00</t>
+  </si>
+  <si>
+    <t>ce27db59-fe81-4e58-a228-4061089f0e89</t>
   </si>
   <si>
     <t>SCP-01</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.4177468+08:00</t>
-  </si>
-  <si>
-    <t>eeb4fb9e-deef-43e5-a1a2-3bcc75caa303</t>
+    <t>2026-02-24T03:06:24.7429693+08:00</t>
+  </si>
+  <si>
+    <t>43337de8-4a3a-4274-ade5-4e4b7b6fed88</t>
   </si>
   <si>
     <t>SM000010A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.4644133+08:00</t>
-  </si>
-  <si>
-    <t>9561af5e-4b2b-4268-86e0-49f24dc60059</t>
+    <t>2026-02-24T03:06:24.7429722+08:00</t>
+  </si>
+  <si>
+    <t>163884ee-9712-43fb-8589-30565bcf92f3</t>
   </si>
   <si>
     <t>SM000010B</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.5147580+08:00</t>
-  </si>
-  <si>
-    <t>a06dceb2-30ed-40a5-a626-354f9f5a544b</t>
+    <t>2026-02-24T03:06:24.7429745+08:00</t>
+  </si>
+  <si>
+    <t>c67291d9-b773-4cb6-9b37-19b42f4ead47</t>
   </si>
   <si>
     <t>SM000011A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.5678213+08:00</t>
-  </si>
-  <si>
-    <t>ba1716c4-3b1a-444a-a4a4-2ea6f7fefd53</t>
+    <t>2026-02-24T03:06:24.7429770+08:00</t>
+  </si>
+  <si>
+    <t>9aa8a227-05c6-4363-bfd9-829e60f871b3</t>
   </si>
   <si>
     <t>SM000011ARA</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.6260732+08:00</t>
-  </si>
-  <si>
-    <t>cbfcdf1e-d257-4620-a174-6c16450c1be4</t>
+    <t>2026-02-24T03:06:24.7429795+08:00</t>
+  </si>
+  <si>
+    <t>63b180f5-518c-42b3-a7e0-bab44dc0308d</t>
   </si>
   <si>
     <t>SM000011ARB</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.6913601+08:00</t>
-  </si>
-  <si>
-    <t>ecbdfba4-d1e5-475a-8bb6-b914d82d1459</t>
+    <t>2026-02-24T03:06:24.7429821+08:00</t>
+  </si>
+  <si>
+    <t>e224a1ce-f87c-4177-93d6-6e498e645df8</t>
   </si>
   <si>
     <t>SM000011B</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.7280322+08:00</t>
-  </si>
-  <si>
-    <t>9d5daf63-9d61-4c50-b947-825781a3c055</t>
+    <t>2026-02-24T03:06:24.7429844+08:00</t>
+  </si>
+  <si>
+    <t>7c52462c-d567-484b-8750-717a584ee19c</t>
   </si>
   <si>
     <t>SM000012A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.7862351+08:00</t>
-  </si>
-  <si>
-    <t>66657778-c4d7-4bc6-b71c-c5a199e21b34</t>
+    <t>2026-02-24T03:06:24.7429867+08:00</t>
+  </si>
+  <si>
+    <t>b73f9f33-08ba-4fc0-bc7c-12adb057fbeb</t>
   </si>
   <si>
     <t>SM000012ARB</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.8325726+08:00</t>
-  </si>
-  <si>
-    <t>9f1e4a63-0413-46b8-b1df-582c22c5e6fc</t>
+    <t>2026-02-24T03:06:24.7429890+08:00</t>
+  </si>
+  <si>
+    <t>83c7fafe-ec40-4237-8c85-c42d1cf74a3b</t>
   </si>
   <si>
     <t>SM000012B</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.8773712+08:00</t>
-  </si>
-  <si>
-    <t>fa9027d4-8163-4c3a-a360-f599becda18f</t>
+    <t>2026-02-24T03:06:24.7429917+08:00</t>
+  </si>
+  <si>
+    <t>34ddb3ff-8377-43ae-8309-442d630d36c7</t>
   </si>
   <si>
     <t>SM000014</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.9311955+08:00</t>
-  </si>
-  <si>
-    <t>4f0974bb-6aa5-4161-93ae-2db83779ad49</t>
+    <t>2026-02-24T03:06:24.7429939+08:00</t>
+  </si>
+  <si>
+    <t>298bd2ad-8887-43a9-a924-4a2d5d2ff89b</t>
   </si>
   <si>
     <t>SM000017A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:07.9989938+08:00</t>
-  </si>
-  <si>
-    <t>074ff6cf-4ebb-4c52-aae5-64aba78130cc</t>
+    <t>2026-02-24T03:06:24.7429964+08:00</t>
+  </si>
+  <si>
+    <t>f4c79fc6-98d0-4e1a-a588-0f3161e2b408</t>
   </si>
   <si>
     <t>SM000017B</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.0484601+08:00</t>
-  </si>
-  <si>
-    <t>fc5ef3d9-c0bc-4233-bc31-ada73faf844b</t>
+    <t>2026-02-24T03:06:24.7429995+08:00</t>
+  </si>
+  <si>
+    <t>bbeaa165-4ae2-4526-9e53-a1b8437ef074</t>
   </si>
   <si>
     <t>SM000019</t>
@@ -1680,241 +1680,241 @@
     <t>Imported plan quantity: 600.00</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.0896654+08:00</t>
-  </si>
-  <si>
-    <t>81a1b098-b475-4d54-8ead-ac4038cb5416</t>
+    <t>2026-02-24T03:06:24.7430021+08:00</t>
+  </si>
+  <si>
+    <t>14dde3ad-e24c-489d-b464-962604d8b957</t>
   </si>
   <si>
     <t>SM000020</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.1357195+08:00</t>
-  </si>
-  <si>
-    <t>98800474-d73f-4036-a021-4995e4b044ca</t>
+    <t>2026-02-24T03:06:24.7430045+08:00</t>
+  </si>
+  <si>
+    <t>588f8d5c-3705-4267-90f7-cbbbb6bf2eb0</t>
   </si>
   <si>
     <t>SM000021</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.1912705+08:00</t>
-  </si>
-  <si>
-    <t>680f5b95-c325-4216-bf42-5bcb254bd9b9</t>
+    <t>2026-02-24T03:06:24.7430068+08:00</t>
+  </si>
+  <si>
+    <t>663ff458-8a13-43bf-8339-95aeff9ff3fb</t>
   </si>
   <si>
     <t>SM000022</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.2467893+08:00</t>
-  </si>
-  <si>
-    <t>278a68d2-08c1-4441-a051-cf02ea19099a</t>
+    <t>2026-02-24T03:06:24.7430099+08:00</t>
+  </si>
+  <si>
+    <t>f278ef20-0be0-4af1-9242-03fa7716b65b</t>
   </si>
   <si>
     <t>SM000023</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.2922551+08:00</t>
-  </si>
-  <si>
-    <t>975270c1-09bb-4631-9222-1fa4dcd6ebe6</t>
+    <t>2026-02-24T03:06:24.7430124+08:00</t>
+  </si>
+  <si>
+    <t>7ef48ce7-3e97-4eab-9b45-86c09334ed4c</t>
   </si>
   <si>
     <t>SM000028</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.3507463+08:00</t>
-  </si>
-  <si>
-    <t>29e2f133-c155-4b53-8874-94232f89c14b</t>
+    <t>2026-02-24T03:06:24.7430146+08:00</t>
+  </si>
+  <si>
+    <t>f9c509a1-b575-4770-9d72-4b8fc2e69a17</t>
   </si>
   <si>
     <t>SM000030BIF-NRFIT</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.4071805+08:00</t>
-  </si>
-  <si>
-    <t>1695444b-3028-4619-a650-c9619b64a99e</t>
+    <t>2026-02-24T03:06:24.7430172+08:00</t>
+  </si>
+  <si>
+    <t>993847b4-4ecd-4352-a7a9-e4b093a58d8c</t>
   </si>
   <si>
     <t>SM000035</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.4593770+08:00</t>
-  </si>
-  <si>
-    <t>33840147-6b4f-407d-ba9b-72ecc89b3978</t>
+    <t>2026-02-24T03:06:24.7430200+08:00</t>
+  </si>
+  <si>
+    <t>0c4ee421-db14-424a-b12f-dbfaf5dd96e9</t>
   </si>
   <si>
     <t>SM000062</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.5281356+08:00</t>
-  </si>
-  <si>
-    <t>3e5d2029-a3f2-411a-ade8-f74427f0710d</t>
+    <t>2026-02-24T03:06:24.7430226+08:00</t>
+  </si>
+  <si>
+    <t>cbaf1559-3163-43fc-a13f-4233e574ff8c</t>
   </si>
   <si>
     <t>SM000063</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.5694350+08:00</t>
-  </si>
-  <si>
-    <t>9477b477-6b23-44bc-8d86-40192f5cb374</t>
+    <t>2026-02-24T03:06:24.7430252+08:00</t>
+  </si>
+  <si>
+    <t>ab976f3f-62b6-41ac-9c1d-3787c5f3cff1</t>
   </si>
   <si>
     <t>SM000078</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.6268438+08:00</t>
-  </si>
-  <si>
-    <t>45658b6f-c4d4-423d-8003-a829bf2c9f60</t>
+    <t>2026-02-24T03:06:24.7430277+08:00</t>
+  </si>
+  <si>
+    <t>04bdbe8c-708b-4852-99cd-542833893ae1</t>
   </si>
   <si>
     <t>SM000082WPU</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.6835608+08:00</t>
-  </si>
-  <si>
-    <t>b6d5aa7d-3224-4cb1-b0de-f7ca87809080</t>
+    <t>2026-02-24T03:06:24.7430305+08:00</t>
+  </si>
+  <si>
+    <t>b266a49e-01ea-46a6-93dc-97d815e2ec21</t>
   </si>
   <si>
     <t>SM000087WPU</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.7405200+08:00</t>
-  </si>
-  <si>
-    <t>45f6a454-ecc4-4212-91bd-089cadfd3360</t>
+    <t>2026-02-24T03:06:24.7430355+08:00</t>
+  </si>
+  <si>
+    <t>7beff6f2-881d-412e-bdf4-fee2515fd6f3</t>
   </si>
   <si>
     <t>SM000090</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.8006726+08:00</t>
-  </si>
-  <si>
-    <t>51ef81ad-4bad-4dcb-b65e-953d0d56a940</t>
+    <t>2026-02-24T03:06:24.7430389+08:00</t>
+  </si>
+  <si>
+    <t>722a40c4-1e39-44a7-8620-eb62fb82f9ab</t>
   </si>
   <si>
     <t>SM000161B</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.8411385+08:00</t>
-  </si>
-  <si>
-    <t>42b4a3a9-feaa-4103-a21b-e0cff70964ef</t>
+    <t>2026-02-24T03:06:24.7430414+08:00</t>
+  </si>
+  <si>
+    <t>94e49bc2-f5d9-42c0-872b-54f54f24d0b5</t>
   </si>
   <si>
     <t>SM000200AG</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.9064604+08:00</t>
-  </si>
-  <si>
-    <t>e330780b-04e2-44cc-82fc-7f0b50482c9d</t>
+    <t>2026-02-24T03:06:24.7430437+08:00</t>
+  </si>
+  <si>
+    <t>c0e65d9e-f8c5-455f-808c-850fefd9e2f9</t>
   </si>
   <si>
     <t>SM000200AG82WPU</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:08.9550405+08:00</t>
-  </si>
-  <si>
-    <t>9c3bf9df-dc0b-41fd-9020-db7f8d354199</t>
+    <t>2026-02-24T03:06:24.7430465+08:00</t>
+  </si>
+  <si>
+    <t>e286893e-11db-4aef-8b01-205f00d7bf88</t>
   </si>
   <si>
     <t>SM000230AG</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.0594981+08:00</t>
-  </si>
-  <si>
-    <t>7a32642f-3f56-4b7b-968b-140a31eda615</t>
+    <t>2026-02-24T03:06:24.7430489+08:00</t>
+  </si>
+  <si>
+    <t>38a97d47-9d1c-41f5-ba5c-96c6966fb598</t>
   </si>
   <si>
     <t>SM000230AG3EX</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.1007480+08:00</t>
-  </si>
-  <si>
-    <t>3ced73e7-edb4-4b28-91f2-0e276dadf254</t>
+    <t>2026-02-24T03:06:24.7430512+08:00</t>
+  </si>
+  <si>
+    <t>ed5777ad-a1f6-4ca9-ae18-62320493801a</t>
   </si>
   <si>
     <t>TR-SB-002</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.1560696+08:00</t>
-  </si>
-  <si>
-    <t>cc78300c-b3e5-4b3b-ad10-47872abc8864</t>
+    <t>2026-02-24T03:06:24.7430536+08:00</t>
+  </si>
+  <si>
+    <t>23a63b2f-27b9-4a6b-921f-23332b741c19</t>
   </si>
   <si>
     <t>TW-001</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.2186504+08:00</t>
-  </si>
-  <si>
-    <t>1bc79725-2e44-497c-899b-b39eb01ee518</t>
+    <t>2026-02-24T03:06:24.7430566+08:00</t>
+  </si>
+  <si>
+    <t>5b8284ba-e21c-47f3-b3ed-c2371d3c69c4</t>
   </si>
   <si>
     <t>TW-002</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.2785748+08:00</t>
-  </si>
-  <si>
-    <t>965553f2-d5bf-419e-8e1e-4a3152213ca0</t>
+    <t>2026-02-24T03:06:24.7430590+08:00</t>
+  </si>
+  <si>
+    <t>2b076bf3-ae6a-4c2a-8573-7cca782ee787</t>
   </si>
   <si>
     <t>TW-003</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.3402954+08:00</t>
-  </si>
-  <si>
-    <t>b77b2295-f081-4e5e-951d-7851527931d2</t>
+    <t>2026-02-24T03:06:24.7430614+08:00</t>
+  </si>
+  <si>
+    <t>ee13e887-7652-48ab-9d3c-afaa2b438365</t>
   </si>
   <si>
     <t>UB-TV-2000</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.3788256+08:00</t>
-  </si>
-  <si>
-    <t>f36b3be0-6e3a-4d2c-b506-d5e306ddf2ab</t>
+    <t>2026-02-24T03:06:24.7430638+08:00</t>
+  </si>
+  <si>
+    <t>72c9fe70-8868-4380-8e98-0f004de17d61</t>
   </si>
   <si>
     <t>Grand Total</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:09.4160811+08:00</t>
-  </si>
-  <si>
-    <t>5de975c5-76cd-4880-9ad5-25368b627173</t>
+    <t>2026-02-24T03:06:24.7430667+08:00</t>
+  </si>
+  <si>
+    <t>27690a44-1a75-462a-b1c9-6f1518931eb0</t>
   </si>
   <si>
     <t>NE-02A</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:13.9941310+08:00</t>
-  </si>
-  <si>
-    <t>46c88353-49c2-4ec9-984e-c2f439d00879</t>
+    <t>2026-02-24T03:06:24.7452395+08:00</t>
+  </si>
+  <si>
+    <t>e1c1821a-c7aa-4d0c-9865-ea51603639c9</t>
   </si>
   <si>
     <t>SM000030BIF (NR-FIT)</t>
   </si>
   <si>
-    <t>2026-02-23T21:50:16.4450945+08:00</t>
+    <t>2026-02-24T03:06:24.7458843+08:00</t>
   </si>
   <si>
     <t>ProductId</t>
@@ -1926,1738 +1926,1738 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>07416cd7-90bf-449d-9fa0-c8181a79dced</t>
-  </si>
-  <si>
-    <t>f005037f-3ae7-4268-8982-d245b58822d8</t>
-  </si>
-  <si>
-    <t>c7c78a20-c225-4706-b25e-bd08f45c82f3</t>
-  </si>
-  <si>
-    <t>6d02659c-c84f-4f39-b4a8-e59f31c6ba78</t>
-  </si>
-  <si>
-    <t>398adf7d-73b3-405c-8634-5673aadad68d</t>
-  </si>
-  <si>
-    <t>2e5aa1fc-2658-4b6b-9b30-9e6aaec8869d</t>
-  </si>
-  <si>
-    <t>5ed3b602-8341-40bb-b6a6-7cf9e22e23f1</t>
-  </si>
-  <si>
-    <t>fed2bbf2-aafa-4e5b-b1fa-a326e4d68aa2</t>
-  </si>
-  <si>
-    <t>b8bbbf18-9c4e-47a0-bfc4-41b907e328ec</t>
-  </si>
-  <si>
-    <t>9752b5b1-976f-46e1-b9a3-c3ee6b2f3e1d</t>
-  </si>
-  <si>
-    <t>f2c6fc89-9514-42f0-8a9f-267f67e1beed</t>
-  </si>
-  <si>
-    <t>634f716f-3052-4d14-834e-e5d3b0de3dda</t>
-  </si>
-  <si>
-    <t>163a7a21-367d-441d-a77b-8ba917c051bd</t>
-  </si>
-  <si>
-    <t>20d48018-3e14-4cff-b801-96324b8a07e8</t>
-  </si>
-  <si>
-    <t>091da86c-4832-4185-a906-c006da3811f2</t>
-  </si>
-  <si>
-    <t>fbc95301-f899-42e7-9dc2-453db8128a24</t>
-  </si>
-  <si>
-    <t>c641e02f-6688-4516-abbc-98ad5a5dd2a5</t>
-  </si>
-  <si>
-    <t>4affca7b-5b9e-4fb0-b3cc-829bd784d7c6</t>
-  </si>
-  <si>
-    <t>b97f3d5a-78fa-46c1-a449-3a2a46f26658</t>
-  </si>
-  <si>
-    <t>d62dfbfc-6ab6-4637-aade-711c62d53a34</t>
-  </si>
-  <si>
-    <t>01d172c3-339a-41b9-bb78-133c29e2e286</t>
-  </si>
-  <si>
-    <t>a145511e-db99-4e09-bccb-44177db43267</t>
-  </si>
-  <si>
-    <t>bf55e4a2-1b17-400d-8919-f8cfb97be3e0</t>
-  </si>
-  <si>
-    <t>6370362f-ad95-4631-b8be-9a6be7d5a482</t>
-  </si>
-  <si>
-    <t>d32ec756-5502-43cc-8c00-773d9acd48c6</t>
-  </si>
-  <si>
-    <t>452febb8-8589-46f9-903d-dd99294457a9</t>
-  </si>
-  <si>
-    <t>e5794c87-35d6-4c31-abc7-4dead506e94e</t>
-  </si>
-  <si>
-    <t>ad7fb4d7-7950-49a6-9f3d-1a4a4f1604f3</t>
-  </si>
-  <si>
-    <t>39cc32d3-ccee-4710-a560-6206b06ca73a</t>
-  </si>
-  <si>
-    <t>1db6d984-3eca-4355-969c-47f044cfb317</t>
-  </si>
-  <si>
-    <t>9ff82457-47a5-4de0-a12b-a3e6d9ec96bc</t>
-  </si>
-  <si>
-    <t>3f5bbe5b-7c92-4bde-8bd7-124aecda18ab</t>
-  </si>
-  <si>
-    <t>1abe2db7-6adc-4d4a-9562-00dd91288f60</t>
-  </si>
-  <si>
-    <t>1c4f4e9d-0f79-4b97-b4ed-e9b2bc200374</t>
-  </si>
-  <si>
-    <t>9f555323-cc53-4be4-bb5c-ad52c88c8b9d</t>
-  </si>
-  <si>
-    <t>6ebb5a3b-5a32-4cbd-a0a4-e2a533eddd9c</t>
-  </si>
-  <si>
-    <t>24aeadb2-b883-47d0-a664-64519424b624</t>
-  </si>
-  <si>
-    <t>f54ff1ac-b5d1-4a39-8682-d18add1da7be</t>
-  </si>
-  <si>
-    <t>51092b55-ad08-4474-85b1-7d105848af97</t>
-  </si>
-  <si>
-    <t>6ed172b8-0b10-47c2-92b1-921c20034d35</t>
-  </si>
-  <si>
-    <t>af404d20-281e-4561-aa6b-cd3116793ed5</t>
-  </si>
-  <si>
-    <t>8653e871-c370-44a3-a9f1-1ffe289b67b0</t>
-  </si>
-  <si>
-    <t>85b81f1f-b7ca-46ae-87b1-346e7451df3d</t>
-  </si>
-  <si>
-    <t>44186fc5-0a86-4d1d-b686-4218681120db</t>
-  </si>
-  <si>
-    <t>05e185f2-9b01-4207-9f52-3248f8416522</t>
-  </si>
-  <si>
-    <t>7e96ea7b-8d7d-4331-8db5-4b91a8423464</t>
-  </si>
-  <si>
-    <t>663af67a-c9ab-4455-be5c-356d3863b1a0</t>
-  </si>
-  <si>
-    <t>702fdd1c-fd15-4cbd-a112-6debb396fa09</t>
-  </si>
-  <si>
-    <t>c50d179d-d346-4e3a-b134-36dc4c0471e4</t>
-  </si>
-  <si>
-    <t>a61cad17-0d9f-4b92-b127-c7bdbb1b6639</t>
-  </si>
-  <si>
-    <t>bea13eac-7c54-4135-878e-45944c0e5cc7</t>
-  </si>
-  <si>
-    <t>b9152177-6488-4e4e-bc74-88ad02338cc5</t>
-  </si>
-  <si>
-    <t>ec4f233d-8429-4563-ba6d-3488747ed924</t>
-  </si>
-  <si>
-    <t>12566a45-bce8-4d05-8238-7cc13ab928b1</t>
-  </si>
-  <si>
-    <t>26036ae3-2e7e-4c34-a9ee-eb4666327c0a</t>
-  </si>
-  <si>
-    <t>096c7b45-919d-4d2a-a0a8-eb3461de76ea</t>
-  </si>
-  <si>
-    <t>c9343890-5986-4e9d-a214-ec2ff0311c20</t>
-  </si>
-  <si>
-    <t>4bbc0e40-a0b8-407e-add3-775419dfff42</t>
-  </si>
-  <si>
-    <t>6b50dc23-c7b5-4d19-95a7-4d9b0d76340e</t>
-  </si>
-  <si>
-    <t>c3b75e4e-12be-437a-ad36-1b9bf8a7ad6c</t>
-  </si>
-  <si>
-    <t>951618e5-45d7-479f-9c1a-76470d646e05</t>
-  </si>
-  <si>
-    <t>397e96d5-c1b5-4e7d-a924-26cc7e354c1f</t>
-  </si>
-  <si>
-    <t>880ce06b-e213-49a1-9020-dcf6cbe39b74</t>
-  </si>
-  <si>
-    <t>c490659a-7b31-423d-8d57-44724d1a8e58</t>
-  </si>
-  <si>
-    <t>f07344a2-137c-4ed2-ad72-96af50b91027</t>
-  </si>
-  <si>
-    <t>2263c1a5-7c00-49e4-a556-06987f3df5fd</t>
-  </si>
-  <si>
-    <t>57b472fb-7eaf-4909-91db-82be3f8753ad</t>
-  </si>
-  <si>
-    <t>33d8eb3e-b352-49ae-b243-55710cd5adb6</t>
-  </si>
-  <si>
-    <t>609da0ef-50a3-4973-94c3-04f8d0338eb6</t>
-  </si>
-  <si>
-    <t>8fa7685c-5e8a-40d1-95f8-8a7d501089c2</t>
-  </si>
-  <si>
-    <t>7c72b655-3bff-4201-9fbb-490480f05d72</t>
-  </si>
-  <si>
-    <t>f411eefc-9d02-4e46-8b87-a8ae175a4219</t>
-  </si>
-  <si>
-    <t>c902f69d-38c8-4dd3-bf0e-0a88a4f6e55a</t>
-  </si>
-  <si>
-    <t>da8d4f48-612f-45e2-914c-e5e442c064f1</t>
-  </si>
-  <si>
-    <t>28b7fa0d-6274-45ca-896b-b7ad3ac4329b</t>
-  </si>
-  <si>
-    <t>49e4fc55-afbc-4c2d-95d7-c914f44fc379</t>
-  </si>
-  <si>
-    <t>fa11b9aa-29d7-451d-b485-c4475f389d3a</t>
-  </si>
-  <si>
-    <t>30687370-2986-45f2-868c-f561eac5a35b</t>
-  </si>
-  <si>
-    <t>d72e7397-8d2f-4a38-8331-22bef47c1ce4</t>
-  </si>
-  <si>
-    <t>1db8748c-91bc-49da-a0db-17fb2426b095</t>
-  </si>
-  <si>
-    <t>adccbb8e-69ad-4f8f-a87c-322272293215</t>
-  </si>
-  <si>
-    <t>153d8854-2de8-4cd8-8947-529878969c32</t>
-  </si>
-  <si>
-    <t>9ac96ca3-7be5-46ab-8d3e-93cddf4c2862</t>
-  </si>
-  <si>
-    <t>7d2f53cc-44f4-48c1-9c1b-7e1009c7e475</t>
-  </si>
-  <si>
-    <t>ff7c8684-e7a5-4e1c-994c-a296422e7a43</t>
-  </si>
-  <si>
-    <t>1349b6b6-76af-4f2c-990a-df4376da7f5c</t>
-  </si>
-  <si>
-    <t>da9642df-492c-41cb-8e8f-841e48ef6346</t>
-  </si>
-  <si>
-    <t>c6a9cf13-ac57-42fd-b012-db57189ccdd6</t>
-  </si>
-  <si>
-    <t>a2a6d8b4-46fc-463c-8548-a38ecbca9317</t>
-  </si>
-  <si>
-    <t>cfd49354-7ed5-4604-ba49-e71f57b40d3e</t>
-  </si>
-  <si>
-    <t>08b06044-0c52-4cef-b8ee-b4e29b1c2520</t>
-  </si>
-  <si>
-    <t>9b6fb14a-04cb-44f4-9148-a4cdc210602a</t>
-  </si>
-  <si>
-    <t>80811c64-bf26-426f-b6ac-c7cec85b7c6b</t>
-  </si>
-  <si>
-    <t>17e651a0-f1c2-4d48-9080-b00058fd5e6b</t>
-  </si>
-  <si>
-    <t>4fc4c337-bb7f-4c96-9835-4c44b3689b9a</t>
-  </si>
-  <si>
-    <t>80816a5d-4411-40d7-9e9b-c36b22ca6674</t>
-  </si>
-  <si>
-    <t>ee9643b0-5b2b-4bc3-bc88-4101fe054387</t>
-  </si>
-  <si>
-    <t>4d3a2ca3-2a2d-4595-b565-0a42394b571c</t>
-  </si>
-  <si>
-    <t>a7ed73d8-7765-47f4-a209-c03616e2b302</t>
-  </si>
-  <si>
-    <t>06febb53-ff9c-4689-a288-958b7a42b63e</t>
-  </si>
-  <si>
-    <t>1ebb3e87-af6c-4790-8811-cc0ca26e7f89</t>
-  </si>
-  <si>
-    <t>6a057bf7-2d86-40f8-972c-eab31e5ef2cb</t>
-  </si>
-  <si>
-    <t>462ba0bc-62b1-40cc-b0e5-269341aa1632</t>
-  </si>
-  <si>
-    <t>8fa72e01-d445-4256-9abd-d42c24814d31</t>
-  </si>
-  <si>
-    <t>eecd8a1a-1dc9-4258-a01d-f69da9c44e27</t>
-  </si>
-  <si>
-    <t>f98d9161-6bc1-446c-825a-058f11ce7c2b</t>
-  </si>
-  <si>
-    <t>0a438851-b2d0-40de-b2f7-640d8ac835a7</t>
-  </si>
-  <si>
-    <t>ea5ad2e4-b351-44c2-a433-034971d80d6e</t>
-  </si>
-  <si>
-    <t>bfd39fde-92a3-4e97-9ce9-1535544f1f5a</t>
-  </si>
-  <si>
-    <t>4b646f99-eed9-42a4-b2dc-5ad32a5eef9d</t>
-  </si>
-  <si>
-    <t>0cd3e9a9-fb98-465e-9870-ccf6b27bbf51</t>
-  </si>
-  <si>
-    <t>2b6d15d9-89b3-433e-8ce4-1d4134bc4346</t>
-  </si>
-  <si>
-    <t>906f339c-09e6-409a-9115-8d6e88fb9301</t>
-  </si>
-  <si>
-    <t>44b96f34-5809-46d2-a6df-8f0e62fca0ef</t>
-  </si>
-  <si>
-    <t>104ccebc-7c01-41dd-b621-8fdd7b40e0ff</t>
-  </si>
-  <si>
-    <t>46aa4ba1-99c1-40f9-9841-45d979c16eae</t>
-  </si>
-  <si>
-    <t>f6cd4b74-f75b-46ee-ba17-6c1febac5980</t>
-  </si>
-  <si>
-    <t>4e184f60-d6dd-4c65-b3f4-6843b9b3a67e</t>
-  </si>
-  <si>
-    <t>bf1fada1-10b4-438e-86c2-033af7e6c4bd</t>
-  </si>
-  <si>
-    <t>eed51d44-58f3-45e2-99e4-e303ac4d5546</t>
-  </si>
-  <si>
-    <t>a9b17fcd-bb42-4c81-ba01-93ad74297de3</t>
-  </si>
-  <si>
-    <t>6fb0ff38-d63a-4cb2-85dd-788669218b27</t>
-  </si>
-  <si>
-    <t>c9bd6766-f466-4e90-8e3a-f5e6e994d07c</t>
-  </si>
-  <si>
-    <t>f7f15490-3d54-4b97-915c-135e04b217e0</t>
-  </si>
-  <si>
-    <t>93a7cd1e-f331-41bd-8892-806526a1a7cf</t>
-  </si>
-  <si>
-    <t>d3f803eb-0b4c-473b-a4e5-ded28973460a</t>
-  </si>
-  <si>
-    <t>41d6312e-2b94-4a55-8882-fed0d01584fe</t>
-  </si>
-  <si>
-    <t>2234ef54-5dc2-4517-9a1c-91c75758742f</t>
-  </si>
-  <si>
-    <t>ad4e7b1a-e022-4a4e-aa0a-99003d26c426</t>
-  </si>
-  <si>
-    <t>eff12d9a-c6e2-46f5-a1db-609f1ba1fc66</t>
-  </si>
-  <si>
-    <t>87564445-c128-43fd-9e93-dd17dd45ee66</t>
-  </si>
-  <si>
-    <t>76c4cea3-8b39-4428-96d4-fd8bb42ab459</t>
-  </si>
-  <si>
-    <t>478d1128-ba0e-4f58-b40d-eeddc334691e</t>
-  </si>
-  <si>
-    <t>7f64691b-8102-4e30-af04-a86edbf82c18</t>
-  </si>
-  <si>
-    <t>3738112e-f4bc-4a12-9d10-e2ae9d976927</t>
-  </si>
-  <si>
-    <t>d1e15020-e9a0-4315-adad-46f8cf6ccedf</t>
-  </si>
-  <si>
-    <t>6bdd7d42-525d-4125-9812-95af8575a440</t>
-  </si>
-  <si>
-    <t>494edaaf-016a-46cd-889e-bd5279f95e97</t>
-  </si>
-  <si>
-    <t>dc672495-8313-425e-b19f-2abb7a36979a</t>
-  </si>
-  <si>
-    <t>0c7c9bed-525e-4b11-8740-9b07fe0228af</t>
-  </si>
-  <si>
-    <t>6bc2335b-9295-4af7-8bde-dc8b3c013a5e</t>
-  </si>
-  <si>
-    <t>295b306c-6778-49b3-95e3-3cfe2438a1d5</t>
-  </si>
-  <si>
-    <t>fb5eb7b2-249e-4d42-bbc5-616231296ee5</t>
-  </si>
-  <si>
-    <t>5f7731b7-8988-4299-8e6b-0a6bd1973fde</t>
-  </si>
-  <si>
-    <t>cbeeb58d-385f-435c-a443-c73bf4511214</t>
-  </si>
-  <si>
-    <t>126fcbd3-7982-46ba-8423-ce3d474c7521</t>
-  </si>
-  <si>
-    <t>335c613a-de0f-46fe-a7ce-3ef37282f406</t>
-  </si>
-  <si>
-    <t>37d35ea8-438a-4e01-adfa-0cf03ebd611d</t>
-  </si>
-  <si>
-    <t>4530721b-ac08-46cc-9a66-a24470fea21c</t>
-  </si>
-  <si>
-    <t>4811b3bf-db78-47df-96e9-7edc07639602</t>
-  </si>
-  <si>
-    <t>8e9b79a8-ce13-42a0-a90e-201c5042c204</t>
-  </si>
-  <si>
-    <t>b6e12ff0-1813-494b-9f2f-525a2a152b5c</t>
-  </si>
-  <si>
-    <t>670890c2-94ea-469b-9b16-eda35d5a298c</t>
-  </si>
-  <si>
-    <t>ec940a06-6a4a-4e01-a766-d2c4116beb64</t>
-  </si>
-  <si>
-    <t>8d52c8fe-1c7f-4415-8325-9ff9debcedea</t>
-  </si>
-  <si>
-    <t>1ed87ef1-1f60-436c-8d94-220b79cd2079</t>
-  </si>
-  <si>
-    <t>ae6f0c99-1736-4b95-a761-24cf384d38da</t>
-  </si>
-  <si>
-    <t>96c9b9f8-b27b-44a0-b031-c04ef00e0193</t>
-  </si>
-  <si>
-    <t>987c3f89-433f-48b6-95a3-fea1c016d0c5</t>
-  </si>
-  <si>
-    <t>0daf2112-6024-4154-80c3-ece05e395657</t>
-  </si>
-  <si>
-    <t>fc8caae8-dc2a-4188-9349-cbd5ca979462</t>
-  </si>
-  <si>
-    <t>a99b0785-afd8-47c0-a917-80f6e9d6a903</t>
-  </si>
-  <si>
-    <t>4a10ced7-66bc-4c2a-80b9-11bd5251e05b</t>
-  </si>
-  <si>
-    <t>73f7dcf8-d607-4c5f-bd1f-8c3bdfc939ff</t>
-  </si>
-  <si>
-    <t>17087b22-f7d3-4cdd-9f41-443071c4cb32</t>
-  </si>
-  <si>
-    <t>712c68b9-5136-4da7-b881-2ad72460d25f</t>
-  </si>
-  <si>
-    <t>1b039d58-7d3d-4da0-9ede-1aa303bf4e70</t>
-  </si>
-  <si>
-    <t>a202e1c0-def2-45a1-b281-510df4192456</t>
-  </si>
-  <si>
-    <t>dfa5f015-89e4-4003-9527-defa30e1f635</t>
-  </si>
-  <si>
-    <t>1b720386-2ad9-4039-b7eb-35f44c705f7f</t>
-  </si>
-  <si>
-    <t>152edede-2e96-4628-9aa3-bc55714a218a</t>
-  </si>
-  <si>
-    <t>1e1ef37c-6ec3-46da-821c-60bc16456ea9</t>
-  </si>
-  <si>
-    <t>848f2818-d26b-4597-8b90-29335238400a</t>
-  </si>
-  <si>
-    <t>df8d77fa-cb88-41e1-af61-f9104f19f110</t>
-  </si>
-  <si>
-    <t>3e15539b-4829-40ca-9f9b-ee8a98db4b4d</t>
-  </si>
-  <si>
-    <t>06e2237b-1562-494d-ba44-e09fc8c41619</t>
-  </si>
-  <si>
-    <t>57af4850-0435-4fb5-af49-7b719f46a6f4</t>
-  </si>
-  <si>
-    <t>b82d6351-aefb-4d83-b667-3ffaf9640bc9</t>
-  </si>
-  <si>
-    <t>76c3b625-f8da-413d-875b-f0cd2e7a6336</t>
-  </si>
-  <si>
-    <t>0ac7199b-e4d8-457b-9a5a-ae7ad1dfc460</t>
-  </si>
-  <si>
-    <t>a2660f42-75a4-456e-ad61-c8d9fe83e94d</t>
-  </si>
-  <si>
-    <t>58d9a458-08fc-4383-aedd-cbf24284e485</t>
-  </si>
-  <si>
-    <t>c5e59762-1305-4c2d-859d-7b0ae5f7a282</t>
-  </si>
-  <si>
-    <t>2abe46ae-bb11-45cb-9fbd-a7964b650845</t>
-  </si>
-  <si>
-    <t>eec49b12-5b95-4627-bd5e-27e45c627da8</t>
-  </si>
-  <si>
-    <t>38b97195-77a9-4c4f-ada0-0cdf1acdd89d</t>
-  </si>
-  <si>
-    <t>28c31936-fc01-49f0-9fbb-2e3244bdcd3f</t>
-  </si>
-  <si>
-    <t>0177a5a8-67b9-4e29-b4be-2dbda75493e0</t>
-  </si>
-  <si>
-    <t>0aed83b9-3573-4c62-a0aa-28424d8af065</t>
-  </si>
-  <si>
-    <t>b30dcbe8-07f8-4044-a082-795fffd6d29d</t>
-  </si>
-  <si>
-    <t>a1e1b737-469b-4414-8336-24d3d003fd82</t>
-  </si>
-  <si>
-    <t>b55e18ee-508b-4f8d-8437-c4ee7400d5c9</t>
-  </si>
-  <si>
-    <t>b0832809-98ec-4053-ac93-cdcd5799c6cf</t>
-  </si>
-  <si>
-    <t>135e3414-a361-4b7f-81dc-8d42c56a0bb8</t>
-  </si>
-  <si>
-    <t>c0257d11-e6bc-479b-95cf-abacb0d5373d</t>
-  </si>
-  <si>
-    <t>df32967e-fe2e-4a6b-bb63-5a5d56afd19a</t>
-  </si>
-  <si>
-    <t>d220413e-026d-455c-a998-d59b4f9a13af</t>
-  </si>
-  <si>
-    <t>536a44e6-f905-4c12-91f3-b6a94179afe6</t>
-  </si>
-  <si>
-    <t>31e84aac-da80-42dc-aa2e-1f83324da3c4</t>
-  </si>
-  <si>
-    <t>26cd8b86-d1ef-44f4-83d0-e62d26049ddb</t>
-  </si>
-  <si>
-    <t>c35832a7-75e4-42c8-b05b-e7816fa9d442</t>
-  </si>
-  <si>
-    <t>8d8f312f-a33c-49f3-9ef4-51bc1684a335</t>
-  </si>
-  <si>
-    <t>f14628b4-2fdf-4e5a-b00c-99509241d967</t>
-  </si>
-  <si>
-    <t>9a6a3d88-ff8f-418b-a0a6-0c588ef34f06</t>
-  </si>
-  <si>
-    <t>cb927b9c-45c1-460d-a352-0a9a1a25a36f</t>
-  </si>
-  <si>
-    <t>734d7820-1545-44ef-b02c-303b1e7aadcf</t>
-  </si>
-  <si>
-    <t>c65e8ab2-65f4-4668-8ad9-8b21bff50e14</t>
-  </si>
-  <si>
-    <t>1419ae35-8f66-4122-b8e0-f4651ffa2c1d</t>
-  </si>
-  <si>
-    <t>efe48277-b88c-4593-a13b-6cf6e1c72034</t>
-  </si>
-  <si>
-    <t>2da139dd-affd-4c09-8a25-0472e748ebc2</t>
-  </si>
-  <si>
-    <t>dbeb1f1b-521d-422f-8345-696d6c2d435a</t>
-  </si>
-  <si>
-    <t>b2f4e7ea-d5bb-4464-9499-e2e879b92a04</t>
-  </si>
-  <si>
-    <t>5e239ca6-da03-49f2-afac-fa3e66df4441</t>
-  </si>
-  <si>
-    <t>58526244-c383-40f2-878c-8f667509b3cc</t>
-  </si>
-  <si>
-    <t>5f6b7103-4dbc-4ced-9025-bc1e30a00165</t>
-  </si>
-  <si>
-    <t>cc92003d-7d52-4d0d-9cc4-0108f3febeca</t>
-  </si>
-  <si>
-    <t>599edb91-7b4a-4c19-8ba3-81c98c4a6b21</t>
-  </si>
-  <si>
-    <t>8be33a36-2daf-48ae-b3af-cc8a011467a3</t>
-  </si>
-  <si>
-    <t>3f427c83-355c-4a9f-81f6-6ca33da953cf</t>
-  </si>
-  <si>
-    <t>9445b0ab-174b-49a8-9473-40e70c1ec0e3</t>
-  </si>
-  <si>
-    <t>1f66cbee-fda3-41ae-b8dd-1c0042a27b6d</t>
-  </si>
-  <si>
-    <t>9a2ba7b6-94b0-43a9-9a39-a3444312328f</t>
-  </si>
-  <si>
-    <t>5a4fab91-6484-4e5f-bf12-4687452e9981</t>
-  </si>
-  <si>
-    <t>4f51f20e-2815-4223-946f-dbb73e8be3e6</t>
-  </si>
-  <si>
-    <t>cc287a7f-e023-44b4-9ce2-52e3e1e48d7d</t>
-  </si>
-  <si>
-    <t>7c488e9b-000a-4056-874f-37c99a8a545b</t>
-  </si>
-  <si>
-    <t>0ca84a14-69be-4dfd-9a05-2dae71586b53</t>
-  </si>
-  <si>
-    <t>a0008d3f-da62-4be7-8b77-084db46fa57e</t>
-  </si>
-  <si>
-    <t>8dd4f919-1b02-44e7-a88b-b332c8a7dbd5</t>
-  </si>
-  <si>
-    <t>dbad5919-4e6e-4900-9302-c50d21b4b534</t>
-  </si>
-  <si>
-    <t>7ce28014-3a5a-4f4b-a3ad-961f7c127b54</t>
-  </si>
-  <si>
-    <t>d368c86a-7db5-46f9-93d3-84deb3f7abfe</t>
-  </si>
-  <si>
-    <t>210277a0-caab-43ab-bd80-60aeaebe17ac</t>
-  </si>
-  <si>
-    <t>c00d1db2-19d7-4174-acdf-081087ebaeae</t>
-  </si>
-  <si>
-    <t>669c3b38-c409-4471-81cd-5377c116c3db</t>
-  </si>
-  <si>
-    <t>cc38cd8d-43fd-4584-a151-a98b45923c6f</t>
-  </si>
-  <si>
-    <t>305595ea-d8fc-4c5d-9727-b9d5b4f38c04</t>
-  </si>
-  <si>
-    <t>1ad6dfde-10be-437c-ace6-511aef18295e</t>
-  </si>
-  <si>
-    <t>c06e3743-dce3-4804-ba32-230155f79b6e</t>
-  </si>
-  <si>
-    <t>c42d3816-2a0b-46e2-b16c-52abe04bdcbb</t>
-  </si>
-  <si>
-    <t>78f6f39d-c0c0-41ce-9747-55d6d6425fb6</t>
-  </si>
-  <si>
-    <t>1109d8e8-1734-48a1-8113-a848ab94eaf0</t>
-  </si>
-  <si>
-    <t>324ff1b4-a56a-4789-9b63-714d36a520e5</t>
-  </si>
-  <si>
-    <t>8cb13368-3669-4565-b837-50235c56885b</t>
-  </si>
-  <si>
-    <t>d2ef598f-e96a-40f6-9dea-c9ef617bae96</t>
-  </si>
-  <si>
-    <t>d239592f-41f7-4390-9b95-e54af3e40c18</t>
-  </si>
-  <si>
-    <t>19415c9e-d3bd-411b-9a56-23a0bd9ebd7a</t>
-  </si>
-  <si>
-    <t>41a01bd1-fd19-4048-8a04-f479304c0e4c</t>
-  </si>
-  <si>
-    <t>de640c7f-477a-48de-9d3d-c91b7140bf61</t>
-  </si>
-  <si>
-    <t>4e2dc440-16ea-49bf-ae51-a4132e40455a</t>
-  </si>
-  <si>
-    <t>5a59294b-dd29-4691-8636-0beb9aa0f22a</t>
-  </si>
-  <si>
-    <t>6609627f-ee2b-468b-a62f-00fe4506bc8b</t>
-  </si>
-  <si>
-    <t>60273ec0-9f39-4e41-9dde-94dbcff45115</t>
-  </si>
-  <si>
-    <t>82715597-4901-4046-a2b7-cec823f80aa5</t>
-  </si>
-  <si>
-    <t>5cb7f98a-f7c2-4c63-a523-ec03b63f2d21</t>
-  </si>
-  <si>
-    <t>eee6984b-6e29-49d9-8462-546f07d44ceb</t>
-  </si>
-  <si>
-    <t>ba921b64-7cee-4b40-ac8c-999e5cffcf78</t>
-  </si>
-  <si>
-    <t>28c9c574-6255-46e5-9869-a719357733aa</t>
-  </si>
-  <si>
-    <t>22b6d001-2fa5-4e11-b0f4-42750264dd68</t>
-  </si>
-  <si>
-    <t>0342dece-2c47-4fb0-b087-715da881e542</t>
-  </si>
-  <si>
-    <t>6e9aef14-83c7-4297-8023-c6ebf7d304f1</t>
-  </si>
-  <si>
-    <t>f09075ee-a2f9-4887-81a3-d40f83c1e3fa</t>
-  </si>
-  <si>
-    <t>43b19956-ff23-4eae-a046-812f09125bf4</t>
-  </si>
-  <si>
-    <t>c5b76b0a-7b96-4655-9ab8-4ddd12ed1530</t>
-  </si>
-  <si>
-    <t>b0a750da-9162-4ab4-8b51-356a994b1be9</t>
-  </si>
-  <si>
-    <t>7467d11e-2e0a-48c0-b8c5-7fd6b868d28b</t>
-  </si>
-  <si>
-    <t>45e4f6a9-d540-4c67-a494-d656e6b2ef8e</t>
-  </si>
-  <si>
-    <t>0e29ce0d-9b29-4553-b58c-1743f6d40913</t>
-  </si>
-  <si>
-    <t>4f3f51d5-71cf-4a1a-a765-eeb7b93fbe37</t>
-  </si>
-  <si>
-    <t>eae6f274-dea4-4d6e-ac59-69a814119a44</t>
-  </si>
-  <si>
-    <t>75b24e2b-fa19-4e5d-9c39-4f08495418fb</t>
-  </si>
-  <si>
-    <t>cf55498b-0697-4eb6-9d51-a73fe0d48e3c</t>
-  </si>
-  <si>
-    <t>80dc3d3e-4bc6-46d7-bbef-10433c3bb67d</t>
-  </si>
-  <si>
-    <t>b214611c-4cfc-4afe-823a-c939ab702dbc</t>
-  </si>
-  <si>
-    <t>06bd3146-3195-416c-ac76-bbb11530f35e</t>
-  </si>
-  <si>
-    <t>8dbbd4a1-e9ee-458d-a0a1-a7750ae2de81</t>
-  </si>
-  <si>
-    <t>b9c82cff-c01e-43da-991e-c4a796a8c8d2</t>
-  </si>
-  <si>
-    <t>b0900d2c-1a74-445a-bf40-9869edc492d7</t>
-  </si>
-  <si>
-    <t>1dbf8a9d-04ab-4e8a-ad41-f40d82ab9957</t>
-  </si>
-  <si>
-    <t>6ffd9d77-5c08-46c0-ae80-896c24bfbfe4</t>
-  </si>
-  <si>
-    <t>050b0d88-ed33-43b9-8a11-8b2c883186b5</t>
-  </si>
-  <si>
-    <t>a27603ac-e394-458b-9ec3-f0e051e26470</t>
-  </si>
-  <si>
-    <t>34c7a81a-3219-47b4-b3be-4f8d90aa6c9c</t>
-  </si>
-  <si>
-    <t>1c4b8671-7b5e-4a4b-802d-572e2c1b5eed</t>
-  </si>
-  <si>
-    <t>d7703251-0b2a-4a05-a67c-715473b5229a</t>
-  </si>
-  <si>
-    <t>370a2950-7728-400e-8ce7-80b36c300f1c</t>
-  </si>
-  <si>
-    <t>b7b0a413-fad5-45cb-aa9d-ba4eaa066c09</t>
-  </si>
-  <si>
-    <t>d1215093-2c1c-4fa0-8439-f77577801761</t>
-  </si>
-  <si>
-    <t>7817b813-73c6-49d6-9ea6-a4ef383373db</t>
-  </si>
-  <si>
-    <t>023cea3c-1d39-4f42-a50f-538466dd877f</t>
-  </si>
-  <si>
-    <t>eba8ec79-ac29-4a0d-bc2b-473323a5b943</t>
-  </si>
-  <si>
-    <t>dcad7842-153e-4ca7-90c4-34b1e26c4a1b</t>
-  </si>
-  <si>
-    <t>662d9d55-255c-4c39-aa1b-cfc55b7a3735</t>
-  </si>
-  <si>
-    <t>745c561e-0218-4a1f-a2b0-25098420dbff</t>
-  </si>
-  <si>
-    <t>d6a9a7a2-c5df-4d04-8701-86fccd4bd9de</t>
-  </si>
-  <si>
-    <t>eac57c27-23a1-4687-8c40-130f3bb91442</t>
-  </si>
-  <si>
-    <t>96da4087-323c-433b-834d-19f365b20ce4</t>
-  </si>
-  <si>
-    <t>daa8a397-79d0-4492-83ac-60831b800ff7</t>
-  </si>
-  <si>
-    <t>0ad669c3-9f35-4f37-9926-22c23405c40a</t>
-  </si>
-  <si>
-    <t>8c995af4-5058-4095-8681-da8e38fa2a22</t>
-  </si>
-  <si>
-    <t>f79e38a6-cbfb-480d-91ed-f1a554128caa</t>
-  </si>
-  <si>
-    <t>de13984e-550b-4fd6-b887-7096c308c163</t>
-  </si>
-  <si>
-    <t>d6fa2f1e-c23f-4824-a530-e93837b2ed44</t>
-  </si>
-  <si>
-    <t>3b1afd29-15a6-4e4a-9a68-b4a6ec4c85b0</t>
-  </si>
-  <si>
-    <t>029c27bf-b330-40bd-b407-17d5ad789e44</t>
-  </si>
-  <si>
-    <t>aebf6fc9-b995-41de-b358-20b6df45c988</t>
-  </si>
-  <si>
-    <t>17bc41dd-99b9-4720-9982-034eaee24df9</t>
-  </si>
-  <si>
-    <t>561db425-e618-4925-bd04-0e4b2995fd9e</t>
-  </si>
-  <si>
-    <t>9acbcad9-5b9e-45e8-9637-1dfd772371bb</t>
-  </si>
-  <si>
-    <t>49bc9dbd-3e46-4c9a-8f1b-bd45956f49c8</t>
-  </si>
-  <si>
-    <t>1ff0d685-07ec-4467-8379-448bd131dcb7</t>
-  </si>
-  <si>
-    <t>ce295d09-95cb-4cca-99ee-fc534cb58bba</t>
-  </si>
-  <si>
-    <t>db6d559d-4039-4b5e-9c05-e4f12a7274d5</t>
-  </si>
-  <si>
-    <t>fde82f78-40f4-4d74-a33f-d162b8452b77</t>
-  </si>
-  <si>
-    <t>e736774b-34ec-47f0-aa48-e3228854b302</t>
-  </si>
-  <si>
-    <t>92b09c22-1eb0-40bc-9619-71cf83c889f7</t>
-  </si>
-  <si>
-    <t>5a7d4911-6e7b-4dfe-811a-d2ec40d6de30</t>
-  </si>
-  <si>
-    <t>5d95ffd6-94a4-4638-b37e-31e12e9c16b4</t>
-  </si>
-  <si>
-    <t>ad5f1b12-a81b-4a2b-9c17-b43748de1609</t>
-  </si>
-  <si>
-    <t>0f8826c5-9cfd-46e9-b075-fd05ab38c4d9</t>
-  </si>
-  <si>
-    <t>8cc17569-eb37-4aaf-ad10-5b5f39df4fa9</t>
-  </si>
-  <si>
-    <t>9ad90628-1375-41da-894a-eab791bf251a</t>
-  </si>
-  <si>
-    <t>d53d12cf-099b-4a68-923f-0a0fd45b3530</t>
-  </si>
-  <si>
-    <t>4d70d700-bbfa-4727-989c-abb37848d586</t>
-  </si>
-  <si>
-    <t>e41f99f5-aa91-4150-b07d-71918318d0e3</t>
-  </si>
-  <si>
-    <t>dd113426-4b47-476a-8546-b88f778c6f80</t>
-  </si>
-  <si>
-    <t>3a169bef-8cfd-45da-a45b-3ec9309bd640</t>
-  </si>
-  <si>
-    <t>63ff2b6d-2b35-4ad0-9f19-da5ca13d851e</t>
-  </si>
-  <si>
-    <t>b947346a-1578-40ca-a488-d2f6bf73be6a</t>
-  </si>
-  <si>
-    <t>6da106c1-16ac-4121-bd02-f876a931bc8c</t>
-  </si>
-  <si>
-    <t>4842bb32-18a5-4b32-83b0-f713c48a0c72</t>
-  </si>
-  <si>
-    <t>ca64de58-16d3-46da-92a6-d40fb5efbd45</t>
-  </si>
-  <si>
-    <t>63df7954-f1ed-4468-a429-0380f8ed01a4</t>
-  </si>
-  <si>
-    <t>545c8519-6e49-4a89-8143-dd2e98fa449d</t>
-  </si>
-  <si>
-    <t>b9059ab0-d580-443e-9fc7-8d4e3a781c0d</t>
-  </si>
-  <si>
-    <t>13a4785d-e157-46ef-9b58-83aa275a4312</t>
-  </si>
-  <si>
-    <t>241f755b-ef4f-4971-9a1d-68ec012b36e9</t>
-  </si>
-  <si>
-    <t>49e7e03f-1a44-4a5d-a173-9f530621e4d2</t>
-  </si>
-  <si>
-    <t>e3c7229a-367b-4752-9c9b-21bd4c46de04</t>
-  </si>
-  <si>
-    <t>a99a0eb7-c582-4110-838e-1790b4208263</t>
-  </si>
-  <si>
-    <t>4c96301c-ce22-484d-8452-1e279cc68212</t>
-  </si>
-  <si>
-    <t>a78b5e70-cd46-4bc0-99f3-2cb542337961</t>
-  </si>
-  <si>
-    <t>23d40364-c56d-4777-a836-b533d69b9184</t>
-  </si>
-  <si>
-    <t>69115062-e43e-4098-b421-725762f9ac8d</t>
-  </si>
-  <si>
-    <t>facd4476-39a7-41f0-bf87-bd235b22ed7c</t>
-  </si>
-  <si>
-    <t>a2e51d03-94dc-46bd-81f8-fbdd0e485946</t>
-  </si>
-  <si>
-    <t>fc39c1cd-71fe-48cb-a895-d082d9143e5f</t>
-  </si>
-  <si>
-    <t>56965821-143d-4be1-8bca-fb6393325ffe</t>
-  </si>
-  <si>
-    <t>40ab691a-fa98-4eca-aac8-4e8da30e5999</t>
-  </si>
-  <si>
-    <t>a3df56fe-c651-4545-a4a7-d46398b44537</t>
-  </si>
-  <si>
-    <t>07b2812d-f9ed-4ee2-a36c-0783f13d70d8</t>
-  </si>
-  <si>
-    <t>68393975-76d3-4edc-9a69-f2d7313720f1</t>
-  </si>
-  <si>
-    <t>11495e25-500e-45d4-8789-fd1c4d8443ac</t>
-  </si>
-  <si>
-    <t>95d1215d-ed71-49dc-a55b-e57914027132</t>
-  </si>
-  <si>
-    <t>fd2050fc-72fa-4ef0-ac00-19918e4d417a</t>
-  </si>
-  <si>
-    <t>e0c46b37-aef8-424e-b926-203167b2fbe8</t>
-  </si>
-  <si>
-    <t>5d860ed4-07f1-4de6-8a96-5ad6fe624f4a</t>
-  </si>
-  <si>
-    <t>bf95a0e4-83a3-47dd-a5af-0c2e6311a725</t>
-  </si>
-  <si>
-    <t>c86a44a5-5ce1-4311-bc14-ceb72f4e38e6</t>
-  </si>
-  <si>
-    <t>9b8fbb84-aa0c-4daa-94d5-a14faa744f4d</t>
-  </si>
-  <si>
-    <t>c1df2a4a-ae05-45be-8221-ca119df29d67</t>
-  </si>
-  <si>
-    <t>9e47d791-7acc-4d8c-aa7b-90bd259ab35c</t>
-  </si>
-  <si>
-    <t>254f5e1f-7346-4d31-98ca-a8dfa5d675f2</t>
-  </si>
-  <si>
-    <t>6cb34531-b38a-4f01-86ec-c1ce114a1db1</t>
-  </si>
-  <si>
-    <t>c3faf991-d962-4a45-b435-120c22c44902</t>
-  </si>
-  <si>
-    <t>8762df56-a6c0-4aa9-8f7a-df74ddf0ef0e</t>
-  </si>
-  <si>
-    <t>a8ab14b0-943a-47a4-b40b-b108e2554375</t>
-  </si>
-  <si>
-    <t>822e464d-c52e-4244-b34d-91c8cfd36ed6</t>
-  </si>
-  <si>
-    <t>1f540abb-4a1e-4d24-93c6-ee8b89b5a3fc</t>
-  </si>
-  <si>
-    <t>b9b96459-aba1-4cc7-b751-63729c272de4</t>
-  </si>
-  <si>
-    <t>b917191b-916b-4d58-9b19-88b8c7cef5e7</t>
-  </si>
-  <si>
-    <t>e9bc9525-5093-48eb-b3ac-41b4b81f3e99</t>
-  </si>
-  <si>
-    <t>f7c59e0d-e6ac-484c-bb33-e4cd945ee300</t>
-  </si>
-  <si>
-    <t>b2e92a31-02e6-4122-9a46-924ad9ff5502</t>
-  </si>
-  <si>
-    <t>75f19b43-f607-4048-8ba5-1fed781438de</t>
-  </si>
-  <si>
-    <t>d12507dc-b0e5-4208-ad66-ee09480203ea</t>
-  </si>
-  <si>
-    <t>607304d0-6849-47d9-87ea-0a1252f65eb3</t>
-  </si>
-  <si>
-    <t>a36df9d8-6e55-4b9b-b41c-652e927cf0bf</t>
-  </si>
-  <si>
-    <t>89cfe99a-f997-4185-9abb-959fb5969eeb</t>
-  </si>
-  <si>
-    <t>e755b32b-10af-47c3-bb49-07c17b09acd9</t>
-  </si>
-  <si>
-    <t>a0798acf-485f-40fc-9e6b-785a30c9a165</t>
-  </si>
-  <si>
-    <t>80b96301-2c30-46d1-96e3-b18d76057f46</t>
-  </si>
-  <si>
-    <t>4b07c889-e00b-47e1-be97-5c14957a04ba</t>
-  </si>
-  <si>
-    <t>8cf22cd0-09e6-46f6-96aa-22051915cc61</t>
-  </si>
-  <si>
-    <t>ba771db7-81b7-42d5-a71c-cef26a3b5d97</t>
-  </si>
-  <si>
-    <t>21ebb1f4-d2b4-4a6a-b1bc-d9ef801453df</t>
-  </si>
-  <si>
-    <t>bd210765-e292-4341-bc5b-30cf0c5620a4</t>
-  </si>
-  <si>
-    <t>b19a760d-d1f6-4b6f-b934-d2fb758d17d9</t>
-  </si>
-  <si>
-    <t>8901bc6d-ec90-4650-9d03-f37c0f7e6dc6</t>
-  </si>
-  <si>
-    <t>73772050-d4c9-4e75-ab04-85466a000c94</t>
-  </si>
-  <si>
-    <t>87669014-26fc-46c2-be1e-b4f9699893fe</t>
-  </si>
-  <si>
-    <t>8b6ef025-05d6-451a-acd2-9d4c7b820b7e</t>
-  </si>
-  <si>
-    <t>fea27ba0-d7e3-4115-9b97-0eafd6971022</t>
-  </si>
-  <si>
-    <t>35c389a1-4611-4f14-bd41-ee8f4232780a</t>
-  </si>
-  <si>
-    <t>cdfe2437-01fa-41ba-8ca5-d6e0556cfe96</t>
-  </si>
-  <si>
-    <t>a89f2b6a-2200-46c2-8bf7-0979de6e01ee</t>
-  </si>
-  <si>
-    <t>8e7a32cd-eb65-4af2-ad73-c0ecf92ff17b</t>
-  </si>
-  <si>
-    <t>11e5aa82-4ece-4620-ab87-d05e1c457ee4</t>
-  </si>
-  <si>
-    <t>41c3ddcf-b99a-488a-a252-be33828cad21</t>
-  </si>
-  <si>
-    <t>0a45bb1e-c35e-4011-8ed6-ae7f5797a7ec</t>
-  </si>
-  <si>
-    <t>eaa262d0-62c2-469f-a67b-45704737b388</t>
-  </si>
-  <si>
-    <t>341987e8-da35-4b9a-b378-bd3094eb8a82</t>
-  </si>
-  <si>
-    <t>ea80d538-fa7b-4be0-b539-e33b6fdd3db3</t>
-  </si>
-  <si>
-    <t>ba751908-0b05-46e7-aabc-92975cb0d7a2</t>
-  </si>
-  <si>
-    <t>fa25043e-7370-41a4-8030-0d99a79ac92c</t>
-  </si>
-  <si>
-    <t>67178998-bb94-4739-bc4b-fce60deacc48</t>
-  </si>
-  <si>
-    <t>68bf9972-bf4c-4f55-aeb9-cf4f01902e90</t>
-  </si>
-  <si>
-    <t>43a03f2f-a5bd-4714-8312-2f89fa518709</t>
-  </si>
-  <si>
-    <t>9157cc89-cf4c-46ba-9190-652213e6799c</t>
-  </si>
-  <si>
-    <t>0c1d9573-fb0a-40bf-8cc6-ce7140fd2a59</t>
-  </si>
-  <si>
-    <t>ced72d5b-1d1e-4789-b645-d52f1c35318a</t>
-  </si>
-  <si>
-    <t>cc77ab16-082e-463c-a48a-957f06685173</t>
-  </si>
-  <si>
-    <t>2d4a4a5b-468b-496a-a39e-c081c810d79a</t>
-  </si>
-  <si>
-    <t>e31d98e6-318b-4eca-9f83-05457a904ea4</t>
-  </si>
-  <si>
-    <t>85cdf18a-26da-4445-9298-4b4fd782065f</t>
-  </si>
-  <si>
-    <t>1cb0322f-d17d-4171-b27e-2033cba6734e</t>
-  </si>
-  <si>
-    <t>e155b2a6-272b-485c-ad23-7aef7eeb34f4</t>
-  </si>
-  <si>
-    <t>b2d8a1b4-4cb1-46d0-aac4-7b1c790c85ea</t>
-  </si>
-  <si>
-    <t>454ca935-26dc-4003-86df-675d6f21b2c3</t>
-  </si>
-  <si>
-    <t>ba5118d1-b54f-4e99-bdf9-780f92490f8c</t>
-  </si>
-  <si>
-    <t>dac1fc47-8436-4ea0-9d07-6ad9f7c30815</t>
-  </si>
-  <si>
-    <t>4904a6bb-93ba-443c-bb80-fdefe98b9188</t>
-  </si>
-  <si>
-    <t>db1da6bf-9db2-4e4d-be65-ea65134f9324</t>
-  </si>
-  <si>
-    <t>980c6ae3-e474-4f41-96a5-3deb932a53f5</t>
-  </si>
-  <si>
-    <t>9aaf1320-6238-4383-8061-d76a2c4cd0d0</t>
-  </si>
-  <si>
-    <t>7afc1a68-431f-4ddd-a31f-29e88d2a641a</t>
-  </si>
-  <si>
-    <t>ea9ccb54-9345-4031-8f6d-3ac9568c8b6e</t>
-  </si>
-  <si>
-    <t>34931aa2-8dca-45c5-9ffb-b0d58159aad2</t>
-  </si>
-  <si>
-    <t>819e9a4f-e878-413b-97a9-e0a75c87cbc7</t>
-  </si>
-  <si>
-    <t>bfaebcf8-0b43-4fc3-8c69-a403fead0f95</t>
-  </si>
-  <si>
-    <t>a3725732-db25-49e9-ae37-34f9c1a27e1f</t>
-  </si>
-  <si>
-    <t>011389eb-bf3f-4ed6-80c9-33b407b926a5</t>
-  </si>
-  <si>
-    <t>dac238f9-07e2-4233-acf7-68c6cbd8d5cc</t>
-  </si>
-  <si>
-    <t>2b56b421-f617-4e3b-8bdf-63dd74b38174</t>
-  </si>
-  <si>
-    <t>b4e584fc-fd25-4308-bdbe-133607628e22</t>
-  </si>
-  <si>
-    <t>237c589b-83d2-437d-8247-6cf9e63f2130</t>
-  </si>
-  <si>
-    <t>3cd071f5-9398-403c-89f8-c14b94ea97c3</t>
-  </si>
-  <si>
-    <t>e2e0aaf9-4a7f-48e0-82d5-da01b19be576</t>
-  </si>
-  <si>
-    <t>5e242757-e833-47da-8c9d-f2b49d49a77e</t>
-  </si>
-  <si>
-    <t>d6893433-c692-47ea-a162-1bc4d6196855</t>
-  </si>
-  <si>
-    <t>61c71f45-bab9-4b45-aac8-c99969ce3733</t>
-  </si>
-  <si>
-    <t>76899c48-63fc-4f77-acd9-55e64cc0ad04</t>
-  </si>
-  <si>
-    <t>dc5f050e-0802-433d-90c3-1ce04f536cca</t>
-  </si>
-  <si>
-    <t>c37ccde9-df03-4ceb-9bca-9bc7febdc604</t>
-  </si>
-  <si>
-    <t>5407a08b-67b4-4bf3-9764-235e7d9dfaff</t>
-  </si>
-  <si>
-    <t>bfd5d790-425e-40a2-be10-5adb6991496c</t>
-  </si>
-  <si>
-    <t>e29d9b88-d330-4ed1-abe6-6be6fc0138cd</t>
-  </si>
-  <si>
-    <t>1abe13e7-f3f2-41da-96b9-e8e73cccb62b</t>
-  </si>
-  <si>
-    <t>4876962c-5c7e-4094-9113-351e6ece3ebe</t>
-  </si>
-  <si>
-    <t>65efd22e-1877-434a-a049-ac32e794a39d</t>
-  </si>
-  <si>
-    <t>0537d736-c22a-4c00-b151-cfb0d6efd1a8</t>
-  </si>
-  <si>
-    <t>bc18c06f-9d38-472f-ae7e-b8fcd7874541</t>
-  </si>
-  <si>
-    <t>b13a167d-c92a-428d-8632-b3a762450851</t>
-  </si>
-  <si>
-    <t>ef2aae52-8dbe-43a7-ba7d-ae7161f39aab</t>
-  </si>
-  <si>
-    <t>95395686-2f6c-4524-bab9-caad6f434d93</t>
-  </si>
-  <si>
-    <t>a4389861-489f-40f7-92e1-35dce8cc9f00</t>
-  </si>
-  <si>
-    <t>a37deb0b-34e2-467a-960f-aee1b445ede7</t>
-  </si>
-  <si>
-    <t>92c96974-6634-4bff-bc52-bbe525faea01</t>
-  </si>
-  <si>
-    <t>19d601ac-3717-4eea-9d19-39f2cc8da3f2</t>
-  </si>
-  <si>
-    <t>7b991696-b709-4c5c-9562-95eda90d165f</t>
-  </si>
-  <si>
-    <t>5dbbbdb1-1f68-4d42-bf66-ab3a927c3a18</t>
-  </si>
-  <si>
-    <t>9a04ef21-f06a-4510-ac5b-3e9f027f3814</t>
-  </si>
-  <si>
-    <t>d948d178-ebab-4f27-8d98-bf6b9873ed1c</t>
-  </si>
-  <si>
-    <t>184548f8-20a7-4d56-9da0-6acc4d958178</t>
-  </si>
-  <si>
-    <t>2fdea35f-4033-4b4e-ab25-034effdc0c5a</t>
-  </si>
-  <si>
-    <t>caf1c2d0-6288-4faf-b441-cb9d1700a1de</t>
-  </si>
-  <si>
-    <t>94d84c14-d952-4202-9693-569f837583fc</t>
-  </si>
-  <si>
-    <t>e2a96a16-a72f-45fa-8fca-79a2aef1d0ef</t>
-  </si>
-  <si>
-    <t>dadc4160-4358-4955-aad3-fe4a368bca0f</t>
-  </si>
-  <si>
-    <t>07c29fef-acca-4971-959f-e1067917955b</t>
-  </si>
-  <si>
-    <t>12992b26-227a-42ec-b486-d6a8d13e2db5</t>
-  </si>
-  <si>
-    <t>a45c84bc-6743-420c-b73e-f3708250afaf</t>
-  </si>
-  <si>
-    <t>7602f43a-8b3a-4ffa-aff3-28c589874c5f</t>
-  </si>
-  <si>
-    <t>931fb6af-a813-410e-a10d-728c4a94b624</t>
-  </si>
-  <si>
-    <t>b2871202-c617-4ae2-8543-088ac79c5cec</t>
-  </si>
-  <si>
-    <t>50fef54d-8b81-467a-85fa-f3d7e5f0327c</t>
-  </si>
-  <si>
-    <t>88eee1ac-fbd7-4905-b456-28130ebc13b7</t>
-  </si>
-  <si>
-    <t>91d29023-e6cb-4de4-b7de-420e108ada78</t>
-  </si>
-  <si>
-    <t>a4f65c6b-7c27-4230-8205-f8580a1aab67</t>
-  </si>
-  <si>
-    <t>028ef86e-4b5c-437a-8cdf-7d3e3c25125d</t>
-  </si>
-  <si>
-    <t>8a8c3a20-c971-43f3-aa17-c6db2fc68d4e</t>
-  </si>
-  <si>
-    <t>804b390f-4f6e-4d18-8a14-9ee9ec9da681</t>
-  </si>
-  <si>
-    <t>dd28f0eb-8f38-451f-b017-a3240d5ff28a</t>
-  </si>
-  <si>
-    <t>97eee0eb-829c-4f76-873a-617b45f0cac2</t>
-  </si>
-  <si>
-    <t>ff790dcf-1b79-41e4-b674-b8db94fc6a5a</t>
-  </si>
-  <si>
-    <t>3957b5e5-1a79-4c37-9ef6-6c6bd4e8e2f9</t>
-  </si>
-  <si>
-    <t>2426c776-d9f7-452f-9922-e48e79185ad3</t>
-  </si>
-  <si>
-    <t>3b028730-1dc4-4834-bc49-2cdf11587def</t>
-  </si>
-  <si>
-    <t>8a0ef9fd-dcc9-4faf-933a-d7181ddb1dfb</t>
-  </si>
-  <si>
-    <t>3cd78abe-ee6e-4150-8a16-4b037ac588e9</t>
-  </si>
-  <si>
-    <t>aaae9dd6-2553-43cd-aa48-441706c78f87</t>
-  </si>
-  <si>
-    <t>8f2f37d1-49a4-4e8e-b45f-13c224efa9d4</t>
-  </si>
-  <si>
-    <t>a9026f70-7bdc-444c-ba37-f817d0c0844c</t>
-  </si>
-  <si>
-    <t>90568de2-cf52-4f8b-9357-bc8a5a61fae1</t>
-  </si>
-  <si>
-    <t>c5fa81f7-2d4e-4a1e-a8e2-b9ee622e8c25</t>
-  </si>
-  <si>
-    <t>b1f089b5-1abf-4089-92c2-5322f9290a5b</t>
-  </si>
-  <si>
-    <t>266f67b2-e755-4946-99de-c982a5e8baf0</t>
-  </si>
-  <si>
-    <t>78a87fd0-1cfc-444a-80ea-54e622dac00f</t>
-  </si>
-  <si>
-    <t>94339e6c-88b8-4b46-ab30-7026f8b0267c</t>
-  </si>
-  <si>
-    <t>824f4d20-dfa0-4338-985e-c0c0e9cd3b2d</t>
-  </si>
-  <si>
-    <t>a59dcffc-16a9-40d5-8404-c083d5d290fc</t>
-  </si>
-  <si>
-    <t>5320143f-063c-4a85-b507-d9dbcb763900</t>
-  </si>
-  <si>
-    <t>1c49efc9-acdf-4a9c-b8c8-63ec17e70536</t>
-  </si>
-  <si>
-    <t>574c01a7-cc52-4ff9-a559-0220b8cb45ca</t>
-  </si>
-  <si>
-    <t>6fc09e56-cf50-4fd6-9ac4-686b2f86da94</t>
-  </si>
-  <si>
-    <t>7c9cd278-a2e7-4baa-b3cb-b5218e8bd915</t>
-  </si>
-  <si>
-    <t>532147b9-4927-4c33-a079-3cecfdfdc3f1</t>
-  </si>
-  <si>
-    <t>2f98f028-661c-4966-96f0-0f032d319380</t>
-  </si>
-  <si>
-    <t>980a42a3-d113-47e7-bfcc-eaf251f9d547</t>
-  </si>
-  <si>
-    <t>caccf0ef-82be-40c4-8e56-d27abd14de18</t>
-  </si>
-  <si>
-    <t>be23d7fe-eed6-43a9-a56c-9c69b1b37192</t>
-  </si>
-  <si>
-    <t>ba25e27d-ea5e-48ac-8a71-da7345cdcd94</t>
-  </si>
-  <si>
-    <t>1c1a2d30-25a1-415e-9ecf-d61f77898343</t>
-  </si>
-  <si>
-    <t>1a837f3f-83f0-48a7-bc2a-ef607bc1518a</t>
-  </si>
-  <si>
-    <t>423eac6c-2c93-4f8f-ae84-9cc6707ce673</t>
-  </si>
-  <si>
-    <t>5be7092d-528a-45ce-80c6-7a785397461b</t>
-  </si>
-  <si>
-    <t>8b01cafc-0aec-4ded-bfe0-fd90238490b4</t>
-  </si>
-  <si>
-    <t>409af498-2c9c-431e-b353-b10db54e6032</t>
-  </si>
-  <si>
-    <t>694f8aa7-350b-4dd9-8971-84449f534db7</t>
-  </si>
-  <si>
-    <t>92b16aaa-35dd-4b3f-8132-200b4e2799a2</t>
-  </si>
-  <si>
-    <t>37f1c697-56c5-4584-b8fe-135a158dbabe</t>
-  </si>
-  <si>
-    <t>802d821a-17c9-41d2-82f0-e35bcafbb9f5</t>
-  </si>
-  <si>
-    <t>5228070c-d15a-4858-bfc9-fadf4167c5d2</t>
-  </si>
-  <si>
-    <t>c92577ed-ac89-44a3-88aa-7211e3bfd16d</t>
-  </si>
-  <si>
-    <t>da7b1ea1-3b2b-40da-b4b6-29d40f285f0e</t>
-  </si>
-  <si>
-    <t>441a8f67-39e8-4bd3-b3df-d77853476390</t>
-  </si>
-  <si>
-    <t>ea90725c-75fa-42aa-8d91-62f34182babc</t>
-  </si>
-  <si>
-    <t>efcfbb53-9ccf-4f39-91a1-37dd7df1aace</t>
-  </si>
-  <si>
-    <t>af11acd0-caee-40d4-be65-8996dd439d38</t>
-  </si>
-  <si>
-    <t>f0afc4c8-c38b-447d-b2df-8ee85522d7ac</t>
-  </si>
-  <si>
-    <t>c6421383-8988-4d00-8641-cab893f504ee</t>
-  </si>
-  <si>
-    <t>6b2456c2-6f28-4e0b-8e63-bcb6b812b210</t>
-  </si>
-  <si>
-    <t>7cdfbdd8-d1b8-439a-836f-b8eac2c4ff48</t>
-  </si>
-  <si>
-    <t>f1262987-e211-4b43-b085-f1f70fc17325</t>
-  </si>
-  <si>
-    <t>f34b433f-d8f3-4667-98f4-65de8b8a9c1c</t>
-  </si>
-  <si>
-    <t>467cf9ea-6754-4052-9143-4de751ef843b</t>
-  </si>
-  <si>
-    <t>daa62585-e55e-4572-91c3-40ebb8efcdad</t>
-  </si>
-  <si>
-    <t>0b34be89-9fd3-49b5-9b5a-96b061532f62</t>
-  </si>
-  <si>
-    <t>9fcdae2f-11c3-4dfd-b33e-cb00c529b16a</t>
-  </si>
-  <si>
-    <t>499bd48d-8a83-42c6-8634-1e2f7f8ee70c</t>
-  </si>
-  <si>
-    <t>548398a0-c74d-4218-874e-a7f4bd41996d</t>
-  </si>
-  <si>
-    <t>945df8f3-3a13-48e6-90ad-d9a7ad2e8cb8</t>
-  </si>
-  <si>
-    <t>4a8a610e-f997-468e-bafa-2b79c24f8442</t>
-  </si>
-  <si>
-    <t>f957d6e7-d4c5-44b6-9c0c-a293afc15103</t>
-  </si>
-  <si>
-    <t>efce6c67-7dd9-485b-a928-df75ea2a7426</t>
-  </si>
-  <si>
-    <t>c8c79f76-66c2-40f2-aba7-b4baefb6c624</t>
-  </si>
-  <si>
-    <t>8652343b-9e1d-488d-b18d-b379cad4ebca</t>
-  </si>
-  <si>
-    <t>ea1a12b9-5a87-41cc-92b6-01bf9aa51fb7</t>
-  </si>
-  <si>
-    <t>2be03946-371b-419c-b95b-7f26245def2d</t>
-  </si>
-  <si>
-    <t>bb687f71-63f2-4927-a406-acb527276296</t>
-  </si>
-  <si>
-    <t>aea1ab64-567c-413f-948b-59290f15756d</t>
-  </si>
-  <si>
-    <t>7c5c2653-89bd-4b46-948b-f20b53481e21</t>
-  </si>
-  <si>
-    <t>f5deaede-fe6a-4aeb-9703-e84e963ba4a7</t>
-  </si>
-  <si>
-    <t>364648c7-c953-45f9-83fe-ab8516dd77a3</t>
-  </si>
-  <si>
-    <t>475be1fc-9b75-4adc-a0b8-4131da32412d</t>
-  </si>
-  <si>
-    <t>caaedec5-d561-4a3a-9982-ecc13f12742c</t>
-  </si>
-  <si>
-    <t>144116f0-9547-45e0-bb99-bb7608f9a187</t>
-  </si>
-  <si>
-    <t>1c402c31-5118-4f7a-acf8-b3c0e1e604cb</t>
-  </si>
-  <si>
-    <t>7707df19-ee56-496b-9535-495c4c614cd0</t>
-  </si>
-  <si>
-    <t>2d67a60b-5d9e-4f93-82d1-bfe7b40ad410</t>
-  </si>
-  <si>
-    <t>12b6e1b9-485c-4da2-b3d5-562e133b60b4</t>
-  </si>
-  <si>
-    <t>b4ec5360-0e52-4ad0-9e97-7b2a04bb102f</t>
-  </si>
-  <si>
-    <t>95f252da-9113-400a-813a-bb3dedb5b355</t>
-  </si>
-  <si>
-    <t>88b724fe-23b8-45cc-bfc6-b11af3c837cf</t>
-  </si>
-  <si>
-    <t>6af7569c-943e-4f6e-9ed7-022c6fdba53e</t>
-  </si>
-  <si>
-    <t>fb568941-137b-41f7-aa85-24412eaf0859</t>
-  </si>
-  <si>
-    <t>e1dc55b4-f520-47f1-b2db-556b3db84b62</t>
-  </si>
-  <si>
-    <t>f7a82bcb-ca86-4768-a115-9fba21c352db</t>
-  </si>
-  <si>
-    <t>2a4425a3-47f8-4457-8986-a4fd8c2ea5b5</t>
-  </si>
-  <si>
-    <t>b9c708b3-dfb6-4f5e-b916-b26db8a2bae7</t>
-  </si>
-  <si>
-    <t>c623166e-f359-46a1-821f-066bd94f064d</t>
-  </si>
-  <si>
-    <t>65091ae7-c752-43e7-a054-7f3ad1b554bf</t>
-  </si>
-  <si>
-    <t>7ad243fc-f56c-44d7-af57-af0d3d7c6c5b</t>
-  </si>
-  <si>
-    <t>a7632179-36fe-463b-8c84-21fb8aa6ea70</t>
-  </si>
-  <si>
-    <t>7c3f610b-0d17-4f73-9333-52542550a145</t>
-  </si>
-  <si>
-    <t>dd43605c-1875-44d9-93e3-9c62a772ff48</t>
-  </si>
-  <si>
-    <t>9fa95850-ca83-423b-a0ee-125da80d0119</t>
-  </si>
-  <si>
-    <t>595d4533-04c3-44b4-9433-c782d52e5efc</t>
+    <t>ce8f00bb-08e7-421d-94f7-d5eb94aa0a18</t>
+  </si>
+  <si>
+    <t>c4f612d5-376a-4d36-80da-453174b53125</t>
+  </si>
+  <si>
+    <t>f03d1cf5-8924-42bc-9789-1a3a913c2618</t>
+  </si>
+  <si>
+    <t>50bd30b6-6a14-40eb-98d2-0163d9da9d46</t>
+  </si>
+  <si>
+    <t>00439f71-b249-4673-a9a4-4b768de6e75e</t>
+  </si>
+  <si>
+    <t>9ac4547f-3d2e-41b7-9679-18349d2cd080</t>
+  </si>
+  <si>
+    <t>b94127de-4b83-41bc-b0b4-8db08958d918</t>
+  </si>
+  <si>
+    <t>a431c657-95d7-4a1e-ad36-a392cc055a7d</t>
+  </si>
+  <si>
+    <t>72c3a8b1-aeee-4cc1-a3c4-144db0139ed6</t>
+  </si>
+  <si>
+    <t>7f56f482-1ec1-4883-bc0f-7346b257fcb8</t>
+  </si>
+  <si>
+    <t>1a9f173c-075c-419a-a69d-f22c2bc24578</t>
+  </si>
+  <si>
+    <t>5e2ecffb-0f81-4c13-b039-2a4070cb66fc</t>
+  </si>
+  <si>
+    <t>e1ddc124-b3b0-4104-b1c9-3464f94a4e41</t>
+  </si>
+  <si>
+    <t>3055f324-a3b8-4f53-bce5-7c775f5d706c</t>
+  </si>
+  <si>
+    <t>daac0c34-0dae-4ed2-a0fa-8b4a47183fe5</t>
+  </si>
+  <si>
+    <t>008cd117-e8f2-4348-938b-2e31c6f0cb31</t>
+  </si>
+  <si>
+    <t>980e1d28-6bb6-4def-b803-b654881590de</t>
+  </si>
+  <si>
+    <t>455f6a01-48cc-44d8-a91d-1dbfe8bdae87</t>
+  </si>
+  <si>
+    <t>a3f5df1a-d050-410d-b293-f5db2c76fb74</t>
+  </si>
+  <si>
+    <t>1e250d6a-4ad4-4fbd-bcf5-04cdeb8993d2</t>
+  </si>
+  <si>
+    <t>5987c031-1552-4652-834f-ba99f7a1ead4</t>
+  </si>
+  <si>
+    <t>009472e5-b81c-4fd4-8f74-5fde02262d49</t>
+  </si>
+  <si>
+    <t>44bad27f-4db3-4d7f-b6a5-42215f5dc70e</t>
+  </si>
+  <si>
+    <t>6ff83d75-f1d0-4381-944e-2e9e3edeccc7</t>
+  </si>
+  <si>
+    <t>e96f3099-7727-4324-9e70-b32cab4940fb</t>
+  </si>
+  <si>
+    <t>0edd2425-4fc3-4226-9934-df5da16f8a78</t>
+  </si>
+  <si>
+    <t>2a4fd9cc-4f67-41a4-8b01-72ddc7da7d56</t>
+  </si>
+  <si>
+    <t>090f1791-c673-4d13-b811-98434b2b838a</t>
+  </si>
+  <si>
+    <t>f18ed439-00ad-4e7e-a2cd-16af0c2a92ba</t>
+  </si>
+  <si>
+    <t>8414e581-f666-4748-96d4-1519d9d3f07e</t>
+  </si>
+  <si>
+    <t>0055bb40-e277-4e18-95e5-f081de9434c9</t>
+  </si>
+  <si>
+    <t>73459e45-f6c3-4c64-9e9b-7e2eb85ed267</t>
+  </si>
+  <si>
+    <t>dfe28758-fcb1-4351-938f-216c72840340</t>
+  </si>
+  <si>
+    <t>36b40d5f-760d-4dc4-890b-80d589a1b3cd</t>
+  </si>
+  <si>
+    <t>9dbcef12-f43e-4a7a-bb5d-bf2ccc3214ec</t>
+  </si>
+  <si>
+    <t>500b440e-6e84-44cd-87ac-157910210634</t>
+  </si>
+  <si>
+    <t>e089e96c-4737-4536-9723-04830013a26c</t>
+  </si>
+  <si>
+    <t>aebb5f33-978d-47f5-b916-3ef4da4fd14e</t>
+  </si>
+  <si>
+    <t>58c466ca-4eb5-4c17-892c-71d2debcb940</t>
+  </si>
+  <si>
+    <t>d42420df-c4ce-449e-9e3c-a6798602bcf6</t>
+  </si>
+  <si>
+    <t>ad171bd4-cdac-4b14-b6c3-9a5e9f8f8bc0</t>
+  </si>
+  <si>
+    <t>2bf2d69b-0da6-4240-8dcc-75cd73965dac</t>
+  </si>
+  <si>
+    <t>409519bd-3625-4cf6-aa32-f67b513770f2</t>
+  </si>
+  <si>
+    <t>d1d77b03-c389-45db-af26-02db969e493c</t>
+  </si>
+  <si>
+    <t>7093ee52-6d1d-4ed7-a7d3-ac9dcb3b32ec</t>
+  </si>
+  <si>
+    <t>995edb2d-1035-4de0-bbce-b8e6a83fa9a2</t>
+  </si>
+  <si>
+    <t>1b3bba50-c666-41f4-b639-7a049ce3f08d</t>
+  </si>
+  <si>
+    <t>1ac229d3-dec3-46f1-a85b-d8c320961fec</t>
+  </si>
+  <si>
+    <t>f376cac0-8f46-4485-b300-909fd8ac7ee9</t>
+  </si>
+  <si>
+    <t>ccb8fe2b-3c0b-45ae-bbcf-bf8a6329a43d</t>
+  </si>
+  <si>
+    <t>7fcb02fb-a67c-42b5-835d-7116b9f5b21f</t>
+  </si>
+  <si>
+    <t>45d463af-033b-4ad5-9da4-b5a5910cac64</t>
+  </si>
+  <si>
+    <t>3ba71ef9-4b54-4350-b351-0b35757686b6</t>
+  </si>
+  <si>
+    <t>24846929-e59d-495d-b50d-6922a6dead25</t>
+  </si>
+  <si>
+    <t>ce471ee9-9181-40af-aaa9-4d98797ac5a1</t>
+  </si>
+  <si>
+    <t>f2b47931-fad6-47f1-9e4f-89cded085720</t>
+  </si>
+  <si>
+    <t>4bb814dd-2e24-4bbe-aa97-83c396e8747a</t>
+  </si>
+  <si>
+    <t>8087a2ce-8dae-489c-92dd-e1299dfe4714</t>
+  </si>
+  <si>
+    <t>b0649dc5-4d1b-43ff-a7d1-176da5d904ae</t>
+  </si>
+  <si>
+    <t>81d6ba68-525f-4be7-b6d4-eee23f673ca3</t>
+  </si>
+  <si>
+    <t>f5a42767-da41-4610-8c4a-bf34f5217388</t>
+  </si>
+  <si>
+    <t>3eeb108c-cb29-48f1-b200-233b1ceaae71</t>
+  </si>
+  <si>
+    <t>634a46ff-26a9-419a-97cc-6723a016a0b4</t>
+  </si>
+  <si>
+    <t>f19d162c-ab2d-4949-84ec-72c9babc3804</t>
+  </si>
+  <si>
+    <t>7bc0dacf-649f-4af6-8a10-ed5451407a1e</t>
+  </si>
+  <si>
+    <t>d1da8a87-7abb-4321-9e5f-eed7ea12685c</t>
+  </si>
+  <si>
+    <t>c0ec9a76-3736-42f6-8245-9b9fc60675a1</t>
+  </si>
+  <si>
+    <t>9a87396a-674a-4c4d-be58-0430fd9637fa</t>
+  </si>
+  <si>
+    <t>b6b94272-0268-41e2-acec-45917d5365a3</t>
+  </si>
+  <si>
+    <t>a88645e2-4f46-4f5e-9d9b-979629a59b4a</t>
+  </si>
+  <si>
+    <t>9d0c1077-b4d8-4d38-b0d2-999e0b996f5a</t>
+  </si>
+  <si>
+    <t>e9772f9a-c162-42d7-94ee-ddada038afa9</t>
+  </si>
+  <si>
+    <t>ec6089d3-24d0-42a6-98f7-f625a1dad5ca</t>
+  </si>
+  <si>
+    <t>04e6dc82-b731-4016-8eaf-c19186978f5c</t>
+  </si>
+  <si>
+    <t>f342b87b-45b5-4c2b-a91c-d30c109c66c8</t>
+  </si>
+  <si>
+    <t>3790c7f0-bedf-45c4-b7af-8800ab8df6a4</t>
+  </si>
+  <si>
+    <t>02305e12-2a8e-4d9d-8442-de515a24d7e6</t>
+  </si>
+  <si>
+    <t>1c057766-d610-45ae-b53b-6acdae381a9c</t>
+  </si>
+  <si>
+    <t>eab88e60-b94e-40e5-a07b-e596ce7ec704</t>
+  </si>
+  <si>
+    <t>c11434e6-749b-43e4-ab7b-9c8629a0ac46</t>
+  </si>
+  <si>
+    <t>67ec2e41-5378-426c-9f30-d93b8d0bd415</t>
+  </si>
+  <si>
+    <t>1e961e64-2e1a-4ef7-94ad-14c05aade374</t>
+  </si>
+  <si>
+    <t>01925753-5eff-47eb-a29f-206b06f75449</t>
+  </si>
+  <si>
+    <t>dcb98052-7558-4e20-bbc9-8d125ea87f46</t>
+  </si>
+  <si>
+    <t>868d3842-359c-45fd-9c76-00cd03023a0d</t>
+  </si>
+  <si>
+    <t>9d59b45e-8ad8-4029-98a7-1456eb40c1a9</t>
+  </si>
+  <si>
+    <t>af8d6364-125b-4b43-9f29-ca22e38b3ce9</t>
+  </si>
+  <si>
+    <t>6daecb4e-bf96-4bea-be80-bfc2f055df40</t>
+  </si>
+  <si>
+    <t>aa6c251d-aacf-4e91-9188-4141154c072d</t>
+  </si>
+  <si>
+    <t>efcdad98-1cf0-40a3-a133-70a395e4975f</t>
+  </si>
+  <si>
+    <t>42a4200f-9203-42a8-ad8e-4ef6cc96a537</t>
+  </si>
+  <si>
+    <t>1e8c39f3-0439-4303-9f99-8b303c795aff</t>
+  </si>
+  <si>
+    <t>037807ef-ffb7-4564-9f3b-252b150a55fb</t>
+  </si>
+  <si>
+    <t>908641be-5401-41d2-9085-303244d5995d</t>
+  </si>
+  <si>
+    <t>fcd43c8d-8604-43fa-b8fd-1fe4b30d122e</t>
+  </si>
+  <si>
+    <t>90490fd2-3632-4ebd-b651-f28e73cb591b</t>
+  </si>
+  <si>
+    <t>fb055f07-426b-4187-948d-146696f6798d</t>
+  </si>
+  <si>
+    <t>9b0593a9-eae8-41a0-9f36-ba1cc0db2d36</t>
+  </si>
+  <si>
+    <t>afa7a400-f847-4a80-ae82-f585688bef1c</t>
+  </si>
+  <si>
+    <t>1f1c2e65-98d7-4b15-aab8-5b5c2f46b77b</t>
+  </si>
+  <si>
+    <t>097dbc25-c7a8-429a-9334-91a54ae54251</t>
+  </si>
+  <si>
+    <t>366ef75f-7a13-4785-8b15-739cc7b3dd6e</t>
+  </si>
+  <si>
+    <t>69f386fd-6563-424e-a67f-8afe74508282</t>
+  </si>
+  <si>
+    <t>e7b92980-9897-4004-90bb-4e73bb087655</t>
+  </si>
+  <si>
+    <t>7bca6493-0de2-43a5-afbb-c60cf59a9686</t>
+  </si>
+  <si>
+    <t>770726d1-82df-4feb-ad47-5b8ed83c1a36</t>
+  </si>
+  <si>
+    <t>5d80126d-8c5f-497d-b519-eeccea472db8</t>
+  </si>
+  <si>
+    <t>7637ac6b-26c8-437c-a3fc-d7a138ab8cfc</t>
+  </si>
+  <si>
+    <t>e5b911c6-7581-4f26-92a3-2ed7002d290a</t>
+  </si>
+  <si>
+    <t>f615b631-ad3a-47de-9d8e-918d476f08ab</t>
+  </si>
+  <si>
+    <t>32238839-b67a-47e4-a34f-d6bba8a287f4</t>
+  </si>
+  <si>
+    <t>3034f558-ca3b-4fed-8ac8-67dd3ef667c4</t>
+  </si>
+  <si>
+    <t>f4da9292-d463-4ead-b080-2faa9ff75aa0</t>
+  </si>
+  <si>
+    <t>cc612b22-db4e-4eab-adb4-d4c07439f8f8</t>
+  </si>
+  <si>
+    <t>1a3a668e-c74d-4761-aff5-246d194987f9</t>
+  </si>
+  <si>
+    <t>844f248c-ef55-4f70-84b6-3ee786a258df</t>
+  </si>
+  <si>
+    <t>89ffc014-5ae3-4309-9da2-e6784237286d</t>
+  </si>
+  <si>
+    <t>1c020324-6e8e-47f8-90ba-d9f342a8b8a7</t>
+  </si>
+  <si>
+    <t>e16fb804-c0d8-4487-934a-af8971ae510d</t>
+  </si>
+  <si>
+    <t>bbcd5611-7a77-4e1f-8316-7a1df3cf400c</t>
+  </si>
+  <si>
+    <t>5ad6bd95-3497-497c-b584-086e511ec096</t>
+  </si>
+  <si>
+    <t>12531daf-2c8c-4a19-a047-460c0fda1c40</t>
+  </si>
+  <si>
+    <t>5d100ad5-505e-48d6-af76-1a487ef9c9d1</t>
+  </si>
+  <si>
+    <t>9a483a0a-baac-4341-bebe-2dcfe753be0f</t>
+  </si>
+  <si>
+    <t>e184fe5e-755d-4f4b-a000-19bd0afb2784</t>
+  </si>
+  <si>
+    <t>263928f7-57cd-4610-8e69-2dba0bd372bd</t>
+  </si>
+  <si>
+    <t>2b335f0b-2411-4030-9c06-64048917ec7b</t>
+  </si>
+  <si>
+    <t>4ed7c290-b83f-4620-98af-d3a28c0ff760</t>
+  </si>
+  <si>
+    <t>8a7a7ca5-1ea0-4e68-bd42-38120377b674</t>
+  </si>
+  <si>
+    <t>2c6001ec-8275-4ad4-8262-e3bb830cef3c</t>
+  </si>
+  <si>
+    <t>96545923-cf39-4066-a9f7-054495a18c6e</t>
+  </si>
+  <si>
+    <t>08b67560-1da0-4c7c-9c40-e920835ef4ce</t>
+  </si>
+  <si>
+    <t>005c6fc2-f4bb-48a5-8a7f-9fce9332b8cc</t>
+  </si>
+  <si>
+    <t>21ae0e12-1ec9-49ae-978d-536c70348cb6</t>
+  </si>
+  <si>
+    <t>28bedd2c-b00b-47c1-808a-424a82a063d7</t>
+  </si>
+  <si>
+    <t>1ae50633-f176-4779-b8b4-60e90fcc7bfe</t>
+  </si>
+  <si>
+    <t>bc4bf35b-a069-4c7b-ad3f-df91e1a12514</t>
+  </si>
+  <si>
+    <t>8926d0bc-536d-4208-ace3-a77b4b33c7f0</t>
+  </si>
+  <si>
+    <t>b08e54b9-89f2-440c-8bc7-96bcb9cffc8f</t>
+  </si>
+  <si>
+    <t>09e8f118-30ec-4fae-83c9-63b5da0b3073</t>
+  </si>
+  <si>
+    <t>8acb3276-d42d-4660-8df9-a0072922cf7e</t>
+  </si>
+  <si>
+    <t>347fd588-9b42-4bd3-bc6b-9cf41769fb1c</t>
+  </si>
+  <si>
+    <t>cf92bf18-73ac-4f7b-b558-61b46caefb6b</t>
+  </si>
+  <si>
+    <t>b3d48d92-15cd-420a-a38f-1ccab2e15b2f</t>
+  </si>
+  <si>
+    <t>a1b5c795-e26c-4342-a5b3-589cb22566f9</t>
+  </si>
+  <si>
+    <t>74f6063a-eac8-4a34-b1b0-67006fd26a48</t>
+  </si>
+  <si>
+    <t>23eb990f-b6ae-4c9e-9f0f-e5e99e3d4fbb</t>
+  </si>
+  <si>
+    <t>a7684801-e37b-464b-8b9a-fc606af0b676</t>
+  </si>
+  <si>
+    <t>efd8317e-9144-4957-a824-c1980b7cf256</t>
+  </si>
+  <si>
+    <t>b3032b4b-537c-491b-9e85-5d662900fb13</t>
+  </si>
+  <si>
+    <t>8448970c-f311-4a15-ac83-62ec3674ed59</t>
+  </si>
+  <si>
+    <t>8d96ff53-b9ec-4fea-9fa3-71804c974a94</t>
+  </si>
+  <si>
+    <t>87cf941f-f01f-44f4-b135-0045e3a42292</t>
+  </si>
+  <si>
+    <t>f85c0404-5fe6-4c65-9525-16bedcefe1b2</t>
+  </si>
+  <si>
+    <t>d3137cc6-01c2-43f4-a6c6-9a3ba0a2d9b2</t>
+  </si>
+  <si>
+    <t>c7542155-8418-460e-8304-c92f25f2ee1e</t>
+  </si>
+  <si>
+    <t>140083f2-be3e-418d-be09-5b2b20d5c54e</t>
+  </si>
+  <si>
+    <t>062f734a-8fff-4031-96b7-09a884d2d62f</t>
+  </si>
+  <si>
+    <t>9e194a98-46d3-4a80-b121-72093fdb36a4</t>
+  </si>
+  <si>
+    <t>b79c1a9a-2c48-4423-a368-b12c468de25d</t>
+  </si>
+  <si>
+    <t>d436b944-d659-4c79-8b94-f13fc54ebebe</t>
+  </si>
+  <si>
+    <t>d9598d73-270c-4996-9609-e6738f39cdae</t>
+  </si>
+  <si>
+    <t>0ebd81b5-fbee-4644-927e-a800e60a3481</t>
+  </si>
+  <si>
+    <t>c9d11459-23bc-4946-9665-189886fd4689</t>
+  </si>
+  <si>
+    <t>6d1ff555-7ce5-4152-92cd-2d66a9b4a397</t>
+  </si>
+  <si>
+    <t>38a1a127-e923-44c1-a637-c8c3bd134f88</t>
+  </si>
+  <si>
+    <t>ca0ec8dc-b2c8-4372-934a-1ff724730d26</t>
+  </si>
+  <si>
+    <t>6765fbd1-2c9f-4873-9f97-285f3c380ace</t>
+  </si>
+  <si>
+    <t>f0f9f23e-47b7-476c-8fe2-05aac64ad1cc</t>
+  </si>
+  <si>
+    <t>54c44f5a-33e7-4447-82c8-b26c4159c94e</t>
+  </si>
+  <si>
+    <t>c8ac5406-dd7d-445e-be7f-0be075755976</t>
+  </si>
+  <si>
+    <t>190ffd43-58a0-4e0a-b482-a02e367bc2e0</t>
+  </si>
+  <si>
+    <t>50713b4b-4908-4264-b8e9-6943890ffd09</t>
+  </si>
+  <si>
+    <t>f9725dee-d372-4760-9df6-faff00e6010b</t>
+  </si>
+  <si>
+    <t>12408021-8762-4ac5-96de-50188eb099e6</t>
+  </si>
+  <si>
+    <t>9e9d2a6f-fd0a-4c09-8e24-6fd3e40f9199</t>
+  </si>
+  <si>
+    <t>bafecea6-0b50-4caf-b579-4f21fd00aa92</t>
+  </si>
+  <si>
+    <t>84ad9ae4-80d9-473b-ab62-4e9ce21805a2</t>
+  </si>
+  <si>
+    <t>a4387cf9-b488-4717-9e44-0367e9a26d3e</t>
+  </si>
+  <si>
+    <t>d2407be7-0d5c-43b3-86bf-d0c92d29fcce</t>
+  </si>
+  <si>
+    <t>909538ba-7ad4-454d-882b-ce469a442037</t>
+  </si>
+  <si>
+    <t>1b31286e-4454-4135-a6de-16def35b0342</t>
+  </si>
+  <si>
+    <t>021a27f7-bdad-44a1-b515-62d482803556</t>
+  </si>
+  <si>
+    <t>4b4d0915-6522-4f72-9653-7ebd06e46b6d</t>
+  </si>
+  <si>
+    <t>f6bb4a5b-439d-4c66-bea8-013bff7b8b19</t>
+  </si>
+  <si>
+    <t>44d11f49-4c6f-4870-a03f-7f019b21d401</t>
+  </si>
+  <si>
+    <t>c74978a7-6272-4209-85f1-c060fce29924</t>
+  </si>
+  <si>
+    <t>614b2632-ba46-4e74-b571-74e0575a7b47</t>
+  </si>
+  <si>
+    <t>5abff554-6fe5-49c9-bcfb-877f99029a70</t>
+  </si>
+  <si>
+    <t>c8d75e72-2e7d-45f4-88e0-b0ea9398b71f</t>
+  </si>
+  <si>
+    <t>33cca3c0-f928-46c6-b69a-67bff16fc0fb</t>
+  </si>
+  <si>
+    <t>f270f99b-02a5-484e-92fa-735164d6a078</t>
+  </si>
+  <si>
+    <t>586be792-c398-483a-a906-8ba64817fda8</t>
+  </si>
+  <si>
+    <t>0f152fb7-8294-4c8f-9323-62ace6841b3a</t>
+  </si>
+  <si>
+    <t>ddf20d15-a0a0-4e65-abf8-40c0011fb515</t>
+  </si>
+  <si>
+    <t>af3d2ca9-d932-43b3-9dcb-816521c91f9f</t>
+  </si>
+  <si>
+    <t>4dac4d15-ea42-41f3-ac2d-9b23f7af0cef</t>
+  </si>
+  <si>
+    <t>0bd188c3-e6ab-4e60-8a91-62348ee330f4</t>
+  </si>
+  <si>
+    <t>7a18ee2c-7db0-4cad-a4e7-97d23463472f</t>
+  </si>
+  <si>
+    <t>ef13d974-68a0-45d6-a001-53e2b9752dda</t>
+  </si>
+  <si>
+    <t>2e5afd8b-d6f3-42db-974a-67d889ac428c</t>
+  </si>
+  <si>
+    <t>756cb6a5-b58d-4797-965f-de8ec640e9a6</t>
+  </si>
+  <si>
+    <t>6a1cfb15-4951-4b91-a4dc-9afe2974e3d7</t>
+  </si>
+  <si>
+    <t>9264afd3-16ba-4c6f-ac40-43f144821706</t>
+  </si>
+  <si>
+    <t>8317c739-75e9-41f8-beb7-94ab77555ffa</t>
+  </si>
+  <si>
+    <t>1c69f9a1-2b9d-491f-bb2c-963e845f01e8</t>
+  </si>
+  <si>
+    <t>8f779902-8cf2-47e4-8e5d-ac322bddc554</t>
+  </si>
+  <si>
+    <t>af47e4fb-49a1-4fce-88bf-556024ab7915</t>
+  </si>
+  <si>
+    <t>d8ec9bee-999d-4b59-87a9-e668a1a72747</t>
+  </si>
+  <si>
+    <t>0a338b8e-91c5-4ec9-8649-00c0d9599871</t>
+  </si>
+  <si>
+    <t>9484096d-b403-4b26-afe9-cd8bbc546a68</t>
+  </si>
+  <si>
+    <t>a019b467-a40a-41c6-ae47-53a3cfac0d5e</t>
+  </si>
+  <si>
+    <t>cda5dbbb-753b-4f4c-bb2b-94bd6c67f094</t>
+  </si>
+  <si>
+    <t>320b6bc2-0199-4cca-9d9a-ef793623cd47</t>
+  </si>
+  <si>
+    <t>9320602f-e35a-4663-95cb-3c3e83287dd0</t>
+  </si>
+  <si>
+    <t>3c744f23-7b8a-44fe-9495-412d699d7e39</t>
+  </si>
+  <si>
+    <t>36dd69fd-b3ac-4178-928e-d518e7cf5d6a</t>
+  </si>
+  <si>
+    <t>b7b40197-a7c3-4cca-a55d-16f56c50f30c</t>
+  </si>
+  <si>
+    <t>248a35a6-3e05-43f4-984c-a9c538b7db77</t>
+  </si>
+  <si>
+    <t>1bcc266a-9ffb-4ada-9915-d837de8f6364</t>
+  </si>
+  <si>
+    <t>3a27d055-a857-4ebe-ad7a-9b84debb0401</t>
+  </si>
+  <si>
+    <t>79c4cdcb-3c2b-45f2-afb1-a1ca16767057</t>
+  </si>
+  <si>
+    <t>f2506bf2-85a8-458a-85ee-aba9e4e82644</t>
+  </si>
+  <si>
+    <t>d479667a-f018-481c-9272-84e79c780b73</t>
+  </si>
+  <si>
+    <t>9a3abfd2-ea4a-400f-8ec6-9501e336c3db</t>
+  </si>
+  <si>
+    <t>d98c9957-e7e2-462e-866d-f79ceb70a448</t>
+  </si>
+  <si>
+    <t>de6ffbf7-2664-4f44-b133-e524e336b74c</t>
+  </si>
+  <si>
+    <t>d00e65ba-e847-40ad-b808-133306dd0d84</t>
+  </si>
+  <si>
+    <t>0cb9fd86-c469-4e18-92d0-05e72166ed57</t>
+  </si>
+  <si>
+    <t>ff32d4b4-4c2b-451a-906c-6035781e5123</t>
+  </si>
+  <si>
+    <t>b32e1f31-edce-4d5d-9be7-c74e20cd3a9c</t>
+  </si>
+  <si>
+    <t>1c634c7d-5255-48c7-a510-3f1b112a76f6</t>
+  </si>
+  <si>
+    <t>7d337712-e728-4a11-9860-36c248ad876e</t>
+  </si>
+  <si>
+    <t>2bccab1e-2e33-4963-8324-ac828998fcd4</t>
+  </si>
+  <si>
+    <t>a5b0b050-247b-4649-a85c-9a67aae1adc5</t>
+  </si>
+  <si>
+    <t>e59cf7ef-6371-4224-9ce6-28dd64afa4fc</t>
+  </si>
+  <si>
+    <t>e6c4ad9b-fa93-4571-baa3-c38ca3a70bb8</t>
+  </si>
+  <si>
+    <t>60dbcb78-3fb9-46f5-b53b-166a3ffe3352</t>
+  </si>
+  <si>
+    <t>d74e3e83-5d0b-46b5-937e-e65434da9e76</t>
+  </si>
+  <si>
+    <t>d259bacd-0253-4d25-8236-74802aa21ccc</t>
+  </si>
+  <si>
+    <t>f1013f70-5761-481e-a8b0-0ac0e9e59089</t>
+  </si>
+  <si>
+    <t>64f26e98-3952-4839-9748-4d2018b34321</t>
+  </si>
+  <si>
+    <t>7271e002-489b-4027-8a2f-805d5df4c241</t>
+  </si>
+  <si>
+    <t>717b29b1-def7-4b8b-a9fe-a3cb011b588c</t>
+  </si>
+  <si>
+    <t>ba3d0874-a86f-480c-8eb5-f24afc7282c7</t>
+  </si>
+  <si>
+    <t>416450f4-332f-48fb-bba7-0611f718b192</t>
+  </si>
+  <si>
+    <t>a413e3f0-1bf0-4a6f-86ab-92e50f83ffc5</t>
+  </si>
+  <si>
+    <t>831425ee-2f13-4da3-a1c4-d8967476ce79</t>
+  </si>
+  <si>
+    <t>78407623-f804-4cac-b323-5691523463e7</t>
+  </si>
+  <si>
+    <t>cc4df32b-2d7b-43d3-b8f6-3c1c0f9ed387</t>
+  </si>
+  <si>
+    <t>8f747505-6475-4b07-875d-4230abf4b76c</t>
+  </si>
+  <si>
+    <t>8d03321e-a85d-4bd3-8cae-8ae5389578e1</t>
+  </si>
+  <si>
+    <t>b560ec37-d870-4075-a029-d5ba2f78d596</t>
+  </si>
+  <si>
+    <t>14ffb46b-1950-497d-9b03-ea0cd0a9b02a</t>
+  </si>
+  <si>
+    <t>eedf5e58-58af-43a2-b3fc-36c6a87b2a59</t>
+  </si>
+  <si>
+    <t>aaa6b9e8-3f3e-43e8-af6f-cff9f1929f7f</t>
+  </si>
+  <si>
+    <t>7854bbec-0249-4e1f-a640-db15be0f1444</t>
+  </si>
+  <si>
+    <t>ba2fa2d4-a00e-4f18-997c-5abe7e69168b</t>
+  </si>
+  <si>
+    <t>c939ee8b-499b-4803-9c3c-36c426dfa935</t>
+  </si>
+  <si>
+    <t>608562c4-a6a0-484e-b292-25aac9ca6804</t>
+  </si>
+  <si>
+    <t>a1dd78e1-6545-4a6c-836f-8472836b7cdc</t>
+  </si>
+  <si>
+    <t>0b5f99d1-0ad8-49fb-a121-1f835752b7c1</t>
+  </si>
+  <si>
+    <t>2beb81bc-27c0-44d7-b714-c40343c882e8</t>
+  </si>
+  <si>
+    <t>9ccd8abb-5af7-40ea-8a13-a413ebd4c0c7</t>
+  </si>
+  <si>
+    <t>5aa70516-8a9e-4ac8-a70c-a699bc56171e</t>
+  </si>
+  <si>
+    <t>8808708a-bdee-4add-b6ad-2bdc02321bdf</t>
+  </si>
+  <si>
+    <t>9d46f8b7-9380-45eb-8856-1c34f767723e</t>
+  </si>
+  <si>
+    <t>697f4caa-9dda-472b-9e8e-de9d398b7069</t>
+  </si>
+  <si>
+    <t>727a3156-9d3a-4403-b4e3-9cf543f2fdb4</t>
+  </si>
+  <si>
+    <t>2eab7747-ed6d-4596-8bb7-82e3482c7145</t>
+  </si>
+  <si>
+    <t>32341b96-5b80-4ff7-81bd-6dd9d976e036</t>
+  </si>
+  <si>
+    <t>f4507e5c-8826-4d85-90d6-2a0adb6083d4</t>
+  </si>
+  <si>
+    <t>6512a305-5184-4a32-8261-e6ca237c12d7</t>
+  </si>
+  <si>
+    <t>0fd14979-174d-4e64-a72c-a6b4d3174a47</t>
+  </si>
+  <si>
+    <t>48c4129c-f878-4f31-a1b9-f59598d952d8</t>
+  </si>
+  <si>
+    <t>760e6374-4cdb-47a4-9ead-e7a2d1b639f0</t>
+  </si>
+  <si>
+    <t>05a429dc-9bc4-4a35-91d3-f16c720ad1a5</t>
+  </si>
+  <si>
+    <t>0f4666b2-aca1-454a-b59e-fa094a5c43ed</t>
+  </si>
+  <si>
+    <t>711f8b5b-5325-44b8-bee9-92b3f82d6637</t>
+  </si>
+  <si>
+    <t>bdba2018-05b4-4981-9086-de391dc9e2d9</t>
+  </si>
+  <si>
+    <t>a294eebe-ccc8-4a03-8c41-9fd5a1eb49f7</t>
+  </si>
+  <si>
+    <t>589bb622-560a-4bc9-ad71-facb2a231a4b</t>
+  </si>
+  <si>
+    <t>0aaaa036-9e8f-4b94-8b07-d7766cfb8a5f</t>
+  </si>
+  <si>
+    <t>f4652665-3640-4362-be03-d55af4b79e78</t>
+  </si>
+  <si>
+    <t>744c3ed2-c791-45c6-8b82-7bf4e1d7e474</t>
+  </si>
+  <si>
+    <t>ab876c40-d682-4ce8-b509-c40803aa9e44</t>
+  </si>
+  <si>
+    <t>45db38f6-9f4e-4366-8b0b-86912c0b783c</t>
+  </si>
+  <si>
+    <t>a6d6a24e-611f-4b06-a12d-dca9a596277b</t>
+  </si>
+  <si>
+    <t>db88fa69-8c80-4058-a86f-23be15b14c2d</t>
+  </si>
+  <si>
+    <t>dd5ce5b0-83c0-4c0e-8e4e-9da8003bfca7</t>
+  </si>
+  <si>
+    <t>d3ecad12-9af8-4de6-b85b-690b09fbce0d</t>
+  </si>
+  <si>
+    <t>83977b4d-0409-437a-ac30-9c88ecc575ec</t>
+  </si>
+  <si>
+    <t>8f143e1f-1a86-4e70-bbf4-2fc7f46d626a</t>
+  </si>
+  <si>
+    <t>9034fa78-8054-4739-a0f6-c815cb6770ec</t>
+  </si>
+  <si>
+    <t>168ed8bb-027f-47f4-9eb7-9a26e485cdb2</t>
+  </si>
+  <si>
+    <t>d818e8db-b12a-47f2-ab2c-ea65281d1e6d</t>
+  </si>
+  <si>
+    <t>cc97d6cd-01f8-46fc-a96d-8d58b9e5454c</t>
+  </si>
+  <si>
+    <t>dbf5f7d5-604f-44e1-8f04-89cf7101eb96</t>
+  </si>
+  <si>
+    <t>0738c51c-08cd-492b-80dd-187626884ef5</t>
+  </si>
+  <si>
+    <t>c14e09c9-e1b1-46a3-81f1-f7ce094f6b9f</t>
+  </si>
+  <si>
+    <t>41335309-def7-4ec5-9529-57c646face3d</t>
+  </si>
+  <si>
+    <t>4191e27d-8f96-4432-9150-284d87d27e6b</t>
+  </si>
+  <si>
+    <t>9d384621-398e-4f06-8b2f-e65d55f84dd5</t>
+  </si>
+  <si>
+    <t>10791dbd-9ed2-4ec1-a080-7a89ad9e72d2</t>
+  </si>
+  <si>
+    <t>897f3be8-40d7-4f80-84f8-1b69c47534de</t>
+  </si>
+  <si>
+    <t>4fb06bcb-e81a-4dc8-8a2c-c182ce01e624</t>
+  </si>
+  <si>
+    <t>aab83604-bda9-45f9-b12e-82988eb09e41</t>
+  </si>
+  <si>
+    <t>0eff7aed-56f6-481f-8f4e-06ba1062fbe8</t>
+  </si>
+  <si>
+    <t>e9b1a159-01fd-4756-9c06-79c5f33cc995</t>
+  </si>
+  <si>
+    <t>d5fa776a-3163-42a6-a472-72505013e91f</t>
+  </si>
+  <si>
+    <t>36ce9e54-4a49-479f-a68e-fd87b5f80187</t>
+  </si>
+  <si>
+    <t>eeb72db0-3c4f-4920-ac1f-b31137f5aa72</t>
+  </si>
+  <si>
+    <t>8983fecd-8d09-464e-bcf6-1f26ef35be0a</t>
+  </si>
+  <si>
+    <t>b9089257-5059-48d2-aa66-407087a649de</t>
+  </si>
+  <si>
+    <t>b906e071-8a36-43eb-b234-bdcbff74a5fe</t>
+  </si>
+  <si>
+    <t>3778ee8e-7bb1-4ca3-9bda-2debecf25a93</t>
+  </si>
+  <si>
+    <t>f1aa61f9-ee0c-4aa2-8d8b-b18644853f1d</t>
+  </si>
+  <si>
+    <t>4ad35142-182d-4b29-9151-3e05afbda408</t>
+  </si>
+  <si>
+    <t>aa96d963-5bc7-46ed-b4bd-94f5c6de60fe</t>
+  </si>
+  <si>
+    <t>cf9feeb6-90bd-42ef-9f4a-8a45d20b1ec2</t>
+  </si>
+  <si>
+    <t>da81f74b-bb70-472f-8993-7c1f0d2b7475</t>
+  </si>
+  <si>
+    <t>31cec95c-1603-4d0d-92e9-6c5bba9d5d97</t>
+  </si>
+  <si>
+    <t>c1847cc4-d223-49fa-b49b-fa0ec9b16d7b</t>
+  </si>
+  <si>
+    <t>c69c225f-9e46-478a-9e7a-1907a0b0cb91</t>
+  </si>
+  <si>
+    <t>3da5b8a7-6163-4bf6-aaf6-9d3e0c9a26d7</t>
+  </si>
+  <si>
+    <t>04965435-bd30-4840-ad61-1e942041491f</t>
+  </si>
+  <si>
+    <t>8bdd62b2-5d8e-443f-8779-2acd9a19c4b0</t>
+  </si>
+  <si>
+    <t>40525e80-7a2a-48d0-9f51-e813ce2c881b</t>
+  </si>
+  <si>
+    <t>1b8457af-bc4d-4768-bb74-ba5b0d7fb271</t>
+  </si>
+  <si>
+    <t>a0ac4507-c347-4d9f-beb5-6dd617a95c0a</t>
+  </si>
+  <si>
+    <t>564a6245-00ce-4fee-96c9-c8b426b97085</t>
+  </si>
+  <si>
+    <t>3ced6aa2-e53c-41c6-89a3-e0aff3c78f99</t>
+  </si>
+  <si>
+    <t>c2758041-5945-41a4-83d9-aaaa8fef6eba</t>
+  </si>
+  <si>
+    <t>8cf09482-509d-46b2-91f1-462f818210dc</t>
+  </si>
+  <si>
+    <t>9ecd54cf-3fec-436c-936f-a2af28efa1a1</t>
+  </si>
+  <si>
+    <t>8ef0ad21-b9cf-41e5-926b-d86d5ccc06c8</t>
+  </si>
+  <si>
+    <t>2fa8a1c9-aadc-47f0-8f6d-9ff10ebb5134</t>
+  </si>
+  <si>
+    <t>91adf37d-e735-43c2-98d3-4eabd3d14de6</t>
+  </si>
+  <si>
+    <t>e8b97e14-b9ca-4166-9b74-13fc26adc96e</t>
+  </si>
+  <si>
+    <t>08be4509-a399-4717-9053-978b810e9b55</t>
+  </si>
+  <si>
+    <t>baeb7cda-f8cb-41db-b242-a9dbe1c83952</t>
+  </si>
+  <si>
+    <t>b8f87ebd-c29b-4004-b862-ddb946dc6666</t>
+  </si>
+  <si>
+    <t>a8f41780-12b0-457a-934c-71ad0c631f01</t>
+  </si>
+  <si>
+    <t>bc96238a-d42c-4dad-abc6-eb7eed6bbd36</t>
+  </si>
+  <si>
+    <t>7eb48c09-eae5-4ab2-9609-abd62cd7b4cc</t>
+  </si>
+  <si>
+    <t>2d87d974-0ad8-4ffb-abfc-fb1c39e26cea</t>
+  </si>
+  <si>
+    <t>efd51cf4-e31a-471d-96c5-c07b53e04237</t>
+  </si>
+  <si>
+    <t>31ee7585-5b2e-42ff-bb79-a9de13196c7f</t>
+  </si>
+  <si>
+    <t>2199558e-434a-4ac3-8ef6-a11ce52a9b13</t>
+  </si>
+  <si>
+    <t>4cfc6b0b-3436-4902-b636-b139a8ca9842</t>
+  </si>
+  <si>
+    <t>1e8f5b24-455e-43dc-bab8-10164e26dd75</t>
+  </si>
+  <si>
+    <t>b56e1cf5-1c7f-40b4-9d39-3f27a4f092e2</t>
+  </si>
+  <si>
+    <t>1ef22346-d616-41d2-b3d5-dee4dfde828b</t>
+  </si>
+  <si>
+    <t>c4bba755-80a3-44be-9a07-8bd60986084f</t>
+  </si>
+  <si>
+    <t>d6b7c0d2-fd62-4227-8353-d1e43795feef</t>
+  </si>
+  <si>
+    <t>5eb3af76-4160-4c52-944e-651f530db326</t>
+  </si>
+  <si>
+    <t>41d5762d-179c-4307-b479-7f74dfe29ffb</t>
+  </si>
+  <si>
+    <t>18b0053a-e0cb-4074-97d5-d594c71ed267</t>
+  </si>
+  <si>
+    <t>aea53aae-951b-4b0c-bb5b-0bfa6f005e61</t>
+  </si>
+  <si>
+    <t>18aaf8a3-99ca-41c8-a9f1-bbf865fbdfd3</t>
+  </si>
+  <si>
+    <t>53062163-ff92-42ab-9978-281fead09456</t>
+  </si>
+  <si>
+    <t>375176e5-fcb1-499e-8021-216422b101df</t>
+  </si>
+  <si>
+    <t>7e617a58-2eb2-4433-a474-f9bf408a14c1</t>
+  </si>
+  <si>
+    <t>a783f8b3-8adb-485a-adbd-8743edd6f912</t>
+  </si>
+  <si>
+    <t>d88eb26c-5af6-475a-a642-be86eb76a88d</t>
+  </si>
+  <si>
+    <t>c7cea646-caba-4700-bb3b-a1da85d7bed9</t>
+  </si>
+  <si>
+    <t>c58680aa-2a93-420c-a0db-f088010db711</t>
+  </si>
+  <si>
+    <t>a2c0017d-1078-4df4-ba78-59e920a14124</t>
+  </si>
+  <si>
+    <t>ae37a22b-96ba-49ef-946a-aea1ac13c631</t>
+  </si>
+  <si>
+    <t>e61ca32a-0e75-4c91-9938-c2fc1eed3788</t>
+  </si>
+  <si>
+    <t>f92ee1c2-6897-4c9d-b401-722edde0b0f1</t>
+  </si>
+  <si>
+    <t>31d546bd-eab8-4db6-a834-96556846296c</t>
+  </si>
+  <si>
+    <t>a72c1882-473f-4c92-b7bb-4ea66f46ad08</t>
+  </si>
+  <si>
+    <t>c3749c6a-e8d9-42ef-bfeb-ab01a55fb01c</t>
+  </si>
+  <si>
+    <t>c00b6976-a555-411e-b1e7-dbeebf976993</t>
+  </si>
+  <si>
+    <t>c69c7098-fa37-46a8-9dee-ac83e050a77b</t>
+  </si>
+  <si>
+    <t>2a6c281f-9799-45f6-900c-fbc5c97df7fa</t>
+  </si>
+  <si>
+    <t>23525cca-f442-4a1e-9726-6ffffd046e8b</t>
+  </si>
+  <si>
+    <t>19a73914-27e7-4ff1-9c90-aa02ae4e2201</t>
+  </si>
+  <si>
+    <t>0e74afe1-77e5-4bc6-a297-bee8d0a5ec89</t>
+  </si>
+  <si>
+    <t>894ce6e3-537d-4f39-8bcf-e4c303d50c71</t>
+  </si>
+  <si>
+    <t>59e8151e-fe76-44fe-bea7-3a5ddc8dcf46</t>
+  </si>
+  <si>
+    <t>12a89f4d-4024-4a3c-978b-947f953c3910</t>
+  </si>
+  <si>
+    <t>692b6761-e7fa-41e5-aad7-b1c927c15167</t>
+  </si>
+  <si>
+    <t>a3c818bc-fadb-498a-9e93-44ddccd8a6b1</t>
+  </si>
+  <si>
+    <t>4440489b-a667-40e8-9e26-87ceb61103e6</t>
+  </si>
+  <si>
+    <t>bb5357c1-c7ce-4ba8-b9bc-fb48bcb381ac</t>
+  </si>
+  <si>
+    <t>d999dd13-6959-4e4e-8ca2-6b05a60398ce</t>
+  </si>
+  <si>
+    <t>fcdeeeeb-c799-4c9d-8828-f5bcd9701031</t>
+  </si>
+  <si>
+    <t>cf3ddaa0-94c8-4246-a1ef-bccf7a3fcc66</t>
+  </si>
+  <si>
+    <t>a3b105aa-f479-4f87-b444-fed0be433b87</t>
+  </si>
+  <si>
+    <t>cc878e75-a98c-47b3-ab08-221a555c9f47</t>
+  </si>
+  <si>
+    <t>73a412ea-657a-4e79-bc15-e1fcb7e9c324</t>
+  </si>
+  <si>
+    <t>1ba81af1-16e8-42d9-ad17-603b8f990fae</t>
+  </si>
+  <si>
+    <t>400ef257-a63b-4090-908b-f65494920f05</t>
+  </si>
+  <si>
+    <t>dfdfb582-5c7f-4c24-bddc-4dba1d16c8b6</t>
+  </si>
+  <si>
+    <t>191047b9-b83f-4cf8-a78a-54e57b78895e</t>
+  </si>
+  <si>
+    <t>3178df8a-4017-4e3e-9829-c9f949e43828</t>
+  </si>
+  <si>
+    <t>b178ff95-ee03-4b30-84c6-ed0f9f50c1a5</t>
+  </si>
+  <si>
+    <t>cafea214-0d8f-4a8a-96cb-7ec6a9f3a6f5</t>
+  </si>
+  <si>
+    <t>572d6368-6eff-4fc5-ba87-835194502162</t>
+  </si>
+  <si>
+    <t>2de980dd-ce8e-426e-ab84-5dd3243183f5</t>
+  </si>
+  <si>
+    <t>c851a0e3-1321-40d6-8c35-7e344be6edb4</t>
+  </si>
+  <si>
+    <t>9241b5b8-2787-4b96-b448-bf018c1989d8</t>
+  </si>
+  <si>
+    <t>540e4a75-d192-434f-8c55-929c8eb3a3cb</t>
+  </si>
+  <si>
+    <t>e5f32ad9-e698-4562-8c56-a745bbd528e3</t>
+  </si>
+  <si>
+    <t>b0ffb1ca-a822-4da9-8401-e6a82b05e3d4</t>
+  </si>
+  <si>
+    <t>6e5e0095-8b6f-44ac-95e2-257ed4b5e865</t>
+  </si>
+  <si>
+    <t>e833dbeb-5c11-4cc1-b159-f922a10191c5</t>
+  </si>
+  <si>
+    <t>b6c7b57a-33ea-4665-bd8e-184ae4a830b2</t>
+  </si>
+  <si>
+    <t>adad97dc-df45-4ff5-bcf8-ce602cd3b2c6</t>
+  </si>
+  <si>
+    <t>20c69219-abeb-4df5-bfe6-f54532af12c2</t>
+  </si>
+  <si>
+    <t>b6ea543e-59d7-4bed-a97d-76de5cc6fdf6</t>
+  </si>
+  <si>
+    <t>ab5c840e-7270-49ac-9ca5-78a4c76adc4f</t>
+  </si>
+  <si>
+    <t>45da9eea-6ca4-48e7-b952-39f33b388a34</t>
+  </si>
+  <si>
+    <t>a32c56a6-d75e-405c-bd46-8f8434ead210</t>
+  </si>
+  <si>
+    <t>3d60fe8f-9b39-4e8e-8d35-ec026ea1f0d1</t>
+  </si>
+  <si>
+    <t>1d6fa4a6-7ea5-493e-8660-01e4809be928</t>
+  </si>
+  <si>
+    <t>23211e24-ff88-44d9-8290-e428c43f2ef6</t>
+  </si>
+  <si>
+    <t>214ee426-e57c-453c-ad5e-7077e7882b35</t>
+  </si>
+  <si>
+    <t>72b1d014-5173-4398-8978-1e8937b57f74</t>
+  </si>
+  <si>
+    <t>11bc931e-522d-4ff0-b673-b53c24ed3d38</t>
+  </si>
+  <si>
+    <t>b115af5b-0639-40c3-a590-99795651b610</t>
+  </si>
+  <si>
+    <t>be41bc66-3361-4ea9-963d-50395b55b2d1</t>
+  </si>
+  <si>
+    <t>396bf3ab-9b0c-4b0e-8621-e6ab7b6611dd</t>
+  </si>
+  <si>
+    <t>c57354dd-1c6d-4268-ac50-210e73a2ca44</t>
+  </si>
+  <si>
+    <t>e820ce8a-44f2-4646-bf77-60ee1de5d66a</t>
+  </si>
+  <si>
+    <t>1b7ecec4-e3ae-4626-9de9-f652b5d2c279</t>
+  </si>
+  <si>
+    <t>622478f1-6d05-4e9d-9283-35d0e72940b9</t>
+  </si>
+  <si>
+    <t>6b5e3c1a-6155-41b5-8c3f-8d75985f003f</t>
+  </si>
+  <si>
+    <t>3a6f3c1a-913b-4ea4-8afb-d21338b1e065</t>
+  </si>
+  <si>
+    <t>c989347c-b960-4aa0-b893-e0f71972c978</t>
+  </si>
+  <si>
+    <t>76ca9576-46cc-4984-9ef6-b15347996581</t>
+  </si>
+  <si>
+    <t>63290d13-f918-44d7-8e0d-a099b53b9fe6</t>
+  </si>
+  <si>
+    <t>3d774781-5e59-4269-9911-7f7eb52bd5bc</t>
+  </si>
+  <si>
+    <t>97ef8ee9-7e05-4095-b56b-716f672a1a99</t>
+  </si>
+  <si>
+    <t>5b4e1b4a-98fa-4aa1-8d72-c52c3e3a0e1f</t>
+  </si>
+  <si>
+    <t>1258670c-c475-4c39-a3ed-9247014aac51</t>
+  </si>
+  <si>
+    <t>1cb4edbd-7f83-412b-80f6-ab3e42572cb2</t>
+  </si>
+  <si>
+    <t>55f411ed-559f-418b-a78c-e01f9d351647</t>
+  </si>
+  <si>
+    <t>c69d4d74-3e47-4786-bcbc-8d3f53db259b</t>
+  </si>
+  <si>
+    <t>a7e569ee-9c3a-4da3-8812-8331d73c4431</t>
+  </si>
+  <si>
+    <t>6a0f37ac-752e-401a-ac8f-c6299cd280bf</t>
+  </si>
+  <si>
+    <t>991caa2c-0457-4efc-a16e-fe29446906cf</t>
+  </si>
+  <si>
+    <t>1616274b-8cd5-44d7-bb63-7ba35dcf2098</t>
+  </si>
+  <si>
+    <t>e45e55ca-1a78-4b90-903c-6a1f0bc73b7e</t>
+  </si>
+  <si>
+    <t>c76f18a6-b2f2-4412-82b3-cd3b21875bda</t>
+  </si>
+  <si>
+    <t>caa858ae-34ca-4d15-a0d7-463d07902092</t>
+  </si>
+  <si>
+    <t>cf2af40d-2fa9-45a6-b8b5-05ab5947b94a</t>
+  </si>
+  <si>
+    <t>727056b0-be07-432a-86e9-29c106ec7207</t>
+  </si>
+  <si>
+    <t>d9ab0182-8446-486a-a1ad-9db15b18e47d</t>
+  </si>
+  <si>
+    <t>964efbbb-bbb3-485c-869d-72896d61e366</t>
+  </si>
+  <si>
+    <t>f6c60bc8-668e-450d-9d89-4f172b4003ed</t>
+  </si>
+  <si>
+    <t>f5da8fe4-a65e-4157-9163-bd1908761d1d</t>
+  </si>
+  <si>
+    <t>fbf47c76-2de5-441c-8518-ce39037b9549</t>
+  </si>
+  <si>
+    <t>4c203aeb-812e-446d-b474-bbb2c4f0b262</t>
+  </si>
+  <si>
+    <t>0e47bcf7-f857-4b62-b364-28e9cbc053ad</t>
+  </si>
+  <si>
+    <t>aa900593-895f-49b5-b33f-55f794d1561f</t>
+  </si>
+  <si>
+    <t>0080890b-7c90-4eac-8ab5-8ec5c01e189d</t>
+  </si>
+  <si>
+    <t>8ad31b4d-c141-42e4-ad9a-f28f072b6efa</t>
+  </si>
+  <si>
+    <t>a5fa63a7-f505-4eb1-b925-16e02c50cea3</t>
+  </si>
+  <si>
+    <t>ea798187-3da9-467f-ac7c-924c4d0afa84</t>
+  </si>
+  <si>
+    <t>89c5932a-22df-40c8-8e2d-adb5c26389fc</t>
+  </si>
+  <si>
+    <t>3f3439b0-b5e9-4005-815f-2fd0daeacd19</t>
+  </si>
+  <si>
+    <t>8b7cfc71-dcda-4c6f-b9b1-f76fea627b99</t>
+  </si>
+  <si>
+    <t>00635f1f-4509-4c1f-b832-9c4f087c954b</t>
+  </si>
+  <si>
+    <t>910b7606-8c11-4208-8dd7-ff5584098d8c</t>
+  </si>
+  <si>
+    <t>e6f26d0d-96ea-475d-955d-6dccd513df02</t>
+  </si>
+  <si>
+    <t>5c6a6e3f-ef39-40b1-ba9b-439e5c5a34ee</t>
+  </si>
+  <si>
+    <t>2fba843b-8fd9-4d3a-a98c-b3bea925dcc7</t>
+  </si>
+  <si>
+    <t>44c5f5cb-5954-4c96-b487-b4cb691fdbe9</t>
+  </si>
+  <si>
+    <t>35706c20-1c95-4cca-8f7f-8109e5519ca7</t>
+  </si>
+  <si>
+    <t>d3881337-3ff0-43e4-87bc-afadd55a45eb</t>
+  </si>
+  <si>
+    <t>43ae454a-254f-4823-b184-dd8d3621fc9f</t>
+  </si>
+  <si>
+    <t>cf8d0b99-ce86-44d6-af64-5428b1045fb9</t>
+  </si>
+  <si>
+    <t>02e24cba-a680-4f1d-8cc2-f71deea1a0d0</t>
+  </si>
+  <si>
+    <t>9be83967-bf20-4e8a-ac57-139a031376a4</t>
+  </si>
+  <si>
+    <t>c1ffe203-0f1b-4ccd-af10-2ad17433617e</t>
+  </si>
+  <si>
+    <t>5776cc83-60af-4337-b102-a179698e0a31</t>
+  </si>
+  <si>
+    <t>3df0d4b9-cc0b-489c-b427-5a14ecd0e16a</t>
+  </si>
+  <si>
+    <t>429e63fc-5b19-4057-b2ee-0712389aa3be</t>
+  </si>
+  <si>
+    <t>7ee3f12b-be9e-4002-b368-8bfba12ea9c6</t>
+  </si>
+  <si>
+    <t>dbd96641-daf1-49bb-a3b2-99ebefe5fda3</t>
+  </si>
+  <si>
+    <t>950c1b0c-7031-4893-9f31-17884ff6b445</t>
+  </si>
+  <si>
+    <t>008ad30d-8f67-49b3-ab75-6ed8a0b31ec7</t>
+  </si>
+  <si>
+    <t>f3b965ce-c96a-4835-825b-1d8b282b3767</t>
+  </si>
+  <si>
+    <t>640c4780-69bd-43b6-a202-f81970a3e7a2</t>
+  </si>
+  <si>
+    <t>aebf4f50-7130-47f7-90ea-54125f126847</t>
+  </si>
+  <si>
+    <t>26a47c03-61c3-407c-8f01-6f1b2a68e4b3</t>
+  </si>
+  <si>
+    <t>af1562ca-50d5-4680-ac3a-237f19f5e71c</t>
+  </si>
+  <si>
+    <t>dc7a9d71-8960-4f72-9067-41b77b3664b9</t>
+  </si>
+  <si>
+    <t>41b37ec9-c9ce-476d-8abd-24db7caec31a</t>
+  </si>
+  <si>
+    <t>8f6dd7c3-c505-42e2-8abb-6f846ed61c9f</t>
+  </si>
+  <si>
+    <t>558446c6-3cd2-4511-8239-a57fc1ac5849</t>
+  </si>
+  <si>
+    <t>30d311a6-641a-4955-a6fb-c429b07537f2</t>
+  </si>
+  <si>
+    <t>c3f093cc-981d-4d8d-8178-6a44bbce725d</t>
+  </si>
+  <si>
+    <t>c7302d26-36d9-46bf-9e93-134791196b88</t>
+  </si>
+  <si>
+    <t>3671b8a9-8f33-46d1-88e5-f3f6d102c106</t>
+  </si>
+  <si>
+    <t>5c06270d-593e-4211-9e3a-1a52ffda38c3</t>
+  </si>
+  <si>
+    <t>12a174cb-92a6-43a4-b2b8-79b3a867ccdd</t>
+  </si>
+  <si>
+    <t>08b86e10-dcde-45fa-a756-6b30e896407e</t>
+  </si>
+  <si>
+    <t>474db25e-8f30-4ee2-a436-6646ca8144d8</t>
+  </si>
+  <si>
+    <t>1105b64d-3309-4789-b25b-9060b65c6bde</t>
+  </si>
+  <si>
+    <t>d3d6c327-7bcf-47a3-a501-09fc04adc876</t>
+  </si>
+  <si>
+    <t>b4d5136b-8bb1-41ef-aeb6-a8bea0dbab0d</t>
+  </si>
+  <si>
+    <t>6903140f-e7ce-4fdf-822f-8d3948e6b11e</t>
+  </si>
+  <si>
+    <t>9536afaa-7c8f-4e2a-ac8c-8a8a8ac29348</t>
+  </si>
+  <si>
+    <t>07cb8d7f-1784-47fb-8ebf-d133509bdbb2</t>
+  </si>
+  <si>
+    <t>bf7abfbb-4478-4f4a-9c0b-517f549365f9</t>
+  </si>
+  <si>
+    <t>d1f76bf2-eb9e-4522-a747-54899e77d0d1</t>
+  </si>
+  <si>
+    <t>2b9ded71-d259-4cc3-98c6-c0f7971e86c1</t>
+  </si>
+  <si>
+    <t>c33be149-6c71-40bb-a463-c7ffccfee5a4</t>
+  </si>
+  <si>
+    <t>69491162-3957-4e09-8022-3cecb1d0e814</t>
+  </si>
+  <si>
+    <t>774fd644-7442-4941-bd3d-884b14b866df</t>
+  </si>
+  <si>
+    <t>07c747f3-1069-4080-8f5f-cd59924bf90c</t>
+  </si>
+  <si>
+    <t>ebd4a8d6-2e88-4b3f-87a3-d78764a7e955</t>
+  </si>
+  <si>
+    <t>3a67d2ed-8552-4397-85ae-4d03b1b3b6b3</t>
+  </si>
+  <si>
+    <t>dda08d73-a764-4634-9fd7-529deaa8a6d0</t>
+  </si>
+  <si>
+    <t>180f9e85-60af-46d4-b9a3-f7c0637387cc</t>
+  </si>
+  <si>
+    <t>7b98377e-f3b2-48f5-ac24-6d1cc9754a3f</t>
+  </si>
+  <si>
+    <t>d84c055c-6cf0-4da9-9dce-5d1c07b828e4</t>
+  </si>
+  <si>
+    <t>ce04a1fd-84c7-41f9-a127-fefbacb6e3e2</t>
+  </si>
+  <si>
+    <t>2cb5fd76-c926-4220-805b-7969f21dcb49</t>
+  </si>
+  <si>
+    <t>ff0daff0-8478-4d26-b0e1-8eaa243c080e</t>
+  </si>
+  <si>
+    <t>1ff4ad55-f304-4a52-9b49-683e820b37c0</t>
+  </si>
+  <si>
+    <t>bfea70c2-e79d-4585-8c35-a026dab23cbb</t>
+  </si>
+  <si>
+    <t>a99237a3-07d8-468b-9325-3e9e5f62c0e9</t>
+  </si>
+  <si>
+    <t>d5ffdbcd-f2fa-4552-8312-47489c92ef58</t>
+  </si>
+  <si>
+    <t>998b0b8d-8406-4cc7-9281-6d62978033a1</t>
+  </si>
+  <si>
+    <t>cb31bb34-0de0-4658-84e1-42cb2b01d1ac</t>
+  </si>
+  <si>
+    <t>6cd3109e-6b10-4b07-8e97-a4d6b6ede015</t>
+  </si>
+  <si>
+    <t>ecf87d18-3698-424c-890b-e6780a8dbec9</t>
+  </si>
+  <si>
+    <t>7af012b5-803a-456e-bffa-2bc3d666df77</t>
+  </si>
+  <si>
+    <t>781c4281-65e6-4fa3-830d-12f4062967de</t>
+  </si>
+  <si>
+    <t>43049f01-7ae5-4d7a-a011-913d5a8016df</t>
+  </si>
+  <si>
+    <t>d607f49f-c813-4d36-b0ee-b8e4911042ef</t>
+  </si>
+  <si>
+    <t>5acdfa5e-dbe4-4154-a2de-583baa4f8510</t>
+  </si>
+  <si>
+    <t>d3f49b10-25f9-4bae-8bc3-7541c882d440</t>
+  </si>
+  <si>
+    <t>b1bf20f2-82eb-4ba7-81d1-288bb60e9084</t>
+  </si>
+  <si>
+    <t>ec4bd7b0-5657-408c-8be9-54bddfecdb42</t>
+  </si>
+  <si>
+    <t>94ed638c-79ca-4dac-9fc2-19827312441c</t>
+  </si>
+  <si>
+    <t>5a5911a3-4572-493f-afc2-a30c7318bc5e</t>
+  </si>
+  <si>
+    <t>d4e6ad98-771f-4ff9-b623-f06de7efb6e5</t>
+  </si>
+  <si>
+    <t>8be1f007-8396-4386-becb-f10ce8afe631</t>
+  </si>
+  <si>
+    <t>b4b7afa9-a9d5-4769-bb82-0c0ae5a03bfd</t>
+  </si>
+  <si>
+    <t>a319bf85-b945-49a1-bc21-b2277ed387b3</t>
+  </si>
+  <si>
+    <t>923c65c8-c147-44ed-9548-afd596d788a5</t>
+  </si>
+  <si>
+    <t>68ed3c1a-6cca-4e99-81c4-584252e429b9</t>
+  </si>
+  <si>
+    <t>3a015219-6918-42cd-ae71-419ec8dc0498</t>
+  </si>
+  <si>
+    <t>1112bedd-a0f3-430f-8e49-cc5fe53f3765</t>
+  </si>
+  <si>
+    <t>13be6bfb-6e4c-4f29-9f4f-272e3d462bd1</t>
+  </si>
+  <si>
+    <t>f3462e49-e0d6-4aa2-96d4-97f2ac38b05b</t>
+  </si>
+  <si>
+    <t>fe27aaa7-018f-421e-8ab4-91c105773944</t>
+  </si>
+  <si>
+    <t>b93d9cf9-2076-401c-8a64-a49c3f629fca</t>
+  </si>
+  <si>
+    <t>6f92b393-da7e-4ce2-8160-d481f617e81d</t>
+  </si>
+  <si>
+    <t>9b25b8fc-cd37-4c76-8a54-637e348a993a</t>
+  </si>
+  <si>
+    <t>faea4d3b-ea84-4b89-8b21-350c88c0c117</t>
+  </si>
+  <si>
+    <t>c1de3fa3-3870-490e-8e92-b6d387a16191</t>
+  </si>
+  <si>
+    <t>22fb881b-32c7-4630-b1b9-cb45eb90a7ac</t>
+  </si>
+  <si>
+    <t>c876c55d-de5e-4787-872b-843255cc5cc5</t>
+  </si>
+  <si>
+    <t>59b38cde-6f6c-41ca-b2da-d50d1d4e0cea</t>
+  </si>
+  <si>
+    <t>20c432fc-8326-464e-87e2-8a52333dec87</t>
+  </si>
+  <si>
+    <t>d6857218-24aa-4f2c-b6e0-3f2f29cd0f4d</t>
+  </si>
+  <si>
+    <t>5cc21ce0-b3f4-4816-8dca-69fbe7e47b1d</t>
+  </si>
+  <si>
+    <t>6f548af2-485f-41b2-a5d5-dce97ef8028a</t>
+  </si>
+  <si>
+    <t>6924a095-887b-4957-b0a8-de9da2d433bd</t>
+  </si>
+  <si>
+    <t>2761a160-b5d3-47eb-aa18-45e09c163aa8</t>
+  </si>
+  <si>
+    <t>f4be77d7-ac31-4cb2-adf8-a3d85d477540</t>
+  </si>
+  <si>
+    <t>9869fee7-74be-48e0-8762-26b5af5626ca</t>
+  </si>
+  <si>
+    <t>c6417e42-13f8-4dd9-8155-fc6c609b99b8</t>
+  </si>
+  <si>
+    <t>04f24a27-5fdb-4278-bdab-2ddf0b8cba2e</t>
+  </si>
+  <si>
+    <t>7ed12636-141c-40e5-92fd-ec61eb16ee71</t>
+  </si>
+  <si>
+    <t>49a275a2-9128-437d-b9d1-506dd2e34dca</t>
+  </si>
+  <si>
+    <t>29d5ae1f-03f8-4a2e-a784-9faaf16f404d</t>
+  </si>
+  <si>
+    <t>046d4277-3aa7-4993-9120-5e8ebc33cc6b</t>
+  </si>
+  <si>
+    <t>f2d13604-eecf-42a9-984b-d9913736134b</t>
+  </si>
+  <si>
+    <t>7b29fffa-135e-4ed0-8faf-fbd159b2fb1c</t>
+  </si>
+  <si>
+    <t>a5823624-bb06-428d-83f3-d0ea8e65588c</t>
   </si>
   <si>
     <t>Key</t>

--- a/MIR/bin/Debug/net8.0-windows/data.xlsx
+++ b/MIR/bin/Debug/net8.0-windows/data.xlsx
@@ -1,16 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pehya\Downloads\Materials-and-inventory-resource\MIR\bin\Debug\net8.0-windows\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74D900A-06AE-42BA-A2C7-8379DB619DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -20,7 +12,7 @@
     <sheet name="Settings" sheetId="5" r:id="rId5"/>
     <sheet name="StockTransactions" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -48,13 +40,13 @@
     <t>CreatedAt</t>
   </si>
   <si>
-    <t>75f56071-12f1-4dbc-a082-932a2eceda96</t>
+    <t>1c064a95-1820-40ec-ba06-e396ba6f2ecb</t>
   </si>
   <si>
     <t>admin</t>
   </si>
   <si>
-    <t>$2a$11$O3aMcFJJCTCYOZGRibMjaeJTkXbx5PNeX3I.4mVRC5XglmO3LXYVG</t>
+    <t>$2a$11$i/FXBlP6bmIDY9KPIl6lqOWiMJ.I8fHhPZHR58OZIGahmwKypT0UC</t>
   </si>
   <si>
     <t>Administrator</t>
@@ -63,7 +55,7 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>2026-02-24T03:05:34.5873258+08:00</t>
+    <t>2026-02-24T03:10:38.9696061+08:00</t>
   </si>
   <si>
     <t>Code</t>
@@ -93,7 +85,7 @@
     <t>LastUpdated</t>
   </si>
   <si>
-    <t>fe309e97-b424-44be-8dfb-52a9a93c18c5</t>
+    <t>1d326abf-3f4e-4bda-98c5-29d5c7a065f3</t>
   </si>
   <si>
     <t>CIF-MM705P1.20-0131</t>
@@ -108,1099 +100,1099 @@
     <t>Raw Materials</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468505+08:00</t>
-  </si>
-  <si>
-    <t>73f87d18-439e-476c-8132-f908ca2d4dc3</t>
+    <t>2026-02-24T03:10:43.2973163+08:00</t>
+  </si>
+  <si>
+    <t>c6a1056d-9f83-4289-8aae-2d1e154164e4</t>
   </si>
   <si>
     <t>CHE-UV-GLUE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468557+08:00</t>
-  </si>
-  <si>
-    <t>82ee61ba-01d2-4d9a-93d4-bb331006b2da</t>
+    <t>2026-02-24T03:10:43.2973250+08:00</t>
+  </si>
+  <si>
+    <t>dfee731f-2b60-4554-babd-fc1c2db3e5f6</t>
   </si>
   <si>
     <t>CHE-UV-GLUE-FL</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468603+08:00</t>
-  </si>
-  <si>
-    <t>1c5954d3-53ab-414c-85eb-b64cd6f4eb66</t>
+    <t>2026-02-24T03:10:43.2973320+08:00</t>
+  </si>
+  <si>
+    <t>6954d4fd-f02b-42e1-927c-5e7e1ffe5539</t>
   </si>
   <si>
     <t>PVC 68A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468643+08:00</t>
-  </si>
-  <si>
-    <t>c9d68ed2-8e2b-4a96-b327-b79b173c4630</t>
+    <t>2026-02-24T03:10:43.2973388+08:00</t>
+  </si>
+  <si>
+    <t>3d6abbdb-798a-4f74-8da8-80a104585186</t>
   </si>
   <si>
     <t>CIF-LLC-0313</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468685+08:00</t>
-  </si>
-  <si>
-    <t>49e90dd0-aab0-486f-8ed4-2743d2ece73b</t>
+    <t>2026-02-24T03:10:43.2973463+08:00</t>
+  </si>
+  <si>
+    <t>924a4868-eab8-42d9-a62b-8062a5d9ee1e</t>
   </si>
   <si>
     <t>CIF-LL-0213</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468729+08:00</t>
-  </si>
-  <si>
-    <t>e9cea2ad-aae8-4a1d-9126-7812ac4b9ff5</t>
+    <t>2026-02-24T03:10:43.2973528+08:00</t>
+  </si>
+  <si>
+    <t>2efd5621-0508-4595-a1ae-113838bf5a8e</t>
   </si>
   <si>
     <t>CIF-HS-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468769+08:00</t>
-  </si>
-  <si>
-    <t>4fa20f2a-2960-4a2c-bf91-6bbec07049e0</t>
+    <t>2026-02-24T03:10:43.2973597+08:00</t>
+  </si>
+  <si>
+    <t>207395b8-25e9-44dc-b75a-2d9e9f856512</t>
   </si>
   <si>
     <t>CIF-RL-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468806+08:00</t>
-  </si>
-  <si>
-    <t>621faccc-cf2c-407f-ac78-f5c91e8a7ef7</t>
+    <t>2026-02-24T03:10:43.2973667+08:00</t>
+  </si>
+  <si>
+    <t>a2e9c843-a35e-415b-b8b4-e33f1d74634c</t>
   </si>
   <si>
     <t>CIF-YP-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468849+08:00</t>
-  </si>
-  <si>
-    <t>af48f7ef-a0b2-4333-962d-cb7a123d85e2</t>
+    <t>2026-02-24T03:10:43.2973738+08:00</t>
+  </si>
+  <si>
+    <t>a45fb3d0-059a-4aa5-b7da-3398cd0f8ebf</t>
   </si>
   <si>
     <t>CIF-AVS20D-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468887+08:00</t>
-  </si>
-  <si>
-    <t>0b62f64d-7a50-4200-940a-b138e18317e2</t>
+    <t>2026-02-24T03:10:43.2973803+08:00</t>
+  </si>
+  <si>
+    <t>c4406415-30c6-40f0-afdf-8cc17c931fbe</t>
   </si>
   <si>
     <t>CIF-SC-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468926+08:00</t>
-  </si>
-  <si>
-    <t>d6ddce92-6921-4cb6-bc26-fd718b584873</t>
+    <t>2026-02-24T03:10:43.2973876+08:00</t>
+  </si>
+  <si>
+    <t>d660f547-cff7-49c7-bacd-9901c33486fa</t>
   </si>
   <si>
     <t>CIF-AVC-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7468966+08:00</t>
-  </si>
-  <si>
-    <t>5d0c0adb-026c-473c-b123-30eba3f4188e</t>
+    <t>2026-02-24T03:10:43.2973939+08:00</t>
+  </si>
+  <si>
+    <t>d7bdecb3-8469-4154-8abe-df9cebe0e65a</t>
   </si>
   <si>
     <t>CIF-DC-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469002+08:00</t>
-  </si>
-  <si>
-    <t>f5b5f48e-fdae-4b48-a3e1-fc04cc5b88fd</t>
+    <t>2026-02-24T03:10:43.2974001+08:00</t>
+  </si>
+  <si>
+    <t>10121c96-c7c4-4a24-945a-c0f1b618ab15</t>
   </si>
   <si>
     <t>PIF-F70M85-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469039+08:00</t>
-  </si>
-  <si>
-    <t>43c1ee48-fd41-41b9-91dc-a13e9253adca</t>
+    <t>2026-02-24T03:10:43.2974069+08:00</t>
+  </si>
+  <si>
+    <t>e13651b9-5c68-46af-910a-8aa5aa403231</t>
   </si>
   <si>
     <t>P-F90M423-0154</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469081+08:00</t>
-  </si>
-  <si>
-    <t>3a55a4d2-9bf1-4b60-b788-625d67f644a0</t>
+    <t>2026-02-24T03:10:43.2974137+08:00</t>
+  </si>
+  <si>
+    <t>42e60cf0-302a-43a9-844e-0355bf8dae37</t>
   </si>
   <si>
     <t>P-MP-0154</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469118+08:00</t>
-  </si>
-  <si>
-    <t>4f43ef52-f2a6-406a-a508-097e9a462523</t>
+    <t>2026-02-24T03:10:43.2974204+08:00</t>
+  </si>
+  <si>
+    <t>91461a39-7250-4403-ab46-b8a0de11ec3a</t>
   </si>
   <si>
     <t>CIF-MM720P5.00-0238</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469155+08:00</t>
-  </si>
-  <si>
-    <t>0d1ad955-48e0-438c-b29b-39ce949d3877</t>
+    <t>2026-02-24T03:10:43.2974274+08:00</t>
+  </si>
+  <si>
+    <t>be216920-32ea-4b05-b2b8-977cbeafb2c0</t>
   </si>
   <si>
     <t>PVC 75A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469194+08:00</t>
-  </si>
-  <si>
-    <t>26f1643d-b2f5-4f05-95b0-a8bffb65e246</t>
+    <t>2026-02-24T03:10:43.2974338+08:00</t>
+  </si>
+  <si>
+    <t>7c4f8bfd-8a15-4223-abb3-1e3815572d37</t>
   </si>
   <si>
     <t>CIF-NP-0125</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469232+08:00</t>
-  </si>
-  <si>
-    <t>71a0903d-35d8-49d3-903a-a94086a480a4</t>
+    <t>2026-02-24T03:10:43.2974407+08:00</t>
+  </si>
+  <si>
+    <t>42211474-4935-4a39-a685-8d41d12ea227</t>
   </si>
   <si>
     <t>CIF-SRC-0413</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469269+08:00</t>
-  </si>
-  <si>
-    <t>7b369940-7059-48e7-a6ba-394c3e89a880</t>
+    <t>2026-02-24T03:10:43.2974475+08:00</t>
+  </si>
+  <si>
+    <t>583477ed-7ab5-404b-89c8-6851efcc8eaa</t>
   </si>
   <si>
     <t>CIF-AVS20D-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469307+08:00</t>
-  </si>
-  <si>
-    <t>3ba1ef02-6ed8-4724-a78e-7277612b9c00</t>
+    <t>2026-02-24T03:10:43.2974544+08:00</t>
+  </si>
+  <si>
+    <t>120628d2-5e22-48a2-a9b7-129e9848a888</t>
   </si>
   <si>
     <t>CIF-DC-0313</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469348+08:00</t>
-  </si>
-  <si>
-    <t>01cc0dae-301c-401f-8aad-9e077caf1f0a</t>
+    <t>2026-02-24T03:10:43.2974606+08:00</t>
+  </si>
+  <si>
+    <t>a9a0dfde-e9b9-467c-b186-b86eb85ae83e</t>
   </si>
   <si>
     <t>CIF-FL(9909-1)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469385+08:00</t>
-  </si>
-  <si>
-    <t>892b9dd5-2062-423d-a97b-f9b62accf15a</t>
+    <t>2026-02-24T03:10:43.2974678+08:00</t>
+  </si>
+  <si>
+    <t>4879894f-290b-41f9-bf51-698ab8ad44f4</t>
   </si>
   <si>
     <t>CIF-EPC-0213</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469422+08:00</t>
-  </si>
-  <si>
-    <t>a0c6f591-c7fe-41c0-996c-1b6b975b080e</t>
+    <t>2026-02-24T03:10:43.2974747+08:00</t>
+  </si>
+  <si>
+    <t>baef1f91-eb50-4957-9f22-16f01cb4b82d</t>
   </si>
   <si>
     <t>CIF-CC-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469463+08:00</t>
-  </si>
-  <si>
-    <t>7d5f08a7-95fb-4ff7-80d6-4233262ed26b</t>
+    <t>2026-02-24T03:10:43.2974812+08:00</t>
+  </si>
+  <si>
+    <t>2ae44551-0dac-4d6f-89ac-aeab74681e8a</t>
   </si>
   <si>
     <t>CIF-2WC-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469497+08:00</t>
-  </si>
-  <si>
-    <t>935eff37-fb24-4539-bab6-5fd78ea4c78b</t>
+    <t>2026-02-24T03:10:43.2974875+08:00</t>
+  </si>
+  <si>
+    <t>ce3c01bc-afdc-4ff3-9437-ba20f57e59ff</t>
   </si>
   <si>
     <t>CIF-3WC-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469534+08:00</t>
-  </si>
-  <si>
-    <t>0ed7b8de-b8cf-4991-aa4b-39a3698e8023</t>
+    <t>2026-02-24T03:10:43.2974945+08:00</t>
+  </si>
+  <si>
+    <t>57bb9ed6-d3d3-49f5-9fad-fea6f0d0ce3c</t>
   </si>
   <si>
     <t>CIF-SLC-0104</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469574+08:00</t>
-  </si>
-  <si>
-    <t>b539f9b4-f8ad-415d-8441-150e4ab313c4</t>
+    <t>2026-02-24T03:10:43.2975009+08:00</t>
+  </si>
+  <si>
+    <t>ac1bbabe-024f-4a41-867d-9c1f72ae43d3</t>
   </si>
   <si>
     <t>CIF-EP-0125</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469612+08:00</t>
-  </si>
-  <si>
-    <t>d3cdcb83-2af6-45bb-8500-0e07675d4a61</t>
+    <t>2026-02-24T03:10:43.2975075+08:00</t>
+  </si>
+  <si>
+    <t>7d4db3e1-f2c7-4188-bc99-2d389e170d51</t>
   </si>
   <si>
     <t>CIF-DC-0108Y</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469649+08:00</t>
-  </si>
-  <si>
-    <t>ced815f8-f3c7-403a-8c49-e0931ce6fe7b</t>
+    <t>2026-02-24T03:10:43.2975141+08:00</t>
+  </si>
+  <si>
+    <t>d94d722e-d245-4eed-8808-b3552650824a</t>
   </si>
   <si>
     <t>RM-PVC75A-JM</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469691+08:00</t>
-  </si>
-  <si>
-    <t>aeebc570-4b64-4b60-ad30-1872b97263e7</t>
+    <t>2026-02-24T03:10:43.2975205+08:00</t>
+  </si>
+  <si>
+    <t>91d5bc71-8155-4944-8b1a-7c38cf070008</t>
   </si>
   <si>
     <t>CHE - UV-GLUE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469727+08:00</t>
-  </si>
-  <si>
-    <t>328e51f2-6285-46aa-80a1-0706bfa97fea</t>
+    <t>2026-02-24T03:10:43.2975270+08:00</t>
+  </si>
+  <si>
+    <t>f288bf09-08ab-44c6-a468-abf4d34ee509</t>
   </si>
   <si>
     <t>CHE - UV-GLUE-FL</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469763+08:00</t>
-  </si>
-  <si>
-    <t>dc52198e-edef-43b9-b6a1-8145fe64d3bf</t>
+    <t>2026-02-24T03:10:43.2975338+08:00</t>
+  </si>
+  <si>
+    <t>1f798e22-1c08-4f08-95a4-cdb903174c26</t>
   </si>
   <si>
     <t>CIF-N60D-0104</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469802+08:00</t>
-  </si>
-  <si>
-    <t>f166e0a0-cd47-4f16-9754-ecc9cae65073</t>
+    <t>2026-02-24T03:10:43.2975405+08:00</t>
+  </si>
+  <si>
+    <t>9a886961-ce10-493d-91f6-44a75a140e0b</t>
   </si>
   <si>
     <t>P-MP-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469839+08:00</t>
-  </si>
-  <si>
-    <t>d9fc9616-5884-4083-87ba-ff0c6accaebf</t>
+    <t>2026-02-24T03:10:43.2975466+08:00</t>
+  </si>
+  <si>
+    <t>9f4491df-0868-458e-8096-3ad320b7040b</t>
   </si>
   <si>
     <t>CIF-SR-0126</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469875+08:00</t>
-  </si>
-  <si>
-    <t>25e1fbb1-7fde-4938-9855-bc01a23fa1df</t>
+    <t>2026-02-24T03:10:43.2975538+08:00</t>
+  </si>
+  <si>
+    <t>79e48593-cceb-4e91-b590-dae153e3d817</t>
   </si>
   <si>
     <t>CISP-ID-0140</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469917+08:00</t>
-  </si>
-  <si>
-    <t>c8c08b72-3327-4386-acca-b58726d545a7</t>
+    <t>2026-02-24T03:10:43.2975603+08:00</t>
+  </si>
+  <si>
+    <t>288916af-8ce2-4928-8fe3-ae302993b5e4</t>
   </si>
   <si>
     <t>CISP-SG-0137</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469954+08:00</t>
-  </si>
-  <si>
-    <t>6a71fa66-dd62-4e44-8138-089a2e2a44f7</t>
+    <t>2026-02-24T03:10:43.2975670+08:00</t>
+  </si>
+  <si>
+    <t>2f858905-9cae-42fb-87d2-b7d3d64607c1</t>
   </si>
   <si>
     <t>CISP-ST-0121</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7469991+08:00</t>
-  </si>
-  <si>
-    <t>82f302e6-fc7c-46fb-9bfa-7034f2158877</t>
+    <t>2026-02-24T03:10:43.2975741+08:00</t>
+  </si>
+  <si>
+    <t>e2411057-c582-43fb-a75e-e5acd5a2f756</t>
   </si>
   <si>
     <t>CISP-SS-0253</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470031+08:00</t>
-  </si>
-  <si>
-    <t>1c3d74ad-86e4-4784-9146-caf8272b0bc5</t>
+    <t>2026-02-24T03:10:43.2975806+08:00</t>
+  </si>
+  <si>
+    <t>461d9829-b66e-4f51-a4d5-1c64fbf25971</t>
   </si>
   <si>
     <t>CISP-SP-0237</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470066+08:00</t>
-  </si>
-  <si>
-    <t>60df407b-24a3-438e-8d4b-7c8f4323cab3</t>
+    <t>2026-02-24T03:10:43.2975869+08:00</t>
+  </si>
+  <si>
+    <t>9a00d8da-5143-4bbc-b1a6-9be8cb506e46</t>
   </si>
   <si>
     <t>CISP-TF-0121</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470104+08:00</t>
-  </si>
-  <si>
-    <t>3b88df16-ecb8-4414-a864-db9044237df6</t>
+    <t>2026-02-24T03:10:43.2975939+08:00</t>
+  </si>
+  <si>
+    <t>c008b049-8370-4add-a43c-8cce1f72ed00</t>
   </si>
   <si>
     <t>CISP-TQ-0221</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470143+08:00</t>
-  </si>
-  <si>
-    <t>24d4114a-3d41-4ff9-bdcd-acb21c8cb560</t>
+    <t>2026-02-24T03:10:43.2976003+08:00</t>
+  </si>
+  <si>
+    <t>c1cc4c26-c384-4512-b1f5-19c6faa23267</t>
   </si>
   <si>
     <t>PVC 80A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470181+08:00</t>
-  </si>
-  <si>
-    <t>ad5b412b-3093-4e84-8402-c928c71e264c</t>
+    <t>2026-02-24T03:10:43.2976065+08:00</t>
+  </si>
+  <si>
+    <t>856ce15b-43a5-43dd-b91a-9773c006d4cc</t>
   </si>
   <si>
     <t>CIF-LLC-0213</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470216+08:00</t>
-  </si>
-  <si>
-    <t>b0dc4ef7-55fa-463d-b4bc-04185e7bb8fc</t>
+    <t>2026-02-24T03:10:43.2976133+08:00</t>
+  </si>
+  <si>
+    <t>2c205a00-a7f6-4a51-87b1-a4f00501e386</t>
   </si>
   <si>
     <t>CIF-R2WC-0342</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470257+08:00</t>
-  </si>
-  <si>
-    <t>9e965e57-db3f-4944-b352-cdd3eaa07cf0</t>
+    <t>2026-02-24T03:10:43.2976199+08:00</t>
+  </si>
+  <si>
+    <t>6800ea64-b950-49cc-914b-2fdd4306e2fc</t>
   </si>
   <si>
     <t>CIF-SLC-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470293+08:00</t>
-  </si>
-  <si>
-    <t>6417bcd2-9c44-41a2-aecd-293241441a42</t>
+    <t>2026-02-24T03:10:43.2976262+08:00</t>
+  </si>
+  <si>
+    <t>e9a4127e-9b95-4e94-8aa9-33d5e5cba071</t>
   </si>
   <si>
     <t>CIF-SLC-0208</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470329+08:00</t>
-  </si>
-  <si>
-    <t>5f4bdea1-869e-4887-8741-97be7d993876</t>
+    <t>2026-02-24T03:10:43.2976331+08:00</t>
+  </si>
+  <si>
+    <t>5dfe576f-9ca7-4e69-9846-1263a68bb1c5</t>
   </si>
   <si>
     <t>CIF-EP-0225</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470369+08:00</t>
-  </si>
-  <si>
-    <t>89976e7b-9ce1-4c10-8adb-f1459f0a2fcd</t>
+    <t>2026-02-24T03:10:43.2976394+08:00</t>
+  </si>
+  <si>
+    <t>c062c9c4-a4d5-4da1-9925-7dae11bdca62</t>
   </si>
   <si>
     <t>CIF-BCV-0413</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470406+08:00</t>
-  </si>
-  <si>
-    <t>470df4ba-213c-4c31-a757-8d6ee97bd092</t>
+    <t>2026-02-24T03:10:43.2976459+08:00</t>
+  </si>
+  <si>
+    <t>9b9988aa-3bec-46cd-b687-a807e7c081f4</t>
   </si>
   <si>
     <t>CIF-NC-0125</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470440+08:00</t>
-  </si>
-  <si>
-    <t>cd274c0b-97e1-426e-a2cb-2b21267c9bec</t>
+    <t>2026-02-24T03:10:43.2976527+08:00</t>
+  </si>
+  <si>
+    <t>aa1e6656-c26a-44f2-932d-198f9a36ce8c</t>
   </si>
   <si>
     <t>CIF-CC-0313</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470481+08:00</t>
-  </si>
-  <si>
-    <t>0a37cad5-b1a4-4f90-8a6c-c0f3b54ea62e</t>
+    <t>2026-02-24T03:10:43.2976594+08:00</t>
+  </si>
+  <si>
+    <t>f7f7dcfb-3518-4897-b2a2-3e15bc743012</t>
   </si>
   <si>
     <t>CIF-CRLL-0513</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470516+08:00</t>
-  </si>
-  <si>
-    <t>46046d7e-cc14-4cb1-8e16-74beb63de195</t>
+    <t>2026-02-24T03:10:43.2976656+08:00</t>
+  </si>
+  <si>
+    <t>18c70039-379a-4a8e-9eb9-18ff99ba8bb3</t>
   </si>
   <si>
     <t>CIF-LL-0413</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470552+08:00</t>
-  </si>
-  <si>
-    <t>3d193536-c870-4e60-afac-59902f39dc03</t>
+    <t>2026-02-24T03:10:43.2976727+08:00</t>
+  </si>
+  <si>
+    <t>20b83515-6fe0-4315-b774-974a71570171</t>
   </si>
   <si>
     <t>CIF-LLC-0513</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470592+08:00</t>
-  </si>
-  <si>
-    <t>ae435059-8315-4d59-a6ce-ad14f9e0f932</t>
+    <t>2026-02-24T03:10:43.2976792+08:00</t>
+  </si>
+  <si>
+    <t>8e268c07-2fec-404d-8c5e-c2222020a5cd</t>
   </si>
   <si>
     <t>CIF-LL-0313</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470628+08:00</t>
-  </si>
-  <si>
-    <t>66415f27-4bbd-4204-91bd-3babebbab32d</t>
+    <t>2026-02-24T03:10:43.2976857+08:00</t>
+  </si>
+  <si>
+    <t>849c1397-3e08-476a-a08b-b69db92c6ceb</t>
   </si>
   <si>
     <t>CIF-LL-0613</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470664+08:00</t>
-  </si>
-  <si>
-    <t>4acc41b0-aa61-4b24-9106-4850bf44bbb1</t>
+    <t>2026-02-24T03:10:43.2976929+08:00</t>
+  </si>
+  <si>
+    <t>eeb41f7f-2722-44cc-9238-106e02a70316</t>
   </si>
   <si>
     <t>PVC 85A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470704+08:00</t>
-  </si>
-  <si>
-    <t>952e1bea-f6b0-4872-a360-9deb59650f77</t>
+    <t>2026-02-24T03:10:43.2976997+08:00</t>
+  </si>
+  <si>
+    <t>c3021363-4436-4e0d-8a93-cef005f20b7e</t>
   </si>
   <si>
     <t>CSC-FC-0114</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470742+08:00</t>
-  </si>
-  <si>
-    <t>abcebb6c-883a-43d5-b993-fc838aa4002b</t>
+    <t>2026-02-24T03:10:43.2977059+08:00</t>
+  </si>
+  <si>
+    <t>9918fb08-07f8-4d4b-b707-b312eb364fcd</t>
   </si>
   <si>
     <t>CSC-T00PVC22-0148</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470779+08:00</t>
-  </si>
-  <si>
-    <t>8f5d2999-9785-4ba2-806e-810e1e0bb87d</t>
+    <t>2026-02-24T03:10:43.2977129+08:00</t>
+  </si>
+  <si>
+    <t>10574a63-8541-44ec-8a6d-ab719b21fe87</t>
   </si>
   <si>
     <t>BAG HDPE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470820+08:00</t>
-  </si>
-  <si>
-    <t>ecc9a75c-c5ab-47da-b390-6a0bc71668d9</t>
+    <t>2026-02-24T03:10:43.2977190+08:00</t>
+  </si>
+  <si>
+    <t>98d0f377-e9d9-4295-8013-30f0ffd95335</t>
   </si>
   <si>
     <t>BAG LDPE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470861+08:00</t>
-  </si>
-  <si>
-    <t>512c4ee8-dab0-4889-bdd3-df2dbb375a83</t>
+    <t>2026-02-24T03:10:43.2977257+08:00</t>
+  </si>
+  <si>
+    <t>b2d97a48-9f3f-4c58-9cb2-6f86564da5ec</t>
   </si>
   <si>
     <t>CIF-CRLL-0342</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470902+08:00</t>
-  </si>
-  <si>
-    <t>4b30542a-11b0-4ffa-b2b4-0d1b82a7b5bb</t>
+    <t>2026-02-24T03:10:43.2977326+08:00</t>
+  </si>
+  <si>
+    <t>e4a66429-51a1-4a16-ae1d-09f7511e6fce</t>
   </si>
   <si>
     <t>P-MPSM001-0154</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470943+08:00</t>
-  </si>
-  <si>
-    <t>88502903-0589-4886-8edf-ccdc641b193e</t>
+    <t>2026-02-24T03:10:43.2977393+08:00</t>
+  </si>
+  <si>
+    <t>1bedde97-217c-4435-804d-54de882bbf20</t>
   </si>
   <si>
     <t>CIF-R3WC-0342</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7470979+08:00</t>
-  </si>
-  <si>
-    <t>2fbea53c-3ea2-400b-a1e6-d7d7501235f0</t>
+    <t>2026-02-24T03:10:43.2977458+08:00</t>
+  </si>
+  <si>
+    <t>b0e31cc0-31c5-440d-bb51-c033fa4f53ba</t>
   </si>
   <si>
     <t>CIF-SLC-0308</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471015+08:00</t>
-  </si>
-  <si>
-    <t>0259640c-413e-4bec-9a15-432b02e668c1</t>
+    <t>2026-02-24T03:10:43.2977521+08:00</t>
+  </si>
+  <si>
+    <t>e56450a4-b833-4cf2-9f89-39f651609e55</t>
   </si>
   <si>
     <t>CIF-R4WC-0342</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471052+08:00</t>
-  </si>
-  <si>
-    <t>a7a939b5-a16f-4f35-aa8a-49789c1fd9a7</t>
+    <t>2026-02-24T03:10:43.2977591+08:00</t>
+  </si>
+  <si>
+    <t>68c23023-18a7-49c6-97b4-7393ec1ea604</t>
   </si>
   <si>
     <t>CIF-SLC-0542</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471094+08:00</t>
-  </si>
-  <si>
-    <t>5f549a46-8558-4bbf-80b0-2fdec966ceb9</t>
+    <t>2026-02-24T03:10:43.2977655+08:00</t>
+  </si>
+  <si>
+    <t>eeb8d7aa-b398-482f-b62c-e380ebc1ce49</t>
   </si>
   <si>
     <t>P-F140M423-0313</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471131+08:00</t>
-  </si>
-  <si>
-    <t>9fde8bed-e8da-4d68-a49f-98bf4515e1fa</t>
+    <t>2026-02-24T03:10:43.2977721+08:00</t>
+  </si>
+  <si>
+    <t>b19fc6c0-9194-4d7b-b394-154ceb0bb2ae</t>
   </si>
   <si>
     <t>CIF-TC-0142</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471166+08:00</t>
-  </si>
-  <si>
-    <t>cc7ad5ea-e35a-41f2-8146-ced87acc8272</t>
+    <t>2026-02-24T03:10:43.2977795+08:00</t>
+  </si>
+  <si>
+    <t>252e30e0-0b65-4b30-b1ca-7753de53ef7a</t>
   </si>
   <si>
     <t>CIF-TC-0242</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471208+08:00</t>
-  </si>
-  <si>
-    <t>ad5416db-e6cf-4199-8993-76c154dc184a</t>
+    <t>2026-02-24T03:10:43.2977860+08:00</t>
+  </si>
+  <si>
+    <t>7f840e5d-d3a2-4c4b-9257-3d9877ce1397</t>
   </si>
   <si>
     <t>CIF-CC-0542</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471244+08:00</t>
-  </si>
-  <si>
-    <t>a8e3ccbf-8fe7-4026-af1d-d54476a8da45</t>
+    <t>2026-02-24T03:10:43.2977923+08:00</t>
+  </si>
+  <si>
+    <t>8dacb4e3-2eb8-46d5-a63a-c19b1a22eb3c</t>
   </si>
   <si>
     <t>CIF-NAVS20D-0249</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471282+08:00</t>
-  </si>
-  <si>
-    <t>41fff471-115f-4ef1-9b1b-69772892424c</t>
+    <t>2026-02-24T03:10:43.2977997+08:00</t>
+  </si>
+  <si>
+    <t>79578ed7-2e16-4e1c-8dc9-0b83cc68cc69</t>
   </si>
   <si>
     <t>CIF-NRFMC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471322+08:00</t>
-  </si>
-  <si>
-    <t>9dcca8e8-2d50-41d0-ad3b-d88410c9d120</t>
+    <t>2026-02-24T03:10:43.2978062+08:00</t>
+  </si>
+  <si>
+    <t>836d289f-b88b-4be0-a38e-1cba98f88457</t>
   </si>
   <si>
     <t>CIF-NRFFLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471356+08:00</t>
-  </si>
-  <si>
-    <t>6b14d4e7-bdee-4959-be70-225843e3a3b5</t>
+    <t>2026-02-24T03:10:43.2978127+08:00</t>
+  </si>
+  <si>
+    <t>473d8e64-6284-445b-926e-14f58dc28a19</t>
   </si>
   <si>
     <t>CIF-3WYC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471393+08:00</t>
-  </si>
-  <si>
-    <t>56551e96-4513-469b-85c4-e558028b6830</t>
+    <t>2026-02-24T03:10:43.2978192+08:00</t>
+  </si>
+  <si>
+    <t>fbaca2ed-5867-495f-a464-d154f9fdd8b8</t>
   </si>
   <si>
     <t>CIF-NRFLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471433+08:00</t>
-  </si>
-  <si>
-    <t>df4d73ed-e260-4627-a0d6-8f4f534f9efd</t>
+    <t>2026-02-24T03:10:43.2978259+08:00</t>
+  </si>
+  <si>
+    <t>13e3a2eb-98e9-436d-b0fb-c6849e57bee9</t>
   </si>
   <si>
     <t>CIF-LLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471470+08:00</t>
-  </si>
-  <si>
-    <t>4a23afe8-4f70-44f3-9d00-1aa210b51903</t>
+    <t>2026-02-24T03:10:43.2978322+08:00</t>
+  </si>
+  <si>
+    <t>d1a49c38-2a68-4746-a53d-eb1e6ff0db72</t>
   </si>
   <si>
     <t>CIF-RCTW-0159</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471517+08:00</t>
-  </si>
-  <si>
-    <t>18451196-3714-45bd-9c67-78dd898081ea</t>
+    <t>2026-02-24T03:10:43.2978392+08:00</t>
+  </si>
+  <si>
+    <t>db114130-266b-4b2c-aa96-f59db97ce9f6</t>
   </si>
   <si>
     <t>P-F140M423-0154</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471559+08:00</t>
-  </si>
-  <si>
-    <t>2cf7c80b-2e3c-4e72-a4ba-7a4e071adc6c</t>
+    <t>2026-02-24T03:10:43.2978455+08:00</t>
+  </si>
+  <si>
+    <t>72c4f3a1-8433-4911-b579-6aec53439e46</t>
   </si>
   <si>
     <t>CIF-CC-0342</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471595+08:00</t>
-  </si>
-  <si>
-    <t>3bac0dc9-7bac-4026-bc9f-0b96c9871d6e</t>
+    <t>2026-02-24T03:10:43.2978520+08:00</t>
+  </si>
+  <si>
+    <t>7c77c826-29af-48d0-8474-08a7ac16fbc0</t>
   </si>
   <si>
     <t>CIF-BCV-0332</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471632+08:00</t>
-  </si>
-  <si>
-    <t>16b8707c-b80c-4680-a1f5-a57b91c4fd27</t>
+    <t>2026-02-24T03:10:43.2978588+08:00</t>
+  </si>
+  <si>
+    <t>66f03147-50d3-4fef-9b48-ead7eeaa3ab4</t>
   </si>
   <si>
     <t>CIF-FL-0118</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471671+08:00</t>
-  </si>
-  <si>
-    <t>bb82c5ea-a63d-4301-aafa-4d643c84b7d9</t>
+    <t>2026-02-24T03:10:43.2978653+08:00</t>
+  </si>
+  <si>
+    <t>848ce88e-b31f-4fd9-84aa-516bb3966828</t>
   </si>
   <si>
     <t>ART WHITE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471704+08:00</t>
-  </si>
-  <si>
-    <t>805bc37f-4aaf-4b4f-9d6b-b7f3a2e7edc6</t>
+    <t>2026-02-24T03:10:43.2978715+08:00</t>
+  </si>
+  <si>
+    <t>f8397586-4295-4f0b-ac2e-6a88ff2a2106</t>
   </si>
   <si>
     <t>ART BLUE</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471741+08:00</t>
-  </si>
-  <si>
-    <t>454f99e3-6bc6-4d16-99a5-6219679adbfb</t>
+    <t>2026-02-24T03:10:43.2978783+08:00</t>
+  </si>
+  <si>
+    <t>67d4111b-ef46-42d0-b9dc-101883dc70fc</t>
   </si>
   <si>
     <t>ART YELLOW</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471780+08:00</t>
-  </si>
-  <si>
-    <t>a0674e43-f549-4dad-ae5b-133aaf7ce1d1</t>
+    <t>2026-02-24T03:10:43.2978846+08:00</t>
+  </si>
+  <si>
+    <t>147893e9-1257-4dcf-9254-50e665ad53d0</t>
   </si>
   <si>
     <t>ART RAINBOW</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471816+08:00</t>
-  </si>
-  <si>
-    <t>7a1fa467-1d76-4e82-8a0d-cb7d7452eb26</t>
+    <t>2026-02-24T03:10:43.2978910+08:00</t>
+  </si>
+  <si>
+    <t>22678331-9cb4-4250-b45f-d38786463766</t>
   </si>
   <si>
     <t>CIF-CC-0442</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471851+08:00</t>
-  </si>
-  <si>
-    <t>35cedf60-1e8f-4cbd-bdea-ed102fa158df</t>
+    <t>2026-02-24T03:10:43.2978978+08:00</t>
+  </si>
+  <si>
+    <t>5d12ed3c-0169-4037-8788-61efc0dc9421</t>
   </si>
   <si>
     <t>CIF-2WC-0242</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471890+08:00</t>
-  </si>
-  <si>
-    <t>36a1f832-58c2-49f1-b9fd-7dbed94df17a</t>
+    <t>2026-02-24T03:10:43.2979041+08:00</t>
+  </si>
+  <si>
+    <t>4d7a529f-3609-44d7-9f54-478702b78e09</t>
   </si>
   <si>
     <t>CIPS-LLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471925+08:00</t>
-  </si>
-  <si>
-    <t>c4ab8b08-e0c5-4aa3-9b69-8dc036913044</t>
+    <t>2026-02-24T03:10:43.2979104+08:00</t>
+  </si>
+  <si>
+    <t>dd0e77c7-0923-41b3-a12e-2a3a6d40fd62</t>
   </si>
   <si>
     <t>CIPS-CLLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7471961+08:00</t>
-  </si>
-  <si>
-    <t>d1942c00-19b5-4afc-8081-7b990364d16b</t>
+    <t>2026-02-24T03:10:43.2979171+08:00</t>
+  </si>
+  <si>
+    <t>da8247b6-420b-4222-8ee4-c79016a11ef5</t>
   </si>
   <si>
     <t>CIPS-BCV-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472001+08:00</t>
-  </si>
-  <si>
-    <t>f42cc723-5dd5-48ee-9218-54a37dc9216b</t>
+    <t>2026-02-24T03:10:43.2979232+08:00</t>
+  </si>
+  <si>
+    <t>965c7795-4802-4b13-abe0-f3817aee6ab3</t>
   </si>
   <si>
     <t>CIPS-CC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472038+08:00</t>
-  </si>
-  <si>
-    <t>2bab2390-dfb2-4f71-ab98-0cd5d778c179</t>
+    <t>2026-02-24T03:10:43.2979295+08:00</t>
+  </si>
+  <si>
+    <t>08a8d0f5-48c3-4ded-aa4c-f4800af2d061</t>
   </si>
   <si>
     <t>CIPS-BCV-0332</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472074+08:00</t>
-  </si>
-  <si>
-    <t>9805496f-6e7f-4d50-a704-3823c54412b4</t>
+    <t>2026-02-24T03:10:43.2979366+08:00</t>
+  </si>
+  <si>
+    <t>73553055-9d52-47f9-8fa3-df9e5d443e85</t>
   </si>
   <si>
     <t>CIPS-YP-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472114+08:00</t>
-  </si>
-  <si>
-    <t>07595d5c-066e-418a-ad90-60bfaaaeef1c</t>
+    <t>2026-02-24T03:10:43.2979427+08:00</t>
+  </si>
+  <si>
+    <t>0a6e8946-b889-4620-bccb-6a5d57163c38</t>
   </si>
   <si>
     <t>CIPS-CRLL-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472151+08:00</t>
-  </si>
-  <si>
-    <t>2b210bac-5610-4fb5-a869-eacde26b700d</t>
+    <t>2026-02-24T03:10:43.2979492+08:00</t>
+  </si>
+  <si>
+    <t>71bb5e15-ad65-4fe8-96dd-68324613914d</t>
   </si>
   <si>
     <t>CIPS-MLLC-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472184+08:00</t>
-  </si>
-  <si>
-    <t>a617a967-060c-4836-81f1-caa51ff0a2cb</t>
+    <t>2026-02-24T03:10:43.2979557+08:00</t>
+  </si>
+  <si>
+    <t>8fa0a55c-305c-410e-bd57-02fe72465293</t>
   </si>
   <si>
     <t>CIPS-T00TRI-PVC165-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472223+08:00</t>
-  </si>
-  <si>
-    <t>509d7019-fdda-49d0-a777-65edbd652e18</t>
+    <t>2026-02-24T03:10:43.2979623+08:00</t>
+  </si>
+  <si>
+    <t>c95830fe-fb08-4172-815c-7df804f1b3d6</t>
   </si>
   <si>
     <t>CIPS-T00TRI-EVA165-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472258+08:00</t>
-  </si>
-  <si>
-    <t>9f93bb1b-dbc0-42f8-ac8d-662847d2bdd4</t>
+    <t>2026-02-24T03:10:43.2979685+08:00</t>
+  </si>
+  <si>
+    <t>2dd6dbf5-d632-4723-a826-e881ccb1c303</t>
   </si>
   <si>
     <t>CIPS-T00TRI-PE165-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472295+08:00</t>
-  </si>
-  <si>
-    <t>a3374a99-1ddb-4056-9b56-9916cbd44f9d</t>
+    <t>2026-02-24T03:10:43.2979756+08:00</t>
+  </si>
+  <si>
+    <t>96d1e5e1-fcc1-4e80-84f2-c9f2e216b35a</t>
   </si>
   <si>
     <t>CIPS-T00DEHP0.2-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472335+08:00</t>
-  </si>
-  <si>
-    <t>11bfc3b0-5094-482f-8563-bbf290b6d840</t>
+    <t>2026-02-24T03:10:43.2979819+08:00</t>
+  </si>
+  <si>
+    <t>c6bb5ade-87d1-41f0-8d61-1ea21a81fad7</t>
   </si>
   <si>
     <t>CIPS-T00PE15-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472370+08:00</t>
-  </si>
-  <si>
-    <t>61464abc-1686-4c54-a17f-a5481231b636</t>
+    <t>2026-02-24T03:10:43.2979885+08:00</t>
+  </si>
+  <si>
+    <t>0f1ba968-9e3d-4487-9fc2-64feb6567f24</t>
   </si>
   <si>
     <t>CIPS-T00EVA15-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472405+08:00</t>
-  </si>
-  <si>
-    <t>c9bc9085-902a-42ab-a7e2-47ce2fbbebb5</t>
+    <t>2026-02-24T03:10:43.2979952+08:00</t>
+  </si>
+  <si>
+    <t>a6263401-b3ee-49a1-b2af-41a5f05e8898</t>
   </si>
   <si>
     <t>CIPS-T00PVC15-0108</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472447+08:00</t>
-  </si>
-  <si>
-    <t>2fe3ac07-ea6e-45de-854b-9e8495368b62</t>
+    <t>2026-02-24T03:10:43.2980018+08:00</t>
+  </si>
+  <si>
+    <t>dd6436da-e199-4e41-b07d-c731af1cae76</t>
   </si>
   <si>
     <t>PIF-SMESC02.2-0150</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472481+08:00</t>
-  </si>
-  <si>
-    <t>51d6a02a-28d3-4b01-ba1c-771b23988e82</t>
+    <t>2026-02-24T03:10:43.2980080+08:00</t>
+  </si>
+  <si>
+    <t>e0f2363b-b48e-4a50-83d9-d6bb55422c47</t>
   </si>
   <si>
     <t>PIF-SMESB02.2-0150</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472515+08:00</t>
-  </si>
-  <si>
-    <t>7aebb747-67e8-46c7-bb54-a4b72f2fc6b5</t>
+    <t>2026-02-24T03:10:43.2980151+08:00</t>
+  </si>
+  <si>
+    <t>9e692409-fa05-4a6f-aaee-37fd3baa3d5f</t>
   </si>
   <si>
     <t>CIF-T00PU30(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472557+08:00</t>
-  </si>
-  <si>
-    <t>c9ddef6a-1f73-4272-91df-047725407f23</t>
+    <t>2026-02-24T03:10:43.2980213+08:00</t>
+  </si>
+  <si>
+    <t>9f91a5dd-e2a1-42e5-8d46-12c5542db58c</t>
   </si>
   <si>
     <t>CIF-LLC-0751</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472594+08:00</t>
-  </si>
-  <si>
-    <t>31404a4b-8c10-473f-8d5d-2c3bd96d10bc</t>
+    <t>2026-02-24T03:10:43.2980276+08:00</t>
+  </si>
+  <si>
+    <t>e3a0f508-ef26-43c5-a5d9-b44853e4c285</t>
   </si>
   <si>
     <t>CIF-LL-0551</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472630+08:00</t>
-  </si>
-  <si>
-    <t>627b5178-2848-424c-a97d-cd173a30ad39</t>
+    <t>2026-02-24T03:10:43.2980349+08:00</t>
+  </si>
+  <si>
+    <t>871ffd01-d61e-4bfb-8a85-da5d1f651bcf</t>
   </si>
   <si>
     <t>CIF-LL-0652</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472665+08:00</t>
-  </si>
-  <si>
-    <t>22679f62-b111-4214-8859-998e64011305</t>
+    <t>2026-02-24T03:10:43.2980419+08:00</t>
+  </si>
+  <si>
+    <t>ee31294f-7d79-4cc2-a344-e0a3f0784aae</t>
   </si>
   <si>
     <t>CIF-4WC-0252</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472704+08:00</t>
-  </si>
-  <si>
-    <t>7089daa8-9583-471f-8df0-005bf714a63b</t>
+    <t>2026-02-24T03:10:43.2980480+08:00</t>
+  </si>
+  <si>
+    <t>59c7335c-2c3a-45c6-8887-46714b2f495d</t>
   </si>
   <si>
     <t>CIF-AVS20D-0613</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472740+08:00</t>
-  </si>
-  <si>
-    <t>61c3190c-a9e5-43b1-89bb-ecdcab4ccbe6</t>
+    <t>2026-02-24T03:10:43.2980547+08:00</t>
+  </si>
+  <si>
+    <t>da379b37-30dc-41b5-96a9-18271c11f83f</t>
   </si>
   <si>
     <t>CIF-T00PU37(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472775+08:00</t>
-  </si>
-  <si>
-    <t>5b65ac03-19f0-4a11-8d88-1e3771b0f4e6</t>
+    <t>2026-02-24T03:10:43.2980618+08:00</t>
+  </si>
+  <si>
+    <t>a1644040-59a7-4811-9ff9-f49e07c163ce</t>
   </si>
   <si>
     <t>CIF-CRLL-0413</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472813+08:00</t>
-  </si>
-  <si>
-    <t>76c7d514-d9d5-44bb-9747-7d0a83145ee4</t>
+    <t>2026-02-24T03:10:43.2980685+08:00</t>
+  </si>
+  <si>
+    <t>7c5bd49d-dd30-42f7-9c1f-7961a4490ba5</t>
   </si>
   <si>
     <t>CIF-NC-0225</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472848+08:00</t>
-  </si>
-  <si>
-    <t>f328d934-43e4-4d37-9421-508f76c65c62</t>
+    <t>2026-02-24T03:10:43.2980747+08:00</t>
+  </si>
+  <si>
+    <t>05e565f7-0410-49fd-8ab3-a6fd4736bde7</t>
   </si>
   <si>
     <t>CIF-T00PU187(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472883+08:00</t>
-  </si>
-  <si>
-    <t>6a9dec6f-09d0-4711-a455-0246403b6958</t>
+    <t>2026-02-24T03:10:43.2980819+08:00</t>
+  </si>
+  <si>
+    <t>5bf1a76b-0f48-4bdb-9458-fcb89bbb6f29</t>
   </si>
   <si>
     <t>CIF-DCC-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472922+08:00</t>
-  </si>
-  <si>
-    <t>1fe4222c-3710-40da-bd83-279f24c670f4</t>
+    <t>2026-02-24T03:10:43.2980884+08:00</t>
+  </si>
+  <si>
+    <t>d3dc9e01-4f56-43e5-98e6-c57dcb83e765</t>
   </si>
   <si>
     <t>CIF-T00PU22(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472956+08:00</t>
-  </si>
-  <si>
-    <t>ac095974-6bdc-4e3e-96bd-7f1aedbf3128</t>
+    <t>2026-02-24T03:10:43.2980950+08:00</t>
+  </si>
+  <si>
+    <t>dd22ef11-2a2b-44aa-b69e-8ca83d6d8ead</t>
   </si>
   <si>
     <t>CIF-T00PU12(Yellow)-0113</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7472991+08:00</t>
-  </si>
-  <si>
-    <t>4b733fb2-92a1-48a4-b0df-2a42885beb21</t>
+    <t>2026-02-24T03:10:43.2981017+08:00</t>
+  </si>
+  <si>
+    <t>89e8a4b2-b2c6-4be4-83c2-f5e414eafbbe</t>
   </si>
   <si>
     <t>CIF-BCV-0232</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7473031+08:00</t>
-  </si>
-  <si>
-    <t>b1c71c3c-553c-415a-bb1f-c7c498b6d82e</t>
+    <t>2026-02-24T03:10:43.2981085+08:00</t>
+  </si>
+  <si>
+    <t>5b709bd3-5fa3-4ec8-9d2b-49198c99d1a3</t>
   </si>
   <si>
     <t>CIF-CRLL-0213</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7473065+08:00</t>
-  </si>
-  <si>
-    <t>f51c0850-0219-474d-aa52-aebc1d539173</t>
+    <t>2026-02-24T03:10:43.2981150+08:00</t>
+  </si>
+  <si>
+    <t>a0c805df-d6cf-458a-b1c2-57b96b6d82e1</t>
   </si>
   <si>
     <t>CIF-CTW-0159</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7473100+08:00</t>
-  </si>
-  <si>
-    <t>d949bb70-3905-434e-93d8-a34895691620</t>
+    <t>2026-02-24T03:10:43.2981219+08:00</t>
+  </si>
+  <si>
+    <t>3b50bfc4-23f5-4ce4-813d-2d857be6d982</t>
   </si>
   <si>
     <t>ED-CF-R45</t>
@@ -1212,10 +1204,10 @@
     <t>Finished Goods</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7416462+08:00</t>
-  </si>
-  <si>
-    <t>cbef9b31-d4f5-4394-88af-67f5ab04cc3d</t>
+    <t>2026-02-24T03:10:43.2897288+08:00</t>
+  </si>
+  <si>
+    <t>edd3a1d1-82c9-49bc-b966-ea77e6065921</t>
   </si>
   <si>
     <t>ED-CF-R55</t>
@@ -1224,37 +1216,37 @@
     <t>Imported plan quantity: 800.00</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7426097+08:00</t>
-  </si>
-  <si>
-    <t>b9c5743d-22ba-4c33-85b3-e0b82595df01</t>
+    <t>2026-02-24T03:10:43.2906703+08:00</t>
+  </si>
+  <si>
+    <t>189b5305-3f6f-4fe6-a7bb-da209e30163f</t>
   </si>
   <si>
     <t>ED-CF-R65</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7426243+08:00</t>
-  </si>
-  <si>
-    <t>8d2a6b20-bd6b-46e8-a2d6-4218d772b27d</t>
+    <t>2026-02-24T03:10:43.2906899+08:00</t>
+  </si>
+  <si>
+    <t>7f277ebe-e4e2-4347-9cc3-84f962e704e9</t>
   </si>
   <si>
     <t>ED-CF-R80</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7426302+08:00</t>
-  </si>
-  <si>
-    <t>61c8a970-ab46-49ad-a4b7-4d807caafc63</t>
+    <t>2026-02-24T03:10:43.2907091+08:00</t>
+  </si>
+  <si>
+    <t>867214dd-82ad-438d-99c6-f6c9d13341c2</t>
   </si>
   <si>
     <t>ED-CF-R85</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428672+08:00</t>
-  </si>
-  <si>
-    <t>5e6dbead-3b7e-4e0d-b71d-5f326f852294</t>
+    <t>2026-02-24T03:10:43.2909731+08:00</t>
+  </si>
+  <si>
+    <t>8ab9bfe8-3027-41b8-a161-ef18a9d0aa67</t>
   </si>
   <si>
     <t>ED-UC-R20</t>
@@ -1263,415 +1255,415 @@
     <t>Imported plan quantity: 700.00</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428718+08:00</t>
-  </si>
-  <si>
-    <t>a7abfe9b-e44f-4660-bde9-8bdc00c0d84a</t>
+    <t>2026-02-24T03:10:43.2909810+08:00</t>
+  </si>
+  <si>
+    <t>bdf9cae9-417d-423e-ba45-e4deccd782e0</t>
   </si>
   <si>
     <t>ED-UC-R30</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428748+08:00</t>
-  </si>
-  <si>
-    <t>5a865fb0-adc9-4f3b-8c7f-493a612c3a07</t>
+    <t>2026-02-24T03:10:43.2909867+08:00</t>
+  </si>
+  <si>
+    <t>804a5294-d9db-4661-ab42-24e75362a891</t>
   </si>
   <si>
     <t>ED-UC-R35</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428787+08:00</t>
-  </si>
-  <si>
-    <t>1262cfb6-5990-4437-9c41-0625b157e894</t>
+    <t>2026-02-24T03:10:43.2909935+08:00</t>
+  </si>
+  <si>
+    <t>3a239873-da6b-473c-972d-29b8224447ee</t>
   </si>
   <si>
     <t>ED-UC-R40</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428827+08:00</t>
-  </si>
-  <si>
-    <t>bfed8a58-b751-4f00-8663-5938c980b611</t>
+    <t>2026-02-24T03:10:43.2910010+08:00</t>
+  </si>
+  <si>
+    <t>3628cab7-5712-4bbf-896b-b20bc8cecf47</t>
   </si>
   <si>
     <t>ED-UC-R45</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428859+08:00</t>
-  </si>
-  <si>
-    <t>49410a88-c6f4-483f-b0d0-c8a07f9252d8</t>
+    <t>2026-02-24T03:10:43.2910066+08:00</t>
+  </si>
+  <si>
+    <t>bcc12d9c-1474-4c07-9f0e-7612da7181d3</t>
   </si>
   <si>
     <t>ED-UC-R65</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428895+08:00</t>
-  </si>
-  <si>
-    <t>da5fa94c-fb9b-4850-8db6-8ef575c82c84</t>
+    <t>2026-02-24T03:10:43.2910121+08:00</t>
+  </si>
+  <si>
+    <t>98c1c0c3-2a48-46c2-8c43-2f52c05c6a6e</t>
   </si>
   <si>
     <t>IB-6002</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428920+08:00</t>
-  </si>
-  <si>
-    <t>a06ffd4b-c893-4dc1-b91b-8b1cdae30d9f</t>
+    <t>2026-02-24T03:10:43.2910178+08:00</t>
+  </si>
+  <si>
+    <t>ff707bd6-cfcc-4ece-8f77-2caf5eb77f9b</t>
   </si>
   <si>
     <t>IC-1181</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428942+08:00</t>
-  </si>
-  <si>
-    <t>64cac8a3-d839-46aa-8690-4e9a0deaede1</t>
+    <t>2026-02-24T03:10:43.2910229+08:00</t>
+  </si>
+  <si>
+    <t>1c91bf87-3bc9-42f3-8687-c06e1789f638</t>
   </si>
   <si>
     <t>IC-1182</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428967+08:00</t>
-  </si>
-  <si>
-    <t>29e5050b-9ea1-47a4-bff4-7a4cf087bade</t>
+    <t>2026-02-24T03:10:43.2910280+08:00</t>
+  </si>
+  <si>
+    <t>da98619f-f3e5-44d5-b8e4-a4ad2e4ca4ff</t>
   </si>
   <si>
     <t>IC-1200</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7428994+08:00</t>
-  </si>
-  <si>
-    <t>74f625b8-eda5-4d53-b42f-59ef9dc8f596</t>
+    <t>2026-02-24T03:10:43.2910338+08:00</t>
+  </si>
+  <si>
+    <t>b3c9046f-706d-46c4-884a-63dfc0d053b5</t>
   </si>
   <si>
     <t>IC-1220</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429027+08:00</t>
-  </si>
-  <si>
-    <t>acf33b8c-6eb7-4174-9f0b-8ae2bae3d249</t>
+    <t>2026-02-24T03:10:43.2910406+08:00</t>
+  </si>
+  <si>
+    <t>748b2b18-4952-47bf-b165-f9552bd39a34</t>
   </si>
   <si>
     <t>IC-1240</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429056+08:00</t>
-  </si>
-  <si>
-    <t>5a0b5e3c-c382-4247-804e-827d8189df15</t>
+    <t>2026-02-24T03:10:43.2910496+08:00</t>
+  </si>
+  <si>
+    <t>a36de3d3-9812-483d-8a4f-9e970352e5b7</t>
   </si>
   <si>
     <t>IF-2003</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429088+08:00</t>
-  </si>
-  <si>
-    <t>41528ed0-55d8-487e-8dd1-46e29e2b5e81</t>
+    <t>2026-02-24T03:10:43.2910556+08:00</t>
+  </si>
+  <si>
+    <t>dce25db1-d188-4fef-9538-683f5b8456e1</t>
   </si>
   <si>
     <t>IF-2005</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429118+08:00</t>
-  </si>
-  <si>
-    <t>ae4cdf60-ae10-4dcf-9f64-c838c296e0d3</t>
+    <t>2026-02-24T03:10:43.2910616+08:00</t>
+  </si>
+  <si>
+    <t>78ff0a5d-4a2f-4e34-ac87-c385d5c77feb</t>
   </si>
   <si>
     <t>IF-2007</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429149+08:00</t>
-  </si>
-  <si>
-    <t>d2b1c485-170f-4906-98de-5679c0b7a292</t>
+    <t>2026-02-24T03:10:43.2910667+08:00</t>
+  </si>
+  <si>
+    <t>e495c217-b8f0-4784-a3f5-ab98b0b7158b</t>
   </si>
   <si>
     <t>IF-2008</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429173+08:00</t>
-  </si>
-  <si>
-    <t>db397c11-70f2-4379-bad2-a112188b0211</t>
+    <t>2026-02-24T03:10:43.2910720+08:00</t>
+  </si>
+  <si>
+    <t>44811c75-fc4a-4dc3-86b4-30af41459876</t>
   </si>
   <si>
     <t>IF-2022</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429196+08:00</t>
-  </si>
-  <si>
-    <t>20e9c9e0-986c-425f-955a-4beb7e9e221b</t>
+    <t>2026-02-24T03:10:43.2910769+08:00</t>
+  </si>
+  <si>
+    <t>e3196185-523c-4cb0-b833-f5d7a159b03b</t>
   </si>
   <si>
     <t>IF-2023</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429221+08:00</t>
-  </si>
-  <si>
-    <t>84641271-a11a-4ab6-94c4-2ec8f1dd0f0c</t>
+    <t>2026-02-24T03:10:43.2910828+08:00</t>
+  </si>
+  <si>
+    <t>741251b5-1cfb-46c7-a733-37a1ff22d51c</t>
   </si>
   <si>
     <t>IF-2027</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429251+08:00</t>
-  </si>
-  <si>
-    <t>36e1c734-2cc3-4a02-82ad-7f9597769b3c</t>
+    <t>2026-02-24T03:10:43.2910883+08:00</t>
+  </si>
+  <si>
+    <t>cd37732a-d0f4-4de0-bfb8-f1c0194501da</t>
   </si>
   <si>
     <t>IF-2030</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429274+08:00</t>
-  </si>
-  <si>
-    <t>2a5295fd-1cf3-4795-a436-a2cd8b590931</t>
+    <t>2026-02-24T03:10:43.2910937+08:00</t>
+  </si>
+  <si>
+    <t>b4401841-b5a8-4bcc-bdcc-f97ea5d80d8f</t>
   </si>
   <si>
     <t>IF-2079A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429298+08:00</t>
-  </si>
-  <si>
-    <t>79680452-647f-42ad-8491-9ce41d28a783</t>
+    <t>2026-02-24T03:10:43.2910987+08:00</t>
+  </si>
+  <si>
+    <t>984bead1-8690-467d-bd33-132922395be9</t>
   </si>
   <si>
     <t>IF-6001</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429329+08:00</t>
-  </si>
-  <si>
-    <t>803b2deb-7a90-432f-b7a0-8e785ab33f19</t>
+    <t>2026-02-24T03:10:43.2911038+08:00</t>
+  </si>
+  <si>
+    <t>598ba765-9cc7-4d7b-a93c-c0b514b27e1e</t>
   </si>
   <si>
     <t>IF-6002</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429373+08:00</t>
-  </si>
-  <si>
-    <t>3dc2af89-6e67-4e43-8cb4-10640f51acb1</t>
+    <t>2026-02-24T03:10:43.2911104+08:00</t>
+  </si>
+  <si>
+    <t>0f84fe54-527f-44f8-bffa-4e1591bd2d4f</t>
   </si>
   <si>
     <t>IF-6006</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429403+08:00</t>
-  </si>
-  <si>
-    <t>c8acac01-e0fd-4c40-b701-b16bd28b299e</t>
+    <t>2026-02-24T03:10:43.2911163+08:00</t>
+  </si>
+  <si>
+    <t>17990e09-15fb-4c20-a8e3-64fb12648b6d</t>
   </si>
   <si>
     <t>IF-6023</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429437+08:00</t>
-  </si>
-  <si>
-    <t>839fc9ee-aea3-481d-a349-acda6b3cc189</t>
+    <t>2026-02-24T03:10:43.2911226+08:00</t>
+  </si>
+  <si>
+    <t>c0510348-5852-4859-b796-c8faae8be8e2</t>
   </si>
   <si>
     <t>IF-6030</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429461+08:00</t>
-  </si>
-  <si>
-    <t>d3d4f475-eb46-47c1-b92b-99a679b6e69a</t>
+    <t>2026-02-24T03:10:43.2911305+08:00</t>
+  </si>
+  <si>
+    <t>827283f9-c34f-4778-b66c-e5da8d790d8d</t>
   </si>
   <si>
     <t>IF-BR-001</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429498+08:00</t>
-  </si>
-  <si>
-    <t>4a9facf7-0ccb-460c-8cb5-3f4c12bb0b09</t>
+    <t>2026-02-24T03:10:43.2911367+08:00</t>
+  </si>
+  <si>
+    <t>1d2270d8-b083-4fe0-a121-fabede10cb49</t>
   </si>
   <si>
     <t>ISP-09</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429526+08:00</t>
-  </si>
-  <si>
-    <t>209b5adf-a927-4a46-b64a-db6cd0483a4f</t>
+    <t>2026-02-24T03:10:43.2911425+08:00</t>
+  </si>
+  <si>
+    <t>bb6f4ebc-a254-4d12-94d4-2d1d50ee1749</t>
   </si>
   <si>
     <t>NE-02</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429552+08:00</t>
-  </si>
-  <si>
-    <t>360fc072-a1fa-4cc2-b344-258df8ad960b</t>
+    <t>2026-02-24T03:10:43.2911474+08:00</t>
+  </si>
+  <si>
+    <t>9c825974-66c0-4e50-8dad-9c44d1e173cc</t>
   </si>
   <si>
     <t>PT-2075</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429575+08:00</t>
-  </si>
-  <si>
-    <t>e1a1a943-cc7b-4e0e-aad3-4843e876c6a3</t>
+    <t>2026-02-24T03:10:43.2911525+08:00</t>
+  </si>
+  <si>
+    <t>b639a0b9-2385-49be-9a90-1f432811dc1b</t>
   </si>
   <si>
     <t>PT-2150</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429605+08:00</t>
-  </si>
-  <si>
-    <t>3cb1d359-306c-4bd4-b963-2b899832e522</t>
+    <t>2026-02-24T03:10:43.2911576+08:00</t>
+  </si>
+  <si>
+    <t>96d019f1-924f-4057-86a2-f0258a87574d</t>
   </si>
   <si>
     <t>PT-2200</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429627+08:00</t>
-  </si>
-  <si>
-    <t>478996ac-988c-4ae8-988d-323ed9875b40</t>
+    <t>2026-02-24T03:10:43.2911631+08:00</t>
+  </si>
+  <si>
+    <t>ed1603d1-3f75-48c5-b472-ffc7523b055c</t>
   </si>
   <si>
     <t>PT-3150</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429656+08:00</t>
-  </si>
-  <si>
-    <t>ce27db59-fe81-4e58-a228-4061089f0e89</t>
+    <t>2026-02-24T03:10:43.2911687+08:00</t>
+  </si>
+  <si>
+    <t>02ba96a1-3282-46b6-bcba-e7aa4b9664b5</t>
   </si>
   <si>
     <t>SCP-01</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429693+08:00</t>
-  </si>
-  <si>
-    <t>43337de8-4a3a-4274-ade5-4e4b7b6fed88</t>
+    <t>2026-02-24T03:10:43.2911757+08:00</t>
+  </si>
+  <si>
+    <t>cebc1d15-a3d4-40a6-85c2-304c23de80cc</t>
   </si>
   <si>
     <t>SM000010A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429722+08:00</t>
-  </si>
-  <si>
-    <t>163884ee-9712-43fb-8589-30565bcf92f3</t>
+    <t>2026-02-24T03:10:43.2911817+08:00</t>
+  </si>
+  <si>
+    <t>5cc510e2-2455-4eb5-b53d-a70c3a6673f8</t>
   </si>
   <si>
     <t>SM000010B</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429745+08:00</t>
-  </si>
-  <si>
-    <t>c67291d9-b773-4cb6-9b37-19b42f4ead47</t>
+    <t>2026-02-24T03:10:43.2911870+08:00</t>
+  </si>
+  <si>
+    <t>04e68b3d-760c-4f5b-8304-96f66bb92a47</t>
   </si>
   <si>
     <t>SM000011A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429770+08:00</t>
-  </si>
-  <si>
-    <t>9aa8a227-05c6-4363-bfd9-829e60f871b3</t>
+    <t>2026-02-24T03:10:43.2911923+08:00</t>
+  </si>
+  <si>
+    <t>3a3da571-e0d3-44a9-812a-fb5612cdb4a8</t>
   </si>
   <si>
     <t>SM000011ARA</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429795+08:00</t>
-  </si>
-  <si>
-    <t>63b180f5-518c-42b3-a7e0-bab44dc0308d</t>
+    <t>2026-02-24T03:10:43.2911975+08:00</t>
+  </si>
+  <si>
+    <t>93e332af-d7b5-44a3-be50-8a3cc3b536ab</t>
   </si>
   <si>
     <t>SM000011ARB</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429821+08:00</t>
-  </si>
-  <si>
-    <t>e224a1ce-f87c-4177-93d6-6e498e645df8</t>
+    <t>2026-02-24T03:10:43.2912031+08:00</t>
+  </si>
+  <si>
+    <t>f58c8148-eb28-4f0d-b480-311306b2f150</t>
   </si>
   <si>
     <t>SM000011B</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429844+08:00</t>
-  </si>
-  <si>
-    <t>7c52462c-d567-484b-8750-717a584ee19c</t>
+    <t>2026-02-24T03:10:43.2912084+08:00</t>
+  </si>
+  <si>
+    <t>9b1a59d6-92b3-437f-ae60-3c9332644bcc</t>
   </si>
   <si>
     <t>SM000012A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429867+08:00</t>
-  </si>
-  <si>
-    <t>b73f9f33-08ba-4fc0-bc7c-12adb057fbeb</t>
+    <t>2026-02-24T03:10:43.2912136+08:00</t>
+  </si>
+  <si>
+    <t>dcf5840d-b1e8-4060-b99b-ac292589832b</t>
   </si>
   <si>
     <t>SM000012ARB</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429890+08:00</t>
-  </si>
-  <si>
-    <t>83c7fafe-ec40-4237-8c85-c42d1cf74a3b</t>
+    <t>2026-02-24T03:10:43.2912188+08:00</t>
+  </si>
+  <si>
+    <t>9e787bd8-50f3-432b-8f9a-6bb469857194</t>
   </si>
   <si>
     <t>SM000012B</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429917+08:00</t>
-  </si>
-  <si>
-    <t>34ddb3ff-8377-43ae-8309-442d630d36c7</t>
+    <t>2026-02-24T03:10:43.2912246+08:00</t>
+  </si>
+  <si>
+    <t>240a8fe8-aaf2-4ec8-895e-1112dd6f9a93</t>
   </si>
   <si>
     <t>SM000014</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429939+08:00</t>
-  </si>
-  <si>
-    <t>298bd2ad-8887-43a9-a924-4a2d5d2ff89b</t>
+    <t>2026-02-24T03:10:43.2912300+08:00</t>
+  </si>
+  <si>
+    <t>9c529c46-0836-4c20-a290-5ccff53fa345</t>
   </si>
   <si>
     <t>SM000017A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429964+08:00</t>
-  </si>
-  <si>
-    <t>f4c79fc6-98d0-4e1a-a588-0f3161e2b408</t>
+    <t>2026-02-24T03:10:43.2912349+08:00</t>
+  </si>
+  <si>
+    <t>6b1e4a49-8f77-4c07-90c0-4db720ca93b9</t>
   </si>
   <si>
     <t>SM000017B</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7429995+08:00</t>
-  </si>
-  <si>
-    <t>bbeaa165-4ae2-4526-9e53-a1b8437ef074</t>
+    <t>2026-02-24T03:10:43.2912401+08:00</t>
+  </si>
+  <si>
+    <t>a52382fd-b35a-4ecf-a68e-a8c365246b4f</t>
   </si>
   <si>
     <t>SM000019</t>
@@ -1680,241 +1672,241 @@
     <t>Imported plan quantity: 600.00</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430021+08:00</t>
-  </si>
-  <si>
-    <t>14dde3ad-e24c-489d-b464-962604d8b957</t>
+    <t>2026-02-24T03:10:43.2912464+08:00</t>
+  </si>
+  <si>
+    <t>294705b4-63c4-4e1a-b65e-3af116da45cf</t>
   </si>
   <si>
     <t>SM000020</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430045+08:00</t>
-  </si>
-  <si>
-    <t>588f8d5c-3705-4267-90f7-cbbbb6bf2eb0</t>
+    <t>2026-02-24T03:10:43.2912516+08:00</t>
+  </si>
+  <si>
+    <t>2d426794-ccaa-44fa-924a-923b5a0cf5cb</t>
   </si>
   <si>
     <t>SM000021</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430068+08:00</t>
-  </si>
-  <si>
-    <t>663ff458-8a13-43bf-8339-95aeff9ff3fb</t>
+    <t>2026-02-24T03:10:43.2912568+08:00</t>
+  </si>
+  <si>
+    <t>e7bad20f-a086-4d5e-a564-9b0e102d9920</t>
   </si>
   <si>
     <t>SM000022</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430099+08:00</t>
-  </si>
-  <si>
-    <t>f278ef20-0be0-4af1-9242-03fa7716b65b</t>
+    <t>2026-02-24T03:10:43.2912624+08:00</t>
+  </si>
+  <si>
+    <t>b95882ed-6682-492e-aa48-c6dbcfb33eae</t>
   </si>
   <si>
     <t>SM000023</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430124+08:00</t>
-  </si>
-  <si>
-    <t>7ef48ce7-3e97-4eab-9b45-86c09334ed4c</t>
+    <t>2026-02-24T03:10:43.2912682+08:00</t>
+  </si>
+  <si>
+    <t>eb77333a-3ad6-46de-a3f0-372fad7fbe08</t>
   </si>
   <si>
     <t>SM000028</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430146+08:00</t>
-  </si>
-  <si>
-    <t>f9c509a1-b575-4770-9d72-4b8fc2e69a17</t>
+    <t>2026-02-24T03:10:43.2912734+08:00</t>
+  </si>
+  <si>
+    <t>d2512ed1-cace-4d27-8c26-b9fc1f13647e</t>
   </si>
   <si>
     <t>SM000030BIF-NRFIT</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430172+08:00</t>
-  </si>
-  <si>
-    <t>993847b4-4ecd-4352-a7a9-e4b093a58d8c</t>
+    <t>2026-02-24T03:10:43.2912786+08:00</t>
+  </si>
+  <si>
+    <t>2d1244a9-6ce2-4aa1-b5da-2ec80f26cd71</t>
   </si>
   <si>
     <t>SM000035</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430200+08:00</t>
-  </si>
-  <si>
-    <t>0c4ee421-db14-424a-b12f-dbfaf5dd96e9</t>
+    <t>2026-02-24T03:10:43.2912837+08:00</t>
+  </si>
+  <si>
+    <t>4270d5fa-d43d-45e5-9557-55624ac7e173</t>
   </si>
   <si>
     <t>SM000062</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430226+08:00</t>
-  </si>
-  <si>
-    <t>cbaf1559-3163-43fc-a13f-4233e574ff8c</t>
+    <t>2026-02-24T03:10:43.2912897+08:00</t>
+  </si>
+  <si>
+    <t>f06591a2-656d-49b2-80a6-004a62bdb5e7</t>
   </si>
   <si>
     <t>SM000063</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430252+08:00</t>
-  </si>
-  <si>
-    <t>ab976f3f-62b6-41ac-9c1d-3787c5f3cff1</t>
+    <t>2026-02-24T03:10:43.2912952+08:00</t>
+  </si>
+  <si>
+    <t>09321a50-354f-4ffa-9475-ecc0c711a0d2</t>
   </si>
   <si>
     <t>SM000078</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430277+08:00</t>
-  </si>
-  <si>
-    <t>04bdbe8c-708b-4852-99cd-542833893ae1</t>
+    <t>2026-02-24T03:10:43.2913004+08:00</t>
+  </si>
+  <si>
+    <t>54836a3b-84bd-45ca-ab60-997b413e59b3</t>
   </si>
   <si>
     <t>SM000082WPU</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430305+08:00</t>
-  </si>
-  <si>
-    <t>b266a49e-01ea-46a6-93dc-97d815e2ec21</t>
+    <t>2026-02-24T03:10:43.2913056+08:00</t>
+  </si>
+  <si>
+    <t>478b700f-824d-4bcb-8bb2-d38f247def22</t>
   </si>
   <si>
     <t>SM000087WPU</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430355+08:00</t>
-  </si>
-  <si>
-    <t>7beff6f2-881d-412e-bdf4-fee2515fd6f3</t>
+    <t>2026-02-24T03:10:43.2913139+08:00</t>
+  </si>
+  <si>
+    <t>958acd45-8ae3-45f3-b519-80f04b9207e1</t>
   </si>
   <si>
     <t>SM000090</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430389+08:00</t>
-  </si>
-  <si>
-    <t>722a40c4-1e39-44a7-8620-eb62fb82f9ab</t>
+    <t>2026-02-24T03:10:43.2913200+08:00</t>
+  </si>
+  <si>
+    <t>11e81e7b-5dda-4b67-8370-bf21d0a92d5f</t>
   </si>
   <si>
     <t>SM000161B</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430414+08:00</t>
-  </si>
-  <si>
-    <t>94e49bc2-f5d9-42c0-872b-54f54f24d0b5</t>
+    <t>2026-02-24T03:10:43.2913254+08:00</t>
+  </si>
+  <si>
+    <t>8e305652-2880-494b-b3eb-3eb18f36da98</t>
   </si>
   <si>
     <t>SM000200AG</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430437+08:00</t>
-  </si>
-  <si>
-    <t>c0e65d9e-f8c5-455f-808c-850fefd9e2f9</t>
+    <t>2026-02-24T03:10:43.2913307+08:00</t>
+  </si>
+  <si>
+    <t>71f84414-a93e-4d33-8286-e6fbf9e8a59d</t>
   </si>
   <si>
     <t>SM000200AG82WPU</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430465+08:00</t>
-  </si>
-  <si>
-    <t>e286893e-11db-4aef-8b01-205f00d7bf88</t>
+    <t>2026-02-24T03:10:43.2913360+08:00</t>
+  </si>
+  <si>
+    <t>a266ecc4-5d20-408a-a00c-20ab89e83d63</t>
   </si>
   <si>
     <t>SM000230AG</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430489+08:00</t>
-  </si>
-  <si>
-    <t>38a97d47-9d1c-41f5-ba5c-96c6966fb598</t>
+    <t>2026-02-24T03:10:43.2913418+08:00</t>
+  </si>
+  <si>
+    <t>76b08926-6d13-4731-94c2-e7965804c5db</t>
   </si>
   <si>
     <t>SM000230AG3EX</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430512+08:00</t>
-  </si>
-  <si>
-    <t>ed5777ad-a1f6-4ca9-ae18-62320493801a</t>
+    <t>2026-02-24T03:10:43.2913472+08:00</t>
+  </si>
+  <si>
+    <t>a42eb205-72cb-43a6-9f9c-51fefd0aadba</t>
   </si>
   <si>
     <t>TR-SB-002</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430536+08:00</t>
-  </si>
-  <si>
-    <t>23a63b2f-27b9-4a6b-921f-23332b741c19</t>
+    <t>2026-02-24T03:10:43.2913528+08:00</t>
+  </si>
+  <si>
+    <t>719172c6-d047-48a9-9352-f1cad24b988a</t>
   </si>
   <si>
     <t>TW-001</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430566+08:00</t>
-  </si>
-  <si>
-    <t>5b8284ba-e21c-47f3-b3ed-c2371d3c69c4</t>
+    <t>2026-02-24T03:10:43.2913580+08:00</t>
+  </si>
+  <si>
+    <t>0c573a96-4f75-4a85-a4f8-7a0ac206b642</t>
   </si>
   <si>
     <t>TW-002</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430590+08:00</t>
-  </si>
-  <si>
-    <t>2b076bf3-ae6a-4c2a-8573-7cca782ee787</t>
+    <t>2026-02-24T03:10:43.2913639+08:00</t>
+  </si>
+  <si>
+    <t>059ed21f-e413-4e48-add8-a0924a372872</t>
   </si>
   <si>
     <t>TW-003</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430614+08:00</t>
-  </si>
-  <si>
-    <t>ee13e887-7652-48ab-9d3c-afaa2b438365</t>
+    <t>2026-02-24T03:10:43.2913693+08:00</t>
+  </si>
+  <si>
+    <t>22d9f75e-30c2-47fe-a648-38e3f2a1c5b7</t>
   </si>
   <si>
     <t>UB-TV-2000</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430638+08:00</t>
-  </si>
-  <si>
-    <t>72c9fe70-8868-4380-8e98-0f004de17d61</t>
+    <t>2026-02-24T03:10:43.2913745+08:00</t>
+  </si>
+  <si>
+    <t>228911a4-a22c-48d1-9724-79a540065ae2</t>
   </si>
   <si>
     <t>Grand Total</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7430667+08:00</t>
-  </si>
-  <si>
-    <t>27690a44-1a75-462a-b1c9-6f1518931eb0</t>
+    <t>2026-02-24T03:10:43.2913803+08:00</t>
+  </si>
+  <si>
+    <t>38afb5ac-d705-4a00-892a-b402b65371c2</t>
   </si>
   <si>
     <t>NE-02A</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7452395+08:00</t>
-  </si>
-  <si>
-    <t>e1c1821a-c7aa-4d0c-9865-ea51603639c9</t>
+    <t>2026-02-24T03:10:43.2945834+08:00</t>
+  </si>
+  <si>
+    <t>d3673ada-7509-4bdd-9519-ceadefdcc626</t>
   </si>
   <si>
     <t>SM000030BIF (NR-FIT)</t>
   </si>
   <si>
-    <t>2026-02-24T03:06:24.7458843+08:00</t>
+    <t>2026-02-24T03:10:43.2958043+08:00</t>
   </si>
   <si>
     <t>ProductId</t>
@@ -1926,1738 +1918,1738 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>ce8f00bb-08e7-421d-94f7-d5eb94aa0a18</t>
-  </si>
-  <si>
-    <t>c4f612d5-376a-4d36-80da-453174b53125</t>
-  </si>
-  <si>
-    <t>f03d1cf5-8924-42bc-9789-1a3a913c2618</t>
-  </si>
-  <si>
-    <t>50bd30b6-6a14-40eb-98d2-0163d9da9d46</t>
-  </si>
-  <si>
-    <t>00439f71-b249-4673-a9a4-4b768de6e75e</t>
-  </si>
-  <si>
-    <t>9ac4547f-3d2e-41b7-9679-18349d2cd080</t>
-  </si>
-  <si>
-    <t>b94127de-4b83-41bc-b0b4-8db08958d918</t>
-  </si>
-  <si>
-    <t>a431c657-95d7-4a1e-ad36-a392cc055a7d</t>
-  </si>
-  <si>
-    <t>72c3a8b1-aeee-4cc1-a3c4-144db0139ed6</t>
-  </si>
-  <si>
-    <t>7f56f482-1ec1-4883-bc0f-7346b257fcb8</t>
-  </si>
-  <si>
-    <t>1a9f173c-075c-419a-a69d-f22c2bc24578</t>
-  </si>
-  <si>
-    <t>5e2ecffb-0f81-4c13-b039-2a4070cb66fc</t>
-  </si>
-  <si>
-    <t>e1ddc124-b3b0-4104-b1c9-3464f94a4e41</t>
-  </si>
-  <si>
-    <t>3055f324-a3b8-4f53-bce5-7c775f5d706c</t>
-  </si>
-  <si>
-    <t>daac0c34-0dae-4ed2-a0fa-8b4a47183fe5</t>
-  </si>
-  <si>
-    <t>008cd117-e8f2-4348-938b-2e31c6f0cb31</t>
-  </si>
-  <si>
-    <t>980e1d28-6bb6-4def-b803-b654881590de</t>
-  </si>
-  <si>
-    <t>455f6a01-48cc-44d8-a91d-1dbfe8bdae87</t>
-  </si>
-  <si>
-    <t>a3f5df1a-d050-410d-b293-f5db2c76fb74</t>
-  </si>
-  <si>
-    <t>1e250d6a-4ad4-4fbd-bcf5-04cdeb8993d2</t>
-  </si>
-  <si>
-    <t>5987c031-1552-4652-834f-ba99f7a1ead4</t>
-  </si>
-  <si>
-    <t>009472e5-b81c-4fd4-8f74-5fde02262d49</t>
-  </si>
-  <si>
-    <t>44bad27f-4db3-4d7f-b6a5-42215f5dc70e</t>
-  </si>
-  <si>
-    <t>6ff83d75-f1d0-4381-944e-2e9e3edeccc7</t>
-  </si>
-  <si>
-    <t>e96f3099-7727-4324-9e70-b32cab4940fb</t>
-  </si>
-  <si>
-    <t>0edd2425-4fc3-4226-9934-df5da16f8a78</t>
-  </si>
-  <si>
-    <t>2a4fd9cc-4f67-41a4-8b01-72ddc7da7d56</t>
-  </si>
-  <si>
-    <t>090f1791-c673-4d13-b811-98434b2b838a</t>
-  </si>
-  <si>
-    <t>f18ed439-00ad-4e7e-a2cd-16af0c2a92ba</t>
-  </si>
-  <si>
-    <t>8414e581-f666-4748-96d4-1519d9d3f07e</t>
-  </si>
-  <si>
-    <t>0055bb40-e277-4e18-95e5-f081de9434c9</t>
-  </si>
-  <si>
-    <t>73459e45-f6c3-4c64-9e9b-7e2eb85ed267</t>
-  </si>
-  <si>
-    <t>dfe28758-fcb1-4351-938f-216c72840340</t>
-  </si>
-  <si>
-    <t>36b40d5f-760d-4dc4-890b-80d589a1b3cd</t>
-  </si>
-  <si>
-    <t>9dbcef12-f43e-4a7a-bb5d-bf2ccc3214ec</t>
-  </si>
-  <si>
-    <t>500b440e-6e84-44cd-87ac-157910210634</t>
-  </si>
-  <si>
-    <t>e089e96c-4737-4536-9723-04830013a26c</t>
-  </si>
-  <si>
-    <t>aebb5f33-978d-47f5-b916-3ef4da4fd14e</t>
-  </si>
-  <si>
-    <t>58c466ca-4eb5-4c17-892c-71d2debcb940</t>
-  </si>
-  <si>
-    <t>d42420df-c4ce-449e-9e3c-a6798602bcf6</t>
-  </si>
-  <si>
-    <t>ad171bd4-cdac-4b14-b6c3-9a5e9f8f8bc0</t>
-  </si>
-  <si>
-    <t>2bf2d69b-0da6-4240-8dcc-75cd73965dac</t>
-  </si>
-  <si>
-    <t>409519bd-3625-4cf6-aa32-f67b513770f2</t>
-  </si>
-  <si>
-    <t>d1d77b03-c389-45db-af26-02db969e493c</t>
-  </si>
-  <si>
-    <t>7093ee52-6d1d-4ed7-a7d3-ac9dcb3b32ec</t>
-  </si>
-  <si>
-    <t>995edb2d-1035-4de0-bbce-b8e6a83fa9a2</t>
-  </si>
-  <si>
-    <t>1b3bba50-c666-41f4-b639-7a049ce3f08d</t>
-  </si>
-  <si>
-    <t>1ac229d3-dec3-46f1-a85b-d8c320961fec</t>
-  </si>
-  <si>
-    <t>f376cac0-8f46-4485-b300-909fd8ac7ee9</t>
-  </si>
-  <si>
-    <t>ccb8fe2b-3c0b-45ae-bbcf-bf8a6329a43d</t>
-  </si>
-  <si>
-    <t>7fcb02fb-a67c-42b5-835d-7116b9f5b21f</t>
-  </si>
-  <si>
-    <t>45d463af-033b-4ad5-9da4-b5a5910cac64</t>
-  </si>
-  <si>
-    <t>3ba71ef9-4b54-4350-b351-0b35757686b6</t>
-  </si>
-  <si>
-    <t>24846929-e59d-495d-b50d-6922a6dead25</t>
-  </si>
-  <si>
-    <t>ce471ee9-9181-40af-aaa9-4d98797ac5a1</t>
-  </si>
-  <si>
-    <t>f2b47931-fad6-47f1-9e4f-89cded085720</t>
-  </si>
-  <si>
-    <t>4bb814dd-2e24-4bbe-aa97-83c396e8747a</t>
-  </si>
-  <si>
-    <t>8087a2ce-8dae-489c-92dd-e1299dfe4714</t>
-  </si>
-  <si>
-    <t>b0649dc5-4d1b-43ff-a7d1-176da5d904ae</t>
-  </si>
-  <si>
-    <t>81d6ba68-525f-4be7-b6d4-eee23f673ca3</t>
-  </si>
-  <si>
-    <t>f5a42767-da41-4610-8c4a-bf34f5217388</t>
-  </si>
-  <si>
-    <t>3eeb108c-cb29-48f1-b200-233b1ceaae71</t>
-  </si>
-  <si>
-    <t>634a46ff-26a9-419a-97cc-6723a016a0b4</t>
-  </si>
-  <si>
-    <t>f19d162c-ab2d-4949-84ec-72c9babc3804</t>
-  </si>
-  <si>
-    <t>7bc0dacf-649f-4af6-8a10-ed5451407a1e</t>
-  </si>
-  <si>
-    <t>d1da8a87-7abb-4321-9e5f-eed7ea12685c</t>
-  </si>
-  <si>
-    <t>c0ec9a76-3736-42f6-8245-9b9fc60675a1</t>
-  </si>
-  <si>
-    <t>9a87396a-674a-4c4d-be58-0430fd9637fa</t>
-  </si>
-  <si>
-    <t>b6b94272-0268-41e2-acec-45917d5365a3</t>
-  </si>
-  <si>
-    <t>a88645e2-4f46-4f5e-9d9b-979629a59b4a</t>
-  </si>
-  <si>
-    <t>9d0c1077-b4d8-4d38-b0d2-999e0b996f5a</t>
-  </si>
-  <si>
-    <t>e9772f9a-c162-42d7-94ee-ddada038afa9</t>
-  </si>
-  <si>
-    <t>ec6089d3-24d0-42a6-98f7-f625a1dad5ca</t>
-  </si>
-  <si>
-    <t>04e6dc82-b731-4016-8eaf-c19186978f5c</t>
-  </si>
-  <si>
-    <t>f342b87b-45b5-4c2b-a91c-d30c109c66c8</t>
-  </si>
-  <si>
-    <t>3790c7f0-bedf-45c4-b7af-8800ab8df6a4</t>
-  </si>
-  <si>
-    <t>02305e12-2a8e-4d9d-8442-de515a24d7e6</t>
-  </si>
-  <si>
-    <t>1c057766-d610-45ae-b53b-6acdae381a9c</t>
-  </si>
-  <si>
-    <t>eab88e60-b94e-40e5-a07b-e596ce7ec704</t>
-  </si>
-  <si>
-    <t>c11434e6-749b-43e4-ab7b-9c8629a0ac46</t>
-  </si>
-  <si>
-    <t>67ec2e41-5378-426c-9f30-d93b8d0bd415</t>
-  </si>
-  <si>
-    <t>1e961e64-2e1a-4ef7-94ad-14c05aade374</t>
-  </si>
-  <si>
-    <t>01925753-5eff-47eb-a29f-206b06f75449</t>
-  </si>
-  <si>
-    <t>dcb98052-7558-4e20-bbc9-8d125ea87f46</t>
-  </si>
-  <si>
-    <t>868d3842-359c-45fd-9c76-00cd03023a0d</t>
-  </si>
-  <si>
-    <t>9d59b45e-8ad8-4029-98a7-1456eb40c1a9</t>
-  </si>
-  <si>
-    <t>af8d6364-125b-4b43-9f29-ca22e38b3ce9</t>
-  </si>
-  <si>
-    <t>6daecb4e-bf96-4bea-be80-bfc2f055df40</t>
-  </si>
-  <si>
-    <t>aa6c251d-aacf-4e91-9188-4141154c072d</t>
-  </si>
-  <si>
-    <t>efcdad98-1cf0-40a3-a133-70a395e4975f</t>
-  </si>
-  <si>
-    <t>42a4200f-9203-42a8-ad8e-4ef6cc96a537</t>
-  </si>
-  <si>
-    <t>1e8c39f3-0439-4303-9f99-8b303c795aff</t>
-  </si>
-  <si>
-    <t>037807ef-ffb7-4564-9f3b-252b150a55fb</t>
-  </si>
-  <si>
-    <t>908641be-5401-41d2-9085-303244d5995d</t>
-  </si>
-  <si>
-    <t>fcd43c8d-8604-43fa-b8fd-1fe4b30d122e</t>
-  </si>
-  <si>
-    <t>90490fd2-3632-4ebd-b651-f28e73cb591b</t>
-  </si>
-  <si>
-    <t>fb055f07-426b-4187-948d-146696f6798d</t>
-  </si>
-  <si>
-    <t>9b0593a9-eae8-41a0-9f36-ba1cc0db2d36</t>
-  </si>
-  <si>
-    <t>afa7a400-f847-4a80-ae82-f585688bef1c</t>
-  </si>
-  <si>
-    <t>1f1c2e65-98d7-4b15-aab8-5b5c2f46b77b</t>
-  </si>
-  <si>
-    <t>097dbc25-c7a8-429a-9334-91a54ae54251</t>
-  </si>
-  <si>
-    <t>366ef75f-7a13-4785-8b15-739cc7b3dd6e</t>
-  </si>
-  <si>
-    <t>69f386fd-6563-424e-a67f-8afe74508282</t>
-  </si>
-  <si>
-    <t>e7b92980-9897-4004-90bb-4e73bb087655</t>
-  </si>
-  <si>
-    <t>7bca6493-0de2-43a5-afbb-c60cf59a9686</t>
-  </si>
-  <si>
-    <t>770726d1-82df-4feb-ad47-5b8ed83c1a36</t>
-  </si>
-  <si>
-    <t>5d80126d-8c5f-497d-b519-eeccea472db8</t>
-  </si>
-  <si>
-    <t>7637ac6b-26c8-437c-a3fc-d7a138ab8cfc</t>
-  </si>
-  <si>
-    <t>e5b911c6-7581-4f26-92a3-2ed7002d290a</t>
-  </si>
-  <si>
-    <t>f615b631-ad3a-47de-9d8e-918d476f08ab</t>
-  </si>
-  <si>
-    <t>32238839-b67a-47e4-a34f-d6bba8a287f4</t>
-  </si>
-  <si>
-    <t>3034f558-ca3b-4fed-8ac8-67dd3ef667c4</t>
-  </si>
-  <si>
-    <t>f4da9292-d463-4ead-b080-2faa9ff75aa0</t>
-  </si>
-  <si>
-    <t>cc612b22-db4e-4eab-adb4-d4c07439f8f8</t>
-  </si>
-  <si>
-    <t>1a3a668e-c74d-4761-aff5-246d194987f9</t>
-  </si>
-  <si>
-    <t>844f248c-ef55-4f70-84b6-3ee786a258df</t>
-  </si>
-  <si>
-    <t>89ffc014-5ae3-4309-9da2-e6784237286d</t>
-  </si>
-  <si>
-    <t>1c020324-6e8e-47f8-90ba-d9f342a8b8a7</t>
-  </si>
-  <si>
-    <t>e16fb804-c0d8-4487-934a-af8971ae510d</t>
-  </si>
-  <si>
-    <t>bbcd5611-7a77-4e1f-8316-7a1df3cf400c</t>
-  </si>
-  <si>
-    <t>5ad6bd95-3497-497c-b584-086e511ec096</t>
-  </si>
-  <si>
-    <t>12531daf-2c8c-4a19-a047-460c0fda1c40</t>
-  </si>
-  <si>
-    <t>5d100ad5-505e-48d6-af76-1a487ef9c9d1</t>
-  </si>
-  <si>
-    <t>9a483a0a-baac-4341-bebe-2dcfe753be0f</t>
-  </si>
-  <si>
-    <t>e184fe5e-755d-4f4b-a000-19bd0afb2784</t>
-  </si>
-  <si>
-    <t>263928f7-57cd-4610-8e69-2dba0bd372bd</t>
-  </si>
-  <si>
-    <t>2b335f0b-2411-4030-9c06-64048917ec7b</t>
-  </si>
-  <si>
-    <t>4ed7c290-b83f-4620-98af-d3a28c0ff760</t>
-  </si>
-  <si>
-    <t>8a7a7ca5-1ea0-4e68-bd42-38120377b674</t>
-  </si>
-  <si>
-    <t>2c6001ec-8275-4ad4-8262-e3bb830cef3c</t>
-  </si>
-  <si>
-    <t>96545923-cf39-4066-a9f7-054495a18c6e</t>
-  </si>
-  <si>
-    <t>08b67560-1da0-4c7c-9c40-e920835ef4ce</t>
-  </si>
-  <si>
-    <t>005c6fc2-f4bb-48a5-8a7f-9fce9332b8cc</t>
-  </si>
-  <si>
-    <t>21ae0e12-1ec9-49ae-978d-536c70348cb6</t>
-  </si>
-  <si>
-    <t>28bedd2c-b00b-47c1-808a-424a82a063d7</t>
-  </si>
-  <si>
-    <t>1ae50633-f176-4779-b8b4-60e90fcc7bfe</t>
-  </si>
-  <si>
-    <t>bc4bf35b-a069-4c7b-ad3f-df91e1a12514</t>
-  </si>
-  <si>
-    <t>8926d0bc-536d-4208-ace3-a77b4b33c7f0</t>
-  </si>
-  <si>
-    <t>b08e54b9-89f2-440c-8bc7-96bcb9cffc8f</t>
-  </si>
-  <si>
-    <t>09e8f118-30ec-4fae-83c9-63b5da0b3073</t>
-  </si>
-  <si>
-    <t>8acb3276-d42d-4660-8df9-a0072922cf7e</t>
-  </si>
-  <si>
-    <t>347fd588-9b42-4bd3-bc6b-9cf41769fb1c</t>
-  </si>
-  <si>
-    <t>cf92bf18-73ac-4f7b-b558-61b46caefb6b</t>
-  </si>
-  <si>
-    <t>b3d48d92-15cd-420a-a38f-1ccab2e15b2f</t>
-  </si>
-  <si>
-    <t>a1b5c795-e26c-4342-a5b3-589cb22566f9</t>
-  </si>
-  <si>
-    <t>74f6063a-eac8-4a34-b1b0-67006fd26a48</t>
-  </si>
-  <si>
-    <t>23eb990f-b6ae-4c9e-9f0f-e5e99e3d4fbb</t>
-  </si>
-  <si>
-    <t>a7684801-e37b-464b-8b9a-fc606af0b676</t>
-  </si>
-  <si>
-    <t>efd8317e-9144-4957-a824-c1980b7cf256</t>
-  </si>
-  <si>
-    <t>b3032b4b-537c-491b-9e85-5d662900fb13</t>
-  </si>
-  <si>
-    <t>8448970c-f311-4a15-ac83-62ec3674ed59</t>
-  </si>
-  <si>
-    <t>8d96ff53-b9ec-4fea-9fa3-71804c974a94</t>
-  </si>
-  <si>
-    <t>87cf941f-f01f-44f4-b135-0045e3a42292</t>
-  </si>
-  <si>
-    <t>f85c0404-5fe6-4c65-9525-16bedcefe1b2</t>
-  </si>
-  <si>
-    <t>d3137cc6-01c2-43f4-a6c6-9a3ba0a2d9b2</t>
-  </si>
-  <si>
-    <t>c7542155-8418-460e-8304-c92f25f2ee1e</t>
-  </si>
-  <si>
-    <t>140083f2-be3e-418d-be09-5b2b20d5c54e</t>
-  </si>
-  <si>
-    <t>062f734a-8fff-4031-96b7-09a884d2d62f</t>
-  </si>
-  <si>
-    <t>9e194a98-46d3-4a80-b121-72093fdb36a4</t>
-  </si>
-  <si>
-    <t>b79c1a9a-2c48-4423-a368-b12c468de25d</t>
-  </si>
-  <si>
-    <t>d436b944-d659-4c79-8b94-f13fc54ebebe</t>
-  </si>
-  <si>
-    <t>d9598d73-270c-4996-9609-e6738f39cdae</t>
-  </si>
-  <si>
-    <t>0ebd81b5-fbee-4644-927e-a800e60a3481</t>
-  </si>
-  <si>
-    <t>c9d11459-23bc-4946-9665-189886fd4689</t>
-  </si>
-  <si>
-    <t>6d1ff555-7ce5-4152-92cd-2d66a9b4a397</t>
-  </si>
-  <si>
-    <t>38a1a127-e923-44c1-a637-c8c3bd134f88</t>
-  </si>
-  <si>
-    <t>ca0ec8dc-b2c8-4372-934a-1ff724730d26</t>
-  </si>
-  <si>
-    <t>6765fbd1-2c9f-4873-9f97-285f3c380ace</t>
-  </si>
-  <si>
-    <t>f0f9f23e-47b7-476c-8fe2-05aac64ad1cc</t>
-  </si>
-  <si>
-    <t>54c44f5a-33e7-4447-82c8-b26c4159c94e</t>
-  </si>
-  <si>
-    <t>c8ac5406-dd7d-445e-be7f-0be075755976</t>
-  </si>
-  <si>
-    <t>190ffd43-58a0-4e0a-b482-a02e367bc2e0</t>
-  </si>
-  <si>
-    <t>50713b4b-4908-4264-b8e9-6943890ffd09</t>
-  </si>
-  <si>
-    <t>f9725dee-d372-4760-9df6-faff00e6010b</t>
-  </si>
-  <si>
-    <t>12408021-8762-4ac5-96de-50188eb099e6</t>
-  </si>
-  <si>
-    <t>9e9d2a6f-fd0a-4c09-8e24-6fd3e40f9199</t>
-  </si>
-  <si>
-    <t>bafecea6-0b50-4caf-b579-4f21fd00aa92</t>
-  </si>
-  <si>
-    <t>84ad9ae4-80d9-473b-ab62-4e9ce21805a2</t>
-  </si>
-  <si>
-    <t>a4387cf9-b488-4717-9e44-0367e9a26d3e</t>
-  </si>
-  <si>
-    <t>d2407be7-0d5c-43b3-86bf-d0c92d29fcce</t>
-  </si>
-  <si>
-    <t>909538ba-7ad4-454d-882b-ce469a442037</t>
-  </si>
-  <si>
-    <t>1b31286e-4454-4135-a6de-16def35b0342</t>
-  </si>
-  <si>
-    <t>021a27f7-bdad-44a1-b515-62d482803556</t>
-  </si>
-  <si>
-    <t>4b4d0915-6522-4f72-9653-7ebd06e46b6d</t>
-  </si>
-  <si>
-    <t>f6bb4a5b-439d-4c66-bea8-013bff7b8b19</t>
-  </si>
-  <si>
-    <t>44d11f49-4c6f-4870-a03f-7f019b21d401</t>
-  </si>
-  <si>
-    <t>c74978a7-6272-4209-85f1-c060fce29924</t>
-  </si>
-  <si>
-    <t>614b2632-ba46-4e74-b571-74e0575a7b47</t>
-  </si>
-  <si>
-    <t>5abff554-6fe5-49c9-bcfb-877f99029a70</t>
-  </si>
-  <si>
-    <t>c8d75e72-2e7d-45f4-88e0-b0ea9398b71f</t>
-  </si>
-  <si>
-    <t>33cca3c0-f928-46c6-b69a-67bff16fc0fb</t>
-  </si>
-  <si>
-    <t>f270f99b-02a5-484e-92fa-735164d6a078</t>
-  </si>
-  <si>
-    <t>586be792-c398-483a-a906-8ba64817fda8</t>
-  </si>
-  <si>
-    <t>0f152fb7-8294-4c8f-9323-62ace6841b3a</t>
-  </si>
-  <si>
-    <t>ddf20d15-a0a0-4e65-abf8-40c0011fb515</t>
-  </si>
-  <si>
-    <t>af3d2ca9-d932-43b3-9dcb-816521c91f9f</t>
-  </si>
-  <si>
-    <t>4dac4d15-ea42-41f3-ac2d-9b23f7af0cef</t>
-  </si>
-  <si>
-    <t>0bd188c3-e6ab-4e60-8a91-62348ee330f4</t>
-  </si>
-  <si>
-    <t>7a18ee2c-7db0-4cad-a4e7-97d23463472f</t>
-  </si>
-  <si>
-    <t>ef13d974-68a0-45d6-a001-53e2b9752dda</t>
-  </si>
-  <si>
-    <t>2e5afd8b-d6f3-42db-974a-67d889ac428c</t>
-  </si>
-  <si>
-    <t>756cb6a5-b58d-4797-965f-de8ec640e9a6</t>
-  </si>
-  <si>
-    <t>6a1cfb15-4951-4b91-a4dc-9afe2974e3d7</t>
-  </si>
-  <si>
-    <t>9264afd3-16ba-4c6f-ac40-43f144821706</t>
-  </si>
-  <si>
-    <t>8317c739-75e9-41f8-beb7-94ab77555ffa</t>
-  </si>
-  <si>
-    <t>1c69f9a1-2b9d-491f-bb2c-963e845f01e8</t>
-  </si>
-  <si>
-    <t>8f779902-8cf2-47e4-8e5d-ac322bddc554</t>
-  </si>
-  <si>
-    <t>af47e4fb-49a1-4fce-88bf-556024ab7915</t>
-  </si>
-  <si>
-    <t>d8ec9bee-999d-4b59-87a9-e668a1a72747</t>
-  </si>
-  <si>
-    <t>0a338b8e-91c5-4ec9-8649-00c0d9599871</t>
-  </si>
-  <si>
-    <t>9484096d-b403-4b26-afe9-cd8bbc546a68</t>
-  </si>
-  <si>
-    <t>a019b467-a40a-41c6-ae47-53a3cfac0d5e</t>
-  </si>
-  <si>
-    <t>cda5dbbb-753b-4f4c-bb2b-94bd6c67f094</t>
-  </si>
-  <si>
-    <t>320b6bc2-0199-4cca-9d9a-ef793623cd47</t>
-  </si>
-  <si>
-    <t>9320602f-e35a-4663-95cb-3c3e83287dd0</t>
-  </si>
-  <si>
-    <t>3c744f23-7b8a-44fe-9495-412d699d7e39</t>
-  </si>
-  <si>
-    <t>36dd69fd-b3ac-4178-928e-d518e7cf5d6a</t>
-  </si>
-  <si>
-    <t>b7b40197-a7c3-4cca-a55d-16f56c50f30c</t>
-  </si>
-  <si>
-    <t>248a35a6-3e05-43f4-984c-a9c538b7db77</t>
-  </si>
-  <si>
-    <t>1bcc266a-9ffb-4ada-9915-d837de8f6364</t>
-  </si>
-  <si>
-    <t>3a27d055-a857-4ebe-ad7a-9b84debb0401</t>
-  </si>
-  <si>
-    <t>79c4cdcb-3c2b-45f2-afb1-a1ca16767057</t>
-  </si>
-  <si>
-    <t>f2506bf2-85a8-458a-85ee-aba9e4e82644</t>
-  </si>
-  <si>
-    <t>d479667a-f018-481c-9272-84e79c780b73</t>
-  </si>
-  <si>
-    <t>9a3abfd2-ea4a-400f-8ec6-9501e336c3db</t>
-  </si>
-  <si>
-    <t>d98c9957-e7e2-462e-866d-f79ceb70a448</t>
-  </si>
-  <si>
-    <t>de6ffbf7-2664-4f44-b133-e524e336b74c</t>
-  </si>
-  <si>
-    <t>d00e65ba-e847-40ad-b808-133306dd0d84</t>
-  </si>
-  <si>
-    <t>0cb9fd86-c469-4e18-92d0-05e72166ed57</t>
-  </si>
-  <si>
-    <t>ff32d4b4-4c2b-451a-906c-6035781e5123</t>
-  </si>
-  <si>
-    <t>b32e1f31-edce-4d5d-9be7-c74e20cd3a9c</t>
-  </si>
-  <si>
-    <t>1c634c7d-5255-48c7-a510-3f1b112a76f6</t>
-  </si>
-  <si>
-    <t>7d337712-e728-4a11-9860-36c248ad876e</t>
-  </si>
-  <si>
-    <t>2bccab1e-2e33-4963-8324-ac828998fcd4</t>
-  </si>
-  <si>
-    <t>a5b0b050-247b-4649-a85c-9a67aae1adc5</t>
-  </si>
-  <si>
-    <t>e59cf7ef-6371-4224-9ce6-28dd64afa4fc</t>
-  </si>
-  <si>
-    <t>e6c4ad9b-fa93-4571-baa3-c38ca3a70bb8</t>
-  </si>
-  <si>
-    <t>60dbcb78-3fb9-46f5-b53b-166a3ffe3352</t>
-  </si>
-  <si>
-    <t>d74e3e83-5d0b-46b5-937e-e65434da9e76</t>
-  </si>
-  <si>
-    <t>d259bacd-0253-4d25-8236-74802aa21ccc</t>
-  </si>
-  <si>
-    <t>f1013f70-5761-481e-a8b0-0ac0e9e59089</t>
-  </si>
-  <si>
-    <t>64f26e98-3952-4839-9748-4d2018b34321</t>
-  </si>
-  <si>
-    <t>7271e002-489b-4027-8a2f-805d5df4c241</t>
-  </si>
-  <si>
-    <t>717b29b1-def7-4b8b-a9fe-a3cb011b588c</t>
-  </si>
-  <si>
-    <t>ba3d0874-a86f-480c-8eb5-f24afc7282c7</t>
-  </si>
-  <si>
-    <t>416450f4-332f-48fb-bba7-0611f718b192</t>
-  </si>
-  <si>
-    <t>a413e3f0-1bf0-4a6f-86ab-92e50f83ffc5</t>
-  </si>
-  <si>
-    <t>831425ee-2f13-4da3-a1c4-d8967476ce79</t>
-  </si>
-  <si>
-    <t>78407623-f804-4cac-b323-5691523463e7</t>
-  </si>
-  <si>
-    <t>cc4df32b-2d7b-43d3-b8f6-3c1c0f9ed387</t>
-  </si>
-  <si>
-    <t>8f747505-6475-4b07-875d-4230abf4b76c</t>
-  </si>
-  <si>
-    <t>8d03321e-a85d-4bd3-8cae-8ae5389578e1</t>
-  </si>
-  <si>
-    <t>b560ec37-d870-4075-a029-d5ba2f78d596</t>
-  </si>
-  <si>
-    <t>14ffb46b-1950-497d-9b03-ea0cd0a9b02a</t>
-  </si>
-  <si>
-    <t>eedf5e58-58af-43a2-b3fc-36c6a87b2a59</t>
-  </si>
-  <si>
-    <t>aaa6b9e8-3f3e-43e8-af6f-cff9f1929f7f</t>
-  </si>
-  <si>
-    <t>7854bbec-0249-4e1f-a640-db15be0f1444</t>
-  </si>
-  <si>
-    <t>ba2fa2d4-a00e-4f18-997c-5abe7e69168b</t>
-  </si>
-  <si>
-    <t>c939ee8b-499b-4803-9c3c-36c426dfa935</t>
-  </si>
-  <si>
-    <t>608562c4-a6a0-484e-b292-25aac9ca6804</t>
-  </si>
-  <si>
-    <t>a1dd78e1-6545-4a6c-836f-8472836b7cdc</t>
-  </si>
-  <si>
-    <t>0b5f99d1-0ad8-49fb-a121-1f835752b7c1</t>
-  </si>
-  <si>
-    <t>2beb81bc-27c0-44d7-b714-c40343c882e8</t>
-  </si>
-  <si>
-    <t>9ccd8abb-5af7-40ea-8a13-a413ebd4c0c7</t>
-  </si>
-  <si>
-    <t>5aa70516-8a9e-4ac8-a70c-a699bc56171e</t>
-  </si>
-  <si>
-    <t>8808708a-bdee-4add-b6ad-2bdc02321bdf</t>
-  </si>
-  <si>
-    <t>9d46f8b7-9380-45eb-8856-1c34f767723e</t>
-  </si>
-  <si>
-    <t>697f4caa-9dda-472b-9e8e-de9d398b7069</t>
-  </si>
-  <si>
-    <t>727a3156-9d3a-4403-b4e3-9cf543f2fdb4</t>
-  </si>
-  <si>
-    <t>2eab7747-ed6d-4596-8bb7-82e3482c7145</t>
-  </si>
-  <si>
-    <t>32341b96-5b80-4ff7-81bd-6dd9d976e036</t>
-  </si>
-  <si>
-    <t>f4507e5c-8826-4d85-90d6-2a0adb6083d4</t>
-  </si>
-  <si>
-    <t>6512a305-5184-4a32-8261-e6ca237c12d7</t>
-  </si>
-  <si>
-    <t>0fd14979-174d-4e64-a72c-a6b4d3174a47</t>
-  </si>
-  <si>
-    <t>48c4129c-f878-4f31-a1b9-f59598d952d8</t>
-  </si>
-  <si>
-    <t>760e6374-4cdb-47a4-9ead-e7a2d1b639f0</t>
-  </si>
-  <si>
-    <t>05a429dc-9bc4-4a35-91d3-f16c720ad1a5</t>
-  </si>
-  <si>
-    <t>0f4666b2-aca1-454a-b59e-fa094a5c43ed</t>
-  </si>
-  <si>
-    <t>711f8b5b-5325-44b8-bee9-92b3f82d6637</t>
-  </si>
-  <si>
-    <t>bdba2018-05b4-4981-9086-de391dc9e2d9</t>
-  </si>
-  <si>
-    <t>a294eebe-ccc8-4a03-8c41-9fd5a1eb49f7</t>
-  </si>
-  <si>
-    <t>589bb622-560a-4bc9-ad71-facb2a231a4b</t>
-  </si>
-  <si>
-    <t>0aaaa036-9e8f-4b94-8b07-d7766cfb8a5f</t>
-  </si>
-  <si>
-    <t>f4652665-3640-4362-be03-d55af4b79e78</t>
-  </si>
-  <si>
-    <t>744c3ed2-c791-45c6-8b82-7bf4e1d7e474</t>
-  </si>
-  <si>
-    <t>ab876c40-d682-4ce8-b509-c40803aa9e44</t>
-  </si>
-  <si>
-    <t>45db38f6-9f4e-4366-8b0b-86912c0b783c</t>
-  </si>
-  <si>
-    <t>a6d6a24e-611f-4b06-a12d-dca9a596277b</t>
-  </si>
-  <si>
-    <t>db88fa69-8c80-4058-a86f-23be15b14c2d</t>
-  </si>
-  <si>
-    <t>dd5ce5b0-83c0-4c0e-8e4e-9da8003bfca7</t>
-  </si>
-  <si>
-    <t>d3ecad12-9af8-4de6-b85b-690b09fbce0d</t>
-  </si>
-  <si>
-    <t>83977b4d-0409-437a-ac30-9c88ecc575ec</t>
-  </si>
-  <si>
-    <t>8f143e1f-1a86-4e70-bbf4-2fc7f46d626a</t>
-  </si>
-  <si>
-    <t>9034fa78-8054-4739-a0f6-c815cb6770ec</t>
-  </si>
-  <si>
-    <t>168ed8bb-027f-47f4-9eb7-9a26e485cdb2</t>
-  </si>
-  <si>
-    <t>d818e8db-b12a-47f2-ab2c-ea65281d1e6d</t>
-  </si>
-  <si>
-    <t>cc97d6cd-01f8-46fc-a96d-8d58b9e5454c</t>
-  </si>
-  <si>
-    <t>dbf5f7d5-604f-44e1-8f04-89cf7101eb96</t>
-  </si>
-  <si>
-    <t>0738c51c-08cd-492b-80dd-187626884ef5</t>
-  </si>
-  <si>
-    <t>c14e09c9-e1b1-46a3-81f1-f7ce094f6b9f</t>
-  </si>
-  <si>
-    <t>41335309-def7-4ec5-9529-57c646face3d</t>
-  </si>
-  <si>
-    <t>4191e27d-8f96-4432-9150-284d87d27e6b</t>
-  </si>
-  <si>
-    <t>9d384621-398e-4f06-8b2f-e65d55f84dd5</t>
-  </si>
-  <si>
-    <t>10791dbd-9ed2-4ec1-a080-7a89ad9e72d2</t>
-  </si>
-  <si>
-    <t>897f3be8-40d7-4f80-84f8-1b69c47534de</t>
-  </si>
-  <si>
-    <t>4fb06bcb-e81a-4dc8-8a2c-c182ce01e624</t>
-  </si>
-  <si>
-    <t>aab83604-bda9-45f9-b12e-82988eb09e41</t>
-  </si>
-  <si>
-    <t>0eff7aed-56f6-481f-8f4e-06ba1062fbe8</t>
-  </si>
-  <si>
-    <t>e9b1a159-01fd-4756-9c06-79c5f33cc995</t>
-  </si>
-  <si>
-    <t>d5fa776a-3163-42a6-a472-72505013e91f</t>
-  </si>
-  <si>
-    <t>36ce9e54-4a49-479f-a68e-fd87b5f80187</t>
-  </si>
-  <si>
-    <t>eeb72db0-3c4f-4920-ac1f-b31137f5aa72</t>
-  </si>
-  <si>
-    <t>8983fecd-8d09-464e-bcf6-1f26ef35be0a</t>
-  </si>
-  <si>
-    <t>b9089257-5059-48d2-aa66-407087a649de</t>
-  </si>
-  <si>
-    <t>b906e071-8a36-43eb-b234-bdcbff74a5fe</t>
-  </si>
-  <si>
-    <t>3778ee8e-7bb1-4ca3-9bda-2debecf25a93</t>
-  </si>
-  <si>
-    <t>f1aa61f9-ee0c-4aa2-8d8b-b18644853f1d</t>
-  </si>
-  <si>
-    <t>4ad35142-182d-4b29-9151-3e05afbda408</t>
-  </si>
-  <si>
-    <t>aa96d963-5bc7-46ed-b4bd-94f5c6de60fe</t>
-  </si>
-  <si>
-    <t>cf9feeb6-90bd-42ef-9f4a-8a45d20b1ec2</t>
-  </si>
-  <si>
-    <t>da81f74b-bb70-472f-8993-7c1f0d2b7475</t>
-  </si>
-  <si>
-    <t>31cec95c-1603-4d0d-92e9-6c5bba9d5d97</t>
-  </si>
-  <si>
-    <t>c1847cc4-d223-49fa-b49b-fa0ec9b16d7b</t>
-  </si>
-  <si>
-    <t>c69c225f-9e46-478a-9e7a-1907a0b0cb91</t>
-  </si>
-  <si>
-    <t>3da5b8a7-6163-4bf6-aaf6-9d3e0c9a26d7</t>
-  </si>
-  <si>
-    <t>04965435-bd30-4840-ad61-1e942041491f</t>
-  </si>
-  <si>
-    <t>8bdd62b2-5d8e-443f-8779-2acd9a19c4b0</t>
-  </si>
-  <si>
-    <t>40525e80-7a2a-48d0-9f51-e813ce2c881b</t>
-  </si>
-  <si>
-    <t>1b8457af-bc4d-4768-bb74-ba5b0d7fb271</t>
-  </si>
-  <si>
-    <t>a0ac4507-c347-4d9f-beb5-6dd617a95c0a</t>
-  </si>
-  <si>
-    <t>564a6245-00ce-4fee-96c9-c8b426b97085</t>
-  </si>
-  <si>
-    <t>3ced6aa2-e53c-41c6-89a3-e0aff3c78f99</t>
-  </si>
-  <si>
-    <t>c2758041-5945-41a4-83d9-aaaa8fef6eba</t>
-  </si>
-  <si>
-    <t>8cf09482-509d-46b2-91f1-462f818210dc</t>
-  </si>
-  <si>
-    <t>9ecd54cf-3fec-436c-936f-a2af28efa1a1</t>
-  </si>
-  <si>
-    <t>8ef0ad21-b9cf-41e5-926b-d86d5ccc06c8</t>
-  </si>
-  <si>
-    <t>2fa8a1c9-aadc-47f0-8f6d-9ff10ebb5134</t>
-  </si>
-  <si>
-    <t>91adf37d-e735-43c2-98d3-4eabd3d14de6</t>
-  </si>
-  <si>
-    <t>e8b97e14-b9ca-4166-9b74-13fc26adc96e</t>
-  </si>
-  <si>
-    <t>08be4509-a399-4717-9053-978b810e9b55</t>
-  </si>
-  <si>
-    <t>baeb7cda-f8cb-41db-b242-a9dbe1c83952</t>
-  </si>
-  <si>
-    <t>b8f87ebd-c29b-4004-b862-ddb946dc6666</t>
-  </si>
-  <si>
-    <t>a8f41780-12b0-457a-934c-71ad0c631f01</t>
-  </si>
-  <si>
-    <t>bc96238a-d42c-4dad-abc6-eb7eed6bbd36</t>
-  </si>
-  <si>
-    <t>7eb48c09-eae5-4ab2-9609-abd62cd7b4cc</t>
-  </si>
-  <si>
-    <t>2d87d974-0ad8-4ffb-abfc-fb1c39e26cea</t>
-  </si>
-  <si>
-    <t>efd51cf4-e31a-471d-96c5-c07b53e04237</t>
-  </si>
-  <si>
-    <t>31ee7585-5b2e-42ff-bb79-a9de13196c7f</t>
-  </si>
-  <si>
-    <t>2199558e-434a-4ac3-8ef6-a11ce52a9b13</t>
-  </si>
-  <si>
-    <t>4cfc6b0b-3436-4902-b636-b139a8ca9842</t>
-  </si>
-  <si>
-    <t>1e8f5b24-455e-43dc-bab8-10164e26dd75</t>
-  </si>
-  <si>
-    <t>b56e1cf5-1c7f-40b4-9d39-3f27a4f092e2</t>
-  </si>
-  <si>
-    <t>1ef22346-d616-41d2-b3d5-dee4dfde828b</t>
-  </si>
-  <si>
-    <t>c4bba755-80a3-44be-9a07-8bd60986084f</t>
-  </si>
-  <si>
-    <t>d6b7c0d2-fd62-4227-8353-d1e43795feef</t>
-  </si>
-  <si>
-    <t>5eb3af76-4160-4c52-944e-651f530db326</t>
-  </si>
-  <si>
-    <t>41d5762d-179c-4307-b479-7f74dfe29ffb</t>
-  </si>
-  <si>
-    <t>18b0053a-e0cb-4074-97d5-d594c71ed267</t>
-  </si>
-  <si>
-    <t>aea53aae-951b-4b0c-bb5b-0bfa6f005e61</t>
-  </si>
-  <si>
-    <t>18aaf8a3-99ca-41c8-a9f1-bbf865fbdfd3</t>
-  </si>
-  <si>
-    <t>53062163-ff92-42ab-9978-281fead09456</t>
-  </si>
-  <si>
-    <t>375176e5-fcb1-499e-8021-216422b101df</t>
-  </si>
-  <si>
-    <t>7e617a58-2eb2-4433-a474-f9bf408a14c1</t>
-  </si>
-  <si>
-    <t>a783f8b3-8adb-485a-adbd-8743edd6f912</t>
-  </si>
-  <si>
-    <t>d88eb26c-5af6-475a-a642-be86eb76a88d</t>
-  </si>
-  <si>
-    <t>c7cea646-caba-4700-bb3b-a1da85d7bed9</t>
-  </si>
-  <si>
-    <t>c58680aa-2a93-420c-a0db-f088010db711</t>
-  </si>
-  <si>
-    <t>a2c0017d-1078-4df4-ba78-59e920a14124</t>
-  </si>
-  <si>
-    <t>ae37a22b-96ba-49ef-946a-aea1ac13c631</t>
-  </si>
-  <si>
-    <t>e61ca32a-0e75-4c91-9938-c2fc1eed3788</t>
-  </si>
-  <si>
-    <t>f92ee1c2-6897-4c9d-b401-722edde0b0f1</t>
-  </si>
-  <si>
-    <t>31d546bd-eab8-4db6-a834-96556846296c</t>
-  </si>
-  <si>
-    <t>a72c1882-473f-4c92-b7bb-4ea66f46ad08</t>
-  </si>
-  <si>
-    <t>c3749c6a-e8d9-42ef-bfeb-ab01a55fb01c</t>
-  </si>
-  <si>
-    <t>c00b6976-a555-411e-b1e7-dbeebf976993</t>
-  </si>
-  <si>
-    <t>c69c7098-fa37-46a8-9dee-ac83e050a77b</t>
-  </si>
-  <si>
-    <t>2a6c281f-9799-45f6-900c-fbc5c97df7fa</t>
-  </si>
-  <si>
-    <t>23525cca-f442-4a1e-9726-6ffffd046e8b</t>
-  </si>
-  <si>
-    <t>19a73914-27e7-4ff1-9c90-aa02ae4e2201</t>
-  </si>
-  <si>
-    <t>0e74afe1-77e5-4bc6-a297-bee8d0a5ec89</t>
-  </si>
-  <si>
-    <t>894ce6e3-537d-4f39-8bcf-e4c303d50c71</t>
-  </si>
-  <si>
-    <t>59e8151e-fe76-44fe-bea7-3a5ddc8dcf46</t>
-  </si>
-  <si>
-    <t>12a89f4d-4024-4a3c-978b-947f953c3910</t>
-  </si>
-  <si>
-    <t>692b6761-e7fa-41e5-aad7-b1c927c15167</t>
-  </si>
-  <si>
-    <t>a3c818bc-fadb-498a-9e93-44ddccd8a6b1</t>
-  </si>
-  <si>
-    <t>4440489b-a667-40e8-9e26-87ceb61103e6</t>
-  </si>
-  <si>
-    <t>bb5357c1-c7ce-4ba8-b9bc-fb48bcb381ac</t>
-  </si>
-  <si>
-    <t>d999dd13-6959-4e4e-8ca2-6b05a60398ce</t>
-  </si>
-  <si>
-    <t>fcdeeeeb-c799-4c9d-8828-f5bcd9701031</t>
-  </si>
-  <si>
-    <t>cf3ddaa0-94c8-4246-a1ef-bccf7a3fcc66</t>
-  </si>
-  <si>
-    <t>a3b105aa-f479-4f87-b444-fed0be433b87</t>
-  </si>
-  <si>
-    <t>cc878e75-a98c-47b3-ab08-221a555c9f47</t>
-  </si>
-  <si>
-    <t>73a412ea-657a-4e79-bc15-e1fcb7e9c324</t>
-  </si>
-  <si>
-    <t>1ba81af1-16e8-42d9-ad17-603b8f990fae</t>
-  </si>
-  <si>
-    <t>400ef257-a63b-4090-908b-f65494920f05</t>
-  </si>
-  <si>
-    <t>dfdfb582-5c7f-4c24-bddc-4dba1d16c8b6</t>
-  </si>
-  <si>
-    <t>191047b9-b83f-4cf8-a78a-54e57b78895e</t>
-  </si>
-  <si>
-    <t>3178df8a-4017-4e3e-9829-c9f949e43828</t>
-  </si>
-  <si>
-    <t>b178ff95-ee03-4b30-84c6-ed0f9f50c1a5</t>
-  </si>
-  <si>
-    <t>cafea214-0d8f-4a8a-96cb-7ec6a9f3a6f5</t>
-  </si>
-  <si>
-    <t>572d6368-6eff-4fc5-ba87-835194502162</t>
-  </si>
-  <si>
-    <t>2de980dd-ce8e-426e-ab84-5dd3243183f5</t>
-  </si>
-  <si>
-    <t>c851a0e3-1321-40d6-8c35-7e344be6edb4</t>
-  </si>
-  <si>
-    <t>9241b5b8-2787-4b96-b448-bf018c1989d8</t>
-  </si>
-  <si>
-    <t>540e4a75-d192-434f-8c55-929c8eb3a3cb</t>
-  </si>
-  <si>
-    <t>e5f32ad9-e698-4562-8c56-a745bbd528e3</t>
-  </si>
-  <si>
-    <t>b0ffb1ca-a822-4da9-8401-e6a82b05e3d4</t>
-  </si>
-  <si>
-    <t>6e5e0095-8b6f-44ac-95e2-257ed4b5e865</t>
-  </si>
-  <si>
-    <t>e833dbeb-5c11-4cc1-b159-f922a10191c5</t>
-  </si>
-  <si>
-    <t>b6c7b57a-33ea-4665-bd8e-184ae4a830b2</t>
-  </si>
-  <si>
-    <t>adad97dc-df45-4ff5-bcf8-ce602cd3b2c6</t>
-  </si>
-  <si>
-    <t>20c69219-abeb-4df5-bfe6-f54532af12c2</t>
-  </si>
-  <si>
-    <t>b6ea543e-59d7-4bed-a97d-76de5cc6fdf6</t>
-  </si>
-  <si>
-    <t>ab5c840e-7270-49ac-9ca5-78a4c76adc4f</t>
-  </si>
-  <si>
-    <t>45da9eea-6ca4-48e7-b952-39f33b388a34</t>
-  </si>
-  <si>
-    <t>a32c56a6-d75e-405c-bd46-8f8434ead210</t>
-  </si>
-  <si>
-    <t>3d60fe8f-9b39-4e8e-8d35-ec026ea1f0d1</t>
-  </si>
-  <si>
-    <t>1d6fa4a6-7ea5-493e-8660-01e4809be928</t>
-  </si>
-  <si>
-    <t>23211e24-ff88-44d9-8290-e428c43f2ef6</t>
-  </si>
-  <si>
-    <t>214ee426-e57c-453c-ad5e-7077e7882b35</t>
-  </si>
-  <si>
-    <t>72b1d014-5173-4398-8978-1e8937b57f74</t>
-  </si>
-  <si>
-    <t>11bc931e-522d-4ff0-b673-b53c24ed3d38</t>
-  </si>
-  <si>
-    <t>b115af5b-0639-40c3-a590-99795651b610</t>
-  </si>
-  <si>
-    <t>be41bc66-3361-4ea9-963d-50395b55b2d1</t>
-  </si>
-  <si>
-    <t>396bf3ab-9b0c-4b0e-8621-e6ab7b6611dd</t>
-  </si>
-  <si>
-    <t>c57354dd-1c6d-4268-ac50-210e73a2ca44</t>
-  </si>
-  <si>
-    <t>e820ce8a-44f2-4646-bf77-60ee1de5d66a</t>
-  </si>
-  <si>
-    <t>1b7ecec4-e3ae-4626-9de9-f652b5d2c279</t>
-  </si>
-  <si>
-    <t>622478f1-6d05-4e9d-9283-35d0e72940b9</t>
-  </si>
-  <si>
-    <t>6b5e3c1a-6155-41b5-8c3f-8d75985f003f</t>
-  </si>
-  <si>
-    <t>3a6f3c1a-913b-4ea4-8afb-d21338b1e065</t>
-  </si>
-  <si>
-    <t>c989347c-b960-4aa0-b893-e0f71972c978</t>
-  </si>
-  <si>
-    <t>76ca9576-46cc-4984-9ef6-b15347996581</t>
-  </si>
-  <si>
-    <t>63290d13-f918-44d7-8e0d-a099b53b9fe6</t>
-  </si>
-  <si>
-    <t>3d774781-5e59-4269-9911-7f7eb52bd5bc</t>
-  </si>
-  <si>
-    <t>97ef8ee9-7e05-4095-b56b-716f672a1a99</t>
-  </si>
-  <si>
-    <t>5b4e1b4a-98fa-4aa1-8d72-c52c3e3a0e1f</t>
-  </si>
-  <si>
-    <t>1258670c-c475-4c39-a3ed-9247014aac51</t>
-  </si>
-  <si>
-    <t>1cb4edbd-7f83-412b-80f6-ab3e42572cb2</t>
-  </si>
-  <si>
-    <t>55f411ed-559f-418b-a78c-e01f9d351647</t>
-  </si>
-  <si>
-    <t>c69d4d74-3e47-4786-bcbc-8d3f53db259b</t>
-  </si>
-  <si>
-    <t>a7e569ee-9c3a-4da3-8812-8331d73c4431</t>
-  </si>
-  <si>
-    <t>6a0f37ac-752e-401a-ac8f-c6299cd280bf</t>
-  </si>
-  <si>
-    <t>991caa2c-0457-4efc-a16e-fe29446906cf</t>
-  </si>
-  <si>
-    <t>1616274b-8cd5-44d7-bb63-7ba35dcf2098</t>
-  </si>
-  <si>
-    <t>e45e55ca-1a78-4b90-903c-6a1f0bc73b7e</t>
-  </si>
-  <si>
-    <t>c76f18a6-b2f2-4412-82b3-cd3b21875bda</t>
-  </si>
-  <si>
-    <t>caa858ae-34ca-4d15-a0d7-463d07902092</t>
-  </si>
-  <si>
-    <t>cf2af40d-2fa9-45a6-b8b5-05ab5947b94a</t>
-  </si>
-  <si>
-    <t>727056b0-be07-432a-86e9-29c106ec7207</t>
-  </si>
-  <si>
-    <t>d9ab0182-8446-486a-a1ad-9db15b18e47d</t>
-  </si>
-  <si>
-    <t>964efbbb-bbb3-485c-869d-72896d61e366</t>
-  </si>
-  <si>
-    <t>f6c60bc8-668e-450d-9d89-4f172b4003ed</t>
-  </si>
-  <si>
-    <t>f5da8fe4-a65e-4157-9163-bd1908761d1d</t>
-  </si>
-  <si>
-    <t>fbf47c76-2de5-441c-8518-ce39037b9549</t>
-  </si>
-  <si>
-    <t>4c203aeb-812e-446d-b474-bbb2c4f0b262</t>
-  </si>
-  <si>
-    <t>0e47bcf7-f857-4b62-b364-28e9cbc053ad</t>
-  </si>
-  <si>
-    <t>aa900593-895f-49b5-b33f-55f794d1561f</t>
-  </si>
-  <si>
-    <t>0080890b-7c90-4eac-8ab5-8ec5c01e189d</t>
-  </si>
-  <si>
-    <t>8ad31b4d-c141-42e4-ad9a-f28f072b6efa</t>
-  </si>
-  <si>
-    <t>a5fa63a7-f505-4eb1-b925-16e02c50cea3</t>
-  </si>
-  <si>
-    <t>ea798187-3da9-467f-ac7c-924c4d0afa84</t>
-  </si>
-  <si>
-    <t>89c5932a-22df-40c8-8e2d-adb5c26389fc</t>
-  </si>
-  <si>
-    <t>3f3439b0-b5e9-4005-815f-2fd0daeacd19</t>
-  </si>
-  <si>
-    <t>8b7cfc71-dcda-4c6f-b9b1-f76fea627b99</t>
-  </si>
-  <si>
-    <t>00635f1f-4509-4c1f-b832-9c4f087c954b</t>
-  </si>
-  <si>
-    <t>910b7606-8c11-4208-8dd7-ff5584098d8c</t>
-  </si>
-  <si>
-    <t>e6f26d0d-96ea-475d-955d-6dccd513df02</t>
-  </si>
-  <si>
-    <t>5c6a6e3f-ef39-40b1-ba9b-439e5c5a34ee</t>
-  </si>
-  <si>
-    <t>2fba843b-8fd9-4d3a-a98c-b3bea925dcc7</t>
-  </si>
-  <si>
-    <t>44c5f5cb-5954-4c96-b487-b4cb691fdbe9</t>
-  </si>
-  <si>
-    <t>35706c20-1c95-4cca-8f7f-8109e5519ca7</t>
-  </si>
-  <si>
-    <t>d3881337-3ff0-43e4-87bc-afadd55a45eb</t>
-  </si>
-  <si>
-    <t>43ae454a-254f-4823-b184-dd8d3621fc9f</t>
-  </si>
-  <si>
-    <t>cf8d0b99-ce86-44d6-af64-5428b1045fb9</t>
-  </si>
-  <si>
-    <t>02e24cba-a680-4f1d-8cc2-f71deea1a0d0</t>
-  </si>
-  <si>
-    <t>9be83967-bf20-4e8a-ac57-139a031376a4</t>
-  </si>
-  <si>
-    <t>c1ffe203-0f1b-4ccd-af10-2ad17433617e</t>
-  </si>
-  <si>
-    <t>5776cc83-60af-4337-b102-a179698e0a31</t>
-  </si>
-  <si>
-    <t>3df0d4b9-cc0b-489c-b427-5a14ecd0e16a</t>
-  </si>
-  <si>
-    <t>429e63fc-5b19-4057-b2ee-0712389aa3be</t>
-  </si>
-  <si>
-    <t>7ee3f12b-be9e-4002-b368-8bfba12ea9c6</t>
-  </si>
-  <si>
-    <t>dbd96641-daf1-49bb-a3b2-99ebefe5fda3</t>
-  </si>
-  <si>
-    <t>950c1b0c-7031-4893-9f31-17884ff6b445</t>
-  </si>
-  <si>
-    <t>008ad30d-8f67-49b3-ab75-6ed8a0b31ec7</t>
-  </si>
-  <si>
-    <t>f3b965ce-c96a-4835-825b-1d8b282b3767</t>
-  </si>
-  <si>
-    <t>640c4780-69bd-43b6-a202-f81970a3e7a2</t>
-  </si>
-  <si>
-    <t>aebf4f50-7130-47f7-90ea-54125f126847</t>
-  </si>
-  <si>
-    <t>26a47c03-61c3-407c-8f01-6f1b2a68e4b3</t>
-  </si>
-  <si>
-    <t>af1562ca-50d5-4680-ac3a-237f19f5e71c</t>
-  </si>
-  <si>
-    <t>dc7a9d71-8960-4f72-9067-41b77b3664b9</t>
-  </si>
-  <si>
-    <t>41b37ec9-c9ce-476d-8abd-24db7caec31a</t>
-  </si>
-  <si>
-    <t>8f6dd7c3-c505-42e2-8abb-6f846ed61c9f</t>
-  </si>
-  <si>
-    <t>558446c6-3cd2-4511-8239-a57fc1ac5849</t>
-  </si>
-  <si>
-    <t>30d311a6-641a-4955-a6fb-c429b07537f2</t>
-  </si>
-  <si>
-    <t>c3f093cc-981d-4d8d-8178-6a44bbce725d</t>
-  </si>
-  <si>
-    <t>c7302d26-36d9-46bf-9e93-134791196b88</t>
-  </si>
-  <si>
-    <t>3671b8a9-8f33-46d1-88e5-f3f6d102c106</t>
-  </si>
-  <si>
-    <t>5c06270d-593e-4211-9e3a-1a52ffda38c3</t>
-  </si>
-  <si>
-    <t>12a174cb-92a6-43a4-b2b8-79b3a867ccdd</t>
-  </si>
-  <si>
-    <t>08b86e10-dcde-45fa-a756-6b30e896407e</t>
-  </si>
-  <si>
-    <t>474db25e-8f30-4ee2-a436-6646ca8144d8</t>
-  </si>
-  <si>
-    <t>1105b64d-3309-4789-b25b-9060b65c6bde</t>
-  </si>
-  <si>
-    <t>d3d6c327-7bcf-47a3-a501-09fc04adc876</t>
-  </si>
-  <si>
-    <t>b4d5136b-8bb1-41ef-aeb6-a8bea0dbab0d</t>
-  </si>
-  <si>
-    <t>6903140f-e7ce-4fdf-822f-8d3948e6b11e</t>
-  </si>
-  <si>
-    <t>9536afaa-7c8f-4e2a-ac8c-8a8a8ac29348</t>
-  </si>
-  <si>
-    <t>07cb8d7f-1784-47fb-8ebf-d133509bdbb2</t>
-  </si>
-  <si>
-    <t>bf7abfbb-4478-4f4a-9c0b-517f549365f9</t>
-  </si>
-  <si>
-    <t>d1f76bf2-eb9e-4522-a747-54899e77d0d1</t>
-  </si>
-  <si>
-    <t>2b9ded71-d259-4cc3-98c6-c0f7971e86c1</t>
-  </si>
-  <si>
-    <t>c33be149-6c71-40bb-a463-c7ffccfee5a4</t>
-  </si>
-  <si>
-    <t>69491162-3957-4e09-8022-3cecb1d0e814</t>
-  </si>
-  <si>
-    <t>774fd644-7442-4941-bd3d-884b14b866df</t>
-  </si>
-  <si>
-    <t>07c747f3-1069-4080-8f5f-cd59924bf90c</t>
-  </si>
-  <si>
-    <t>ebd4a8d6-2e88-4b3f-87a3-d78764a7e955</t>
-  </si>
-  <si>
-    <t>3a67d2ed-8552-4397-85ae-4d03b1b3b6b3</t>
-  </si>
-  <si>
-    <t>dda08d73-a764-4634-9fd7-529deaa8a6d0</t>
-  </si>
-  <si>
-    <t>180f9e85-60af-46d4-b9a3-f7c0637387cc</t>
-  </si>
-  <si>
-    <t>7b98377e-f3b2-48f5-ac24-6d1cc9754a3f</t>
-  </si>
-  <si>
-    <t>d84c055c-6cf0-4da9-9dce-5d1c07b828e4</t>
-  </si>
-  <si>
-    <t>ce04a1fd-84c7-41f9-a127-fefbacb6e3e2</t>
-  </si>
-  <si>
-    <t>2cb5fd76-c926-4220-805b-7969f21dcb49</t>
-  </si>
-  <si>
-    <t>ff0daff0-8478-4d26-b0e1-8eaa243c080e</t>
-  </si>
-  <si>
-    <t>1ff4ad55-f304-4a52-9b49-683e820b37c0</t>
-  </si>
-  <si>
-    <t>bfea70c2-e79d-4585-8c35-a026dab23cbb</t>
-  </si>
-  <si>
-    <t>a99237a3-07d8-468b-9325-3e9e5f62c0e9</t>
-  </si>
-  <si>
-    <t>d5ffdbcd-f2fa-4552-8312-47489c92ef58</t>
-  </si>
-  <si>
-    <t>998b0b8d-8406-4cc7-9281-6d62978033a1</t>
-  </si>
-  <si>
-    <t>cb31bb34-0de0-4658-84e1-42cb2b01d1ac</t>
-  </si>
-  <si>
-    <t>6cd3109e-6b10-4b07-8e97-a4d6b6ede015</t>
-  </si>
-  <si>
-    <t>ecf87d18-3698-424c-890b-e6780a8dbec9</t>
-  </si>
-  <si>
-    <t>7af012b5-803a-456e-bffa-2bc3d666df77</t>
-  </si>
-  <si>
-    <t>781c4281-65e6-4fa3-830d-12f4062967de</t>
-  </si>
-  <si>
-    <t>43049f01-7ae5-4d7a-a011-913d5a8016df</t>
-  </si>
-  <si>
-    <t>d607f49f-c813-4d36-b0ee-b8e4911042ef</t>
-  </si>
-  <si>
-    <t>5acdfa5e-dbe4-4154-a2de-583baa4f8510</t>
-  </si>
-  <si>
-    <t>d3f49b10-25f9-4bae-8bc3-7541c882d440</t>
-  </si>
-  <si>
-    <t>b1bf20f2-82eb-4ba7-81d1-288bb60e9084</t>
-  </si>
-  <si>
-    <t>ec4bd7b0-5657-408c-8be9-54bddfecdb42</t>
-  </si>
-  <si>
-    <t>94ed638c-79ca-4dac-9fc2-19827312441c</t>
-  </si>
-  <si>
-    <t>5a5911a3-4572-493f-afc2-a30c7318bc5e</t>
-  </si>
-  <si>
-    <t>d4e6ad98-771f-4ff9-b623-f06de7efb6e5</t>
-  </si>
-  <si>
-    <t>8be1f007-8396-4386-becb-f10ce8afe631</t>
-  </si>
-  <si>
-    <t>b4b7afa9-a9d5-4769-bb82-0c0ae5a03bfd</t>
-  </si>
-  <si>
-    <t>a319bf85-b945-49a1-bc21-b2277ed387b3</t>
-  </si>
-  <si>
-    <t>923c65c8-c147-44ed-9548-afd596d788a5</t>
-  </si>
-  <si>
-    <t>68ed3c1a-6cca-4e99-81c4-584252e429b9</t>
-  </si>
-  <si>
-    <t>3a015219-6918-42cd-ae71-419ec8dc0498</t>
-  </si>
-  <si>
-    <t>1112bedd-a0f3-430f-8e49-cc5fe53f3765</t>
-  </si>
-  <si>
-    <t>13be6bfb-6e4c-4f29-9f4f-272e3d462bd1</t>
-  </si>
-  <si>
-    <t>f3462e49-e0d6-4aa2-96d4-97f2ac38b05b</t>
-  </si>
-  <si>
-    <t>fe27aaa7-018f-421e-8ab4-91c105773944</t>
-  </si>
-  <si>
-    <t>b93d9cf9-2076-401c-8a64-a49c3f629fca</t>
-  </si>
-  <si>
-    <t>6f92b393-da7e-4ce2-8160-d481f617e81d</t>
-  </si>
-  <si>
-    <t>9b25b8fc-cd37-4c76-8a54-637e348a993a</t>
-  </si>
-  <si>
-    <t>faea4d3b-ea84-4b89-8b21-350c88c0c117</t>
-  </si>
-  <si>
-    <t>c1de3fa3-3870-490e-8e92-b6d387a16191</t>
-  </si>
-  <si>
-    <t>22fb881b-32c7-4630-b1b9-cb45eb90a7ac</t>
-  </si>
-  <si>
-    <t>c876c55d-de5e-4787-872b-843255cc5cc5</t>
-  </si>
-  <si>
-    <t>59b38cde-6f6c-41ca-b2da-d50d1d4e0cea</t>
-  </si>
-  <si>
-    <t>20c432fc-8326-464e-87e2-8a52333dec87</t>
-  </si>
-  <si>
-    <t>d6857218-24aa-4f2c-b6e0-3f2f29cd0f4d</t>
-  </si>
-  <si>
-    <t>5cc21ce0-b3f4-4816-8dca-69fbe7e47b1d</t>
-  </si>
-  <si>
-    <t>6f548af2-485f-41b2-a5d5-dce97ef8028a</t>
-  </si>
-  <si>
-    <t>6924a095-887b-4957-b0a8-de9da2d433bd</t>
-  </si>
-  <si>
-    <t>2761a160-b5d3-47eb-aa18-45e09c163aa8</t>
-  </si>
-  <si>
-    <t>f4be77d7-ac31-4cb2-adf8-a3d85d477540</t>
-  </si>
-  <si>
-    <t>9869fee7-74be-48e0-8762-26b5af5626ca</t>
-  </si>
-  <si>
-    <t>c6417e42-13f8-4dd9-8155-fc6c609b99b8</t>
-  </si>
-  <si>
-    <t>04f24a27-5fdb-4278-bdab-2ddf0b8cba2e</t>
-  </si>
-  <si>
-    <t>7ed12636-141c-40e5-92fd-ec61eb16ee71</t>
-  </si>
-  <si>
-    <t>49a275a2-9128-437d-b9d1-506dd2e34dca</t>
-  </si>
-  <si>
-    <t>29d5ae1f-03f8-4a2e-a784-9faaf16f404d</t>
-  </si>
-  <si>
-    <t>046d4277-3aa7-4993-9120-5e8ebc33cc6b</t>
-  </si>
-  <si>
-    <t>f2d13604-eecf-42a9-984b-d9913736134b</t>
-  </si>
-  <si>
-    <t>7b29fffa-135e-4ed0-8faf-fbd159b2fb1c</t>
-  </si>
-  <si>
-    <t>a5823624-bb06-428d-83f3-d0ea8e65588c</t>
+    <t>deda7f74-818b-47f7-81d6-faa4f3810fcc</t>
+  </si>
+  <si>
+    <t>0b81b440-0a6f-4252-b095-8ea57c790a9c</t>
+  </si>
+  <si>
+    <t>da97914d-f4bb-4ee6-a5a5-64f6ddedd097</t>
+  </si>
+  <si>
+    <t>0342f35c-2608-43f6-91b1-349bdba408fd</t>
+  </si>
+  <si>
+    <t>6ed7c93c-5594-4023-9d57-f1fc03c0ef34</t>
+  </si>
+  <si>
+    <t>351d1d67-4609-4abb-a7f4-70be5906c5a2</t>
+  </si>
+  <si>
+    <t>fc57f094-a3c7-40d3-a9b4-e5520f275f6c</t>
+  </si>
+  <si>
+    <t>ae9f0093-6acc-4a2b-8301-1f4892f4ddcb</t>
+  </si>
+  <si>
+    <t>51078d09-2a3f-4ab3-9fbd-4bfec73d8b30</t>
+  </si>
+  <si>
+    <t>7506ae9e-bf79-4db0-9406-1fbb8c8b7796</t>
+  </si>
+  <si>
+    <t>9fef360d-0060-42cc-b1fd-519eeaef32b0</t>
+  </si>
+  <si>
+    <t>35298d2e-df45-4653-a431-c13e40e53c69</t>
+  </si>
+  <si>
+    <t>eb4bc408-15e8-4cff-82ff-85998d884a6d</t>
+  </si>
+  <si>
+    <t>319a536f-7d30-46a6-839f-3205c4e3fd25</t>
+  </si>
+  <si>
+    <t>03d396b9-7e77-4ed2-9934-c641710e6d65</t>
+  </si>
+  <si>
+    <t>f36ce0ec-690a-438d-b42f-f8c79bef6e5a</t>
+  </si>
+  <si>
+    <t>9d68190e-815a-4bdb-9d21-5b9543787b1f</t>
+  </si>
+  <si>
+    <t>65cf2fb0-4df5-4800-92e8-7644240ef13b</t>
+  </si>
+  <si>
+    <t>d433bff2-5b20-415b-ac54-9f45d7c90a31</t>
+  </si>
+  <si>
+    <t>1c91bf22-ae5e-4ba6-9465-2d59f98c3d82</t>
+  </si>
+  <si>
+    <t>1fb6df92-c1d1-4dd8-bf7f-af63a1b00fb9</t>
+  </si>
+  <si>
+    <t>93885a9c-9820-4d2d-b885-f3ebe37ee754</t>
+  </si>
+  <si>
+    <t>a79d8b76-d783-45b4-bcd6-a9f1c91b1a13</t>
+  </si>
+  <si>
+    <t>8667ac1c-5623-4c3b-9247-0a14fd919515</t>
+  </si>
+  <si>
+    <t>0d24f4e9-b893-480a-b50a-2f74ca21ac1a</t>
+  </si>
+  <si>
+    <t>ff5c3eb9-8499-42ce-a2b5-1e695efefef0</t>
+  </si>
+  <si>
+    <t>e136e448-268c-4890-9ad3-96824df07405</t>
+  </si>
+  <si>
+    <t>5270d553-4795-4a4a-8ebc-55d35298742f</t>
+  </si>
+  <si>
+    <t>ab51d247-aa23-4846-908c-37f68cee0e07</t>
+  </si>
+  <si>
+    <t>44bbf40a-83d2-404d-9550-ca3494920733</t>
+  </si>
+  <si>
+    <t>706975a2-0900-4062-bcde-68a7ef579d08</t>
+  </si>
+  <si>
+    <t>f710b152-ace8-4f2d-9c0f-ede752020337</t>
+  </si>
+  <si>
+    <t>2d3cddd1-bcf9-4f54-8f78-c847427007e3</t>
+  </si>
+  <si>
+    <t>a31798e1-e505-433b-a453-ef9bb6abd379</t>
+  </si>
+  <si>
+    <t>f094d2b4-5d71-4c1d-89ef-1bfa2a1ddbe9</t>
+  </si>
+  <si>
+    <t>6d886645-d185-453d-9a93-ab7e0e968ed8</t>
+  </si>
+  <si>
+    <t>fa16db35-f447-4ae6-8b65-dd0bbc193591</t>
+  </si>
+  <si>
+    <t>4a21144b-2a84-46f7-ba66-d1898c15986c</t>
+  </si>
+  <si>
+    <t>92fc5fa1-9fd5-415b-bb38-5e22ac269f9b</t>
+  </si>
+  <si>
+    <t>a7e6899f-b2af-4ba5-bc6a-ae9d1946a9d3</t>
+  </si>
+  <si>
+    <t>4624f72b-e003-4e46-86e7-3b501b86588c</t>
+  </si>
+  <si>
+    <t>45f6ee73-ba0b-40d8-b0eb-4d7ff7b40a6e</t>
+  </si>
+  <si>
+    <t>e89dafc6-4898-43b8-92c1-0159ba5a979c</t>
+  </si>
+  <si>
+    <t>ac4f17d1-e32d-4958-b9f1-46c11a70f99b</t>
+  </si>
+  <si>
+    <t>47d642f0-ded4-45f1-9402-f5a769fd7a63</t>
+  </si>
+  <si>
+    <t>f91570bf-5821-4709-aab5-3af0c60d4f54</t>
+  </si>
+  <si>
+    <t>245e2607-f33a-444b-9915-3366d78f80a0</t>
+  </si>
+  <si>
+    <t>2c19a2e9-544f-4fb9-8bb0-b6c1d6796112</t>
+  </si>
+  <si>
+    <t>c004368d-0adf-4244-8f89-5fec2fa7f118</t>
+  </si>
+  <si>
+    <t>c0279197-04fa-49bf-b54f-78353f12a5da</t>
+  </si>
+  <si>
+    <t>8627554c-2819-4c82-b3f6-23cb9592aa6f</t>
+  </si>
+  <si>
+    <t>b8f97436-c676-49b3-b2b9-4df911130dd6</t>
+  </si>
+  <si>
+    <t>f2f65d55-a9d5-4a0f-a909-9d88342c015f</t>
+  </si>
+  <si>
+    <t>f05892c5-0ed1-4f3e-9a32-dbff32588b11</t>
+  </si>
+  <si>
+    <t>7026daff-1b62-41e2-9840-606591ac03b9</t>
+  </si>
+  <si>
+    <t>48e8ab65-ce35-4565-b884-b2ecd94d86f3</t>
+  </si>
+  <si>
+    <t>d6ba373d-c621-4866-8a9c-b8ca7aa78049</t>
+  </si>
+  <si>
+    <t>a67e8e04-3f81-4e96-85ac-33793c86f09d</t>
+  </si>
+  <si>
+    <t>7c122d43-510b-4155-83b5-2098368d4796</t>
+  </si>
+  <si>
+    <t>3f338883-1c8b-46fb-8fb7-3c9de4f3593d</t>
+  </si>
+  <si>
+    <t>bafd8f2e-733b-4a18-aa62-f0f439af9923</t>
+  </si>
+  <si>
+    <t>f008d9f1-20cd-4144-b8a2-516f55bfddd1</t>
+  </si>
+  <si>
+    <t>c9805cac-9e8f-4861-81fa-75ce44a93cb9</t>
+  </si>
+  <si>
+    <t>0a93d42a-9782-4702-baf1-c41ef9397dbf</t>
+  </si>
+  <si>
+    <t>6cb02789-771f-48ad-a64e-01ff0dbd294b</t>
+  </si>
+  <si>
+    <t>7fb56f35-8694-49e5-9497-03e810b91909</t>
+  </si>
+  <si>
+    <t>ad7dd934-9e25-4319-87cf-a51e0eb7cbf9</t>
+  </si>
+  <si>
+    <t>d229ea29-04b4-4fd5-8e2a-05273dd29a4b</t>
+  </si>
+  <si>
+    <t>a60bac27-4aa8-4287-b33b-2f126051b52a</t>
+  </si>
+  <si>
+    <t>3581ea97-c509-42d6-b4b9-98d8178e5b7a</t>
+  </si>
+  <si>
+    <t>cdc5a34c-0d28-4d05-8b95-df6c2c7cdb19</t>
+  </si>
+  <si>
+    <t>5b4bb4a6-d74e-46be-8338-0447b8db7c4e</t>
+  </si>
+  <si>
+    <t>dd0d8565-837f-4fe9-9835-445a73fb1282</t>
+  </si>
+  <si>
+    <t>86d0e3c1-e1b9-4150-bb0d-606e3492584f</t>
+  </si>
+  <si>
+    <t>4996934d-59b5-4384-ae31-de058a268e54</t>
+  </si>
+  <si>
+    <t>4d1ea31f-6697-4b7a-9335-4e97cdfebc0c</t>
+  </si>
+  <si>
+    <t>27c5710e-2122-4ea5-8273-563ed7d5f920</t>
+  </si>
+  <si>
+    <t>abb85125-7058-4042-ba84-9703665a2c66</t>
+  </si>
+  <si>
+    <t>f30ef5a7-decc-4d36-a17d-7b8071f0dfed</t>
+  </si>
+  <si>
+    <t>3741f175-ea19-4f12-963b-de502635e26e</t>
+  </si>
+  <si>
+    <t>a2bb2149-2b98-448a-b841-22e54dec6925</t>
+  </si>
+  <si>
+    <t>35195c1b-dcb1-4bc5-96f6-5e89b4f3e2b1</t>
+  </si>
+  <si>
+    <t>8ebac53a-acb9-47b0-b7de-6ead17d8378f</t>
+  </si>
+  <si>
+    <t>fb19e028-57e1-4369-84b4-1545abc0a92e</t>
+  </si>
+  <si>
+    <t>fb8cd3f3-f36b-42e6-8a72-4d62511b0589</t>
+  </si>
+  <si>
+    <t>dc0ba6d0-b04a-4ea6-a469-793b2272bc68</t>
+  </si>
+  <si>
+    <t>661bd9f9-cf56-4946-91a4-6d29ccc8f54b</t>
+  </si>
+  <si>
+    <t>52620fca-b05c-48f4-bb8f-d23bc7400538</t>
+  </si>
+  <si>
+    <t>97e3e435-21bb-4d83-9260-97d5f61fc50e</t>
+  </si>
+  <si>
+    <t>f7550198-69ce-41b6-8077-8e947c499884</t>
+  </si>
+  <si>
+    <t>7603191c-c018-4986-a4cb-169f2e1e3c1a</t>
+  </si>
+  <si>
+    <t>0164daff-59d6-4a86-acb5-a57297bb7038</t>
+  </si>
+  <si>
+    <t>fdf1afb8-a28d-4e5b-900b-6cbc45a3261e</t>
+  </si>
+  <si>
+    <t>79cb3347-b6ef-4362-ab90-b39287166b43</t>
+  </si>
+  <si>
+    <t>1af45278-9fe1-4c22-8ef2-b18d8eb7a24f</t>
+  </si>
+  <si>
+    <t>7f1ac588-cbe4-4317-bbe9-acd73923fef0</t>
+  </si>
+  <si>
+    <t>38825e64-10dd-4c67-b101-530f4abdcd42</t>
+  </si>
+  <si>
+    <t>e193cb8d-b009-4f18-9273-cda1c68a314b</t>
+  </si>
+  <si>
+    <t>a7dea98c-cf4f-4a9a-ad5b-f9440df8e3ed</t>
+  </si>
+  <si>
+    <t>cf9b86a8-c7bb-4657-b238-1d412a00c14a</t>
+  </si>
+  <si>
+    <t>a0c6e12e-ee4f-44ff-a949-cc3d110cb7f6</t>
+  </si>
+  <si>
+    <t>cf0eae25-e63a-4972-a92b-deb482ec411e</t>
+  </si>
+  <si>
+    <t>96bb17eb-6229-43ce-bf90-db73c957d81b</t>
+  </si>
+  <si>
+    <t>a59c0314-7a8f-4488-bff9-7f9cf5308992</t>
+  </si>
+  <si>
+    <t>3c41a5a6-ef2f-45fd-a5b8-831e01931295</t>
+  </si>
+  <si>
+    <t>6eab879a-48b5-47c1-91cf-9fde31bb60a0</t>
+  </si>
+  <si>
+    <t>eb12e197-09d7-4cb3-8524-946c6585cec2</t>
+  </si>
+  <si>
+    <t>436b2754-cb1e-4d78-8bcc-165c6dd464a2</t>
+  </si>
+  <si>
+    <t>abd91ecf-512c-4837-86ba-cbaf94f099fb</t>
+  </si>
+  <si>
+    <t>430edd4f-23b2-49a2-a366-59c6591967c5</t>
+  </si>
+  <si>
+    <t>d070b424-afa4-49d2-8de2-f76227485a51</t>
+  </si>
+  <si>
+    <t>a117c738-40e5-485b-9805-04a2d9ec1970</t>
+  </si>
+  <si>
+    <t>00f99f2e-e42c-42d3-96c6-a4686bf7cf6f</t>
+  </si>
+  <si>
+    <t>b9ec52a8-4417-4933-8eb3-9ebc6267d840</t>
+  </si>
+  <si>
+    <t>9d23197a-5218-46ee-8c2d-3866b600725a</t>
+  </si>
+  <si>
+    <t>dcc91419-e9f8-4434-9ded-316e9c8a13aa</t>
+  </si>
+  <si>
+    <t>c1082d16-fdfc-4a1e-ba76-f7d53e20f902</t>
+  </si>
+  <si>
+    <t>8e376848-5cc1-4761-9ce6-16c60d319a21</t>
+  </si>
+  <si>
+    <t>22151690-d074-4f98-8cae-28fb0b2e4ea7</t>
+  </si>
+  <si>
+    <t>072a8cfb-b783-4fdb-8316-af26d8568c76</t>
+  </si>
+  <si>
+    <t>ae917ef2-2dd9-4f7a-901b-8cec3dbd81ed</t>
+  </si>
+  <si>
+    <t>2deaa3f2-f7ed-466b-b455-b410d369aebd</t>
+  </si>
+  <si>
+    <t>718b8e32-614a-4e96-ad27-ee5f36b9d1e0</t>
+  </si>
+  <si>
+    <t>e97714a0-f161-4405-9700-257fdf613559</t>
+  </si>
+  <si>
+    <t>f3a1d471-91b0-44c0-9e6d-6c21cb08f79f</t>
+  </si>
+  <si>
+    <t>3f616605-ccdc-40cf-a1ad-ab5178f75822</t>
+  </si>
+  <si>
+    <t>150b58a4-9063-4d21-81ae-16d51e4bf941</t>
+  </si>
+  <si>
+    <t>112d44d0-b648-4a6c-baca-ba2d67dd1559</t>
+  </si>
+  <si>
+    <t>281c6f7d-402b-4d0d-a1b1-44f114ebb7c2</t>
+  </si>
+  <si>
+    <t>d0b9f4dc-a29a-4a47-9ef8-187835a7ae69</t>
+  </si>
+  <si>
+    <t>22ea0d88-e290-493b-86d1-8c2549dcffed</t>
+  </si>
+  <si>
+    <t>fd039b48-9d60-4d8b-9dec-b1c6723eb001</t>
+  </si>
+  <si>
+    <t>69ace157-c4b2-45d3-b1c5-98e89120cb0d</t>
+  </si>
+  <si>
+    <t>a4c15b9f-23a5-4575-8053-bcaf32ff5da0</t>
+  </si>
+  <si>
+    <t>1ab87b96-6a2c-40c0-ac84-ade42458edca</t>
+  </si>
+  <si>
+    <t>c0d2d4b9-0997-487b-acf1-03f110af2ff4</t>
+  </si>
+  <si>
+    <t>26a7da9f-1379-4a4e-a04e-6791a89209c8</t>
+  </si>
+  <si>
+    <t>17217c98-4737-4441-afcd-a9f7c7edd6a2</t>
+  </si>
+  <si>
+    <t>4f3079ad-c190-484d-92c8-2c9da087b597</t>
+  </si>
+  <si>
+    <t>0aab4a2d-1e08-4846-b2bd-062623a98324</t>
+  </si>
+  <si>
+    <t>ecf158cd-5aa7-4e79-9150-530624e909d4</t>
+  </si>
+  <si>
+    <t>148266a6-167c-4159-8682-ec0cfba64485</t>
+  </si>
+  <si>
+    <t>e0b0812b-d764-492f-946e-b2bd20bc8df9</t>
+  </si>
+  <si>
+    <t>a6a2e47f-e1e7-4044-8fde-711f9d17c427</t>
+  </si>
+  <si>
+    <t>58425168-66b5-4d4d-a3ca-3e829b72f6c3</t>
+  </si>
+  <si>
+    <t>11721bd7-2c47-4a3f-a685-f1765fecd08b</t>
+  </si>
+  <si>
+    <t>50df9ee5-cb4e-425a-8e70-1522da511abd</t>
+  </si>
+  <si>
+    <t>17e61f37-f79e-4a49-afc3-1cbaa41cabc2</t>
+  </si>
+  <si>
+    <t>b981626d-df18-494d-a6eb-b075ce9e88d3</t>
+  </si>
+  <si>
+    <t>24551567-28b1-4781-89ac-7552507c5a40</t>
+  </si>
+  <si>
+    <t>7c991146-981d-4579-865e-827cd7ec8a2f</t>
+  </si>
+  <si>
+    <t>ae15abc4-defc-489b-a641-917340618a2e</t>
+  </si>
+  <si>
+    <t>22fcc295-b06c-4e9e-b24c-28e5864db2ee</t>
+  </si>
+  <si>
+    <t>3348822d-ca7c-464b-bf09-3e158f8e1682</t>
+  </si>
+  <si>
+    <t>75bb2407-4c19-4388-a35f-f9091a724e45</t>
+  </si>
+  <si>
+    <t>3603c910-e474-42b1-8e20-517fe371d63f</t>
+  </si>
+  <si>
+    <t>7fe1241c-6917-4941-8267-f41afd3e1f2f</t>
+  </si>
+  <si>
+    <t>256d183a-a11c-4cc6-9d74-42df7e99bacf</t>
+  </si>
+  <si>
+    <t>d1717066-d9ed-479e-ac0d-aa65db9b1d6f</t>
+  </si>
+  <si>
+    <t>3d77bf1f-f29f-4075-b938-f3a8f427ed12</t>
+  </si>
+  <si>
+    <t>a682bafd-daf0-438d-9f91-50ab3226d98d</t>
+  </si>
+  <si>
+    <t>575eda47-506b-4aac-b099-ed13ccf1eecb</t>
+  </si>
+  <si>
+    <t>181fff9c-eea6-4020-8c8a-487d332189a7</t>
+  </si>
+  <si>
+    <t>fd4bb532-1afd-4fd3-9018-aa4f0dd8862c</t>
+  </si>
+  <si>
+    <t>3d8855eb-c85b-4950-87d2-e8785170d441</t>
+  </si>
+  <si>
+    <t>1fc27360-a5e6-4297-994a-2288510e06a4</t>
+  </si>
+  <si>
+    <t>597d2d3e-1520-415e-a0d7-2ed2249e7cfd</t>
+  </si>
+  <si>
+    <t>5850e3ee-7672-445b-80f5-073b54e6b4ad</t>
+  </si>
+  <si>
+    <t>3768ee0f-a8fd-4d0f-a542-93a2b0872c41</t>
+  </si>
+  <si>
+    <t>5cec1284-3e76-4245-af89-67f87fba9c55</t>
+  </si>
+  <si>
+    <t>1adc3bde-b903-4323-9495-86790438ab4a</t>
+  </si>
+  <si>
+    <t>b50c51e1-cc7c-4440-a458-15387c198265</t>
+  </si>
+  <si>
+    <t>855d38ed-641f-4908-b373-cda90ccf7fa8</t>
+  </si>
+  <si>
+    <t>d2163595-2907-4c5a-871e-13c96aba5d3a</t>
+  </si>
+  <si>
+    <t>366072b1-0e1a-4d5b-aa86-2737bdcc4bd4</t>
+  </si>
+  <si>
+    <t>3f130ad8-084e-48d8-b751-c3013310f773</t>
+  </si>
+  <si>
+    <t>0e16dcab-afa5-4294-8850-a653a924a221</t>
+  </si>
+  <si>
+    <t>1bb3b8a9-5028-495f-8ae8-01a68aea855c</t>
+  </si>
+  <si>
+    <t>7ac191b3-e149-4ec3-b541-98bc3fa53797</t>
+  </si>
+  <si>
+    <t>066f4af6-8439-415f-8341-bdc56a4dca4d</t>
+  </si>
+  <si>
+    <t>ef11b6d7-e5da-44f1-808d-ea74e2df042c</t>
+  </si>
+  <si>
+    <t>7e1c699e-88ed-4a1d-87e7-8aa5a6596b02</t>
+  </si>
+  <si>
+    <t>23875f05-fbc1-4dde-8276-40c24282bc5e</t>
+  </si>
+  <si>
+    <t>8e7097fd-50c8-4395-aa33-727ea64034a6</t>
+  </si>
+  <si>
+    <t>8072dd92-6c93-4d0e-9148-86fcdf6248dc</t>
+  </si>
+  <si>
+    <t>076d3004-c953-4e6e-896c-aefaf59bd825</t>
+  </si>
+  <si>
+    <t>16c5a892-9d1b-4541-937a-c3bc966634ad</t>
+  </si>
+  <si>
+    <t>65fef113-b2bf-4e7b-9166-0e78fdf2c46f</t>
+  </si>
+  <si>
+    <t>f638d017-15f4-4557-a5ff-ef77bfcec0be</t>
+  </si>
+  <si>
+    <t>7c4042d3-98c6-48af-9047-5be4b79248ef</t>
+  </si>
+  <si>
+    <t>43ea6de3-1f3f-4af1-8c3c-708efb4b95ae</t>
+  </si>
+  <si>
+    <t>5ea26c6c-928f-4a7c-859c-ce93b1fe3cc5</t>
+  </si>
+  <si>
+    <t>9db9097d-1b79-474e-b561-6563c28faedb</t>
+  </si>
+  <si>
+    <t>65c94924-d3e3-4c80-955b-5389bae8d307</t>
+  </si>
+  <si>
+    <t>23742d12-b323-440a-bd65-ba95621250fa</t>
+  </si>
+  <si>
+    <t>b2a7413e-cc5f-4279-b6bb-97da8471de7c</t>
+  </si>
+  <si>
+    <t>051cabd0-8140-4932-a0d2-e69d170e06f3</t>
+  </si>
+  <si>
+    <t>47ba2cd5-2b6d-4e13-baf2-cfaa52830dee</t>
+  </si>
+  <si>
+    <t>87125d53-d706-4fd7-b258-a697d7520314</t>
+  </si>
+  <si>
+    <t>7f2d7792-6618-40c3-b404-4bf77d4ff73f</t>
+  </si>
+  <si>
+    <t>1c96e8ff-a132-4339-b4b0-6ad304fff00b</t>
+  </si>
+  <si>
+    <t>f505b36d-dd58-46b9-88c4-2214a63dcb42</t>
+  </si>
+  <si>
+    <t>7d663b97-841f-44eb-977b-67b4dd13dfd2</t>
+  </si>
+  <si>
+    <t>f45b758c-80c5-445c-86f9-d97a0e486037</t>
+  </si>
+  <si>
+    <t>7dcc1fca-dbef-41f1-ae3f-f4d9d2a19646</t>
+  </si>
+  <si>
+    <t>0b0844bb-32f9-4f25-b10b-4dacbe1edaee</t>
+  </si>
+  <si>
+    <t>84725159-efed-4da1-af1e-5483feba1350</t>
+  </si>
+  <si>
+    <t>a42d86ec-4d17-4b5a-995b-50a3000355e3</t>
+  </si>
+  <si>
+    <t>9123cbf3-aa5d-4d29-9933-57e133349a9b</t>
+  </si>
+  <si>
+    <t>85284e4d-02f9-4bea-ac0b-64a3208f3a81</t>
+  </si>
+  <si>
+    <t>c4e9350e-6033-448f-92e0-2c29f794cc8a</t>
+  </si>
+  <si>
+    <t>3b88e069-cb68-4f1d-a4fd-e7a033e654bb</t>
+  </si>
+  <si>
+    <t>1eb63d7e-1bbe-49f1-b337-643fafdfcd9e</t>
+  </si>
+  <si>
+    <t>a719a07b-1744-42be-83e0-c46624985dd0</t>
+  </si>
+  <si>
+    <t>2a84a42e-18f2-4126-873d-063c7162835f</t>
+  </si>
+  <si>
+    <t>ce1d5d73-9955-42aa-bd8a-3dc9b0c01819</t>
+  </si>
+  <si>
+    <t>fcd908b0-cb0a-4a1e-b00b-f9313de9feec</t>
+  </si>
+  <si>
+    <t>71931bb0-2e29-4f68-9411-cfcf9d02499e</t>
+  </si>
+  <si>
+    <t>4b504ea3-ea46-47b6-a6d5-0d1e6a36afa1</t>
+  </si>
+  <si>
+    <t>fc05d9eb-98f6-46f9-9a41-eb2642727671</t>
+  </si>
+  <si>
+    <t>4390967e-4dca-406b-a65b-88edcfd35df9</t>
+  </si>
+  <si>
+    <t>2969934c-dcad-43ad-8088-232fd1579546</t>
+  </si>
+  <si>
+    <t>24ba36a9-266e-4f3c-a133-ea7d2b4fcba4</t>
+  </si>
+  <si>
+    <t>0b35df8d-0a60-420a-b159-d1351310a006</t>
+  </si>
+  <si>
+    <t>31a289ae-2a2a-48b2-8c11-7e5c1637294e</t>
+  </si>
+  <si>
+    <t>c7e8c21b-9059-4f07-a1b5-36cc94c518ef</t>
+  </si>
+  <si>
+    <t>99e3e879-e733-4c04-ac3d-145777758b18</t>
+  </si>
+  <si>
+    <t>d106a75c-2f2a-4b87-9c55-8aa7ef4f6856</t>
+  </si>
+  <si>
+    <t>d6ee0303-e0b3-4815-8a03-3a3e3823b7ee</t>
+  </si>
+  <si>
+    <t>0b9b619e-a546-4edc-99a7-3779e209ce47</t>
+  </si>
+  <si>
+    <t>9e672a90-ccbf-4ad4-837c-e38a2c53d163</t>
+  </si>
+  <si>
+    <t>e8a43a26-0467-46fd-be35-baa978ec496a</t>
+  </si>
+  <si>
+    <t>c7e23ecd-059a-4150-a1ee-ffc7fdfb1ddc</t>
+  </si>
+  <si>
+    <t>8d36de0f-1370-4377-ae5e-85766da2d9d5</t>
+  </si>
+  <si>
+    <t>8e3dd3bd-23e5-44d5-b864-bba880680181</t>
+  </si>
+  <si>
+    <t>7bdef840-a269-4321-9784-08e1a41b1bf3</t>
+  </si>
+  <si>
+    <t>5ca60f94-4259-4bca-8972-28d3c0c9d9e8</t>
+  </si>
+  <si>
+    <t>b7769405-ddbc-4a26-83df-4b2375ba72f6</t>
+  </si>
+  <si>
+    <t>d5e0b576-5b98-4f91-880d-6a999769289f</t>
+  </si>
+  <si>
+    <t>222b3501-3a42-48cb-bebf-b274dddf4f34</t>
+  </si>
+  <si>
+    <t>2a3ccc90-4d49-4850-b652-5984aec8578d</t>
+  </si>
+  <si>
+    <t>751d0a2a-8b09-49b0-a6fc-631b2805c019</t>
+  </si>
+  <si>
+    <t>04ca852e-564a-4ce1-af13-820f51e4c53c</t>
+  </si>
+  <si>
+    <t>2c8f763d-9c5a-4e62-b763-e40614d8a932</t>
+  </si>
+  <si>
+    <t>428fa3b4-3fd2-4b76-982a-59d8190577b4</t>
+  </si>
+  <si>
+    <t>ae17c671-3d2a-41ef-905a-c65b8dda59ee</t>
+  </si>
+  <si>
+    <t>3248646f-e062-4871-a301-9c2abfc8c881</t>
+  </si>
+  <si>
+    <t>42836d9a-70b2-4d57-a1e5-f2aba338f2a7</t>
+  </si>
+  <si>
+    <t>083e692e-5bb1-4589-bb62-ab785b8bae15</t>
+  </si>
+  <si>
+    <t>265eabea-ef4b-4e4e-8272-35f40a1647ed</t>
+  </si>
+  <si>
+    <t>9852b380-7082-42d8-b5d2-d4fb46c28bc9</t>
+  </si>
+  <si>
+    <t>9d05be54-b3c0-4683-abd6-1e5a64576d76</t>
+  </si>
+  <si>
+    <t>53558b02-b206-463c-b0aa-bb0ffa203934</t>
+  </si>
+  <si>
+    <t>34419b51-08bc-44a1-8a17-ef97c7148eca</t>
+  </si>
+  <si>
+    <t>763ed80e-4925-4002-8439-84f8af336594</t>
+  </si>
+  <si>
+    <t>f77d1b93-a2c3-471b-b628-b5eee992aed5</t>
+  </si>
+  <si>
+    <t>f39f53c3-50c3-439a-bb3f-1a2c96751c91</t>
+  </si>
+  <si>
+    <t>a34bd618-2b00-4981-ba87-060fa9c55296</t>
+  </si>
+  <si>
+    <t>b69a149a-d7a7-43a4-ac2e-1274563c70ca</t>
+  </si>
+  <si>
+    <t>a0016345-809e-4c3f-b821-7ecf1a924b31</t>
+  </si>
+  <si>
+    <t>b354ecca-5144-40d2-bbdc-4bd3b1f0f3b7</t>
+  </si>
+  <si>
+    <t>cb526199-d733-430e-ac3f-868bf405c16f</t>
+  </si>
+  <si>
+    <t>82715770-199c-4a30-842b-09b2844f74d2</t>
+  </si>
+  <si>
+    <t>6d162530-6dd3-432c-b35a-f4f76b234936</t>
+  </si>
+  <si>
+    <t>8ec6621e-6b6f-47bc-8a4d-78c6cb32b755</t>
+  </si>
+  <si>
+    <t>9c8c4d29-ae37-417d-a7c3-58b53c708f7b</t>
+  </si>
+  <si>
+    <t>28c678a8-90b5-4f76-b692-4a0751f2ebfb</t>
+  </si>
+  <si>
+    <t>ed79dfc7-07ee-4f19-b981-70699638f7eb</t>
+  </si>
+  <si>
+    <t>58e9c33e-faeb-46bf-8d6c-a4e40c703ea9</t>
+  </si>
+  <si>
+    <t>acd6e1bd-614f-413c-adc4-6288abcc530d</t>
+  </si>
+  <si>
+    <t>cb550ae9-f3af-4029-98f1-5b6df08276a8</t>
+  </si>
+  <si>
+    <t>bec560c5-bb24-47cb-a6ca-4b8dea37d87b</t>
+  </si>
+  <si>
+    <t>7d218a12-6f9d-46cf-9d34-f51008645445</t>
+  </si>
+  <si>
+    <t>6a575765-6834-4c75-93b3-f66c2841b41d</t>
+  </si>
+  <si>
+    <t>82ceeb33-10ce-42d2-ad06-7b8dc18108f6</t>
+  </si>
+  <si>
+    <t>0a41a809-0d12-4947-a6d9-9938a1275d8c</t>
+  </si>
+  <si>
+    <t>1047af5a-2f5b-4b7c-a8fa-8de265dd13cc</t>
+  </si>
+  <si>
+    <t>d4d8f414-56b9-4e6c-959a-bc93a42b1ed1</t>
+  </si>
+  <si>
+    <t>b1ba443f-8a45-4af9-8731-884737533367</t>
+  </si>
+  <si>
+    <t>7210d544-7cf4-4d8f-991a-9e83872c9ef0</t>
+  </si>
+  <si>
+    <t>a7161234-adbf-4c49-abbb-c09f850a74c2</t>
+  </si>
+  <si>
+    <t>2252d502-60a6-49f4-adb4-3e5a189a411e</t>
+  </si>
+  <si>
+    <t>a44eb296-e701-4f61-b126-4c9d2ff07be7</t>
+  </si>
+  <si>
+    <t>ed418718-5279-48a1-b524-c2388b6d85f9</t>
+  </si>
+  <si>
+    <t>703e7e38-17f3-476c-93ed-84c38c48d325</t>
+  </si>
+  <si>
+    <t>a16a0661-b66c-4713-a9de-733d10571b8c</t>
+  </si>
+  <si>
+    <t>45da6694-6cea-4157-8429-844717ff94d5</t>
+  </si>
+  <si>
+    <t>6ea390f4-628e-4f5b-81d5-bdd77e050614</t>
+  </si>
+  <si>
+    <t>cae45ee4-a0af-45e0-8e97-495ae00ffad0</t>
+  </si>
+  <si>
+    <t>505046f9-db68-4616-a328-5c0d1a93d721</t>
+  </si>
+  <si>
+    <t>700e6847-7b72-43f1-afa1-91bb4fc158b3</t>
+  </si>
+  <si>
+    <t>13a36488-2d70-4c49-b465-aa3513c85167</t>
+  </si>
+  <si>
+    <t>6fe743f6-08a9-4d38-a0a3-d49f1046309c</t>
+  </si>
+  <si>
+    <t>8cd30b73-3ac8-4784-9215-e03bcd160da2</t>
+  </si>
+  <si>
+    <t>67e0fcbd-79e6-4ce6-a5da-02b156d9f0b5</t>
+  </si>
+  <si>
+    <t>c657d0e8-d281-4174-810e-1cfd87ae709c</t>
+  </si>
+  <si>
+    <t>3f37e74e-3760-4a98-8a8b-b92f793fe89d</t>
+  </si>
+  <si>
+    <t>b0ccdd98-6576-4d85-8165-e9098471376e</t>
+  </si>
+  <si>
+    <t>e90905aa-e5e4-4c45-84bf-293bbf20cac9</t>
+  </si>
+  <si>
+    <t>93d8fbf9-c9bd-4533-bdc6-6665792ed7aa</t>
+  </si>
+  <si>
+    <t>ca11a6e0-4ed3-4ff2-a14f-81a33a0f37e0</t>
+  </si>
+  <si>
+    <t>a3c3fd50-e2b0-4150-8755-35ad3b957cbd</t>
+  </si>
+  <si>
+    <t>fcab49e2-c6f5-4c97-a77c-2e35c3e02440</t>
+  </si>
+  <si>
+    <t>6f6ca4b6-300e-47e8-bd0b-f5ed41bbda4f</t>
+  </si>
+  <si>
+    <t>cd5d3eb5-fc81-4d95-ab97-71344bbef8e4</t>
+  </si>
+  <si>
+    <t>2b3a297d-3b25-4755-913a-f0c52ffde187</t>
+  </si>
+  <si>
+    <t>0736cc66-b13a-427a-9e52-89cb9e8847af</t>
+  </si>
+  <si>
+    <t>00e8321a-4c75-4e38-b993-04179fc069b6</t>
+  </si>
+  <si>
+    <t>38f60119-ca25-4606-893f-579387bafab0</t>
+  </si>
+  <si>
+    <t>7f62815a-eec0-4b29-ba25-862511e6c303</t>
+  </si>
+  <si>
+    <t>f534072a-3ba5-4323-9761-d4fe4161594b</t>
+  </si>
+  <si>
+    <t>a3b12596-cdd5-44cc-9f47-3ca9be447339</t>
+  </si>
+  <si>
+    <t>73651abc-65dd-4ac3-967d-a272aff38176</t>
+  </si>
+  <si>
+    <t>08a639c3-1003-4078-8e85-ed90f09e12ae</t>
+  </si>
+  <si>
+    <t>4ee29ece-9574-4330-92b3-9d737d2d5105</t>
+  </si>
+  <si>
+    <t>1c067704-eac9-4d21-8000-2ab8076e5a1f</t>
+  </si>
+  <si>
+    <t>2ab250c0-a15f-42a8-8fdd-14c00cec0a49</t>
+  </si>
+  <si>
+    <t>3f23326d-4274-4054-a0a5-6f236a81f930</t>
+  </si>
+  <si>
+    <t>685d8e6c-a96a-4b9e-a5a1-901ecc686595</t>
+  </si>
+  <si>
+    <t>f7131286-3202-47b0-af93-9e54f6126bbd</t>
+  </si>
+  <si>
+    <t>6c9405e9-ba1f-4c0a-8be6-398f2db909b0</t>
+  </si>
+  <si>
+    <t>b2ad6685-5ae3-472d-9a08-64308e465cae</t>
+  </si>
+  <si>
+    <t>269d2adf-3590-4747-bf7a-30383f4f604f</t>
+  </si>
+  <si>
+    <t>7ff9d014-d170-4ccd-b5b8-6c29ce47df6e</t>
+  </si>
+  <si>
+    <t>688d9060-74be-40c2-a5b1-876baf636c34</t>
+  </si>
+  <si>
+    <t>6a819f74-b89f-472b-8429-4f6f6854441a</t>
+  </si>
+  <si>
+    <t>9160a411-db00-4047-b10d-89032b59ac0e</t>
+  </si>
+  <si>
+    <t>6bff4387-3b77-4e95-a682-937a1c4a3616</t>
+  </si>
+  <si>
+    <t>8c5fbaf0-166d-41a1-9460-8956f4a3e325</t>
+  </si>
+  <si>
+    <t>2abde5fd-05a6-4897-9561-8559e577ec50</t>
+  </si>
+  <si>
+    <t>d11949f8-1e69-4170-8abf-efb14b047743</t>
+  </si>
+  <si>
+    <t>8b4b1c77-9339-410a-b74e-e65e29f7c87e</t>
+  </si>
+  <si>
+    <t>851444ff-1f81-469e-a4bf-c6b7f070c6c4</t>
+  </si>
+  <si>
+    <t>aa87a4e1-4f2f-49ec-81d3-9f4364e72205</t>
+  </si>
+  <si>
+    <t>e9b885b8-b08f-4e0a-b78d-abf02edcf6f4</t>
+  </si>
+  <si>
+    <t>acef3109-1918-47a6-a96f-b8b27906bc8c</t>
+  </si>
+  <si>
+    <t>31040d8f-46b2-46ee-8b7e-e250eb67c8e5</t>
+  </si>
+  <si>
+    <t>b1599e84-f898-4c1d-bffb-917260679e46</t>
+  </si>
+  <si>
+    <t>3819eaa4-ac0c-4fee-a681-ed3f93920fc7</t>
+  </si>
+  <si>
+    <t>c604057a-1c54-4e3b-a7fb-36ac655a033c</t>
+  </si>
+  <si>
+    <t>a5c389e7-fd49-42c7-88df-3945e4816a3d</t>
+  </si>
+  <si>
+    <t>4424f591-8a38-4d37-bb51-04e4c97b1476</t>
+  </si>
+  <si>
+    <t>30c61472-04ff-4a0f-9af9-3e9ea4cb5f4c</t>
+  </si>
+  <si>
+    <t>26bd6c6a-b52c-459e-8d5a-3031d973647b</t>
+  </si>
+  <si>
+    <t>851f604a-9500-4fca-b6fe-2bd4ddde0ed9</t>
+  </si>
+  <si>
+    <t>7e994e32-9283-4712-89f2-47a0992e3249</t>
+  </si>
+  <si>
+    <t>5c30a9e1-c8d7-4f21-a21e-cb6fe40be131</t>
+  </si>
+  <si>
+    <t>97725a85-861d-4402-8769-ed782c0fc653</t>
+  </si>
+  <si>
+    <t>f9236f4f-cf9a-4144-a941-4d3f8cdcda5f</t>
+  </si>
+  <si>
+    <t>27710d96-7c81-4add-b475-56c25ed3ea2f</t>
+  </si>
+  <si>
+    <t>8f8276b7-4b4a-4ef1-9970-edfe5407eaa4</t>
+  </si>
+  <si>
+    <t>7412c2dd-3769-4330-965f-30c15f1a8705</t>
+  </si>
+  <si>
+    <t>d65c51b0-65c1-426e-b5e4-1b0d257010bb</t>
+  </si>
+  <si>
+    <t>3be0a2bc-1784-48cd-9be8-fb03561de4e2</t>
+  </si>
+  <si>
+    <t>11f5b22a-864c-4be3-aa54-7b38bc0686c3</t>
+  </si>
+  <si>
+    <t>ce79d39d-7572-46fa-ad43-75a61b20903e</t>
+  </si>
+  <si>
+    <t>0e012719-caea-44c1-82af-0f3da3528fda</t>
+  </si>
+  <si>
+    <t>d93100b5-eedf-4a10-97e8-ffb97fe8e131</t>
+  </si>
+  <si>
+    <t>601a936d-a3cd-44d3-a00a-81963d9d0031</t>
+  </si>
+  <si>
+    <t>229c554c-5f14-49cf-8f9d-35b7111132e7</t>
+  </si>
+  <si>
+    <t>664843d9-f535-4409-8ffa-08ed30020e15</t>
+  </si>
+  <si>
+    <t>b6f93843-dfa7-4b8e-99dc-01eb789e7fb1</t>
+  </si>
+  <si>
+    <t>196d4410-05c3-4849-8fcf-bb25accf1916</t>
+  </si>
+  <si>
+    <t>74523c72-9248-4a5a-bc5a-44a2252318f9</t>
+  </si>
+  <si>
+    <t>32db7ea4-314a-465b-b33b-4d8d545baadd</t>
+  </si>
+  <si>
+    <t>0776c537-4f42-4199-af63-13e134f93e4a</t>
+  </si>
+  <si>
+    <t>dcee7923-21a6-4159-a346-9788cd0cc2cc</t>
+  </si>
+  <si>
+    <t>89702220-d326-4b5b-85cb-fbb87a256e25</t>
+  </si>
+  <si>
+    <t>9c86cf18-b4bf-428a-ab1f-e770867ed89a</t>
+  </si>
+  <si>
+    <t>c1d5f920-11fd-46bb-9d6c-db6bd5c10267</t>
+  </si>
+  <si>
+    <t>bbc303d3-95cc-404e-8039-0bf258435e3a</t>
+  </si>
+  <si>
+    <t>b557d8e8-51df-4b28-97b0-142c36c7eaec</t>
+  </si>
+  <si>
+    <t>1cf3d812-e9af-4b42-8dea-14868fab6966</t>
+  </si>
+  <si>
+    <t>fa085ec5-fd0e-447f-86d3-4e5e9c908b08</t>
+  </si>
+  <si>
+    <t>c401b5f4-7168-4525-b6ab-b54974b4a0c3</t>
+  </si>
+  <si>
+    <t>5663c643-a42c-4434-8964-8565152a052f</t>
+  </si>
+  <si>
+    <t>02ad64d7-f3f5-41ae-a6c5-00e78b95c116</t>
+  </si>
+  <si>
+    <t>e217533d-7d45-4011-8e21-8e59b44d4923</t>
+  </si>
+  <si>
+    <t>81eda008-7379-49ff-b1d1-48b65ece076e</t>
+  </si>
+  <si>
+    <t>06cd9893-ff38-4b19-9d6c-25d21411acfb</t>
+  </si>
+  <si>
+    <t>3a73734b-4ea6-4b9d-8d0b-1bbdef919d40</t>
+  </si>
+  <si>
+    <t>b3d16852-338b-4faf-bdc4-ef542008e638</t>
+  </si>
+  <si>
+    <t>6604099d-823b-4e10-bc90-0dd5b97fc57f</t>
+  </si>
+  <si>
+    <t>4f03567c-38ec-415c-9445-8867351d746a</t>
+  </si>
+  <si>
+    <t>fdb94720-61cd-4db4-9908-3053fae5dfea</t>
+  </si>
+  <si>
+    <t>cde36933-18ac-48b5-9181-97956d2d491e</t>
+  </si>
+  <si>
+    <t>56aa2d78-4d50-4bfa-b659-792f9cd9c992</t>
+  </si>
+  <si>
+    <t>a67e5a3c-2baf-4838-b1ad-171b47f2b580</t>
+  </si>
+  <si>
+    <t>1a56d0ba-5b35-48bb-86d1-bd3d2afab5e0</t>
+  </si>
+  <si>
+    <t>23cf9d11-e5be-4d35-b167-0c4459f85968</t>
+  </si>
+  <si>
+    <t>415b9113-ed24-41c1-a3ac-19986245c948</t>
+  </si>
+  <si>
+    <t>09c8d8c5-c636-45b1-8750-ad44431a2cac</t>
+  </si>
+  <si>
+    <t>0ccde621-71a6-4841-b91c-c49e63494eed</t>
+  </si>
+  <si>
+    <t>ee03045a-045f-4993-b417-c27b74853f58</t>
+  </si>
+  <si>
+    <t>a2bc7189-ab70-4c4c-a1c6-dcd55bc74a22</t>
+  </si>
+  <si>
+    <t>bf76cdfa-cd2f-4b00-9b46-ac9d0c72da55</t>
+  </si>
+  <si>
+    <t>eb190ac9-44de-46a2-afef-1f3620581e54</t>
+  </si>
+  <si>
+    <t>1a71897a-b9e8-4b9e-b33c-260b46e80508</t>
+  </si>
+  <si>
+    <t>921cb96a-4035-4345-8bcd-523f0d53e304</t>
+  </si>
+  <si>
+    <t>4d47f632-bc00-4851-bde3-320f1b174698</t>
+  </si>
+  <si>
+    <t>245ef7ab-86c6-468b-8c97-fd05112e23bc</t>
+  </si>
+  <si>
+    <t>a8e67254-677d-4dd7-9638-bea94f9cd433</t>
+  </si>
+  <si>
+    <t>c37eb440-232a-4ab4-bcd9-29d3e354137a</t>
+  </si>
+  <si>
+    <t>404de6fe-fbe4-4d36-bdf1-ce5a6ab9448e</t>
+  </si>
+  <si>
+    <t>dd2905ab-43b3-4dad-96f2-5e31c6bf07ef</t>
+  </si>
+  <si>
+    <t>402b025c-395e-4e93-83c3-cd39def77787</t>
+  </si>
+  <si>
+    <t>3cebc88e-b8a4-47ed-82e2-8e6112521378</t>
+  </si>
+  <si>
+    <t>23061a56-85c8-4892-92f3-2f0eed1ede13</t>
+  </si>
+  <si>
+    <t>85f4d37b-c274-4f9d-b153-8e560db5f940</t>
+  </si>
+  <si>
+    <t>97db542f-f9a7-46bb-81e8-d6087418317b</t>
+  </si>
+  <si>
+    <t>b3d7de82-7cde-46e9-8b8a-37034b70820c</t>
+  </si>
+  <si>
+    <t>27bb1882-0345-4ea9-a6f4-b3861c3299d1</t>
+  </si>
+  <si>
+    <t>ec667959-bcfb-4b4c-8286-232c6c951714</t>
+  </si>
+  <si>
+    <t>d250ad15-910b-4418-b5ae-ef602b1980f1</t>
+  </si>
+  <si>
+    <t>c1216304-b38f-4d0f-9f64-41953c05f84c</t>
+  </si>
+  <si>
+    <t>bcbb07cd-767e-4ad1-b2e2-fda3d2ff0cfb</t>
+  </si>
+  <si>
+    <t>c187e6fe-71b6-435a-9afb-1a1b5a1477fe</t>
+  </si>
+  <si>
+    <t>8528a7ef-4d4d-449f-913b-f9289cf1ce0d</t>
+  </si>
+  <si>
+    <t>fd3d36c7-e522-451e-9d61-2622fc32b53b</t>
+  </si>
+  <si>
+    <t>4a0c39ea-4270-4ab0-8f07-9126ceae5d86</t>
+  </si>
+  <si>
+    <t>ae3c2148-b0b1-4d36-9c44-b50e699c868a</t>
+  </si>
+  <si>
+    <t>4192cf88-2038-4854-a039-e88faaf66f83</t>
+  </si>
+  <si>
+    <t>ab219dd0-1d99-4267-8906-74fcb186cf7f</t>
+  </si>
+  <si>
+    <t>15ff43c0-6d4b-41de-8f8e-de8f3ea00e5b</t>
+  </si>
+  <si>
+    <t>b1a21351-2401-4362-9086-b12a20349a03</t>
+  </si>
+  <si>
+    <t>3ae8ae8d-d069-453d-8c2f-faa60c93e373</t>
+  </si>
+  <si>
+    <t>493833bd-36be-4087-ba28-23c32dd6c622</t>
+  </si>
+  <si>
+    <t>885ff178-caa3-4c51-aa06-062d9b843d83</t>
+  </si>
+  <si>
+    <t>75a7852e-d120-49f5-a5a2-008235e91884</t>
+  </si>
+  <si>
+    <t>4dbfb169-a0fb-43e8-b4b7-8c64d52eee6b</t>
+  </si>
+  <si>
+    <t>82f39477-5b46-4984-a28a-b7362b6aa045</t>
+  </si>
+  <si>
+    <t>170e7eb4-dcdf-45bb-949f-b130eec97cec</t>
+  </si>
+  <si>
+    <t>06ce9dd2-acd7-4374-a9b5-916fe2bf1400</t>
+  </si>
+  <si>
+    <t>36d35e8a-466b-4248-8568-d456a8fcbbdc</t>
+  </si>
+  <si>
+    <t>069b2e03-bc69-4de2-83d2-695ca4495495</t>
+  </si>
+  <si>
+    <t>3b0f8d6f-91e5-452c-9a76-b604f924a1e6</t>
+  </si>
+  <si>
+    <t>79519e4d-d20a-4ae6-b578-a202c2d716ba</t>
+  </si>
+  <si>
+    <t>de2c8a19-4ad2-425c-940b-d715b8f4c7ef</t>
+  </si>
+  <si>
+    <t>cab894b3-7f22-4e17-9c94-addcb1373308</t>
+  </si>
+  <si>
+    <t>3829d3b5-1536-4e34-81d7-842e1d1efe04</t>
+  </si>
+  <si>
+    <t>157ac3de-5d75-4809-8a3b-9aa292296ffa</t>
+  </si>
+  <si>
+    <t>858cb91c-170f-409d-963a-a8c61d4d677a</t>
+  </si>
+  <si>
+    <t>dd011875-e8b7-424a-ae77-ddcbe94ee1cf</t>
+  </si>
+  <si>
+    <t>ec586a68-d976-4bd4-8fa1-8d2cf1109c76</t>
+  </si>
+  <si>
+    <t>693c704b-2c20-4996-ae3a-11d02196cef4</t>
+  </si>
+  <si>
+    <t>3ce56484-0a3a-4e8c-95b4-7a5f203b0191</t>
+  </si>
+  <si>
+    <t>23d31f8e-3a4f-4946-8193-f66b93829a30</t>
+  </si>
+  <si>
+    <t>67643b22-1792-4377-9338-ece60c1867fd</t>
+  </si>
+  <si>
+    <t>6c53bfd9-7b64-4c75-aeee-5a4ab5f0fadb</t>
+  </si>
+  <si>
+    <t>79cfa39f-dac6-4e2b-a1b8-6ddf39cb54e7</t>
+  </si>
+  <si>
+    <t>7d1d4b9f-2052-407f-969b-ff353e54dd55</t>
+  </si>
+  <si>
+    <t>ca672274-219f-4ec4-916f-b81c9c33372c</t>
+  </si>
+  <si>
+    <t>3e635f5d-db2a-4757-8b82-c1bafadc441a</t>
+  </si>
+  <si>
+    <t>121bde2e-7510-462b-b04b-2b83d1a0bf4f</t>
+  </si>
+  <si>
+    <t>bab22b44-6bb7-43cf-a565-83a9411eac40</t>
+  </si>
+  <si>
+    <t>f9455121-610e-4645-9a87-8f26d0729193</t>
+  </si>
+  <si>
+    <t>ba1801cb-fb0f-4635-9fae-e871e3d20bdf</t>
+  </si>
+  <si>
+    <t>1557a1dd-c118-443b-9527-c97b27040b58</t>
+  </si>
+  <si>
+    <t>10394de6-935b-49b3-908d-691d71201168</t>
+  </si>
+  <si>
+    <t>e88a216b-ee26-42c8-8f90-ff4515aa712b</t>
+  </si>
+  <si>
+    <t>b0ae60c3-a3b6-40d8-8f73-2b8735a03c71</t>
+  </si>
+  <si>
+    <t>74d8c370-e8b8-41e4-a7c5-be0fbf39da81</t>
+  </si>
+  <si>
+    <t>0b159154-392e-464f-b22c-7b30d2e67c1b</t>
+  </si>
+  <si>
+    <t>b6d4deb3-8b4f-4a1f-bf04-36c8deb7d48d</t>
+  </si>
+  <si>
+    <t>6947f32f-0898-45b2-badd-c06d3846ad09</t>
+  </si>
+  <si>
+    <t>43dfb289-da55-430a-a6ed-5ac291908ad8</t>
+  </si>
+  <si>
+    <t>19a45535-36bf-42a3-ab93-39c5e740f1f7</t>
+  </si>
+  <si>
+    <t>fc5086fc-013d-47be-a4aa-5f333691f9d2</t>
+  </si>
+  <si>
+    <t>90d24399-3c46-4f80-b21c-48ccf532a563</t>
+  </si>
+  <si>
+    <t>8d6bc5ac-d3a4-4fae-9267-8018768da06b</t>
+  </si>
+  <si>
+    <t>4973bb05-bc4a-4a78-8f81-9c69c46939a1</t>
+  </si>
+  <si>
+    <t>dcc137bc-04e2-4a5c-ac5d-626d4d32bde3</t>
+  </si>
+  <si>
+    <t>ecdd4af9-e9f2-4dcc-9acd-f54204fe28e5</t>
+  </si>
+  <si>
+    <t>679fb6c3-1568-40b5-86dd-cdbe9289f8ac</t>
+  </si>
+  <si>
+    <t>eef92083-9a5b-4f9d-af93-c3f1f894f9a0</t>
+  </si>
+  <si>
+    <t>03165202-ae4d-41a0-a237-1a3cd36449f1</t>
+  </si>
+  <si>
+    <t>b40513e1-d17d-4852-8627-28e4454f81f4</t>
+  </si>
+  <si>
+    <t>0eb46623-dff1-43c4-a132-32a291fff95e</t>
+  </si>
+  <si>
+    <t>331e5b07-3207-41d1-95e6-4df236d6846e</t>
+  </si>
+  <si>
+    <t>a3f50fc3-3ce1-4865-ad34-aa2b16f89749</t>
+  </si>
+  <si>
+    <t>cd306b27-0f10-4421-afab-1248e8a137db</t>
+  </si>
+  <si>
+    <t>f07b2b9c-4591-4425-b737-26360567e9a5</t>
+  </si>
+  <si>
+    <t>b774e3a7-e45f-4a9f-8362-ee6dffa0af16</t>
+  </si>
+  <si>
+    <t>82273495-b64b-4ab2-b1ce-423ad069baa2</t>
+  </si>
+  <si>
+    <t>dfc1c82f-6512-4a3d-a896-4837c47d40e2</t>
+  </si>
+  <si>
+    <t>6431e617-6a05-483e-9cdf-7f2835514ecd</t>
+  </si>
+  <si>
+    <t>d739d296-2a2c-4459-add2-c44f4660cd0a</t>
+  </si>
+  <si>
+    <t>61ac70ba-e706-43d0-96fb-63c441106c1a</t>
+  </si>
+  <si>
+    <t>f2c08149-2a1a-4e4f-83d3-a4f4944fdd97</t>
+  </si>
+  <si>
+    <t>50092f7d-0a24-4f0e-ad79-40c640c80a9f</t>
+  </si>
+  <si>
+    <t>995cccd3-2d7b-443f-bc58-eb88a859c874</t>
+  </si>
+  <si>
+    <t>dc3fb183-84bb-4476-a666-f1946dd5123e</t>
+  </si>
+  <si>
+    <t>315b82ec-44ac-4f87-9eee-405fce438fff</t>
+  </si>
+  <si>
+    <t>2b8edd5d-8802-4d10-b168-a618602f20b5</t>
+  </si>
+  <si>
+    <t>aaef462c-4afd-4c7b-91a3-72b26036192c</t>
+  </si>
+  <si>
+    <t>8c7f0fc0-ade9-4af9-85e5-30014abedaf7</t>
+  </si>
+  <si>
+    <t>85a7a1c2-af59-4655-926a-bd88638d19d6</t>
+  </si>
+  <si>
+    <t>bdadf375-5b70-4fa9-964a-02c24747471a</t>
+  </si>
+  <si>
+    <t>05757c18-bea8-4623-ad3d-d3ae45c0229d</t>
+  </si>
+  <si>
+    <t>60e3df6a-97f7-4b7f-b3ff-e1bb92449ca2</t>
+  </si>
+  <si>
+    <t>145ba7ee-2fdb-4e04-9637-20f35c3bfb07</t>
+  </si>
+  <si>
+    <t>eb36f0f0-8b41-463a-938b-7607c2535251</t>
+  </si>
+  <si>
+    <t>234a0a7b-7cc0-43d6-bc97-3bb618f461e0</t>
+  </si>
+  <si>
+    <t>25a46538-5dc1-45fa-bbf2-d1d044a193d1</t>
+  </si>
+  <si>
+    <t>5949b2e3-3092-4f6d-90fb-02a4c0a38aea</t>
+  </si>
+  <si>
+    <t>14fa0dcf-012e-41e5-b1c5-ddf5fb4f815e</t>
+  </si>
+  <si>
+    <t>5282abab-038e-4872-b907-f0525c94d5cc</t>
+  </si>
+  <si>
+    <t>edda95fc-2b7c-4b6e-be31-22b561e268d8</t>
+  </si>
+  <si>
+    <t>ead96e87-92e5-493f-b492-e60d6fb1e894</t>
+  </si>
+  <si>
+    <t>075ef427-f031-4c76-87bb-7fecd9abc532</t>
+  </si>
+  <si>
+    <t>c24f0a3c-1280-466f-a4ad-f84441f45aec</t>
+  </si>
+  <si>
+    <t>4454136a-1619-437d-81ad-600bc8532dbd</t>
+  </si>
+  <si>
+    <t>8836949e-c818-4da2-8cd1-35a2bb78660d</t>
+  </si>
+  <si>
+    <t>b595c979-40c9-4e2e-a93f-6ed5e037bf90</t>
+  </si>
+  <si>
+    <t>8fdb69bd-4886-49cd-b8c2-825eeeacfa9a</t>
+  </si>
+  <si>
+    <t>27322d8f-450d-4352-bf39-b31febbfd068</t>
+  </si>
+  <si>
+    <t>8a5b0f92-0842-4e7c-bb35-6a56ccbbf12f</t>
+  </si>
+  <si>
+    <t>d8c043b1-4a37-4458-9432-f8059310e58f</t>
+  </si>
+  <si>
+    <t>1cd7431c-16d1-49b9-b58d-7dc78cdb5d85</t>
+  </si>
+  <si>
+    <t>cba9ab22-907f-41b4-9937-c37b16a6261d</t>
+  </si>
+  <si>
+    <t>9548d29d-78e1-4175-80f3-2195c327b8a7</t>
+  </si>
+  <si>
+    <t>45e93191-3903-476f-9548-ea3972b3d8f4</t>
+  </si>
+  <si>
+    <t>9f0269a0-9481-481a-bd53-e1f468dca1ee</t>
+  </si>
+  <si>
+    <t>600c738d-4ed0-4292-81c0-10e84680c6ca</t>
+  </si>
+  <si>
+    <t>6e7f2d8b-ed14-4c61-9559-fd988c8bae1b</t>
+  </si>
+  <si>
+    <t>e3d6a4f1-f4ae-4ada-bfe4-7ee92d7eb7e9</t>
+  </si>
+  <si>
+    <t>3bb7bfc5-50ea-4e7c-a86b-fda30ef31210</t>
+  </si>
+  <si>
+    <t>86bd8af1-28e2-401d-b35b-c7dd04d4e30d</t>
+  </si>
+  <si>
+    <t>d9ada5b0-ad78-40ca-98af-2aaaf2a35388</t>
+  </si>
+  <si>
+    <t>463d2ee8-1569-4e97-a0be-84e444816ed3</t>
+  </si>
+  <si>
+    <t>a5b79720-c8b0-4a17-9eaf-eec09c2942ae</t>
+  </si>
+  <si>
+    <t>5d1da05c-60fd-4280-bdaf-7f6015e6b728</t>
+  </si>
+  <si>
+    <t>b36ce889-93b8-4aeb-a14b-24a263f18081</t>
+  </si>
+  <si>
+    <t>f9830b79-bc6b-41de-887a-5c33bbf35bf5</t>
+  </si>
+  <si>
+    <t>ea2ef379-d805-41b0-8c4d-1019c0799545</t>
+  </si>
+  <si>
+    <t>30695349-95a6-4630-8c5d-09fb123f299d</t>
+  </si>
+  <si>
+    <t>79b424f7-9261-4aa3-bbeb-a602edca7198</t>
+  </si>
+  <si>
+    <t>25e4a9ef-f6c3-4d77-bef2-b8c096016619</t>
+  </si>
+  <si>
+    <t>674e80f9-7373-4268-b403-4fa44f7bfc40</t>
+  </si>
+  <si>
+    <t>a653746c-9714-40d0-9b9a-c4ce54b3f155</t>
+  </si>
+  <si>
+    <t>ec5afe9e-effa-4354-815e-47da465179c3</t>
+  </si>
+  <si>
+    <t>98680d06-cbe8-4105-96a0-c4813bb039e4</t>
+  </si>
+  <si>
+    <t>a15fc8e5-be7a-4487-a588-072f3a5fe102</t>
+  </si>
+  <si>
+    <t>d8c40f1e-37b9-4de6-bac2-765d25c9b596</t>
+  </si>
+  <si>
+    <t>6e160307-1138-42b1-90e5-774283dd6544</t>
+  </si>
+  <si>
+    <t>a1e07f61-3e49-4be6-b9fb-6cb3e3a672de</t>
+  </si>
+  <si>
+    <t>f18551f4-f5b6-4516-8c70-1ee51bb34a62</t>
+  </si>
+  <si>
+    <t>d9744c2b-bd45-4bd0-a0d5-87dd51a33347</t>
+  </si>
+  <si>
+    <t>bf929435-d058-454a-b234-a4e0fce4d4c3</t>
+  </si>
+  <si>
+    <t>97801dcc-caed-4eab-be94-a8870cb65249</t>
+  </si>
+  <si>
+    <t>c4643b0a-4613-4ec4-8ced-b9dfde3f2bc9</t>
+  </si>
+  <si>
+    <t>f6f554e4-bb4f-4ad9-8754-1246477ea57f</t>
+  </si>
+  <si>
+    <t>d57221e5-371e-47cc-8f97-8cd8bfc2f35c</t>
+  </si>
+  <si>
+    <t>e25c4360-c5fc-44f6-bb04-80f04fc107e0</t>
+  </si>
+  <si>
+    <t>4b6cd3e3-c9c0-460a-b907-a1380be97c37</t>
+  </si>
+  <si>
+    <t>352a9bcf-d797-493e-8373-0e0340bdc285</t>
+  </si>
+  <si>
+    <t>0066d007-766c-4d40-9ce4-2fde6505b12a</t>
+  </si>
+  <si>
+    <t>edf96d9f-b4b8-4e8f-bd0b-fc2dfa0c9a66</t>
+  </si>
+  <si>
+    <t>395b6bc5-8324-4b21-b339-9a62f8963797</t>
+  </si>
+  <si>
+    <t>f606c398-caff-4274-9ce1-5c917aa84e9e</t>
+  </si>
+  <si>
+    <t>5ce9e881-ad9f-4d43-a7de-d132c7ce9be1</t>
+  </si>
+  <si>
+    <t>ce48ebc3-68f8-46ee-9c22-7376c0e3be15</t>
+  </si>
+  <si>
+    <t>166e2217-3e6b-45a1-afb5-e9d7e5d806ce</t>
+  </si>
+  <si>
+    <t>709512fe-e6df-4371-b388-fbe5ed3523cd</t>
+  </si>
+  <si>
+    <t>ea26fafe-18e1-4768-b306-778a976b4af5</t>
+  </si>
+  <si>
+    <t>21797b1a-5c70-41ea-849f-ddaf0ebb461b</t>
+  </si>
+  <si>
+    <t>525367a5-787b-48db-823c-779f9bb45610</t>
+  </si>
+  <si>
+    <t>958a6dd1-17d5-4f96-bdca-452b9ea0fe90</t>
+  </si>
+  <si>
+    <t>a64687e6-0b2b-4834-8066-ad8919082743</t>
+  </si>
+  <si>
+    <t>6d1fe63a-860a-41dd-8c92-d6ec0264d52b</t>
+  </si>
+  <si>
+    <t>2b9bfca1-1d89-43ff-893e-7b696375db10</t>
+  </si>
+  <si>
+    <t>73f7854b-825b-4e36-8649-b1d5f96cada5</t>
+  </si>
+  <si>
+    <t>d1f39c6d-a303-40c6-9323-2eff94bf5f82</t>
+  </si>
+  <si>
+    <t>c358b2f1-4adf-4dc7-9d89-06371eb86572</t>
+  </si>
+  <si>
+    <t>6e7e8bed-7b4a-4f40-8911-eaffc647c390</t>
+  </si>
+  <si>
+    <t>d10ae870-df62-4e03-a349-bdba05594c9a</t>
+  </si>
+  <si>
+    <t>90c3cff7-375f-4aff-b3ca-cc6cdc38b9e3</t>
+  </si>
+  <si>
+    <t>67d9abdd-78fa-4df1-935a-24f7d09da203</t>
   </si>
   <si>
     <t>Key</t>
@@ -3669,7 +3661,7 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>RM</t>
+    <t>$</t>
   </si>
   <si>
     <t>Type</t>
@@ -3687,7 +3679,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
@@ -3713,346 +3705,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -4101,15 +3769,14 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:J123"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -8048,15 +7715,14 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G79"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -9876,15 +9542,14 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D579"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -17993,15 +17658,14 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -18020,15 +17684,14 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -18054,7 +17717,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>